--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consolidado" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Geral Diário" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Consolidado" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Geral Diário" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -513,22 +513,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1257</v>
+        <v>4285</v>
       </c>
       <c r="C3" t="n">
-        <v>1074</v>
+        <v>3922</v>
       </c>
       <c r="D3" t="n">
-        <v>1213</v>
+        <v>4240</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.8543999999999999</v>
+        <v>0.9153</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.965</v>
+        <v>0.9895</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.8713</v>
+        <v>0.8715999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -538,22 +538,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14798</v>
+        <v>40761</v>
       </c>
       <c r="C4" t="n">
-        <v>10166</v>
+        <v>34007</v>
       </c>
       <c r="D4" t="n">
-        <v>14320</v>
+        <v>39226</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.8343</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.9677</v>
+        <v>0.9623</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9228000000000001</v>
+        <v>0.9314</v>
       </c>
     </row>
     <row r="5">
@@ -582,22 +582,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33737</v>
+        <v>68801</v>
       </c>
       <c r="C6" t="n">
-        <v>25289</v>
+        <v>54472</v>
       </c>
       <c r="D6" t="n">
-        <v>32987</v>
+        <v>66599</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.7495999999999999</v>
+        <v>0.7917000000000001</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.9778</v>
+        <v>0.968</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9792000000000001</v>
+        <v>0.9849</v>
       </c>
     </row>
     <row r="7">
@@ -607,22 +607,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4321</v>
+        <v>12344</v>
       </c>
       <c r="C7" t="n">
-        <v>1857</v>
+        <v>8593</v>
       </c>
       <c r="D7" t="n">
-        <v>4313</v>
+        <v>12331</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.4298</v>
+        <v>0.6960999999999999</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.9981</v>
+        <v>0.9989</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.4317</v>
+        <v>0.4689</v>
       </c>
     </row>
     <row r="8">
@@ -632,22 +632,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7234</v>
+        <v>16324</v>
       </c>
       <c r="C8" t="n">
-        <v>4701</v>
+        <v>11045</v>
       </c>
       <c r="D8" t="n">
-        <v>7069</v>
+        <v>16111</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.6498</v>
+        <v>0.6766</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.9772</v>
+        <v>0.987</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8036</v>
+        <v>0.8588</v>
       </c>
     </row>
     <row r="9">
@@ -676,22 +676,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1131</v>
+        <v>2298</v>
       </c>
       <c r="C10" t="n">
-        <v>666</v>
+        <v>1501</v>
       </c>
       <c r="D10" t="n">
-        <v>835</v>
+        <v>1865</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.5889</v>
+        <v>0.6531999999999999</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.7383</v>
+        <v>0.8116</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9125</v>
+        <v>0.9264</v>
       </c>
     </row>
     <row r="11">
@@ -701,16 +701,20 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2" t="n"/>
-      <c r="F11" s="3" t="n"/>
+        <v>80</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="G11" s="2" t="n">
         <v>1</v>
       </c>
@@ -741,22 +745,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>536</v>
+        <v>10842</v>
       </c>
       <c r="C13" t="n">
-        <v>495</v>
+        <v>10672</v>
       </c>
       <c r="D13" t="n">
-        <v>533</v>
+        <v>10804</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9235</v>
+        <v>0.9843000000000001</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.9944</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.8326</v>
+        <v>0.8741</v>
       </c>
     </row>
     <row r="14">
@@ -811,7 +815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1248,8 +1252,394 @@
       <c r="G15" s="3" t="n"/>
       <c r="H15" s="2" t="n"/>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>3028</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2848</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3027</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>0.9406</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>0.872</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>25963</v>
+      </c>
+      <c r="D18" t="n">
+        <v>23841</v>
+      </c>
+      <c r="E18" t="n">
+        <v>24906</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>0.9183</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>0.9593</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>0.9390999999999999</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="2" t="n"/>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>35064</v>
+      </c>
+      <c r="D20" t="n">
+        <v>29183</v>
+      </c>
+      <c r="E20" t="n">
+        <v>33612</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>0.8323</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>0.9586</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>0.9904000000000001</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>8023</v>
+      </c>
+      <c r="D21" t="n">
+        <v>6736</v>
+      </c>
+      <c r="E21" t="n">
+        <v>8018</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>0.8395999999999999</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>0.5075</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>9090</v>
+      </c>
+      <c r="D22" t="n">
+        <v>6344</v>
+      </c>
+      <c r="E22" t="n">
+        <v>9042</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>0.6979000000000001</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>0.9947</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>0.9128000000000001</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="2" t="n"/>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1167</v>
+      </c>
+      <c r="D24" t="n">
+        <v>835</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1030</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>0.7155</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>0.8826000000000001</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>0.9398000000000001</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>80</v>
+      </c>
+      <c r="D25" t="n">
+        <v>80</v>
+      </c>
+      <c r="E25" t="n">
+        <v>80</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2" t="n"/>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>10306</v>
+      </c>
+      <c r="D27" t="n">
+        <v>10177</v>
+      </c>
+      <c r="E27" t="n">
+        <v>10271</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>0.9875</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>0.9965999999999999</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>0.9235</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2" t="n"/>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H15"/>
+  <autoFilter ref="A1:H29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -528,7 +528,7 @@
         <v>0.9895</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.8715999999999999</v>
+        <v>0.8618000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -553,7 +553,7 @@
         <v>0.9623</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9314</v>
+        <v>0.9195</v>
       </c>
     </row>
     <row r="5">
@@ -597,7 +597,7 @@
         <v>0.968</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9849</v>
+        <v>0.9868000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -622,7 +622,7 @@
         <v>0.9989</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.4689</v>
+        <v>0.4774</v>
       </c>
     </row>
     <row r="8">
@@ -647,7 +647,7 @@
         <v>0.987</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8588</v>
+        <v>0.8542000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -691,7 +691,7 @@
         <v>0.8116</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9264</v>
+        <v>0.929</v>
       </c>
     </row>
     <row r="11">
@@ -760,7 +760,7 @@
         <v>0.9965000000000001</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.8741</v>
+        <v>0.8862000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1303,7 +1303,7 @@
         <v>0.9997</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>0.872</v>
+        <v>0.852</v>
       </c>
     </row>
     <row r="18">
@@ -1333,7 +1333,7 @@
         <v>0.9593</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>0.9390999999999999</v>
+        <v>0.9164</v>
       </c>
     </row>
     <row r="19">
@@ -1387,7 +1387,7 @@
         <v>0.9586</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>0.9904000000000001</v>
+        <v>0.9939</v>
       </c>
     </row>
     <row r="21">
@@ -1417,7 +1417,7 @@
         <v>0.9994</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>0.5075</v>
+        <v>0.5276</v>
       </c>
     </row>
     <row r="22">
@@ -1447,7 +1447,7 @@
         <v>0.9947</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>0.9128000000000001</v>
+        <v>0.9029</v>
       </c>
     </row>
     <row r="23">
@@ -1501,7 +1501,7 @@
         <v>0.8826000000000001</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>0.9398000000000001</v>
+        <v>0.9451000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -1585,7 +1585,7 @@
         <v>0.9965999999999999</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>0.9235</v>
+        <v>0.9442</v>
       </c>
     </row>
     <row r="28">

--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -513,22 +513,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4285</v>
+        <v>6494</v>
       </c>
       <c r="C3" t="n">
-        <v>3922</v>
+        <v>5970</v>
       </c>
       <c r="D3" t="n">
-        <v>4240</v>
+        <v>6448</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9153</v>
+        <v>0.9193000000000001</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.9895</v>
+        <v>0.9929000000000001</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.8618000000000001</v>
+        <v>0.8803</v>
       </c>
     </row>
     <row r="4">
@@ -538,22 +538,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40761</v>
+        <v>63185</v>
       </c>
       <c r="C4" t="n">
-        <v>34007</v>
+        <v>54786</v>
       </c>
       <c r="D4" t="n">
-        <v>39226</v>
+        <v>61275</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.8343</v>
+        <v>0.8671</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.9623</v>
+        <v>0.9698</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9195</v>
+        <v>0.9148999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -582,22 +582,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>68801</v>
+        <v>98315</v>
       </c>
       <c r="C6" t="n">
-        <v>54472</v>
+        <v>80366</v>
       </c>
       <c r="D6" t="n">
-        <v>66599</v>
+        <v>94191</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.7917000000000001</v>
+        <v>0.8173999999999999</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.968</v>
+        <v>0.9581000000000001</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9868000000000001</v>
+        <v>0.9884999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -607,22 +607,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12344</v>
+        <v>19578</v>
       </c>
       <c r="C7" t="n">
-        <v>8593</v>
+        <v>15125</v>
       </c>
       <c r="D7" t="n">
-        <v>12331</v>
+        <v>19564</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.6960999999999999</v>
+        <v>0.7726000000000001</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.9989</v>
+        <v>0.9993000000000001</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.4774</v>
+        <v>0.5296999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -632,22 +632,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16324</v>
+        <v>24355</v>
       </c>
       <c r="C8" t="n">
-        <v>11045</v>
+        <v>16965</v>
       </c>
       <c r="D8" t="n">
-        <v>16111</v>
+        <v>22560</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.6766</v>
+        <v>0.6966</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.987</v>
+        <v>0.9262999999999999</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8542000000000001</v>
+        <v>0.8672</v>
       </c>
     </row>
     <row r="9">
@@ -676,22 +676,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2298</v>
+        <v>3701</v>
       </c>
       <c r="C10" t="n">
-        <v>1501</v>
+        <v>2675</v>
       </c>
       <c r="D10" t="n">
-        <v>1865</v>
+        <v>3187</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.6531999999999999</v>
+        <v>0.7228</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.8116</v>
+        <v>0.8611</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.929</v>
+        <v>0.9404</v>
       </c>
     </row>
     <row r="11">
@@ -701,13 +701,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C11" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D11" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1</v>
@@ -745,22 +745,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10842</v>
+        <v>20297</v>
       </c>
       <c r="C13" t="n">
-        <v>10672</v>
+        <v>19997</v>
       </c>
       <c r="D13" t="n">
-        <v>10804</v>
+        <v>20245</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9843000000000001</v>
+        <v>0.9852</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.9965000000000001</v>
+        <v>0.9974</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.8862000000000001</v>
+        <v>0.9056000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -815,7 +815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1638,8 +1638,394 @@
       <c r="G29" s="3" t="n"/>
       <c r="H29" s="2" t="n"/>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>2209</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2048</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2208</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>0.9270999999999999</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>0.9995000000000001</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>0.9136</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>22424</v>
+      </c>
+      <c r="D32" t="n">
+        <v>20779</v>
+      </c>
+      <c r="E32" t="n">
+        <v>22049</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>0.9266</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>0.9833</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>0.9066</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="2" t="n"/>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>29514</v>
+      </c>
+      <c r="D34" t="n">
+        <v>25894</v>
+      </c>
+      <c r="E34" t="n">
+        <v>27592</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>0.8773000000000001</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>0.9349</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>0.9918</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>7234</v>
+      </c>
+      <c r="D35" t="n">
+        <v>6532</v>
+      </c>
+      <c r="E35" t="n">
+        <v>7233</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>0.9998999999999999</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>0.6104999999999999</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>8031</v>
+      </c>
+      <c r="D36" t="n">
+        <v>5920</v>
+      </c>
+      <c r="E36" t="n">
+        <v>6449</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>0.7371</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>0.8029999999999999</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>0.8913</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="2" t="n"/>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="2" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1403</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1174</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1322</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>0.8368000000000001</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>0.9423</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>0.9609000000000001</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="2" t="n"/>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="2" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>9455</v>
+      </c>
+      <c r="D41" t="n">
+        <v>9325</v>
+      </c>
+      <c r="E41" t="n">
+        <v>9441</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>0.9863</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>0.9984999999999999</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>0.9375</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="2" t="n"/>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="2" t="n"/>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H29"/>
+  <autoFilter ref="A1:H43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -494,17 +494,23 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="2" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -513,22 +519,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6494</v>
+        <v>24970</v>
       </c>
       <c r="C3" t="n">
-        <v>5970</v>
+        <v>23296</v>
       </c>
       <c r="D3" t="n">
-        <v>6448</v>
+        <v>24310</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9193000000000001</v>
+        <v>0.9329999999999999</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.9929000000000001</v>
+        <v>0.9736</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.8803</v>
+        <v>0.9373999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -538,22 +544,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>63185</v>
+        <v>238019</v>
       </c>
       <c r="C4" t="n">
-        <v>54786</v>
+        <v>199049</v>
       </c>
       <c r="D4" t="n">
-        <v>61275</v>
+        <v>230298</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.8671</v>
+        <v>0.8362999999999999</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.9698</v>
+        <v>0.9676</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9148999999999999</v>
+        <v>0.9428</v>
       </c>
     </row>
     <row r="5">
@@ -582,22 +588,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>98315</v>
+        <v>393950</v>
       </c>
       <c r="C6" t="n">
-        <v>80366</v>
+        <v>333428</v>
       </c>
       <c r="D6" t="n">
-        <v>94191</v>
+        <v>380097</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.8173999999999999</v>
+        <v>0.8464</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.9581000000000001</v>
+        <v>0.9648</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9884999999999999</v>
+        <v>0.9773000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -607,22 +613,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19578</v>
+        <v>87686</v>
       </c>
       <c r="C7" t="n">
-        <v>15125</v>
+        <v>62355</v>
       </c>
       <c r="D7" t="n">
-        <v>19564</v>
+        <v>87490</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.7726000000000001</v>
+        <v>0.7111</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.9993000000000001</v>
+        <v>0.9978</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.5296999999999999</v>
+        <v>0.6831999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -632,22 +638,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24355</v>
+        <v>95649</v>
       </c>
       <c r="C8" t="n">
-        <v>16965</v>
+        <v>79944</v>
       </c>
       <c r="D8" t="n">
-        <v>22560</v>
+        <v>92169</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.6966</v>
+        <v>0.8358</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.9262999999999999</v>
+        <v>0.9636</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8672</v>
+        <v>0.9137999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -676,22 +682,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3701</v>
+        <v>13658</v>
       </c>
       <c r="C10" t="n">
-        <v>2675</v>
+        <v>9982</v>
       </c>
       <c r="D10" t="n">
-        <v>3187</v>
+        <v>11730</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.7228</v>
+        <v>0.7309</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.8611</v>
+        <v>0.8588</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9404</v>
+        <v>0.9621</v>
       </c>
     </row>
     <row r="11">
@@ -701,22 +707,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>82</v>
+        <v>1453</v>
       </c>
       <c r="C11" t="n">
-        <v>82</v>
+        <v>1187</v>
       </c>
       <c r="D11" t="n">
-        <v>82</v>
+        <v>1238</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1</v>
+        <v>0.8169</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1</v>
+        <v>0.852</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>1</v>
+        <v>0.9976999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -726,17 +732,23 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>779</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>776</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="3" t="n"/>
-      <c r="G12" s="2" t="n"/>
+        <v>776</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>0.9961</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0.9961</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -745,22 +757,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20297</v>
+        <v>53441</v>
       </c>
       <c r="C13" t="n">
-        <v>19997</v>
+        <v>51874</v>
       </c>
       <c r="D13" t="n">
-        <v>20245</v>
+        <v>52912</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9852</v>
+        <v>0.9706999999999999</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.9974</v>
+        <v>0.9901000000000001</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.9056000000000001</v>
+        <v>0.9114</v>
       </c>
     </row>
     <row r="14">
@@ -770,18 +782,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3938</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>3938</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="3" t="n"/>
+        <v>3938</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="G14" s="2" t="n">
-        <v>0</v>
+        <v>0.4064</v>
       </c>
     </row>
     <row r="15">
@@ -801,7 +817,9 @@
       </c>
       <c r="E15" s="2" t="n"/>
       <c r="F15" s="3" t="n"/>
-      <c r="G15" s="2" t="n"/>
+      <c r="G15" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G15"/>
@@ -815,7 +833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -873,7 +891,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -882,22 +900,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="2" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -906,28 +930,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1257</v>
+        <v>1701</v>
       </c>
       <c r="D3" t="n">
-        <v>1074</v>
+        <v>1552</v>
       </c>
       <c r="E3" t="n">
-        <v>1213</v>
+        <v>1578</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.8543999999999999</v>
+        <v>0.9124</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.965</v>
+        <v>0.9277</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.8713</v>
+        <v>0.9601999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -936,28 +960,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14798</v>
+        <v>14847</v>
       </c>
       <c r="D4" t="n">
-        <v>10166</v>
+        <v>9700</v>
       </c>
       <c r="E4" t="n">
-        <v>14320</v>
+        <v>13779</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6533</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9677</v>
+        <v>0.9281</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.9228000000000001</v>
+        <v>0.9782999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -981,7 +1005,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -990,28 +1014,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>33737</v>
+        <v>22634</v>
       </c>
       <c r="D6" t="n">
-        <v>25289</v>
+        <v>19752</v>
       </c>
       <c r="E6" t="n">
-        <v>32987</v>
+        <v>22176</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.7495999999999999</v>
+        <v>0.8726999999999999</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.9778</v>
+        <v>0.9798</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9792000000000001</v>
+        <v>0.9582999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1020,28 +1044,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4321</v>
+        <v>7255</v>
       </c>
       <c r="D7" t="n">
-        <v>1857</v>
+        <v>4037</v>
       </c>
       <c r="E7" t="n">
-        <v>4313</v>
+        <v>7224</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.4298</v>
+        <v>0.5564</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9981</v>
+        <v>0.9956999999999999</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.4317</v>
+        <v>0.8015000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1050,28 +1074,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7234</v>
+        <v>5878</v>
       </c>
       <c r="D8" t="n">
-        <v>4701</v>
+        <v>5619</v>
       </c>
       <c r="E8" t="n">
-        <v>7069</v>
+        <v>5621</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.6498</v>
+        <v>0.9559000000000001</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.9772</v>
+        <v>0.9562999999999999</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.8036</v>
+        <v>0.9640000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1095,7 +1119,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1104,28 +1128,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1131</v>
+        <v>1003</v>
       </c>
       <c r="D10" t="n">
-        <v>666</v>
+        <v>278</v>
       </c>
       <c r="E10" t="n">
-        <v>835</v>
+        <v>279</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.5889</v>
+        <v>0.2772</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.7383</v>
+        <v>0.2782</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9125</v>
+        <v>0.9606</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1134,16 +1158,20 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2" t="n"/>
-      <c r="G11" s="3" t="n"/>
+        <v>89</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>0.7040000000000001</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0.7120000000000001</v>
+      </c>
       <c r="H11" s="2" t="n">
         <v>1</v>
       </c>
@@ -1151,7 +1179,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1160,22 +1188,28 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>248</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2" t="n"/>
-      <c r="G12" s="3" t="n"/>
-      <c r="H12" s="2" t="n"/>
+        <v>248</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0.988</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>0.988</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1184,28 +1218,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>536</v>
+        <v>2144</v>
       </c>
       <c r="D13" t="n">
-        <v>495</v>
+        <v>2039</v>
       </c>
       <c r="E13" t="n">
-        <v>533</v>
+        <v>2050</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9235</v>
+        <v>0.951</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.9944</v>
+        <v>0.9562</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.8326</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1214,24 +1248,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>3192</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>3192</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2" t="n"/>
-      <c r="G14" s="3" t="n"/>
+        <v>3192</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="H14" s="2" t="n">
-        <v>0</v>
+        <v>0.8281000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1250,12 +1288,14 @@
       </c>
       <c r="F15" s="2" t="n"/>
       <c r="G15" s="3" t="n"/>
-      <c r="H15" s="2" t="n"/>
+      <c r="H15" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1274,12 +1314,14 @@
       </c>
       <c r="F16" s="2" t="n"/>
       <c r="G16" s="3" t="n"/>
-      <c r="H16" s="2" t="n"/>
+      <c r="H16" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1288,28 +1330,28 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3028</v>
+        <v>1484</v>
       </c>
       <c r="D17" t="n">
-        <v>2848</v>
+        <v>1364</v>
       </c>
       <c r="E17" t="n">
-        <v>3027</v>
+        <v>1458</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0.9406</v>
+        <v>0.9190999999999999</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.9997</v>
+        <v>0.9825</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>0.852</v>
+        <v>0.9520999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1318,28 +1360,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>25963</v>
+        <v>14601</v>
       </c>
       <c r="D18" t="n">
-        <v>23841</v>
+        <v>10100</v>
       </c>
       <c r="E18" t="n">
-        <v>24906</v>
+        <v>14461</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0.9183</v>
+        <v>0.6917</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.9593</v>
+        <v>0.9904000000000001</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>0.9164</v>
+        <v>0.9590000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1363,7 +1405,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1372,28 +1414,28 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>35064</v>
+        <v>23128</v>
       </c>
       <c r="D20" t="n">
-        <v>29183</v>
+        <v>18960</v>
       </c>
       <c r="E20" t="n">
-        <v>33612</v>
+        <v>22227</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.8323</v>
+        <v>0.8198000000000001</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.9586</v>
+        <v>0.961</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>0.9939</v>
+        <v>0.9423</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1402,28 +1444,28 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>8023</v>
+        <v>8381</v>
       </c>
       <c r="D21" t="n">
-        <v>6736</v>
+        <v>5140</v>
       </c>
       <c r="E21" t="n">
-        <v>8018</v>
+        <v>8377</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.8395999999999999</v>
+        <v>0.6133</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.9994</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>0.5276</v>
+        <v>0.7358</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1432,28 +1474,28 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>9090</v>
+        <v>5363</v>
       </c>
       <c r="D22" t="n">
-        <v>6344</v>
+        <v>5154</v>
       </c>
       <c r="E22" t="n">
-        <v>9042</v>
+        <v>5158</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.6979000000000001</v>
+        <v>0.961</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.9947</v>
+        <v>0.9618000000000001</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>0.9029</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1477,7 +1519,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1486,28 +1528,28 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1167</v>
+        <v>456</v>
       </c>
       <c r="D24" t="n">
-        <v>835</v>
+        <v>276</v>
       </c>
       <c r="E24" t="n">
-        <v>1030</v>
+        <v>403</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0.7155</v>
+        <v>0.6053000000000001</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0.8826000000000001</v>
+        <v>0.8837999999999999</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>0.9451000000000001</v>
+        <v>0.9423</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1516,19 +1558,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>80</v>
+        <v>207</v>
       </c>
       <c r="D25" t="n">
-        <v>80</v>
+        <v>149</v>
       </c>
       <c r="E25" t="n">
-        <v>80</v>
+        <v>152</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>1</v>
+        <v>0.7198</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1</v>
+        <v>0.7343000000000001</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>1</v>
@@ -1537,7 +1579,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1546,22 +1588,28 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="2" t="n"/>
-      <c r="G26" s="3" t="n"/>
-      <c r="H26" s="2" t="n"/>
+        <v>150</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1570,28 +1618,28 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>10306</v>
+        <v>674</v>
       </c>
       <c r="D27" t="n">
-        <v>10177</v>
+        <v>646</v>
       </c>
       <c r="E27" t="n">
-        <v>10271</v>
+        <v>649</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.9875</v>
+        <v>0.9584999999999999</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.9965999999999999</v>
+        <v>0.9629000000000001</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>0.9442</v>
+        <v>0.888</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1600,24 +1648,28 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>746</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>746</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="2" t="n"/>
-      <c r="G28" s="3" t="n"/>
+        <v>746</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="H28" s="2" t="n">
-        <v>0</v>
+        <v>0.8371999999999999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1636,12 +1688,14 @@
       </c>
       <c r="F29" s="2" t="n"/>
       <c r="G29" s="3" t="n"/>
-      <c r="H29" s="2" t="n"/>
+      <c r="H29" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1660,12 +1714,14 @@
       </c>
       <c r="F30" s="2" t="n"/>
       <c r="G30" s="3" t="n"/>
-      <c r="H30" s="2" t="n"/>
+      <c r="H30" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1674,28 +1730,28 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2209</v>
+        <v>1149</v>
       </c>
       <c r="D31" t="n">
-        <v>2048</v>
+        <v>914</v>
       </c>
       <c r="E31" t="n">
-        <v>2208</v>
+        <v>1070</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>0.9270999999999999</v>
+        <v>0.7955</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9312</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>0.9136</v>
+        <v>0.9586</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1704,28 +1760,28 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>22424</v>
+        <v>13081</v>
       </c>
       <c r="D32" t="n">
-        <v>20779</v>
+        <v>10044</v>
       </c>
       <c r="E32" t="n">
-        <v>22049</v>
+        <v>12868</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.9266</v>
+        <v>0.7678</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.9833</v>
+        <v>0.9837</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>0.9066</v>
+        <v>0.9569</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1749,7 +1805,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1758,28 +1814,28 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>29514</v>
+        <v>29780</v>
       </c>
       <c r="D34" t="n">
-        <v>25894</v>
+        <v>22942</v>
       </c>
       <c r="E34" t="n">
-        <v>27592</v>
+        <v>27720</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>0.8773000000000001</v>
+        <v>0.7704000000000001</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.9349</v>
+        <v>0.9308</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>0.9918</v>
+        <v>0.977</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1788,28 +1844,28 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>7234</v>
+        <v>7942</v>
       </c>
       <c r="D35" t="n">
-        <v>6532</v>
+        <v>1591</v>
       </c>
       <c r="E35" t="n">
-        <v>7233</v>
+        <v>7926</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>0.903</v>
+        <v>0.2003</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.9998999999999999</v>
+        <v>0.998</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>0.6104999999999999</v>
+        <v>0.7818000000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1818,28 +1874,28 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>8031</v>
+        <v>5405</v>
       </c>
       <c r="D36" t="n">
-        <v>5920</v>
+        <v>5013</v>
       </c>
       <c r="E36" t="n">
-        <v>6449</v>
+        <v>5018</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0.7371</v>
+        <v>0.9275</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.8029999999999999</v>
+        <v>0.9284</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>0.8913</v>
+        <v>0.9542</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1863,7 +1919,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1872,28 +1928,28 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1403</v>
+        <v>405</v>
       </c>
       <c r="D38" t="n">
-        <v>1174</v>
+        <v>215</v>
       </c>
       <c r="E38" t="n">
-        <v>1322</v>
+        <v>372</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>0.8368000000000001</v>
+        <v>0.5309</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.9423</v>
+        <v>0.9185</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>0.9609000000000001</v>
+        <v>0.9048</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1902,19 +1958,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>115</v>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>71</v>
       </c>
       <c r="E39" t="n">
-        <v>2</v>
+        <v>81</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>1</v>
+        <v>0.6174000000000001</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>1</v>
+        <v>0.7043</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>1</v>
@@ -1923,7 +1979,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1942,12 +1998,14 @@
       </c>
       <c r="F40" s="2" t="n"/>
       <c r="G40" s="3" t="n"/>
-      <c r="H40" s="2" t="n"/>
+      <c r="H40" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1956,28 +2014,28 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>9455</v>
+        <v>208</v>
       </c>
       <c r="D41" t="n">
-        <v>9325</v>
+        <v>157</v>
       </c>
       <c r="E41" t="n">
-        <v>9441</v>
+        <v>158</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>0.9863</v>
+        <v>0.7548</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.9984999999999999</v>
+        <v>0.7595999999999999</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>0.9375</v>
+        <v>0.8793000000000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2003,7 +2061,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2022,10 +2080,3874 @@
       </c>
       <c r="F43" s="2" t="n"/>
       <c r="G43" s="3" t="n"/>
-      <c r="H43" s="2" t="n"/>
+      <c r="H43" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="2" t="n"/>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="2" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>3465</v>
+      </c>
+      <c r="D45" t="n">
+        <v>3449</v>
+      </c>
+      <c r="E45" t="n">
+        <v>3451</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>0.9954000000000001</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>0.9691</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>20274</v>
+      </c>
+      <c r="D46" t="n">
+        <v>18196</v>
+      </c>
+      <c r="E46" t="n">
+        <v>19281</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>0.8975</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>0.951</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>0.9493</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="2" t="n"/>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="2" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>31115</v>
+      </c>
+      <c r="D48" t="n">
+        <v>26611</v>
+      </c>
+      <c r="E48" t="n">
+        <v>30066</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>0.8552</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>0.9662999999999999</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>0.9632999999999999</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>7212</v>
+      </c>
+      <c r="D49" t="n">
+        <v>4217</v>
+      </c>
+      <c r="E49" t="n">
+        <v>7207</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>0.5847</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>0.9993000000000001</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>0.7881</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>7124</v>
+      </c>
+      <c r="D50" t="n">
+        <v>6128</v>
+      </c>
+      <c r="E50" t="n">
+        <v>7022</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>0.8602</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>0.9856999999999999</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>0.9429999999999999</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="2" t="n"/>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="2" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>839</v>
+      </c>
+      <c r="D52" t="n">
+        <v>773</v>
+      </c>
+      <c r="E52" t="n">
+        <v>773</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>0.9213</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>0.9213</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>0.9808</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>201</v>
+      </c>
+      <c r="D53" t="n">
+        <v>170</v>
+      </c>
+      <c r="E53" t="n">
+        <v>170</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>0.8458</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>0.8458</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>378</v>
+      </c>
+      <c r="D54" t="n">
+        <v>378</v>
+      </c>
+      <c r="E54" t="n">
+        <v>378</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>5354</v>
+      </c>
+      <c r="D55" t="n">
+        <v>5346</v>
+      </c>
+      <c r="E55" t="n">
+        <v>5349</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>0.9984999999999999</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>0.9991</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>0.8779</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="2" t="n"/>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="2" t="n"/>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="2" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="2" t="n"/>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="2" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>2086</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1951</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1956</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>0.9353</v>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>0.9377</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>0.9268999999999999</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>16426</v>
+      </c>
+      <c r="D60" t="n">
+        <v>14869</v>
+      </c>
+      <c r="E60" t="n">
+        <v>16353</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>0.9052</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>0.9956</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>0.9456</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="2" t="n"/>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="2" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>29228</v>
+      </c>
+      <c r="D62" t="n">
+        <v>26229</v>
+      </c>
+      <c r="E62" t="n">
+        <v>28901</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>0.8974</v>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>0.9887999999999999</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>0.9701000000000001</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>5552</v>
+      </c>
+      <c r="D63" t="n">
+        <v>4887</v>
+      </c>
+      <c r="E63" t="n">
+        <v>5548</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>0.8802</v>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>0.9993000000000001</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>0.7870999999999999</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>8250</v>
+      </c>
+      <c r="D64" t="n">
+        <v>7618</v>
+      </c>
+      <c r="E64" t="n">
+        <v>8095</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>0.9234</v>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>0.9812000000000001</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>0.8784000000000001</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="2" t="n"/>
+      <c r="G65" s="3" t="n"/>
+      <c r="H65" s="2" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>783</v>
+      </c>
+      <c r="D66" t="n">
+        <v>773</v>
+      </c>
+      <c r="E66" t="n">
+        <v>773</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>0.9872</v>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>0.9872</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>0.9936</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>242</v>
+      </c>
+      <c r="D67" t="n">
+        <v>184</v>
+      </c>
+      <c r="E67" t="n">
+        <v>186</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>0.7603</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>0.7685999999999999</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="2" t="n"/>
+      <c r="G68" s="3" t="n"/>
+      <c r="H68" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>3688</v>
+      </c>
+      <c r="D69" t="n">
+        <v>3654</v>
+      </c>
+      <c r="E69" t="n">
+        <v>3662</v>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>0.9908</v>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>0.9087000000000001</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="2" t="n"/>
+      <c r="G70" s="3" t="n"/>
+      <c r="H70" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="2" t="n"/>
+      <c r="G71" s="3" t="n"/>
+      <c r="H71" s="2" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="2" t="n"/>
+      <c r="G72" s="3" t="n"/>
+      <c r="H72" s="2" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>1561</v>
+      </c>
+      <c r="D73" t="n">
+        <v>1417</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1511</v>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>0.9078000000000001</v>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>0.968</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>0.9425</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>20747</v>
+      </c>
+      <c r="D74" t="n">
+        <v>17794</v>
+      </c>
+      <c r="E74" t="n">
+        <v>20659</v>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>0.8576999999999999</v>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>0.9958</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>0.9531000000000001</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="2" t="n"/>
+      <c r="G75" s="3" t="n"/>
+      <c r="H75" s="2" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>32104</v>
+      </c>
+      <c r="D76" t="n">
+        <v>27968</v>
+      </c>
+      <c r="E76" t="n">
+        <v>30919</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>0.8712000000000001</v>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v>0.9631000000000001</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>0.9653</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>6685</v>
+      </c>
+      <c r="D77" t="n">
+        <v>6517</v>
+      </c>
+      <c r="E77" t="n">
+        <v>6679</v>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>0.9749</v>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>0.9991</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>0.7569</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>7900</v>
+      </c>
+      <c r="D78" t="n">
+        <v>7430</v>
+      </c>
+      <c r="E78" t="n">
+        <v>7814</v>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>0.9405</v>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>0.9891</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>0.9067000000000001</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="2" t="n"/>
+      <c r="G79" s="3" t="n"/>
+      <c r="H79" s="2" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>997</v>
+      </c>
+      <c r="D80" t="n">
+        <v>933</v>
+      </c>
+      <c r="E80" t="n">
+        <v>937</v>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>0.9358</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>0.9398000000000001</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>0.9570000000000001</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>231</v>
+      </c>
+      <c r="D81" t="n">
+        <v>230</v>
+      </c>
+      <c r="E81" t="n">
+        <v>230</v>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>0.9956999999999999</v>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>0.9956999999999999</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="2" t="n"/>
+      <c r="G82" s="3" t="n"/>
+      <c r="H82" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>4199</v>
+      </c>
+      <c r="D83" t="n">
+        <v>4191</v>
+      </c>
+      <c r="E83" t="n">
+        <v>4195</v>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>0.9981</v>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>0.9990000000000001</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>0.9186</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="2" t="n"/>
+      <c r="G84" s="3" t="n"/>
+      <c r="H84" s="2" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="2" t="n"/>
+      <c r="G85" s="3" t="n"/>
+      <c r="H85" s="2" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="2" t="n"/>
+      <c r="G86" s="3" t="n"/>
+      <c r="H86" s="2" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>2063</v>
+      </c>
+      <c r="D87" t="n">
+        <v>1959</v>
+      </c>
+      <c r="E87" t="n">
+        <v>2018</v>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>0.9495999999999999</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>0.9782</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>0.9543</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>19588</v>
+      </c>
+      <c r="D88" t="n">
+        <v>17653</v>
+      </c>
+      <c r="E88" t="n">
+        <v>19383</v>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>0.9012</v>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>0.9895</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>0.9594</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="2" t="n"/>
+      <c r="G89" s="3" t="n"/>
+      <c r="H89" s="2" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>32259</v>
+      </c>
+      <c r="D90" t="n">
+        <v>27382</v>
+      </c>
+      <c r="E90" t="n">
+        <v>30536</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>0.8488</v>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>0.9466</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>0.9884000000000001</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>6848</v>
+      </c>
+      <c r="D91" t="n">
+        <v>6684</v>
+      </c>
+      <c r="E91" t="n">
+        <v>6846</v>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>0.9761</v>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>0.7209</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>8522</v>
+      </c>
+      <c r="D92" t="n">
+        <v>7746</v>
+      </c>
+      <c r="E92" t="n">
+        <v>8489</v>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>0.9089</v>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>0.9961</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>0.9295</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="2" t="n"/>
+      <c r="G93" s="3" t="n"/>
+      <c r="H93" s="2" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>876</v>
+      </c>
+      <c r="D94" t="n">
+        <v>872</v>
+      </c>
+      <c r="E94" t="n">
+        <v>874</v>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>0.9954000000000001</v>
+      </c>
+      <c r="G94" s="3" t="n">
+        <v>0.9976999999999999</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>0.9787</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>117</v>
+      </c>
+      <c r="D95" t="n">
+        <v>117</v>
+      </c>
+      <c r="E95" t="n">
+        <v>117</v>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>0.975</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="2" t="n"/>
+      <c r="G96" s="3" t="n"/>
+      <c r="H96" s="2" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>4552</v>
+      </c>
+      <c r="D97" t="n">
+        <v>4539</v>
+      </c>
+      <c r="E97" t="n">
+        <v>4544</v>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>0.9971</v>
+      </c>
+      <c r="G97" s="3" t="n">
+        <v>0.9982</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>0.9504</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="2" t="n"/>
+      <c r="G98" s="3" t="n"/>
+      <c r="H98" s="2" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="2" t="n"/>
+      <c r="G99" s="3" t="n"/>
+      <c r="H99" s="2" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="2" t="n"/>
+      <c r="G100" s="3" t="n"/>
+      <c r="H100" s="2" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>2035</v>
+      </c>
+      <c r="D101" t="n">
+        <v>1951</v>
+      </c>
+      <c r="E101" t="n">
+        <v>1951</v>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>0.9587</v>
+      </c>
+      <c r="G101" s="3" t="n">
+        <v>0.9587</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>0.9688</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>20266</v>
+      </c>
+      <c r="D102" t="n">
+        <v>14967</v>
+      </c>
+      <c r="E102" t="n">
+        <v>17783</v>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>0.7384999999999999</v>
+      </c>
+      <c r="G102" s="3" t="n">
+        <v>0.8774999999999999</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>0.9495</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="2" t="n"/>
+      <c r="G103" s="3" t="n"/>
+      <c r="H103" s="2" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>35868</v>
+      </c>
+      <c r="D104" t="n">
+        <v>31132</v>
+      </c>
+      <c r="E104" t="n">
+        <v>34486</v>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="G104" s="3" t="n">
+        <v>0.9615</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>0.9871</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>6458</v>
+      </c>
+      <c r="D105" t="n">
+        <v>3837</v>
+      </c>
+      <c r="E105" t="n">
+        <v>6349</v>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>0.5941</v>
+      </c>
+      <c r="G105" s="3" t="n">
+        <v>0.9831</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>0.7279000000000001</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>8247</v>
+      </c>
+      <c r="D106" t="n">
+        <v>6529</v>
+      </c>
+      <c r="E106" t="n">
+        <v>7993</v>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>0.7917000000000001</v>
+      </c>
+      <c r="G106" s="3" t="n">
+        <v>0.9692000000000001</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>0.8815999999999999</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="2" t="n"/>
+      <c r="G107" s="3" t="n"/>
+      <c r="H107" s="2" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D108" t="n">
+        <v>734</v>
+      </c>
+      <c r="E108" t="n">
+        <v>746</v>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>0.7333</v>
+      </c>
+      <c r="G108" s="3" t="n">
+        <v>0.7453</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>0.9895999999999999</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>15</v>
+      </c>
+      <c r="D109" t="n">
+        <v>3</v>
+      </c>
+      <c r="E109" t="n">
+        <v>15</v>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G109" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="2" t="n"/>
+      <c r="G110" s="3" t="n"/>
+      <c r="H110" s="2" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>4870</v>
+      </c>
+      <c r="D111" t="n">
+        <v>4242</v>
+      </c>
+      <c r="E111" t="n">
+        <v>4712</v>
+      </c>
+      <c r="F111" s="2" t="n">
+        <v>0.871</v>
+      </c>
+      <c r="G111" s="3" t="n">
+        <v>0.9676</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>0.9303</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="2" t="n"/>
+      <c r="G112" s="3" t="n"/>
+      <c r="H112" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="2" t="n"/>
+      <c r="G113" s="3" t="n"/>
+      <c r="H113" s="2" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="2" t="n"/>
+      <c r="G114" s="3" t="n"/>
+      <c r="H114" s="2" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>1065</v>
+      </c>
+      <c r="D115" t="n">
+        <v>946</v>
+      </c>
+      <c r="E115" t="n">
+        <v>1002</v>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>0.8883</v>
+      </c>
+      <c r="G115" s="3" t="n">
+        <v>0.9408</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>0.9728</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>15416</v>
+      </c>
+      <c r="D116" t="n">
+        <v>13054</v>
+      </c>
+      <c r="E116" t="n">
+        <v>14879</v>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>0.8468000000000001</v>
+      </c>
+      <c r="G116" s="3" t="n">
+        <v>0.9651999999999999</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>0.9328</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="2" t="n"/>
+      <c r="G117" s="3" t="n"/>
+      <c r="H117" s="2" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>27973</v>
+      </c>
+      <c r="D118" t="n">
+        <v>24243</v>
+      </c>
+      <c r="E118" t="n">
+        <v>27491</v>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>0.8667</v>
+      </c>
+      <c r="G118" s="3" t="n">
+        <v>0.9828</v>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>0.9893999999999999</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>5293</v>
+      </c>
+      <c r="D119" t="n">
+        <v>4158</v>
+      </c>
+      <c r="E119" t="n">
+        <v>5292</v>
+      </c>
+      <c r="F119" s="2" t="n">
+        <v>0.7856000000000001</v>
+      </c>
+      <c r="G119" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>0.5832999999999999</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>7004</v>
+      </c>
+      <c r="D120" t="n">
+        <v>5190</v>
+      </c>
+      <c r="E120" t="n">
+        <v>6810</v>
+      </c>
+      <c r="F120" s="2" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="G120" s="3" t="n">
+        <v>0.9723000000000001</v>
+      </c>
+      <c r="H120" s="2" t="n">
+        <v>0.9484999999999999</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="2" t="n"/>
+      <c r="G121" s="3" t="n"/>
+      <c r="H121" s="2" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>1508</v>
+      </c>
+      <c r="D122" t="n">
+        <v>1035</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1448</v>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>0.6862999999999999</v>
+      </c>
+      <c r="G122" s="3" t="n">
+        <v>0.9601999999999999</v>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>25</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" t="n">
+        <v>23</v>
+      </c>
+      <c r="F123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" s="3" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" s="2" t="n"/>
+      <c r="G124" s="3" t="n"/>
+      <c r="H124" s="2" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>1414</v>
+      </c>
+      <c r="D125" t="n">
+        <v>1160</v>
+      </c>
+      <c r="E125" t="n">
+        <v>1314</v>
+      </c>
+      <c r="F125" s="2" t="n">
+        <v>0.8204</v>
+      </c>
+      <c r="G125" s="3" t="n">
+        <v>0.9293</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>0.9136</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" s="2" t="n"/>
+      <c r="G126" s="3" t="n"/>
+      <c r="H126" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>0</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" s="2" t="n"/>
+      <c r="G127" s="3" t="n"/>
+      <c r="H127" s="2" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="2" t="n"/>
+      <c r="G128" s="3" t="n"/>
+      <c r="H128" s="2" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>1257</v>
+      </c>
+      <c r="D129" t="n">
+        <v>1074</v>
+      </c>
+      <c r="E129" t="n">
+        <v>1213</v>
+      </c>
+      <c r="F129" s="2" t="n">
+        <v>0.8543999999999999</v>
+      </c>
+      <c r="G129" s="3" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="H129" s="2" t="n">
+        <v>0.8713</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>14798</v>
+      </c>
+      <c r="D130" t="n">
+        <v>10166</v>
+      </c>
+      <c r="E130" t="n">
+        <v>14320</v>
+      </c>
+      <c r="F130" s="2" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="G130" s="3" t="n">
+        <v>0.9677</v>
+      </c>
+      <c r="H130" s="2" t="n">
+        <v>0.9228000000000001</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="2" t="n"/>
+      <c r="G131" s="3" t="n"/>
+      <c r="H131" s="2" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>33737</v>
+      </c>
+      <c r="D132" t="n">
+        <v>25289</v>
+      </c>
+      <c r="E132" t="n">
+        <v>32987</v>
+      </c>
+      <c r="F132" s="2" t="n">
+        <v>0.7495999999999999</v>
+      </c>
+      <c r="G132" s="3" t="n">
+        <v>0.9778</v>
+      </c>
+      <c r="H132" s="2" t="n">
+        <v>0.9792000000000001</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>4321</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1857</v>
+      </c>
+      <c r="E133" t="n">
+        <v>4313</v>
+      </c>
+      <c r="F133" s="2" t="n">
+        <v>0.4298</v>
+      </c>
+      <c r="G133" s="3" t="n">
+        <v>0.9981</v>
+      </c>
+      <c r="H133" s="2" t="n">
+        <v>0.4317</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>7234</v>
+      </c>
+      <c r="D134" t="n">
+        <v>4701</v>
+      </c>
+      <c r="E134" t="n">
+        <v>7069</v>
+      </c>
+      <c r="F134" s="2" t="n">
+        <v>0.6498</v>
+      </c>
+      <c r="G134" s="3" t="n">
+        <v>0.9772</v>
+      </c>
+      <c r="H134" s="2" t="n">
+        <v>0.8036</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>0</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" s="2" t="n"/>
+      <c r="G135" s="3" t="n"/>
+      <c r="H135" s="2" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>1131</v>
+      </c>
+      <c r="D136" t="n">
+        <v>666</v>
+      </c>
+      <c r="E136" t="n">
+        <v>835</v>
+      </c>
+      <c r="F136" s="2" t="n">
+        <v>0.5889</v>
+      </c>
+      <c r="G136" s="3" t="n">
+        <v>0.7383</v>
+      </c>
+      <c r="H136" s="2" t="n">
+        <v>0.9125</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>0</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" s="2" t="n"/>
+      <c r="G137" s="3" t="n"/>
+      <c r="H137" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>0</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" s="2" t="n"/>
+      <c r="G138" s="3" t="n"/>
+      <c r="H138" s="2" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>536</v>
+      </c>
+      <c r="D139" t="n">
+        <v>495</v>
+      </c>
+      <c r="E139" t="n">
+        <v>533</v>
+      </c>
+      <c r="F139" s="2" t="n">
+        <v>0.9235</v>
+      </c>
+      <c r="G139" s="3" t="n">
+        <v>0.9944</v>
+      </c>
+      <c r="H139" s="2" t="n">
+        <v>0.8326</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>0</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" s="2" t="n"/>
+      <c r="G140" s="3" t="n"/>
+      <c r="H140" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>0</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" s="2" t="n"/>
+      <c r="G141" s="3" t="n"/>
+      <c r="H141" s="2" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>0</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" s="2" t="n"/>
+      <c r="G142" s="3" t="n"/>
+      <c r="H142" s="2" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>3028</v>
+      </c>
+      <c r="D143" t="n">
+        <v>2848</v>
+      </c>
+      <c r="E143" t="n">
+        <v>3027</v>
+      </c>
+      <c r="F143" s="2" t="n">
+        <v>0.9406</v>
+      </c>
+      <c r="G143" s="3" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="H143" s="2" t="n">
+        <v>0.852</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>25963</v>
+      </c>
+      <c r="D144" t="n">
+        <v>23841</v>
+      </c>
+      <c r="E144" t="n">
+        <v>24906</v>
+      </c>
+      <c r="F144" s="2" t="n">
+        <v>0.9183</v>
+      </c>
+      <c r="G144" s="3" t="n">
+        <v>0.9593</v>
+      </c>
+      <c r="H144" s="2" t="n">
+        <v>0.9164</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>0</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" s="2" t="n"/>
+      <c r="G145" s="3" t="n"/>
+      <c r="H145" s="2" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>35064</v>
+      </c>
+      <c r="D146" t="n">
+        <v>29183</v>
+      </c>
+      <c r="E146" t="n">
+        <v>33612</v>
+      </c>
+      <c r="F146" s="2" t="n">
+        <v>0.8323</v>
+      </c>
+      <c r="G146" s="3" t="n">
+        <v>0.9586</v>
+      </c>
+      <c r="H146" s="2" t="n">
+        <v>0.9939</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>8023</v>
+      </c>
+      <c r="D147" t="n">
+        <v>6736</v>
+      </c>
+      <c r="E147" t="n">
+        <v>8018</v>
+      </c>
+      <c r="F147" s="2" t="n">
+        <v>0.8395999999999999</v>
+      </c>
+      <c r="G147" s="3" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="H147" s="2" t="n">
+        <v>0.5276</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>9090</v>
+      </c>
+      <c r="D148" t="n">
+        <v>6344</v>
+      </c>
+      <c r="E148" t="n">
+        <v>9042</v>
+      </c>
+      <c r="F148" s="2" t="n">
+        <v>0.6979000000000001</v>
+      </c>
+      <c r="G148" s="3" t="n">
+        <v>0.9947</v>
+      </c>
+      <c r="H148" s="2" t="n">
+        <v>0.9029</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>0</v>
+      </c>
+      <c r="D149" t="n">
+        <v>0</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0</v>
+      </c>
+      <c r="F149" s="2" t="n"/>
+      <c r="G149" s="3" t="n"/>
+      <c r="H149" s="2" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>1167</v>
+      </c>
+      <c r="D150" t="n">
+        <v>835</v>
+      </c>
+      <c r="E150" t="n">
+        <v>1030</v>
+      </c>
+      <c r="F150" s="2" t="n">
+        <v>0.7155</v>
+      </c>
+      <c r="G150" s="3" t="n">
+        <v>0.8826000000000001</v>
+      </c>
+      <c r="H150" s="2" t="n">
+        <v>0.9451000000000001</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>80</v>
+      </c>
+      <c r="D151" t="n">
+        <v>80</v>
+      </c>
+      <c r="E151" t="n">
+        <v>80</v>
+      </c>
+      <c r="F151" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G151" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H151" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>0</v>
+      </c>
+      <c r="D152" t="n">
+        <v>0</v>
+      </c>
+      <c r="E152" t="n">
+        <v>0</v>
+      </c>
+      <c r="F152" s="2" t="n"/>
+      <c r="G152" s="3" t="n"/>
+      <c r="H152" s="2" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>10306</v>
+      </c>
+      <c r="D153" t="n">
+        <v>10177</v>
+      </c>
+      <c r="E153" t="n">
+        <v>10271</v>
+      </c>
+      <c r="F153" s="2" t="n">
+        <v>0.9875</v>
+      </c>
+      <c r="G153" s="3" t="n">
+        <v>0.9965999999999999</v>
+      </c>
+      <c r="H153" s="2" t="n">
+        <v>0.9442</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>0</v>
+      </c>
+      <c r="D154" t="n">
+        <v>0</v>
+      </c>
+      <c r="E154" t="n">
+        <v>0</v>
+      </c>
+      <c r="F154" s="2" t="n"/>
+      <c r="G154" s="3" t="n"/>
+      <c r="H154" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>0</v>
+      </c>
+      <c r="D155" t="n">
+        <v>0</v>
+      </c>
+      <c r="E155" t="n">
+        <v>0</v>
+      </c>
+      <c r="F155" s="2" t="n"/>
+      <c r="G155" s="3" t="n"/>
+      <c r="H155" s="2" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>0</v>
+      </c>
+      <c r="D156" t="n">
+        <v>0</v>
+      </c>
+      <c r="E156" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" s="2" t="n"/>
+      <c r="G156" s="3" t="n"/>
+      <c r="H156" s="2" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>2209</v>
+      </c>
+      <c r="D157" t="n">
+        <v>2048</v>
+      </c>
+      <c r="E157" t="n">
+        <v>2208</v>
+      </c>
+      <c r="F157" s="2" t="n">
+        <v>0.9270999999999999</v>
+      </c>
+      <c r="G157" s="3" t="n">
+        <v>0.9995000000000001</v>
+      </c>
+      <c r="H157" s="2" t="n">
+        <v>0.9136</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>22424</v>
+      </c>
+      <c r="D158" t="n">
+        <v>20779</v>
+      </c>
+      <c r="E158" t="n">
+        <v>22049</v>
+      </c>
+      <c r="F158" s="2" t="n">
+        <v>0.9266</v>
+      </c>
+      <c r="G158" s="3" t="n">
+        <v>0.9833</v>
+      </c>
+      <c r="H158" s="2" t="n">
+        <v>0.9066</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>0</v>
+      </c>
+      <c r="D159" t="n">
+        <v>0</v>
+      </c>
+      <c r="E159" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" s="2" t="n"/>
+      <c r="G159" s="3" t="n"/>
+      <c r="H159" s="2" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>29514</v>
+      </c>
+      <c r="D160" t="n">
+        <v>25894</v>
+      </c>
+      <c r="E160" t="n">
+        <v>27592</v>
+      </c>
+      <c r="F160" s="2" t="n">
+        <v>0.8773000000000001</v>
+      </c>
+      <c r="G160" s="3" t="n">
+        <v>0.9349</v>
+      </c>
+      <c r="H160" s="2" t="n">
+        <v>0.9918</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>7234</v>
+      </c>
+      <c r="D161" t="n">
+        <v>6532</v>
+      </c>
+      <c r="E161" t="n">
+        <v>7233</v>
+      </c>
+      <c r="F161" s="2" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="G161" s="3" t="n">
+        <v>0.9998999999999999</v>
+      </c>
+      <c r="H161" s="2" t="n">
+        <v>0.6104999999999999</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>8031</v>
+      </c>
+      <c r="D162" t="n">
+        <v>5920</v>
+      </c>
+      <c r="E162" t="n">
+        <v>6449</v>
+      </c>
+      <c r="F162" s="2" t="n">
+        <v>0.7371</v>
+      </c>
+      <c r="G162" s="3" t="n">
+        <v>0.8029999999999999</v>
+      </c>
+      <c r="H162" s="2" t="n">
+        <v>0.8913</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>0</v>
+      </c>
+      <c r="D163" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" t="n">
+        <v>0</v>
+      </c>
+      <c r="F163" s="2" t="n"/>
+      <c r="G163" s="3" t="n"/>
+      <c r="H163" s="2" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>1403</v>
+      </c>
+      <c r="D164" t="n">
+        <v>1174</v>
+      </c>
+      <c r="E164" t="n">
+        <v>1322</v>
+      </c>
+      <c r="F164" s="2" t="n">
+        <v>0.8368000000000001</v>
+      </c>
+      <c r="G164" s="3" t="n">
+        <v>0.9423</v>
+      </c>
+      <c r="H164" s="2" t="n">
+        <v>0.9609000000000001</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>2</v>
+      </c>
+      <c r="D165" t="n">
+        <v>2</v>
+      </c>
+      <c r="E165" t="n">
+        <v>2</v>
+      </c>
+      <c r="F165" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G165" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H165" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>0</v>
+      </c>
+      <c r="D166" t="n">
+        <v>0</v>
+      </c>
+      <c r="E166" t="n">
+        <v>0</v>
+      </c>
+      <c r="F166" s="2" t="n"/>
+      <c r="G166" s="3" t="n"/>
+      <c r="H166" s="2" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>9455</v>
+      </c>
+      <c r="D167" t="n">
+        <v>9325</v>
+      </c>
+      <c r="E167" t="n">
+        <v>9441</v>
+      </c>
+      <c r="F167" s="2" t="n">
+        <v>0.9863</v>
+      </c>
+      <c r="G167" s="3" t="n">
+        <v>0.9984999999999999</v>
+      </c>
+      <c r="H167" s="2" t="n">
+        <v>0.9375</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>0</v>
+      </c>
+      <c r="D168" t="n">
+        <v>0</v>
+      </c>
+      <c r="E168" t="n">
+        <v>0</v>
+      </c>
+      <c r="F168" s="2" t="n"/>
+      <c r="G168" s="3" t="n"/>
+      <c r="H168" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>0</v>
+      </c>
+      <c r="D169" t="n">
+        <v>0</v>
+      </c>
+      <c r="E169" t="n">
+        <v>0</v>
+      </c>
+      <c r="F169" s="2" t="n"/>
+      <c r="G169" s="3" t="n"/>
+      <c r="H169" s="2" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>0</v>
+      </c>
+      <c r="D170" t="n">
+        <v>0</v>
+      </c>
+      <c r="E170" t="n">
+        <v>0</v>
+      </c>
+      <c r="F170" s="2" t="n"/>
+      <c r="G170" s="3" t="n"/>
+      <c r="H170" s="2" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>1867</v>
+      </c>
+      <c r="D171" t="n">
+        <v>1823</v>
+      </c>
+      <c r="E171" t="n">
+        <v>1867</v>
+      </c>
+      <c r="F171" s="2" t="n">
+        <v>0.9764</v>
+      </c>
+      <c r="G171" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H171" s="2" t="n">
+        <v>0.9579000000000001</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>19588</v>
+      </c>
+      <c r="D172" t="n">
+        <v>17886</v>
+      </c>
+      <c r="E172" t="n">
+        <v>19577</v>
+      </c>
+      <c r="F172" s="2" t="n">
+        <v>0.9131</v>
+      </c>
+      <c r="G172" s="3" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="H172" s="2" t="n">
+        <v>0.9187000000000001</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>0</v>
+      </c>
+      <c r="D173" t="n">
+        <v>0</v>
+      </c>
+      <c r="E173" t="n">
+        <v>0</v>
+      </c>
+      <c r="F173" s="2" t="n"/>
+      <c r="G173" s="3" t="n"/>
+      <c r="H173" s="2" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>31546</v>
+      </c>
+      <c r="D174" t="n">
+        <v>27843</v>
+      </c>
+      <c r="E174" t="n">
+        <v>31384</v>
+      </c>
+      <c r="F174" s="2" t="n">
+        <v>0.8826000000000001</v>
+      </c>
+      <c r="G174" s="3" t="n">
+        <v>0.9948999999999999</v>
+      </c>
+      <c r="H174" s="2" t="n">
+        <v>0.9889</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>6482</v>
+      </c>
+      <c r="D175" t="n">
+        <v>6162</v>
+      </c>
+      <c r="E175" t="n">
+        <v>6478</v>
+      </c>
+      <c r="F175" s="2" t="n">
+        <v>0.9506</v>
+      </c>
+      <c r="G175" s="3" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="H175" s="2" t="n">
+        <v>0.6609</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>7601</v>
+      </c>
+      <c r="D176" t="n">
+        <v>6552</v>
+      </c>
+      <c r="E176" t="n">
+        <v>7589</v>
+      </c>
+      <c r="F176" s="2" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="G176" s="3" t="n">
+        <v>0.9984000000000001</v>
+      </c>
+      <c r="H176" s="2" t="n">
+        <v>0.9157</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>0</v>
+      </c>
+      <c r="D177" t="n">
+        <v>0</v>
+      </c>
+      <c r="E177" t="n">
+        <v>0</v>
+      </c>
+      <c r="F177" s="2" t="n"/>
+      <c r="G177" s="3" t="n"/>
+      <c r="H177" s="2" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>2089</v>
+      </c>
+      <c r="D178" t="n">
+        <v>1418</v>
+      </c>
+      <c r="E178" t="n">
+        <v>1938</v>
+      </c>
+      <c r="F178" s="2" t="n">
+        <v>0.6788</v>
+      </c>
+      <c r="G178" s="3" t="n">
+        <v>0.9277</v>
+      </c>
+      <c r="H178" s="2" t="n">
+        <v>0.9523999999999999</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>93</v>
+      </c>
+      <c r="D179" t="n">
+        <v>93</v>
+      </c>
+      <c r="E179" t="n">
+        <v>93</v>
+      </c>
+      <c r="F179" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G179" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H179" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>0</v>
+      </c>
+      <c r="D180" t="n">
+        <v>0</v>
+      </c>
+      <c r="E180" t="n">
+        <v>0</v>
+      </c>
+      <c r="F180" s="2" t="n"/>
+      <c r="G180" s="3" t="n"/>
+      <c r="H180" s="2" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>6041</v>
+      </c>
+      <c r="D181" t="n">
+        <v>5903</v>
+      </c>
+      <c r="E181" t="n">
+        <v>6034</v>
+      </c>
+      <c r="F181" s="2" t="n">
+        <v>0.9772</v>
+      </c>
+      <c r="G181" s="3" t="n">
+        <v>0.9987999999999999</v>
+      </c>
+      <c r="H181" s="2" t="n">
+        <v>0.9323999999999999</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>0</v>
+      </c>
+      <c r="D182" t="n">
+        <v>0</v>
+      </c>
+      <c r="E182" t="n">
+        <v>0</v>
+      </c>
+      <c r="F182" s="2" t="n"/>
+      <c r="G182" s="3" t="n"/>
+      <c r="H182" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>0</v>
+      </c>
+      <c r="D183" t="n">
+        <v>0</v>
+      </c>
+      <c r="E183" t="n">
+        <v>0</v>
+      </c>
+      <c r="F183" s="2" t="n"/>
+      <c r="G183" s="3" t="n"/>
+      <c r="H183" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H43"/>
+  <autoFilter ref="A1:H183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$183</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$197</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,22 +519,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24970</v>
+        <v>26992</v>
       </c>
       <c r="C3" t="n">
-        <v>23296</v>
+        <v>25293</v>
       </c>
       <c r="D3" t="n">
-        <v>24310</v>
+        <v>26307</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9329999999999999</v>
+        <v>0.9370999999999999</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.9736</v>
+        <v>0.9745999999999999</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9373999999999999</v>
+        <v>0.9348000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -544,22 +544,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>238019</v>
+        <v>257304</v>
       </c>
       <c r="C4" t="n">
-        <v>199049</v>
+        <v>216166</v>
       </c>
       <c r="D4" t="n">
-        <v>230298</v>
+        <v>249514</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.8362999999999999</v>
+        <v>0.8401000000000001</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.9676</v>
+        <v>0.9697</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9428</v>
+        <v>0.9393</v>
       </c>
     </row>
     <row r="5">
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>393950</v>
+        <v>425411</v>
       </c>
       <c r="C6" t="n">
-        <v>333428</v>
+        <v>361495</v>
       </c>
       <c r="D6" t="n">
-        <v>380097</v>
+        <v>411434</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.8464</v>
+        <v>0.8498</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.9648</v>
+        <v>0.9671</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9773000000000001</v>
+        <v>0.9778</v>
       </c>
     </row>
     <row r="7">
@@ -613,22 +613,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>87686</v>
+        <v>94938</v>
       </c>
       <c r="C7" t="n">
-        <v>62355</v>
+        <v>69150</v>
       </c>
       <c r="D7" t="n">
-        <v>87490</v>
+        <v>94736</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.7111</v>
+        <v>0.7284</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.9978</v>
+        <v>0.9979</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6831999999999999</v>
+        <v>0.6785</v>
       </c>
     </row>
     <row r="8">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>95649</v>
+        <v>102805</v>
       </c>
       <c r="C8" t="n">
-        <v>79944</v>
+        <v>86388</v>
       </c>
       <c r="D8" t="n">
-        <v>92169</v>
+        <v>99301</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.8358</v>
+        <v>0.8403</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.9636</v>
+        <v>0.9659</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.9137999999999999</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="9">
@@ -682,22 +682,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13658</v>
+        <v>14703</v>
       </c>
       <c r="C10" t="n">
-        <v>9982</v>
+        <v>11018</v>
       </c>
       <c r="D10" t="n">
-        <v>11730</v>
+        <v>12774</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.7309</v>
+        <v>0.7494</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.8588</v>
+        <v>0.8687999999999999</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9621</v>
+        <v>0.9641</v>
       </c>
     </row>
     <row r="11">
@@ -707,22 +707,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1453</v>
+        <v>1504</v>
       </c>
       <c r="C11" t="n">
-        <v>1187</v>
+        <v>1238</v>
       </c>
       <c r="D11" t="n">
-        <v>1238</v>
+        <v>1289</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.8169</v>
+        <v>0.8231000000000001</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.852</v>
+        <v>0.857</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.9976999999999999</v>
+        <v>0.9978</v>
       </c>
     </row>
     <row r="12">
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>53441</v>
+        <v>57735</v>
       </c>
       <c r="C13" t="n">
-        <v>51874</v>
+        <v>56023</v>
       </c>
       <c r="D13" t="n">
-        <v>52912</v>
+        <v>57067</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9706999999999999</v>
+        <v>0.9703000000000001</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.9901000000000001</v>
+        <v>0.9884000000000001</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.9114</v>
+        <v>0.9142</v>
       </c>
     </row>
     <row r="14">
@@ -833,7 +833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H183"/>
+  <dimension ref="A1:H197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5946,8 +5946,392 @@
       <c r="G183" s="3" t="n"/>
       <c r="H183" s="2" t="n"/>
     </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>0</v>
+      </c>
+      <c r="D184" t="n">
+        <v>0</v>
+      </c>
+      <c r="E184" t="n">
+        <v>0</v>
+      </c>
+      <c r="F184" s="2" t="n"/>
+      <c r="G184" s="3" t="n"/>
+      <c r="H184" s="2" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D185" t="n">
+        <v>1997</v>
+      </c>
+      <c r="E185" t="n">
+        <v>1997</v>
+      </c>
+      <c r="F185" s="2" t="n">
+        <v>0.9876</v>
+      </c>
+      <c r="G185" s="3" t="n">
+        <v>0.9876</v>
+      </c>
+      <c r="H185" s="2" t="n">
+        <v>0.8989</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>19285</v>
+      </c>
+      <c r="D186" t="n">
+        <v>17117</v>
+      </c>
+      <c r="E186" t="n">
+        <v>19216</v>
+      </c>
+      <c r="F186" s="2" t="n">
+        <v>0.8876000000000001</v>
+      </c>
+      <c r="G186" s="3" t="n">
+        <v>0.9964</v>
+      </c>
+      <c r="H186" s="2" t="n">
+        <v>0.8922</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>0</v>
+      </c>
+      <c r="D187" t="n">
+        <v>0</v>
+      </c>
+      <c r="E187" t="n">
+        <v>0</v>
+      </c>
+      <c r="F187" s="2" t="n"/>
+      <c r="G187" s="3" t="n"/>
+      <c r="H187" s="2" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>31461</v>
+      </c>
+      <c r="D188" t="n">
+        <v>28067</v>
+      </c>
+      <c r="E188" t="n">
+        <v>31337</v>
+      </c>
+      <c r="F188" s="2" t="n">
+        <v>0.8920999999999999</v>
+      </c>
+      <c r="G188" s="3" t="n">
+        <v>0.9961</v>
+      </c>
+      <c r="H188" s="2" t="n">
+        <v>0.9838</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>7252</v>
+      </c>
+      <c r="D189" t="n">
+        <v>6795</v>
+      </c>
+      <c r="E189" t="n">
+        <v>7246</v>
+      </c>
+      <c r="F189" s="2" t="n">
+        <v>0.9370000000000001</v>
+      </c>
+      <c r="G189" s="3" t="n">
+        <v>0.9992</v>
+      </c>
+      <c r="H189" s="2" t="n">
+        <v>0.6207</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>7156</v>
+      </c>
+      <c r="D190" t="n">
+        <v>6444</v>
+      </c>
+      <c r="E190" t="n">
+        <v>7132</v>
+      </c>
+      <c r="F190" s="2" t="n">
+        <v>0.9005</v>
+      </c>
+      <c r="G190" s="3" t="n">
+        <v>0.9965999999999999</v>
+      </c>
+      <c r="H190" s="2" t="n">
+        <v>0.8719</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>0</v>
+      </c>
+      <c r="D191" t="n">
+        <v>0</v>
+      </c>
+      <c r="E191" t="n">
+        <v>0</v>
+      </c>
+      <c r="F191" s="2" t="n"/>
+      <c r="G191" s="3" t="n"/>
+      <c r="H191" s="2" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>1045</v>
+      </c>
+      <c r="D192" t="n">
+        <v>1036</v>
+      </c>
+      <c r="E192" t="n">
+        <v>1044</v>
+      </c>
+      <c r="F192" s="2" t="n">
+        <v>0.9914000000000001</v>
+      </c>
+      <c r="G192" s="3" t="n">
+        <v>0.9990000000000001</v>
+      </c>
+      <c r="H192" s="2" t="n">
+        <v>0.9882</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>51</v>
+      </c>
+      <c r="D193" t="n">
+        <v>51</v>
+      </c>
+      <c r="E193" t="n">
+        <v>51</v>
+      </c>
+      <c r="F193" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G193" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H193" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>0</v>
+      </c>
+      <c r="D194" t="n">
+        <v>0</v>
+      </c>
+      <c r="E194" t="n">
+        <v>0</v>
+      </c>
+      <c r="F194" s="2" t="n"/>
+      <c r="G194" s="3" t="n"/>
+      <c r="H194" s="2" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>4294</v>
+      </c>
+      <c r="D195" t="n">
+        <v>4149</v>
+      </c>
+      <c r="E195" t="n">
+        <v>4155</v>
+      </c>
+      <c r="F195" s="2" t="n">
+        <v>0.9662000000000001</v>
+      </c>
+      <c r="G195" s="3" t="n">
+        <v>0.9676</v>
+      </c>
+      <c r="H195" s="2" t="n">
+        <v>0.9429999999999999</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>0</v>
+      </c>
+      <c r="D196" t="n">
+        <v>0</v>
+      </c>
+      <c r="E196" t="n">
+        <v>0</v>
+      </c>
+      <c r="F196" s="2" t="n"/>
+      <c r="G196" s="3" t="n"/>
+      <c r="H196" s="2" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>0</v>
+      </c>
+      <c r="D197" t="n">
+        <v>0</v>
+      </c>
+      <c r="E197" t="n">
+        <v>0</v>
+      </c>
+      <c r="F197" s="2" t="n"/>
+      <c r="G197" s="3" t="n"/>
+      <c r="H197" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H183"/>
+  <autoFilter ref="A1:H197"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$197</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$211</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,22 +519,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26992</v>
+        <v>28989</v>
       </c>
       <c r="C3" t="n">
-        <v>25293</v>
+        <v>27112</v>
       </c>
       <c r="D3" t="n">
-        <v>26307</v>
+        <v>28126</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9370999999999999</v>
+        <v>0.9353</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.9745999999999999</v>
+        <v>0.9702</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9348000000000001</v>
+        <v>0.9349</v>
       </c>
     </row>
     <row r="4">
@@ -544,22 +544,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>257304</v>
+        <v>271688</v>
       </c>
       <c r="C4" t="n">
-        <v>216166</v>
+        <v>227145</v>
       </c>
       <c r="D4" t="n">
-        <v>249514</v>
+        <v>262947</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.8401000000000001</v>
+        <v>0.8361</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.9697</v>
+        <v>0.9678</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9393</v>
+        <v>0.9335</v>
       </c>
     </row>
     <row r="5">
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>425411</v>
+        <v>448748</v>
       </c>
       <c r="C6" t="n">
-        <v>361495</v>
+        <v>379411</v>
       </c>
       <c r="D6" t="n">
-        <v>411434</v>
+        <v>434729</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.8498</v>
+        <v>0.8454999999999999</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.9671</v>
+        <v>0.9688</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9778</v>
+        <v>0.9773999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -613,22 +613,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>94938</v>
+        <v>100092</v>
       </c>
       <c r="C7" t="n">
-        <v>69150</v>
+        <v>72561</v>
       </c>
       <c r="D7" t="n">
-        <v>94736</v>
+        <v>98147</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.7284</v>
+        <v>0.7249</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.9979</v>
+        <v>0.9806</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6785</v>
+        <v>0.6603</v>
       </c>
     </row>
     <row r="8">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>102805</v>
+        <v>109412</v>
       </c>
       <c r="C8" t="n">
-        <v>86388</v>
+        <v>91680</v>
       </c>
       <c r="D8" t="n">
-        <v>99301</v>
+        <v>105867</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.8403</v>
+        <v>0.8379000000000001</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.9659</v>
+        <v>0.9676</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.91</v>
+        <v>0.903</v>
       </c>
     </row>
     <row r="9">
@@ -682,22 +682,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14703</v>
+        <v>16332</v>
       </c>
       <c r="C10" t="n">
-        <v>11018</v>
+        <v>11454</v>
       </c>
       <c r="D10" t="n">
-        <v>12774</v>
+        <v>13215</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.7494</v>
+        <v>0.7012999999999999</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.8687999999999999</v>
+        <v>0.8090999999999999</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9641</v>
+        <v>0.9627</v>
       </c>
     </row>
     <row r="11">
@@ -707,22 +707,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1504</v>
+        <v>1531</v>
       </c>
       <c r="C11" t="n">
-        <v>1238</v>
+        <v>1265</v>
       </c>
       <c r="D11" t="n">
-        <v>1289</v>
+        <v>1316</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.8231000000000001</v>
+        <v>0.8262999999999999</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.857</v>
+        <v>0.8595999999999999</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.9978</v>
+        <v>0.998</v>
       </c>
     </row>
     <row r="12">
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>57735</v>
+        <v>61037</v>
       </c>
       <c r="C13" t="n">
-        <v>56023</v>
+        <v>58706</v>
       </c>
       <c r="D13" t="n">
-        <v>57067</v>
+        <v>60036</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9703000000000001</v>
+        <v>0.9618000000000001</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.9884000000000001</v>
+        <v>0.9836</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.9142</v>
+        <v>0.9115000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -833,7 +833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H197"/>
+  <dimension ref="A1:H211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6330,8 +6330,392 @@
       <c r="G197" s="3" t="n"/>
       <c r="H197" s="2" t="n"/>
     </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>0</v>
+      </c>
+      <c r="D198" t="n">
+        <v>0</v>
+      </c>
+      <c r="E198" t="n">
+        <v>0</v>
+      </c>
+      <c r="F198" s="2" t="n"/>
+      <c r="G198" s="3" t="n"/>
+      <c r="H198" s="2" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>1997</v>
+      </c>
+      <c r="D199" t="n">
+        <v>1819</v>
+      </c>
+      <c r="E199" t="n">
+        <v>1819</v>
+      </c>
+      <c r="F199" s="2" t="n">
+        <v>0.9109</v>
+      </c>
+      <c r="G199" s="3" t="n">
+        <v>0.9109</v>
+      </c>
+      <c r="H199" s="2" t="n">
+        <v>0.9362</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>14384</v>
+      </c>
+      <c r="D200" t="n">
+        <v>10979</v>
+      </c>
+      <c r="E200" t="n">
+        <v>13433</v>
+      </c>
+      <c r="F200" s="2" t="n">
+        <v>0.7633</v>
+      </c>
+      <c r="G200" s="3" t="n">
+        <v>0.9339</v>
+      </c>
+      <c r="H200" s="2" t="n">
+        <v>0.8602</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>0</v>
+      </c>
+      <c r="D201" t="n">
+        <v>0</v>
+      </c>
+      <c r="E201" t="n">
+        <v>0</v>
+      </c>
+      <c r="F201" s="2" t="n"/>
+      <c r="G201" s="3" t="n"/>
+      <c r="H201" s="2" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>23337</v>
+      </c>
+      <c r="D202" t="n">
+        <v>17916</v>
+      </c>
+      <c r="E202" t="n">
+        <v>23295</v>
+      </c>
+      <c r="F202" s="2" t="n">
+        <v>0.7676999999999999</v>
+      </c>
+      <c r="G202" s="3" t="n">
+        <v>0.9982</v>
+      </c>
+      <c r="H202" s="2" t="n">
+        <v>0.9725</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>5154</v>
+      </c>
+      <c r="D203" t="n">
+        <v>3411</v>
+      </c>
+      <c r="E203" t="n">
+        <v>3411</v>
+      </c>
+      <c r="F203" s="2" t="n">
+        <v>0.6618000000000001</v>
+      </c>
+      <c r="G203" s="3" t="n">
+        <v>0.6618000000000001</v>
+      </c>
+      <c r="H203" s="2" t="n">
+        <v>0.4387</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>6607</v>
+      </c>
+      <c r="D204" t="n">
+        <v>5292</v>
+      </c>
+      <c r="E204" t="n">
+        <v>6566</v>
+      </c>
+      <c r="F204" s="2" t="n">
+        <v>0.8009999999999999</v>
+      </c>
+      <c r="G204" s="3" t="n">
+        <v>0.9937999999999999</v>
+      </c>
+      <c r="H204" s="2" t="n">
+        <v>0.8118000000000001</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>0</v>
+      </c>
+      <c r="D205" t="n">
+        <v>0</v>
+      </c>
+      <c r="E205" t="n">
+        <v>0</v>
+      </c>
+      <c r="F205" s="2" t="n"/>
+      <c r="G205" s="3" t="n"/>
+      <c r="H205" s="2" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>1629</v>
+      </c>
+      <c r="D206" t="n">
+        <v>436</v>
+      </c>
+      <c r="E206" t="n">
+        <v>441</v>
+      </c>
+      <c r="F206" s="2" t="n">
+        <v>0.2676</v>
+      </c>
+      <c r="G206" s="3" t="n">
+        <v>0.2707</v>
+      </c>
+      <c r="H206" s="2" t="n">
+        <v>0.9440999999999999</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>27</v>
+      </c>
+      <c r="D207" t="n">
+        <v>27</v>
+      </c>
+      <c r="E207" t="n">
+        <v>27</v>
+      </c>
+      <c r="F207" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G207" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H207" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>0</v>
+      </c>
+      <c r="D208" t="n">
+        <v>0</v>
+      </c>
+      <c r="E208" t="n">
+        <v>0</v>
+      </c>
+      <c r="F208" s="2" t="n"/>
+      <c r="G208" s="3" t="n"/>
+      <c r="H208" s="2" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>3302</v>
+      </c>
+      <c r="D209" t="n">
+        <v>2683</v>
+      </c>
+      <c r="E209" t="n">
+        <v>2969</v>
+      </c>
+      <c r="F209" s="2" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="G209" s="3" t="n">
+        <v>0.8992</v>
+      </c>
+      <c r="H209" s="2" t="n">
+        <v>0.8798</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>0</v>
+      </c>
+      <c r="D210" t="n">
+        <v>0</v>
+      </c>
+      <c r="E210" t="n">
+        <v>0</v>
+      </c>
+      <c r="F210" s="2" t="n"/>
+      <c r="G210" s="3" t="n"/>
+      <c r="H210" s="2" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>0</v>
+      </c>
+      <c r="D211" t="n">
+        <v>0</v>
+      </c>
+      <c r="E211" t="n">
+        <v>0</v>
+      </c>
+      <c r="F211" s="2" t="n"/>
+      <c r="G211" s="3" t="n"/>
+      <c r="H211" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H197"/>
+  <autoFilter ref="A1:H211"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$211</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$225</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,22 +519,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28989</v>
+        <v>30153</v>
       </c>
       <c r="C3" t="n">
-        <v>27112</v>
+        <v>27552</v>
       </c>
       <c r="D3" t="n">
-        <v>28126</v>
+        <v>28566</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9353</v>
+        <v>0.9137000000000001</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.9702</v>
+        <v>0.9473999999999999</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9349</v>
+        <v>0.9290999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -544,22 +544,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>271688</v>
+        <v>282244</v>
       </c>
       <c r="C4" t="n">
-        <v>227145</v>
+        <v>229057</v>
       </c>
       <c r="D4" t="n">
-        <v>262947</v>
+        <v>264859</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.8361</v>
+        <v>0.8116</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.9678</v>
+        <v>0.9384</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9335</v>
+        <v>0.9278</v>
       </c>
     </row>
     <row r="5">
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>448748</v>
+        <v>468040</v>
       </c>
       <c r="C6" t="n">
-        <v>379411</v>
+        <v>387623</v>
       </c>
       <c r="D6" t="n">
-        <v>434729</v>
+        <v>442961</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.8454999999999999</v>
+        <v>0.8281999999999999</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.9688</v>
+        <v>0.9464</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9773999999999999</v>
+        <v>0.9768000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -613,22 +613,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>100092</v>
+        <v>104553</v>
       </c>
       <c r="C7" t="n">
-        <v>72561</v>
+        <v>73446</v>
       </c>
       <c r="D7" t="n">
-        <v>98147</v>
+        <v>99032</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.7249</v>
+        <v>0.7025</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.9806</v>
+        <v>0.9472</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6603</v>
+        <v>0.6546</v>
       </c>
     </row>
     <row r="8">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>109412</v>
+        <v>115511</v>
       </c>
       <c r="C8" t="n">
-        <v>91680</v>
+        <v>93512</v>
       </c>
       <c r="D8" t="n">
-        <v>105867</v>
+        <v>107699</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.8379000000000001</v>
+        <v>0.8096</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.9676</v>
+        <v>0.9323999999999999</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.903</v>
+        <v>0.8901</v>
       </c>
     </row>
     <row r="9">
@@ -682,22 +682,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16332</v>
+        <v>17023</v>
       </c>
       <c r="C10" t="n">
-        <v>11454</v>
+        <v>11632</v>
       </c>
       <c r="D10" t="n">
-        <v>13215</v>
+        <v>13393</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.7012999999999999</v>
+        <v>0.6833</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.8090999999999999</v>
+        <v>0.7868000000000001</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9627</v>
+        <v>0.9619</v>
       </c>
     </row>
     <row r="11">
@@ -722,7 +722,7 @@
         <v>0.8595999999999999</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.998</v>
+        <v>0.9982</v>
       </c>
     </row>
     <row r="12">
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>61037</v>
+        <v>62781</v>
       </c>
       <c r="C13" t="n">
-        <v>58706</v>
+        <v>58773</v>
       </c>
       <c r="D13" t="n">
-        <v>60036</v>
+        <v>60103</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9618000000000001</v>
+        <v>0.9362</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.9836</v>
+        <v>0.9573</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.9115000000000001</v>
+        <v>0.9048</v>
       </c>
     </row>
     <row r="14">
@@ -833,7 +833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H211"/>
+  <dimension ref="A1:H225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6714,8 +6714,388 @@
       <c r="G211" s="3" t="n"/>
       <c r="H211" s="2" t="n"/>
     </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>0</v>
+      </c>
+      <c r="D212" t="n">
+        <v>0</v>
+      </c>
+      <c r="E212" t="n">
+        <v>0</v>
+      </c>
+      <c r="F212" s="2" t="n"/>
+      <c r="G212" s="3" t="n"/>
+      <c r="H212" s="2" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>1164</v>
+      </c>
+      <c r="D213" t="n">
+        <v>440</v>
+      </c>
+      <c r="E213" t="n">
+        <v>440</v>
+      </c>
+      <c r="F213" s="2" t="n">
+        <v>0.3779999999999999</v>
+      </c>
+      <c r="G213" s="3" t="n">
+        <v>0.3779999999999999</v>
+      </c>
+      <c r="H213" s="2" t="n">
+        <v>0.8434</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>10556</v>
+      </c>
+      <c r="D214" t="n">
+        <v>1912</v>
+      </c>
+      <c r="E214" t="n">
+        <v>1912</v>
+      </c>
+      <c r="F214" s="2" t="n">
+        <v>0.1811</v>
+      </c>
+      <c r="G214" s="3" t="n">
+        <v>0.1811</v>
+      </c>
+      <c r="H214" s="2" t="n">
+        <v>0.8381999999999999</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>0</v>
+      </c>
+      <c r="D215" t="n">
+        <v>0</v>
+      </c>
+      <c r="E215" t="n">
+        <v>0</v>
+      </c>
+      <c r="F215" s="2" t="n"/>
+      <c r="G215" s="3" t="n"/>
+      <c r="H215" s="2" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>19292</v>
+      </c>
+      <c r="D216" t="n">
+        <v>8212</v>
+      </c>
+      <c r="E216" t="n">
+        <v>8232</v>
+      </c>
+      <c r="F216" s="2" t="n">
+        <v>0.4257</v>
+      </c>
+      <c r="G216" s="3" t="n">
+        <v>0.4267</v>
+      </c>
+      <c r="H216" s="2" t="n">
+        <v>0.9676</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>4461</v>
+      </c>
+      <c r="D217" t="n">
+        <v>885</v>
+      </c>
+      <c r="E217" t="n">
+        <v>885</v>
+      </c>
+      <c r="F217" s="2" t="n">
+        <v>0.1984</v>
+      </c>
+      <c r="G217" s="3" t="n">
+        <v>0.1984</v>
+      </c>
+      <c r="H217" s="2" t="n">
+        <v>0.5779</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>6099</v>
+      </c>
+      <c r="D218" t="n">
+        <v>1832</v>
+      </c>
+      <c r="E218" t="n">
+        <v>1832</v>
+      </c>
+      <c r="F218" s="2" t="n">
+        <v>0.3004</v>
+      </c>
+      <c r="G218" s="3" t="n">
+        <v>0.3004</v>
+      </c>
+      <c r="H218" s="2" t="n">
+        <v>0.6943</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>0</v>
+      </c>
+      <c r="D219" t="n">
+        <v>0</v>
+      </c>
+      <c r="E219" t="n">
+        <v>0</v>
+      </c>
+      <c r="F219" s="2" t="n"/>
+      <c r="G219" s="3" t="n"/>
+      <c r="H219" s="2" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>691</v>
+      </c>
+      <c r="D220" t="n">
+        <v>178</v>
+      </c>
+      <c r="E220" t="n">
+        <v>178</v>
+      </c>
+      <c r="F220" s="2" t="n">
+        <v>0.2576</v>
+      </c>
+      <c r="G220" s="3" t="n">
+        <v>0.2576</v>
+      </c>
+      <c r="H220" s="2" t="n">
+        <v>0.9478</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>0</v>
+      </c>
+      <c r="D221" t="n">
+        <v>0</v>
+      </c>
+      <c r="E221" t="n">
+        <v>0</v>
+      </c>
+      <c r="F221" s="2" t="n"/>
+      <c r="G221" s="3" t="n"/>
+      <c r="H221" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>0</v>
+      </c>
+      <c r="D222" t="n">
+        <v>0</v>
+      </c>
+      <c r="E222" t="n">
+        <v>0</v>
+      </c>
+      <c r="F222" s="2" t="n"/>
+      <c r="G222" s="3" t="n"/>
+      <c r="H222" s="2" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>1744</v>
+      </c>
+      <c r="D223" t="n">
+        <v>67</v>
+      </c>
+      <c r="E223" t="n">
+        <v>67</v>
+      </c>
+      <c r="F223" s="2" t="n">
+        <v>0.0384</v>
+      </c>
+      <c r="G223" s="3" t="n">
+        <v>0.0384</v>
+      </c>
+      <c r="H223" s="2" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>0</v>
+      </c>
+      <c r="D224" t="n">
+        <v>0</v>
+      </c>
+      <c r="E224" t="n">
+        <v>0</v>
+      </c>
+      <c r="F224" s="2" t="n"/>
+      <c r="G224" s="3" t="n"/>
+      <c r="H224" s="2" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>0</v>
+      </c>
+      <c r="D225" t="n">
+        <v>0</v>
+      </c>
+      <c r="E225" t="n">
+        <v>0</v>
+      </c>
+      <c r="F225" s="2" t="n"/>
+      <c r="G225" s="3" t="n"/>
+      <c r="H225" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H211"/>
+  <autoFilter ref="A1:H225"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$225</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$239</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,22 +519,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30153</v>
+        <v>31456</v>
       </c>
       <c r="C3" t="n">
-        <v>27552</v>
+        <v>28618</v>
       </c>
       <c r="D3" t="n">
-        <v>28566</v>
+        <v>29632</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9137000000000001</v>
+        <v>0.9098000000000001</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.9473999999999999</v>
+        <v>0.9420000000000001</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9290999999999999</v>
+        <v>0.9265000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -544,22 +544,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>282244</v>
+        <v>296473</v>
       </c>
       <c r="C4" t="n">
-        <v>229057</v>
+        <v>239435</v>
       </c>
       <c r="D4" t="n">
-        <v>264859</v>
+        <v>277282</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.8116</v>
+        <v>0.8076000000000001</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.9384</v>
+        <v>0.9353</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9278</v>
+        <v>0.9216</v>
       </c>
     </row>
     <row r="5">
@@ -588,19 +588,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>468040</v>
+        <v>495955</v>
       </c>
       <c r="C6" t="n">
-        <v>387623</v>
+        <v>408284</v>
       </c>
       <c r="D6" t="n">
-        <v>442961</v>
+        <v>470787</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.8281999999999999</v>
+        <v>0.8231999999999999</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.9464</v>
+        <v>0.9493</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>0.9768000000000001</v>
@@ -613,22 +613,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>104553</v>
+        <v>108767</v>
       </c>
       <c r="C7" t="n">
-        <v>73446</v>
+        <v>75320</v>
       </c>
       <c r="D7" t="n">
-        <v>99032</v>
+        <v>103241</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.7025</v>
+        <v>0.6925</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.9472</v>
+        <v>0.9492</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6546</v>
+        <v>0.6433</v>
       </c>
     </row>
     <row r="8">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>115511</v>
+        <v>122735</v>
       </c>
       <c r="C8" t="n">
-        <v>93512</v>
+        <v>97762</v>
       </c>
       <c r="D8" t="n">
-        <v>107699</v>
+        <v>113935</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.8096</v>
+        <v>0.7965000000000001</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.9323999999999999</v>
+        <v>0.9283</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8901</v>
+        <v>0.8798999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -682,22 +682,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17023</v>
+        <v>18113</v>
       </c>
       <c r="C10" t="n">
-        <v>11632</v>
+        <v>12512</v>
       </c>
       <c r="D10" t="n">
-        <v>13393</v>
+        <v>14338</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.6833</v>
+        <v>0.6908</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.7868000000000001</v>
+        <v>0.7916</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9619</v>
+        <v>0.9582999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -722,7 +722,7 @@
         <v>0.8595999999999999</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.9982</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="12">
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>62781</v>
+        <v>64181</v>
       </c>
       <c r="C13" t="n">
-        <v>58773</v>
+        <v>60029</v>
       </c>
       <c r="D13" t="n">
-        <v>60103</v>
+        <v>61478</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9362</v>
+        <v>0.9353</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.9573</v>
+        <v>0.9579000000000001</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.9048</v>
+        <v>0.9037999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -797,7 +797,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.4064</v>
+        <v>0.4699</v>
       </c>
     </row>
     <row r="15">
@@ -833,7 +833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H225"/>
+  <dimension ref="A1:H239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7094,8 +7094,390 @@
       <c r="G225" s="3" t="n"/>
       <c r="H225" s="2" t="n"/>
     </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>0</v>
+      </c>
+      <c r="D226" t="n">
+        <v>0</v>
+      </c>
+      <c r="E226" t="n">
+        <v>0</v>
+      </c>
+      <c r="F226" s="2" t="n"/>
+      <c r="G226" s="3" t="n"/>
+      <c r="H226" s="2" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>1303</v>
+      </c>
+      <c r="D227" t="n">
+        <v>1066</v>
+      </c>
+      <c r="E227" t="n">
+        <v>1066</v>
+      </c>
+      <c r="F227" s="2" t="n">
+        <v>0.8181</v>
+      </c>
+      <c r="G227" s="3" t="n">
+        <v>0.8181</v>
+      </c>
+      <c r="H227" s="2" t="n">
+        <v>0.8773000000000001</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>14229</v>
+      </c>
+      <c r="D228" t="n">
+        <v>10378</v>
+      </c>
+      <c r="E228" t="n">
+        <v>12423</v>
+      </c>
+      <c r="F228" s="2" t="n">
+        <v>0.7293999999999999</v>
+      </c>
+      <c r="G228" s="3" t="n">
+        <v>0.8731</v>
+      </c>
+      <c r="H228" s="2" t="n">
+        <v>0.8066</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>0</v>
+      </c>
+      <c r="D229" t="n">
+        <v>0</v>
+      </c>
+      <c r="E229" t="n">
+        <v>0</v>
+      </c>
+      <c r="F229" s="2" t="n"/>
+      <c r="G229" s="3" t="n"/>
+      <c r="H229" s="2" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>27915</v>
+      </c>
+      <c r="D230" t="n">
+        <v>20661</v>
+      </c>
+      <c r="E230" t="n">
+        <v>27826</v>
+      </c>
+      <c r="F230" s="2" t="n">
+        <v>0.7401000000000001</v>
+      </c>
+      <c r="G230" s="3" t="n">
+        <v>0.9968</v>
+      </c>
+      <c r="H230" s="2" t="n">
+        <v>0.9765999999999999</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>4214</v>
+      </c>
+      <c r="D231" t="n">
+        <v>1874</v>
+      </c>
+      <c r="E231" t="n">
+        <v>4209</v>
+      </c>
+      <c r="F231" s="2" t="n">
+        <v>0.4447</v>
+      </c>
+      <c r="G231" s="3" t="n">
+        <v>0.9987999999999999</v>
+      </c>
+      <c r="H231" s="2" t="n">
+        <v>0.4839</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>7224</v>
+      </c>
+      <c r="D232" t="n">
+        <v>4250</v>
+      </c>
+      <c r="E232" t="n">
+        <v>6236</v>
+      </c>
+      <c r="F232" s="2" t="n">
+        <v>0.5882999999999999</v>
+      </c>
+      <c r="G232" s="3" t="n">
+        <v>0.8632</v>
+      </c>
+      <c r="H232" s="2" t="n">
+        <v>0.7105</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>0</v>
+      </c>
+      <c r="D233" t="n">
+        <v>0</v>
+      </c>
+      <c r="E233" t="n">
+        <v>0</v>
+      </c>
+      <c r="F233" s="2" t="n"/>
+      <c r="G233" s="3" t="n"/>
+      <c r="H233" s="2" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>1090</v>
+      </c>
+      <c r="D234" t="n">
+        <v>880</v>
+      </c>
+      <c r="E234" t="n">
+        <v>945</v>
+      </c>
+      <c r="F234" s="2" t="n">
+        <v>0.8073</v>
+      </c>
+      <c r="G234" s="3" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="H234" s="2" t="n">
+        <v>0.8944</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>0</v>
+      </c>
+      <c r="D235" t="n">
+        <v>0</v>
+      </c>
+      <c r="E235" t="n">
+        <v>0</v>
+      </c>
+      <c r="F235" s="2" t="n"/>
+      <c r="G235" s="3" t="n"/>
+      <c r="H235" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>0</v>
+      </c>
+      <c r="D236" t="n">
+        <v>0</v>
+      </c>
+      <c r="E236" t="n">
+        <v>0</v>
+      </c>
+      <c r="F236" s="2" t="n"/>
+      <c r="G236" s="3" t="n"/>
+      <c r="H236" s="2" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>1400</v>
+      </c>
+      <c r="D237" t="n">
+        <v>1256</v>
+      </c>
+      <c r="E237" t="n">
+        <v>1375</v>
+      </c>
+      <c r="F237" s="2" t="n">
+        <v>0.8970999999999999</v>
+      </c>
+      <c r="G237" s="3" t="n">
+        <v>0.9821</v>
+      </c>
+      <c r="H237" s="2" t="n">
+        <v>0.8884000000000001</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>0</v>
+      </c>
+      <c r="D238" t="n">
+        <v>0</v>
+      </c>
+      <c r="E238" t="n">
+        <v>0</v>
+      </c>
+      <c r="F238" s="2" t="n"/>
+      <c r="G238" s="3" t="n"/>
+      <c r="H238" s="2" t="n">
+        <v>0.9333</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>0</v>
+      </c>
+      <c r="D239" t="n">
+        <v>0</v>
+      </c>
+      <c r="E239" t="n">
+        <v>0</v>
+      </c>
+      <c r="F239" s="2" t="n"/>
+      <c r="G239" s="3" t="n"/>
+      <c r="H239" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H225"/>
+  <autoFilter ref="A1:H239"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$239</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$253</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,22 +519,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31456</v>
+        <v>35214</v>
       </c>
       <c r="C3" t="n">
-        <v>28618</v>
+        <v>31941</v>
       </c>
       <c r="D3" t="n">
-        <v>29632</v>
+        <v>33105</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9098000000000001</v>
+        <v>0.9070999999999999</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.9420000000000001</v>
+        <v>0.9401</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9265000000000001</v>
+        <v>0.9278</v>
       </c>
     </row>
     <row r="4">
@@ -544,22 +544,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>296473</v>
+        <v>318106</v>
       </c>
       <c r="C4" t="n">
-        <v>239435</v>
+        <v>259074</v>
       </c>
       <c r="D4" t="n">
-        <v>277282</v>
+        <v>298300</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.8076000000000001</v>
+        <v>0.8144</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.9353</v>
+        <v>0.9377</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9216</v>
+        <v>0.9218000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>495955</v>
+        <v>527681</v>
       </c>
       <c r="C6" t="n">
-        <v>408284</v>
+        <v>435872</v>
       </c>
       <c r="D6" t="n">
-        <v>470787</v>
+        <v>502282</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.8231999999999999</v>
+        <v>0.826</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.9493</v>
+        <v>0.9519</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9768000000000001</v>
+        <v>0.9765</v>
       </c>
     </row>
     <row r="7">
@@ -613,22 +613,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>108767</v>
+        <v>115423</v>
       </c>
       <c r="C7" t="n">
-        <v>75320</v>
+        <v>81300</v>
       </c>
       <c r="D7" t="n">
-        <v>103241</v>
+        <v>109889</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.6925</v>
+        <v>0.7044</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.9492</v>
+        <v>0.9520999999999999</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6433</v>
+        <v>0.6445000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>122735</v>
+        <v>132161</v>
       </c>
       <c r="C8" t="n">
-        <v>97762</v>
+        <v>104155</v>
       </c>
       <c r="D8" t="n">
-        <v>113935</v>
+        <v>122498</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.7965000000000001</v>
+        <v>0.7881</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.9283</v>
+        <v>0.9268999999999999</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8798999999999999</v>
+        <v>0.8722</v>
       </c>
     </row>
     <row r="9">
@@ -682,22 +682,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18113</v>
+        <v>20237</v>
       </c>
       <c r="C10" t="n">
-        <v>12512</v>
+        <v>14178</v>
       </c>
       <c r="D10" t="n">
-        <v>14338</v>
+        <v>16451</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.6908</v>
+        <v>0.7006</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.7916</v>
+        <v>0.8129000000000001</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9582999999999999</v>
+        <v>0.9577</v>
       </c>
     </row>
     <row r="11">
@@ -707,19 +707,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1531</v>
+        <v>1624</v>
       </c>
       <c r="C11" t="n">
-        <v>1265</v>
+        <v>1358</v>
       </c>
       <c r="D11" t="n">
-        <v>1316</v>
+        <v>1409</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.8262999999999999</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.8595999999999999</v>
+        <v>0.8676</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0.9983</v>
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>64181</v>
+        <v>69138</v>
       </c>
       <c r="C13" t="n">
-        <v>60029</v>
+        <v>64885</v>
       </c>
       <c r="D13" t="n">
-        <v>61478</v>
+        <v>66432</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9353</v>
+        <v>0.9384999999999999</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.9579000000000001</v>
+        <v>0.9609000000000001</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.9037999999999999</v>
+        <v>0.9033</v>
       </c>
     </row>
     <row r="14">
@@ -782,13 +782,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3938</v>
+        <v>4322</v>
       </c>
       <c r="C14" t="n">
-        <v>3938</v>
+        <v>4322</v>
       </c>
       <c r="D14" t="n">
-        <v>3938</v>
+        <v>4322</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>1</v>
@@ -797,7 +797,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.4699</v>
+        <v>0.5556</v>
       </c>
     </row>
     <row r="15">
@@ -833,7 +833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H239"/>
+  <dimension ref="A1:H253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7476,8 +7476,398 @@
       <c r="G239" s="3" t="n"/>
       <c r="H239" s="2" t="n"/>
     </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>0</v>
+      </c>
+      <c r="D240" t="n">
+        <v>0</v>
+      </c>
+      <c r="E240" t="n">
+        <v>0</v>
+      </c>
+      <c r="F240" s="2" t="n"/>
+      <c r="G240" s="3" t="n"/>
+      <c r="H240" s="2" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>3758</v>
+      </c>
+      <c r="D241" t="n">
+        <v>3323</v>
+      </c>
+      <c r="E241" t="n">
+        <v>3473</v>
+      </c>
+      <c r="F241" s="2" t="n">
+        <v>0.8842</v>
+      </c>
+      <c r="G241" s="3" t="n">
+        <v>0.9242</v>
+      </c>
+      <c r="H241" s="2" t="n">
+        <v>0.9527</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>21633</v>
+      </c>
+      <c r="D242" t="n">
+        <v>19639</v>
+      </c>
+      <c r="E242" t="n">
+        <v>21018</v>
+      </c>
+      <c r="F242" s="2" t="n">
+        <v>0.9078000000000001</v>
+      </c>
+      <c r="G242" s="3" t="n">
+        <v>0.9716</v>
+      </c>
+      <c r="H242" s="2" t="n">
+        <v>0.9251999999999999</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>0</v>
+      </c>
+      <c r="D243" t="n">
+        <v>0</v>
+      </c>
+      <c r="E243" t="n">
+        <v>0</v>
+      </c>
+      <c r="F243" s="2" t="n"/>
+      <c r="G243" s="3" t="n"/>
+      <c r="H243" s="2" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>31726</v>
+      </c>
+      <c r="D244" t="n">
+        <v>27588</v>
+      </c>
+      <c r="E244" t="n">
+        <v>31495</v>
+      </c>
+      <c r="F244" s="2" t="n">
+        <v>0.8695999999999999</v>
+      </c>
+      <c r="G244" s="3" t="n">
+        <v>0.9926999999999999</v>
+      </c>
+      <c r="H244" s="2" t="n">
+        <v>0.9723000000000001</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>6656</v>
+      </c>
+      <c r="D245" t="n">
+        <v>5980</v>
+      </c>
+      <c r="E245" t="n">
+        <v>6648</v>
+      </c>
+      <c r="F245" s="2" t="n">
+        <v>0.8984000000000001</v>
+      </c>
+      <c r="G245" s="3" t="n">
+        <v>0.9987999999999999</v>
+      </c>
+      <c r="H245" s="2" t="n">
+        <v>0.6609</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>9426</v>
+      </c>
+      <c r="D246" t="n">
+        <v>6393</v>
+      </c>
+      <c r="E246" t="n">
+        <v>8563</v>
+      </c>
+      <c r="F246" s="2" t="n">
+        <v>0.6781999999999999</v>
+      </c>
+      <c r="G246" s="3" t="n">
+        <v>0.9084</v>
+      </c>
+      <c r="H246" s="2" t="n">
+        <v>0.7773</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>0</v>
+      </c>
+      <c r="D247" t="n">
+        <v>0</v>
+      </c>
+      <c r="E247" t="n">
+        <v>0</v>
+      </c>
+      <c r="F247" s="2" t="n"/>
+      <c r="G247" s="3" t="n"/>
+      <c r="H247" s="2" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>2124</v>
+      </c>
+      <c r="D248" t="n">
+        <v>1666</v>
+      </c>
+      <c r="E248" t="n">
+        <v>2113</v>
+      </c>
+      <c r="F248" s="2" t="n">
+        <v>0.7844</v>
+      </c>
+      <c r="G248" s="3" t="n">
+        <v>0.9948</v>
+      </c>
+      <c r="H248" s="2" t="n">
+        <v>0.9506999999999999</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>93</v>
+      </c>
+      <c r="D249" t="n">
+        <v>93</v>
+      </c>
+      <c r="E249" t="n">
+        <v>93</v>
+      </c>
+      <c r="F249" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G249" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H249" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>0</v>
+      </c>
+      <c r="D250" t="n">
+        <v>0</v>
+      </c>
+      <c r="E250" t="n">
+        <v>0</v>
+      </c>
+      <c r="F250" s="2" t="n"/>
+      <c r="G250" s="3" t="n"/>
+      <c r="H250" s="2" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>4957</v>
+      </c>
+      <c r="D251" t="n">
+        <v>4856</v>
+      </c>
+      <c r="E251" t="n">
+        <v>4954</v>
+      </c>
+      <c r="F251" s="2" t="n">
+        <v>0.9795999999999999</v>
+      </c>
+      <c r="G251" s="3" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="H251" s="2" t="n">
+        <v>0.8968</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>384</v>
+      </c>
+      <c r="D252" t="n">
+        <v>384</v>
+      </c>
+      <c r="E252" t="n">
+        <v>384</v>
+      </c>
+      <c r="F252" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G252" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H252" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>0</v>
+      </c>
+      <c r="D253" t="n">
+        <v>0</v>
+      </c>
+      <c r="E253" t="n">
+        <v>0</v>
+      </c>
+      <c r="F253" s="2" t="n"/>
+      <c r="G253" s="3" t="n"/>
+      <c r="H253" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H239"/>
+  <autoFilter ref="A1:H253"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$253</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$267</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,22 +519,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35214</v>
+        <v>37490</v>
       </c>
       <c r="C3" t="n">
-        <v>31941</v>
+        <v>34186</v>
       </c>
       <c r="D3" t="n">
-        <v>33105</v>
+        <v>35352</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9070999999999999</v>
+        <v>0.9118999999999999</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.9401</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9278</v>
+        <v>0.9279999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -544,22 +544,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>318106</v>
+        <v>334593</v>
       </c>
       <c r="C4" t="n">
-        <v>259074</v>
+        <v>274954</v>
       </c>
       <c r="D4" t="n">
-        <v>298300</v>
+        <v>314575</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.8144</v>
+        <v>0.8218000000000001</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.9377</v>
+        <v>0.9401999999999999</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9218000000000001</v>
+        <v>0.9227</v>
       </c>
     </row>
     <row r="5">
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>527681</v>
+        <v>556866</v>
       </c>
       <c r="C6" t="n">
-        <v>435872</v>
+        <v>461581</v>
       </c>
       <c r="D6" t="n">
-        <v>502282</v>
+        <v>531219</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.826</v>
+        <v>0.8289</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.9519</v>
+        <v>0.9539</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9765</v>
+        <v>0.9769</v>
       </c>
     </row>
     <row r="7">
@@ -613,22 +613,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>115423</v>
+        <v>122002</v>
       </c>
       <c r="C7" t="n">
-        <v>81300</v>
+        <v>87751</v>
       </c>
       <c r="D7" t="n">
-        <v>109889</v>
+        <v>116462</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.7044</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.9520999999999999</v>
+        <v>0.9545999999999999</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6445000000000001</v>
+        <v>0.6463</v>
       </c>
     </row>
     <row r="8">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>132161</v>
+        <v>139576</v>
       </c>
       <c r="C8" t="n">
-        <v>104155</v>
+        <v>109576</v>
       </c>
       <c r="D8" t="n">
-        <v>122498</v>
+        <v>129883</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.7881</v>
+        <v>0.7851</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.9268999999999999</v>
+        <v>0.9306</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8722</v>
+        <v>0.8706</v>
       </c>
     </row>
     <row r="9">
@@ -682,22 +682,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20237</v>
+        <v>22581</v>
       </c>
       <c r="C10" t="n">
-        <v>14178</v>
+        <v>15923</v>
       </c>
       <c r="D10" t="n">
-        <v>16451</v>
+        <v>18711</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.7006</v>
+        <v>0.7051999999999999</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.8129000000000001</v>
+        <v>0.8286</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9577</v>
+        <v>0.9570000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -707,22 +707,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1624</v>
+        <v>1938</v>
       </c>
       <c r="C11" t="n">
-        <v>1358</v>
+        <v>1672</v>
       </c>
       <c r="D11" t="n">
-        <v>1409</v>
+        <v>1723</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.8362000000000001</v>
+        <v>0.8626999999999999</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.8676</v>
+        <v>0.8891</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.9983</v>
+        <v>0.9968</v>
       </c>
     </row>
     <row r="12">
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>69138</v>
+        <v>72912</v>
       </c>
       <c r="C13" t="n">
-        <v>64885</v>
+        <v>68466</v>
       </c>
       <c r="D13" t="n">
-        <v>66432</v>
+        <v>70194</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9384999999999999</v>
+        <v>0.9390000000000001</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.9609000000000001</v>
+        <v>0.9627</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.9033</v>
+        <v>0.8996999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -782,22 +782,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4322</v>
+        <v>9218</v>
       </c>
       <c r="C14" t="n">
-        <v>4322</v>
+        <v>4644</v>
       </c>
       <c r="D14" t="n">
-        <v>4322</v>
+        <v>7721</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1</v>
+        <v>0.5038</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1</v>
+        <v>0.8376</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.5556</v>
+        <v>0.6009</v>
       </c>
     </row>
     <row r="15">
@@ -833,7 +833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H253"/>
+  <dimension ref="A1:H267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7866,8 +7866,398 @@
       <c r="G253" s="3" t="n"/>
       <c r="H253" s="2" t="n"/>
     </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>0</v>
+      </c>
+      <c r="D254" t="n">
+        <v>0</v>
+      </c>
+      <c r="E254" t="n">
+        <v>0</v>
+      </c>
+      <c r="F254" s="2" t="n"/>
+      <c r="G254" s="3" t="n"/>
+      <c r="H254" s="2" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>2276</v>
+      </c>
+      <c r="D255" t="n">
+        <v>2245</v>
+      </c>
+      <c r="E255" t="n">
+        <v>2247</v>
+      </c>
+      <c r="F255" s="2" t="n">
+        <v>0.9864000000000001</v>
+      </c>
+      <c r="G255" s="3" t="n">
+        <v>0.9873000000000001</v>
+      </c>
+      <c r="H255" s="2" t="n">
+        <v>0.9309000000000001</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>16487</v>
+      </c>
+      <c r="D256" t="n">
+        <v>15880</v>
+      </c>
+      <c r="E256" t="n">
+        <v>16275</v>
+      </c>
+      <c r="F256" s="2" t="n">
+        <v>0.9631999999999999</v>
+      </c>
+      <c r="G256" s="3" t="n">
+        <v>0.9871</v>
+      </c>
+      <c r="H256" s="2" t="n">
+        <v>0.9362999999999999</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>0</v>
+      </c>
+      <c r="D257" t="n">
+        <v>0</v>
+      </c>
+      <c r="E257" t="n">
+        <v>0</v>
+      </c>
+      <c r="F257" s="2" t="n"/>
+      <c r="G257" s="3" t="n"/>
+      <c r="H257" s="2" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>29185</v>
+      </c>
+      <c r="D258" t="n">
+        <v>25709</v>
+      </c>
+      <c r="E258" t="n">
+        <v>28937</v>
+      </c>
+      <c r="F258" s="2" t="n">
+        <v>0.8809</v>
+      </c>
+      <c r="G258" s="3" t="n">
+        <v>0.9915</v>
+      </c>
+      <c r="H258" s="2" t="n">
+        <v>0.9825</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>6579</v>
+      </c>
+      <c r="D259" t="n">
+        <v>6451</v>
+      </c>
+      <c r="E259" t="n">
+        <v>6573</v>
+      </c>
+      <c r="F259" s="2" t="n">
+        <v>0.9804999999999999</v>
+      </c>
+      <c r="G259" s="3" t="n">
+        <v>0.9991</v>
+      </c>
+      <c r="H259" s="2" t="n">
+        <v>0.6726000000000001</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>7415</v>
+      </c>
+      <c r="D260" t="n">
+        <v>5421</v>
+      </c>
+      <c r="E260" t="n">
+        <v>7385</v>
+      </c>
+      <c r="F260" s="2" t="n">
+        <v>0.7311</v>
+      </c>
+      <c r="G260" s="3" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="H260" s="2" t="n">
+        <v>0.8453000000000001</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>0</v>
+      </c>
+      <c r="D261" t="n">
+        <v>0</v>
+      </c>
+      <c r="E261" t="n">
+        <v>0</v>
+      </c>
+      <c r="F261" s="2" t="n"/>
+      <c r="G261" s="3" t="n"/>
+      <c r="H261" s="2" t="n"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C262" t="n">
+        <v>2344</v>
+      </c>
+      <c r="D262" t="n">
+        <v>1745</v>
+      </c>
+      <c r="E262" t="n">
+        <v>2260</v>
+      </c>
+      <c r="F262" s="2" t="n">
+        <v>0.7445000000000001</v>
+      </c>
+      <c r="G262" s="3" t="n">
+        <v>0.9642000000000001</v>
+      </c>
+      <c r="H262" s="2" t="n">
+        <v>0.9495999999999999</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C263" t="n">
+        <v>314</v>
+      </c>
+      <c r="D263" t="n">
+        <v>314</v>
+      </c>
+      <c r="E263" t="n">
+        <v>314</v>
+      </c>
+      <c r="F263" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G263" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H263" s="2" t="n">
+        <v>0.9718000000000001</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
+        <v>0</v>
+      </c>
+      <c r="D264" t="n">
+        <v>0</v>
+      </c>
+      <c r="E264" t="n">
+        <v>0</v>
+      </c>
+      <c r="F264" s="2" t="n"/>
+      <c r="G264" s="3" t="n"/>
+      <c r="H264" s="2" t="n"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C265" t="n">
+        <v>3774</v>
+      </c>
+      <c r="D265" t="n">
+        <v>3581</v>
+      </c>
+      <c r="E265" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F265" s="2" t="n">
+        <v>0.9489</v>
+      </c>
+      <c r="G265" s="3" t="n">
+        <v>0.9968</v>
+      </c>
+      <c r="H265" s="2" t="n">
+        <v>0.8497</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>4896</v>
+      </c>
+      <c r="D266" t="n">
+        <v>322</v>
+      </c>
+      <c r="E266" t="n">
+        <v>3399</v>
+      </c>
+      <c r="F266" s="2" t="n">
+        <v>0.0658</v>
+      </c>
+      <c r="G266" s="3" t="n">
+        <v>0.6942</v>
+      </c>
+      <c r="H266" s="2" t="n">
+        <v>0.6944</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>0</v>
+      </c>
+      <c r="D267" t="n">
+        <v>0</v>
+      </c>
+      <c r="E267" t="n">
+        <v>0</v>
+      </c>
+      <c r="F267" s="2" t="n"/>
+      <c r="G267" s="3" t="n"/>
+      <c r="H267" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H253"/>
+  <autoFilter ref="A1:H267"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$267</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$281</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,22 +519,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>37490</v>
+        <v>39891</v>
       </c>
       <c r="C3" t="n">
-        <v>34186</v>
+        <v>36503</v>
       </c>
       <c r="D3" t="n">
-        <v>35352</v>
+        <v>37752</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9118999999999999</v>
+        <v>0.9151</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.9464</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9279999999999999</v>
+        <v>0.9290999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -544,22 +544,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>334593</v>
+        <v>351183</v>
       </c>
       <c r="C4" t="n">
-        <v>274954</v>
+        <v>291124</v>
       </c>
       <c r="D4" t="n">
-        <v>314575</v>
+        <v>331153</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.8218000000000001</v>
+        <v>0.8290000000000001</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.9401999999999999</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9227</v>
+        <v>0.9231</v>
       </c>
     </row>
     <row r="5">
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>556866</v>
+        <v>585112</v>
       </c>
       <c r="C6" t="n">
-        <v>461581</v>
+        <v>486858</v>
       </c>
       <c r="D6" t="n">
-        <v>531219</v>
+        <v>559430</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.8289</v>
+        <v>0.8321</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.9539</v>
+        <v>0.9560999999999999</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9769</v>
+        <v>0.9772</v>
       </c>
     </row>
     <row r="7">
@@ -613,22 +613,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>122002</v>
+        <v>128247</v>
       </c>
       <c r="C7" t="n">
-        <v>87751</v>
+        <v>93878</v>
       </c>
       <c r="D7" t="n">
-        <v>116462</v>
+        <v>122695</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.7193000000000001</v>
+        <v>0.732</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.9545999999999999</v>
+        <v>0.9567</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6463</v>
+        <v>0.6453</v>
       </c>
     </row>
     <row r="8">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>139576</v>
+        <v>148251</v>
       </c>
       <c r="C8" t="n">
-        <v>109576</v>
+        <v>117485</v>
       </c>
       <c r="D8" t="n">
-        <v>129883</v>
+        <v>138555</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.7851</v>
+        <v>0.7925</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.9306</v>
+        <v>0.9346</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8706</v>
+        <v>0.8713</v>
       </c>
     </row>
     <row r="9">
@@ -682,22 +682,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22581</v>
+        <v>25408</v>
       </c>
       <c r="C10" t="n">
-        <v>15923</v>
+        <v>17657</v>
       </c>
       <c r="D10" t="n">
-        <v>18711</v>
+        <v>20445</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.7051999999999999</v>
+        <v>0.6949</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.8286</v>
+        <v>0.8047</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9570000000000001</v>
+        <v>0.9581999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -707,22 +707,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1938</v>
+        <v>2258</v>
       </c>
       <c r="C11" t="n">
-        <v>1672</v>
+        <v>1992</v>
       </c>
       <c r="D11" t="n">
-        <v>1723</v>
+        <v>2043</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.8626999999999999</v>
+        <v>0.8822</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.8891</v>
+        <v>0.9048</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.9968</v>
+        <v>0.997</v>
       </c>
     </row>
     <row r="12">
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>72912</v>
+        <v>75688</v>
       </c>
       <c r="C13" t="n">
-        <v>68466</v>
+        <v>71226</v>
       </c>
       <c r="D13" t="n">
-        <v>70194</v>
+        <v>72968</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9390000000000001</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.9627</v>
+        <v>0.9641</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.8996999999999999</v>
+        <v>0.899</v>
       </c>
     </row>
     <row r="14">
@@ -782,22 +782,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9218</v>
+        <v>17738</v>
       </c>
       <c r="C14" t="n">
-        <v>4644</v>
+        <v>10791</v>
       </c>
       <c r="D14" t="n">
-        <v>7721</v>
+        <v>14601</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.5038</v>
+        <v>0.6084000000000001</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.8376</v>
+        <v>0.8231000000000001</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.6009</v>
+        <v>0.7115</v>
       </c>
     </row>
     <row r="15">
@@ -833,7 +833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H267"/>
+  <dimension ref="A1:H281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8256,8 +8256,398 @@
       <c r="G267" s="3" t="n"/>
       <c r="H267" s="2" t="n"/>
     </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>0</v>
+      </c>
+      <c r="D268" t="n">
+        <v>0</v>
+      </c>
+      <c r="E268" t="n">
+        <v>0</v>
+      </c>
+      <c r="F268" s="2" t="n"/>
+      <c r="G268" s="3" t="n"/>
+      <c r="H268" s="2" t="n"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C269" t="n">
+        <v>2401</v>
+      </c>
+      <c r="D269" t="n">
+        <v>2317</v>
+      </c>
+      <c r="E269" t="n">
+        <v>2400</v>
+      </c>
+      <c r="F269" s="2" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="G269" s="3" t="n">
+        <v>0.9995999999999999</v>
+      </c>
+      <c r="H269" s="2" t="n">
+        <v>0.9490999999999999</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>16590</v>
+      </c>
+      <c r="D270" t="n">
+        <v>16170</v>
+      </c>
+      <c r="E270" t="n">
+        <v>16578</v>
+      </c>
+      <c r="F270" s="2" t="n">
+        <v>0.9747</v>
+      </c>
+      <c r="G270" s="3" t="n">
+        <v>0.9993000000000001</v>
+      </c>
+      <c r="H270" s="2" t="n">
+        <v>0.9312</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>0</v>
+      </c>
+      <c r="D271" t="n">
+        <v>0</v>
+      </c>
+      <c r="E271" t="n">
+        <v>0</v>
+      </c>
+      <c r="F271" s="2" t="n"/>
+      <c r="G271" s="3" t="n"/>
+      <c r="H271" s="2" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>28246</v>
+      </c>
+      <c r="D272" t="n">
+        <v>25277</v>
+      </c>
+      <c r="E272" t="n">
+        <v>28211</v>
+      </c>
+      <c r="F272" s="2" t="n">
+        <v>0.8948999999999999</v>
+      </c>
+      <c r="G272" s="3" t="n">
+        <v>0.9987999999999999</v>
+      </c>
+      <c r="H272" s="2" t="n">
+        <v>0.9826</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>6245</v>
+      </c>
+      <c r="D273" t="n">
+        <v>6127</v>
+      </c>
+      <c r="E273" t="n">
+        <v>6233</v>
+      </c>
+      <c r="F273" s="2" t="n">
+        <v>0.9811</v>
+      </c>
+      <c r="G273" s="3" t="n">
+        <v>0.9981</v>
+      </c>
+      <c r="H273" s="2" t="n">
+        <v>0.631</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>8675</v>
+      </c>
+      <c r="D274" t="n">
+        <v>7909</v>
+      </c>
+      <c r="E274" t="n">
+        <v>8672</v>
+      </c>
+      <c r="F274" s="2" t="n">
+        <v>0.9117000000000001</v>
+      </c>
+      <c r="G274" s="3" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="H274" s="2" t="n">
+        <v>0.8809999999999999</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>0</v>
+      </c>
+      <c r="D275" t="n">
+        <v>0</v>
+      </c>
+      <c r="E275" t="n">
+        <v>0</v>
+      </c>
+      <c r="F275" s="2" t="n"/>
+      <c r="G275" s="3" t="n"/>
+      <c r="H275" s="2" t="n"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>2827</v>
+      </c>
+      <c r="D276" t="n">
+        <v>1734</v>
+      </c>
+      <c r="E276" t="n">
+        <v>1734</v>
+      </c>
+      <c r="F276" s="2" t="n">
+        <v>0.6134000000000001</v>
+      </c>
+      <c r="G276" s="3" t="n">
+        <v>0.6134000000000001</v>
+      </c>
+      <c r="H276" s="2" t="n">
+        <v>0.9712000000000001</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>320</v>
+      </c>
+      <c r="D277" t="n">
+        <v>320</v>
+      </c>
+      <c r="E277" t="n">
+        <v>320</v>
+      </c>
+      <c r="F277" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G277" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H277" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>0</v>
+      </c>
+      <c r="D278" t="n">
+        <v>0</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0</v>
+      </c>
+      <c r="F278" s="2" t="n"/>
+      <c r="G278" s="3" t="n"/>
+      <c r="H278" s="2" t="n"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>2776</v>
+      </c>
+      <c r="D279" t="n">
+        <v>2760</v>
+      </c>
+      <c r="E279" t="n">
+        <v>2774</v>
+      </c>
+      <c r="F279" s="2" t="n">
+        <v>0.9942</v>
+      </c>
+      <c r="G279" s="3" t="n">
+        <v>0.9993000000000001</v>
+      </c>
+      <c r="H279" s="2" t="n">
+        <v>0.8896999999999999</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>8520</v>
+      </c>
+      <c r="D280" t="n">
+        <v>6147</v>
+      </c>
+      <c r="E280" t="n">
+        <v>6880</v>
+      </c>
+      <c r="F280" s="2" t="n">
+        <v>0.7215</v>
+      </c>
+      <c r="G280" s="3" t="n">
+        <v>0.8075</v>
+      </c>
+      <c r="H280" s="2" t="n">
+        <v>0.8431999999999999</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>0</v>
+      </c>
+      <c r="D281" t="n">
+        <v>0</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0</v>
+      </c>
+      <c r="F281" s="2" t="n"/>
+      <c r="G281" s="3" t="n"/>
+      <c r="H281" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H267"/>
+  <autoFilter ref="A1:H281"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$281</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$295</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,22 +519,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>39891</v>
+        <v>42010</v>
       </c>
       <c r="C3" t="n">
-        <v>36503</v>
+        <v>38544</v>
       </c>
       <c r="D3" t="n">
-        <v>37752</v>
+        <v>39833</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9151</v>
+        <v>0.9175</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.9464</v>
+        <v>0.9481999999999999</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9290999999999999</v>
+        <v>0.9287000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -544,22 +544,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>351183</v>
+        <v>367516</v>
       </c>
       <c r="C4" t="n">
-        <v>291124</v>
+        <v>306921</v>
       </c>
       <c r="D4" t="n">
-        <v>331153</v>
+        <v>347455</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.8290000000000001</v>
+        <v>0.8351000000000001</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.9454</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9231</v>
+        <v>0.9238</v>
       </c>
     </row>
     <row r="5">
@@ -588,19 +588,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>585112</v>
+        <v>616351</v>
       </c>
       <c r="C6" t="n">
-        <v>486858</v>
+        <v>517097</v>
       </c>
       <c r="D6" t="n">
-        <v>559430</v>
+        <v>590660</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.8321</v>
+        <v>0.8390000000000001</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.9560999999999999</v>
+        <v>0.9582999999999999</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>0.9772</v>
@@ -613,22 +613,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>128247</v>
+        <v>134922</v>
       </c>
       <c r="C7" t="n">
-        <v>93878</v>
+        <v>100506</v>
       </c>
       <c r="D7" t="n">
-        <v>122695</v>
+        <v>129360</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.732</v>
+        <v>0.7448999999999999</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.9567</v>
+        <v>0.9588</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6453</v>
+        <v>0.6472</v>
       </c>
     </row>
     <row r="8">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>148251</v>
+        <v>155595</v>
       </c>
       <c r="C8" t="n">
-        <v>117485</v>
+        <v>123996</v>
       </c>
       <c r="D8" t="n">
-        <v>138555</v>
+        <v>145884</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.7925</v>
+        <v>0.7968999999999999</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.9346</v>
+        <v>0.9376000000000001</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8713</v>
+        <v>0.8678</v>
       </c>
     </row>
     <row r="9">
@@ -682,22 +682,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25408</v>
+        <v>26300</v>
       </c>
       <c r="C10" t="n">
-        <v>17657</v>
+        <v>18459</v>
       </c>
       <c r="D10" t="n">
-        <v>20445</v>
+        <v>21326</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.6949</v>
+        <v>0.7019</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.8047</v>
+        <v>0.8109000000000001</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9581999999999999</v>
+        <v>0.9592000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -707,22 +707,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2258</v>
+        <v>2508</v>
       </c>
       <c r="C11" t="n">
-        <v>1992</v>
+        <v>2242</v>
       </c>
       <c r="D11" t="n">
-        <v>2043</v>
+        <v>2293</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.8822</v>
+        <v>0.8939</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.9048</v>
+        <v>0.9143000000000001</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.997</v>
+        <v>0.9956999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>75688</v>
+        <v>78955</v>
       </c>
       <c r="C13" t="n">
-        <v>71226</v>
+        <v>74406</v>
       </c>
       <c r="D13" t="n">
-        <v>72968</v>
+        <v>76229</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.9423999999999999</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.9641</v>
+        <v>0.9655</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.899</v>
+        <v>0.8987999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -782,22 +782,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17738</v>
+        <v>28939</v>
       </c>
       <c r="C14" t="n">
-        <v>10791</v>
+        <v>20218</v>
       </c>
       <c r="D14" t="n">
-        <v>14601</v>
+        <v>25495</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.6084000000000001</v>
+        <v>0.6986</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.8231000000000001</v>
+        <v>0.8809999999999999</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.7115</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="15">
@@ -833,7 +833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H281"/>
+  <dimension ref="A1:H295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8646,8 +8646,398 @@
       <c r="G281" s="3" t="n"/>
       <c r="H281" s="2" t="n"/>
     </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C282" t="n">
+        <v>0</v>
+      </c>
+      <c r="D282" t="n">
+        <v>0</v>
+      </c>
+      <c r="E282" t="n">
+        <v>0</v>
+      </c>
+      <c r="F282" s="2" t="n"/>
+      <c r="G282" s="3" t="n"/>
+      <c r="H282" s="2" t="n"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C283" t="n">
+        <v>2119</v>
+      </c>
+      <c r="D283" t="n">
+        <v>2041</v>
+      </c>
+      <c r="E283" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F283" s="2" t="n">
+        <v>0.9631999999999999</v>
+      </c>
+      <c r="G283" s="3" t="n">
+        <v>0.9821</v>
+      </c>
+      <c r="H283" s="2" t="n">
+        <v>0.9198000000000001</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C284" t="n">
+        <v>16333</v>
+      </c>
+      <c r="D284" t="n">
+        <v>15797</v>
+      </c>
+      <c r="E284" t="n">
+        <v>16302</v>
+      </c>
+      <c r="F284" s="2" t="n">
+        <v>0.9671999999999999</v>
+      </c>
+      <c r="G284" s="3" t="n">
+        <v>0.9981</v>
+      </c>
+      <c r="H284" s="2" t="n">
+        <v>0.9370000000000001</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C285" t="n">
+        <v>0</v>
+      </c>
+      <c r="D285" t="n">
+        <v>0</v>
+      </c>
+      <c r="E285" t="n">
+        <v>0</v>
+      </c>
+      <c r="F285" s="2" t="n"/>
+      <c r="G285" s="3" t="n"/>
+      <c r="H285" s="2" t="n"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C286" t="n">
+        <v>31239</v>
+      </c>
+      <c r="D286" t="n">
+        <v>30239</v>
+      </c>
+      <c r="E286" t="n">
+        <v>31230</v>
+      </c>
+      <c r="F286" s="2" t="n">
+        <v>0.968</v>
+      </c>
+      <c r="G286" s="3" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="H286" s="2" t="n">
+        <v>0.978</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C287" t="n">
+        <v>6675</v>
+      </c>
+      <c r="D287" t="n">
+        <v>6628</v>
+      </c>
+      <c r="E287" t="n">
+        <v>6665</v>
+      </c>
+      <c r="F287" s="2" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="G287" s="3" t="n">
+        <v>0.9984999999999999</v>
+      </c>
+      <c r="H287" s="2" t="n">
+        <v>0.6776000000000001</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C288" t="n">
+        <v>7344</v>
+      </c>
+      <c r="D288" t="n">
+        <v>6511</v>
+      </c>
+      <c r="E288" t="n">
+        <v>7329</v>
+      </c>
+      <c r="F288" s="2" t="n">
+        <v>0.8865999999999999</v>
+      </c>
+      <c r="G288" s="3" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="H288" s="2" t="n">
+        <v>0.8134</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C289" t="n">
+        <v>0</v>
+      </c>
+      <c r="D289" t="n">
+        <v>0</v>
+      </c>
+      <c r="E289" t="n">
+        <v>0</v>
+      </c>
+      <c r="F289" s="2" t="n"/>
+      <c r="G289" s="3" t="n"/>
+      <c r="H289" s="2" t="n"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C290" t="n">
+        <v>892</v>
+      </c>
+      <c r="D290" t="n">
+        <v>802</v>
+      </c>
+      <c r="E290" t="n">
+        <v>881</v>
+      </c>
+      <c r="F290" s="2" t="n">
+        <v>0.8991</v>
+      </c>
+      <c r="G290" s="3" t="n">
+        <v>0.9876999999999999</v>
+      </c>
+      <c r="H290" s="2" t="n">
+        <v>0.9712999999999999</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C291" t="n">
+        <v>250</v>
+      </c>
+      <c r="D291" t="n">
+        <v>250</v>
+      </c>
+      <c r="E291" t="n">
+        <v>250</v>
+      </c>
+      <c r="F291" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G291" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H291" s="2" t="n">
+        <v>0.9667</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C292" t="n">
+        <v>0</v>
+      </c>
+      <c r="D292" t="n">
+        <v>0</v>
+      </c>
+      <c r="E292" t="n">
+        <v>0</v>
+      </c>
+      <c r="F292" s="2" t="n"/>
+      <c r="G292" s="3" t="n"/>
+      <c r="H292" s="2" t="n"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C293" t="n">
+        <v>3267</v>
+      </c>
+      <c r="D293" t="n">
+        <v>3180</v>
+      </c>
+      <c r="E293" t="n">
+        <v>3261</v>
+      </c>
+      <c r="F293" s="2" t="n">
+        <v>0.9734</v>
+      </c>
+      <c r="G293" s="3" t="n">
+        <v>0.9982</v>
+      </c>
+      <c r="H293" s="2" t="n">
+        <v>0.8945000000000001</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>11201</v>
+      </c>
+      <c r="D294" t="n">
+        <v>9427</v>
+      </c>
+      <c r="E294" t="n">
+        <v>10894</v>
+      </c>
+      <c r="F294" s="2" t="n">
+        <v>0.8416</v>
+      </c>
+      <c r="G294" s="3" t="n">
+        <v>0.9726</v>
+      </c>
+      <c r="H294" s="2" t="n">
+        <v>0.9209000000000001</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>0</v>
+      </c>
+      <c r="D295" t="n">
+        <v>0</v>
+      </c>
+      <c r="E295" t="n">
+        <v>0</v>
+      </c>
+      <c r="F295" s="2" t="n"/>
+      <c r="G295" s="3" t="n"/>
+      <c r="H295" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H281"/>
+  <autoFilter ref="A1:H295"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$295</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$309</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,22 +519,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>42010</v>
+        <v>44540</v>
       </c>
       <c r="C3" t="n">
-        <v>38544</v>
+        <v>40842</v>
       </c>
       <c r="D3" t="n">
-        <v>39833</v>
+        <v>42249</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9175</v>
+        <v>0.917</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.9481999999999999</v>
+        <v>0.9486</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9287000000000001</v>
+        <v>0.9283</v>
       </c>
     </row>
     <row r="4">
@@ -544,22 +544,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>367516</v>
+        <v>386074</v>
       </c>
       <c r="C4" t="n">
-        <v>306921</v>
+        <v>320608</v>
       </c>
       <c r="D4" t="n">
-        <v>347455</v>
+        <v>364628</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.8351000000000001</v>
+        <v>0.8304</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.9454</v>
+        <v>0.9445</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9238</v>
+        <v>0.9234</v>
       </c>
     </row>
     <row r="5">
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>616351</v>
+        <v>646940</v>
       </c>
       <c r="C6" t="n">
-        <v>517097</v>
+        <v>542967</v>
       </c>
       <c r="D6" t="n">
-        <v>590660</v>
+        <v>620988</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.8390000000000001</v>
+        <v>0.8393</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.9582999999999999</v>
+        <v>0.9599</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9772</v>
+        <v>0.9771</v>
       </c>
     </row>
     <row r="7">
@@ -613,22 +613,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>134922</v>
+        <v>141142</v>
       </c>
       <c r="C7" t="n">
-        <v>100506</v>
+        <v>105064</v>
       </c>
       <c r="D7" t="n">
-        <v>129360</v>
+        <v>133918</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.7448999999999999</v>
+        <v>0.7444</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.9588</v>
+        <v>0.9488</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6472</v>
+        <v>0.6461</v>
       </c>
     </row>
     <row r="8">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>155595</v>
+        <v>162140</v>
       </c>
       <c r="C8" t="n">
-        <v>123996</v>
+        <v>128826</v>
       </c>
       <c r="D8" t="n">
-        <v>145884</v>
+        <v>152290</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.7968999999999999</v>
+        <v>0.7945</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.9376000000000001</v>
+        <v>0.9393</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8678</v>
+        <v>0.8604999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -682,22 +682,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>26300</v>
+        <v>27204</v>
       </c>
       <c r="C10" t="n">
-        <v>18459</v>
+        <v>19065</v>
       </c>
       <c r="D10" t="n">
-        <v>21326</v>
+        <v>22073</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.7019</v>
+        <v>0.7008</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.8109000000000001</v>
+        <v>0.8114</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9592000000000001</v>
+        <v>0.9571999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -707,22 +707,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2508</v>
+        <v>2593</v>
       </c>
       <c r="C11" t="n">
-        <v>2242</v>
+        <v>2327</v>
       </c>
       <c r="D11" t="n">
-        <v>2293</v>
+        <v>2378</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.8939</v>
+        <v>0.8974</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.9143000000000001</v>
+        <v>0.9170999999999999</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.9956999999999999</v>
+        <v>0.9959</v>
       </c>
     </row>
     <row r="12">
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>78955</v>
+        <v>82085</v>
       </c>
       <c r="C13" t="n">
-        <v>74406</v>
+        <v>77263</v>
       </c>
       <c r="D13" t="n">
-        <v>76229</v>
+        <v>79322</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9423999999999999</v>
+        <v>0.9412999999999999</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.9655</v>
+        <v>0.9662999999999999</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.8987999999999999</v>
+        <v>0.8956000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -782,22 +782,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>28939</v>
+        <v>38884</v>
       </c>
       <c r="C14" t="n">
-        <v>20218</v>
+        <v>27520</v>
       </c>
       <c r="D14" t="n">
-        <v>25495</v>
+        <v>34788</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.6986</v>
+        <v>0.7077</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.8809999999999999</v>
+        <v>0.8946999999999999</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.8</v>
+        <v>0.8244</v>
       </c>
     </row>
     <row r="15">
@@ -833,7 +833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H295"/>
+  <dimension ref="A1:H309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9036,8 +9036,398 @@
       <c r="G295" s="3" t="n"/>
       <c r="H295" s="2" t="n"/>
     </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C296" t="n">
+        <v>0</v>
+      </c>
+      <c r="D296" t="n">
+        <v>0</v>
+      </c>
+      <c r="E296" t="n">
+        <v>0</v>
+      </c>
+      <c r="F296" s="2" t="n"/>
+      <c r="G296" s="3" t="n"/>
+      <c r="H296" s="2" t="n"/>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C297" t="n">
+        <v>2530</v>
+      </c>
+      <c r="D297" t="n">
+        <v>2298</v>
+      </c>
+      <c r="E297" t="n">
+        <v>2416</v>
+      </c>
+      <c r="F297" s="2" t="n">
+        <v>0.9083</v>
+      </c>
+      <c r="G297" s="3" t="n">
+        <v>0.9549</v>
+      </c>
+      <c r="H297" s="2" t="n">
+        <v>0.9215000000000001</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C298" t="n">
+        <v>18558</v>
+      </c>
+      <c r="D298" t="n">
+        <v>13687</v>
+      </c>
+      <c r="E298" t="n">
+        <v>17173</v>
+      </c>
+      <c r="F298" s="2" t="n">
+        <v>0.7375</v>
+      </c>
+      <c r="G298" s="3" t="n">
+        <v>0.9254000000000001</v>
+      </c>
+      <c r="H298" s="2" t="n">
+        <v>0.9156</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C299" t="n">
+        <v>0</v>
+      </c>
+      <c r="D299" t="n">
+        <v>0</v>
+      </c>
+      <c r="E299" t="n">
+        <v>0</v>
+      </c>
+      <c r="F299" s="2" t="n"/>
+      <c r="G299" s="3" t="n"/>
+      <c r="H299" s="2" t="n"/>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C300" t="n">
+        <v>30589</v>
+      </c>
+      <c r="D300" t="n">
+        <v>25870</v>
+      </c>
+      <c r="E300" t="n">
+        <v>30328</v>
+      </c>
+      <c r="F300" s="2" t="n">
+        <v>0.8456999999999999</v>
+      </c>
+      <c r="G300" s="3" t="n">
+        <v>0.9915</v>
+      </c>
+      <c r="H300" s="2" t="n">
+        <v>0.9739</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C301" t="n">
+        <v>6220</v>
+      </c>
+      <c r="D301" t="n">
+        <v>4558</v>
+      </c>
+      <c r="E301" t="n">
+        <v>4558</v>
+      </c>
+      <c r="F301" s="2" t="n">
+        <v>0.7328</v>
+      </c>
+      <c r="G301" s="3" t="n">
+        <v>0.7328</v>
+      </c>
+      <c r="H301" s="2" t="n">
+        <v>0.6286999999999999</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C302" t="n">
+        <v>6545</v>
+      </c>
+      <c r="D302" t="n">
+        <v>4830</v>
+      </c>
+      <c r="E302" t="n">
+        <v>6406</v>
+      </c>
+      <c r="F302" s="2" t="n">
+        <v>0.738</v>
+      </c>
+      <c r="G302" s="3" t="n">
+        <v>0.9788</v>
+      </c>
+      <c r="H302" s="2" t="n">
+        <v>0.7454999999999999</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C303" t="n">
+        <v>0</v>
+      </c>
+      <c r="D303" t="n">
+        <v>0</v>
+      </c>
+      <c r="E303" t="n">
+        <v>0</v>
+      </c>
+      <c r="F303" s="2" t="n"/>
+      <c r="G303" s="3" t="n"/>
+      <c r="H303" s="2" t="n"/>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C304" t="n">
+        <v>904</v>
+      </c>
+      <c r="D304" t="n">
+        <v>606</v>
+      </c>
+      <c r="E304" t="n">
+        <v>747</v>
+      </c>
+      <c r="F304" s="2" t="n">
+        <v>0.6704000000000001</v>
+      </c>
+      <c r="G304" s="3" t="n">
+        <v>0.8262999999999999</v>
+      </c>
+      <c r="H304" s="2" t="n">
+        <v>0.9317</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C305" t="n">
+        <v>85</v>
+      </c>
+      <c r="D305" t="n">
+        <v>85</v>
+      </c>
+      <c r="E305" t="n">
+        <v>85</v>
+      </c>
+      <c r="F305" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G305" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H305" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C306" t="n">
+        <v>0</v>
+      </c>
+      <c r="D306" t="n">
+        <v>0</v>
+      </c>
+      <c r="E306" t="n">
+        <v>0</v>
+      </c>
+      <c r="F306" s="2" t="n"/>
+      <c r="G306" s="3" t="n"/>
+      <c r="H306" s="2" t="n"/>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C307" t="n">
+        <v>3130</v>
+      </c>
+      <c r="D307" t="n">
+        <v>2857</v>
+      </c>
+      <c r="E307" t="n">
+        <v>3093</v>
+      </c>
+      <c r="F307" s="2" t="n">
+        <v>0.9128000000000001</v>
+      </c>
+      <c r="G307" s="3" t="n">
+        <v>0.9882</v>
+      </c>
+      <c r="H307" s="2" t="n">
+        <v>0.8345999999999999</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C308" t="n">
+        <v>9945</v>
+      </c>
+      <c r="D308" t="n">
+        <v>7302</v>
+      </c>
+      <c r="E308" t="n">
+        <v>9293</v>
+      </c>
+      <c r="F308" s="2" t="n">
+        <v>0.7342</v>
+      </c>
+      <c r="G308" s="3" t="n">
+        <v>0.9344</v>
+      </c>
+      <c r="H308" s="2" t="n">
+        <v>0.8724</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C309" t="n">
+        <v>0</v>
+      </c>
+      <c r="D309" t="n">
+        <v>0</v>
+      </c>
+      <c r="E309" t="n">
+        <v>0</v>
+      </c>
+      <c r="F309" s="2" t="n"/>
+      <c r="G309" s="3" t="n"/>
+      <c r="H309" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H295"/>
+  <autoFilter ref="A1:H309"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$309</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$323</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,22 +519,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44540</v>
+        <v>46683</v>
       </c>
       <c r="C3" t="n">
-        <v>40842</v>
+        <v>41221</v>
       </c>
       <c r="D3" t="n">
-        <v>42249</v>
+        <v>42628</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.917</v>
+        <v>0.883</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.9486</v>
+        <v>0.9131</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9283</v>
+        <v>0.9274</v>
       </c>
     </row>
     <row r="4">
@@ -544,22 +544,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>386074</v>
+        <v>399424</v>
       </c>
       <c r="C4" t="n">
-        <v>320608</v>
+        <v>323107</v>
       </c>
       <c r="D4" t="n">
-        <v>364628</v>
+        <v>367127</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.8304</v>
+        <v>0.8089</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.9445</v>
+        <v>0.9190999999999999</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9234</v>
+        <v>0.9211</v>
       </c>
     </row>
     <row r="5">
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>646940</v>
+        <v>667397</v>
       </c>
       <c r="C6" t="n">
-        <v>542967</v>
+        <v>551094</v>
       </c>
       <c r="D6" t="n">
-        <v>620988</v>
+        <v>629115</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.8393</v>
+        <v>0.8256999999999999</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.9599</v>
+        <v>0.9426000000000001</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9771</v>
+        <v>0.977</v>
       </c>
     </row>
     <row r="7">
@@ -613,22 +613,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>141142</v>
+        <v>147070</v>
       </c>
       <c r="C7" t="n">
-        <v>105064</v>
+        <v>105668</v>
       </c>
       <c r="D7" t="n">
-        <v>133918</v>
+        <v>134522</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.7444</v>
+        <v>0.7184999999999999</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.9488</v>
+        <v>0.9147</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6461</v>
+        <v>0.6479</v>
       </c>
     </row>
     <row r="8">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>162140</v>
+        <v>167692</v>
       </c>
       <c r="C8" t="n">
-        <v>128826</v>
+        <v>129487</v>
       </c>
       <c r="D8" t="n">
-        <v>152290</v>
+        <v>152951</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.7945</v>
+        <v>0.7722</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.9393</v>
+        <v>0.9120999999999999</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8604999999999999</v>
+        <v>0.848</v>
       </c>
     </row>
     <row r="9">
@@ -682,22 +682,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27204</v>
+        <v>27823</v>
       </c>
       <c r="C10" t="n">
-        <v>19065</v>
+        <v>19157</v>
       </c>
       <c r="D10" t="n">
-        <v>22073</v>
+        <v>22165</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.7008</v>
+        <v>0.6884999999999999</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.8114</v>
+        <v>0.7966</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9571999999999999</v>
+        <v>0.9556999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -707,22 +707,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2593</v>
+        <v>2595</v>
       </c>
       <c r="C11" t="n">
-        <v>2327</v>
+        <v>2329</v>
       </c>
       <c r="D11" t="n">
-        <v>2378</v>
+        <v>2380</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.8974</v>
+        <v>0.8975</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>0.9170999999999999</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.9959</v>
+        <v>0.996</v>
       </c>
     </row>
     <row r="12">
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>82085</v>
+        <v>83403</v>
       </c>
       <c r="C13" t="n">
-        <v>77263</v>
+        <v>77469</v>
       </c>
       <c r="D13" t="n">
-        <v>79322</v>
+        <v>79528</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9412999999999999</v>
+        <v>0.9289000000000001</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.9662999999999999</v>
+        <v>0.9534999999999999</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.8956000000000001</v>
+        <v>0.8931</v>
       </c>
     </row>
     <row r="14">
@@ -782,22 +782,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>38884</v>
+        <v>48925</v>
       </c>
       <c r="C14" t="n">
-        <v>27520</v>
+        <v>29193</v>
       </c>
       <c r="D14" t="n">
-        <v>34788</v>
+        <v>36461</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.7077</v>
+        <v>0.5967</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.8946999999999999</v>
+        <v>0.7452</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.8244</v>
+        <v>0.8320000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -833,7 +833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H309"/>
+  <dimension ref="A1:H323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9426,8 +9426,398 @@
       <c r="G309" s="3" t="n"/>
       <c r="H309" s="2" t="n"/>
     </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C310" t="n">
+        <v>0</v>
+      </c>
+      <c r="D310" t="n">
+        <v>0</v>
+      </c>
+      <c r="E310" t="n">
+        <v>0</v>
+      </c>
+      <c r="F310" s="2" t="n"/>
+      <c r="G310" s="3" t="n"/>
+      <c r="H310" s="2" t="n"/>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C311" t="n">
+        <v>2143</v>
+      </c>
+      <c r="D311" t="n">
+        <v>379</v>
+      </c>
+      <c r="E311" t="n">
+        <v>379</v>
+      </c>
+      <c r="F311" s="2" t="n">
+        <v>0.1769</v>
+      </c>
+      <c r="G311" s="3" t="n">
+        <v>0.1769</v>
+      </c>
+      <c r="H311" s="2" t="n">
+        <v>0.902</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C312" t="n">
+        <v>13350</v>
+      </c>
+      <c r="D312" t="n">
+        <v>2499</v>
+      </c>
+      <c r="E312" t="n">
+        <v>2499</v>
+      </c>
+      <c r="F312" s="2" t="n">
+        <v>0.1872</v>
+      </c>
+      <c r="G312" s="3" t="n">
+        <v>0.1872</v>
+      </c>
+      <c r="H312" s="2" t="n">
+        <v>0.8702</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C313" t="n">
+        <v>0</v>
+      </c>
+      <c r="D313" t="n">
+        <v>0</v>
+      </c>
+      <c r="E313" t="n">
+        <v>0</v>
+      </c>
+      <c r="F313" s="2" t="n"/>
+      <c r="G313" s="3" t="n"/>
+      <c r="H313" s="2" t="n"/>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C314" t="n">
+        <v>20457</v>
+      </c>
+      <c r="D314" t="n">
+        <v>8127</v>
+      </c>
+      <c r="E314" t="n">
+        <v>8127</v>
+      </c>
+      <c r="F314" s="2" t="n">
+        <v>0.3973</v>
+      </c>
+      <c r="G314" s="3" t="n">
+        <v>0.3973</v>
+      </c>
+      <c r="H314" s="2" t="n">
+        <v>0.9759</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C315" t="n">
+        <v>5928</v>
+      </c>
+      <c r="D315" t="n">
+        <v>604</v>
+      </c>
+      <c r="E315" t="n">
+        <v>604</v>
+      </c>
+      <c r="F315" s="2" t="n">
+        <v>0.1019</v>
+      </c>
+      <c r="G315" s="3" t="n">
+        <v>0.1019</v>
+      </c>
+      <c r="H315" s="2" t="n">
+        <v>0.6766</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C316" t="n">
+        <v>5552</v>
+      </c>
+      <c r="D316" t="n">
+        <v>661</v>
+      </c>
+      <c r="E316" t="n">
+        <v>661</v>
+      </c>
+      <c r="F316" s="2" t="n">
+        <v>0.1191</v>
+      </c>
+      <c r="G316" s="3" t="n">
+        <v>0.1191</v>
+      </c>
+      <c r="H316" s="2" t="n">
+        <v>0.6232</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C317" t="n">
+        <v>0</v>
+      </c>
+      <c r="D317" t="n">
+        <v>0</v>
+      </c>
+      <c r="E317" t="n">
+        <v>0</v>
+      </c>
+      <c r="F317" s="2" t="n"/>
+      <c r="G317" s="3" t="n"/>
+      <c r="H317" s="2" t="n"/>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C318" t="n">
+        <v>619</v>
+      </c>
+      <c r="D318" t="n">
+        <v>92</v>
+      </c>
+      <c r="E318" t="n">
+        <v>92</v>
+      </c>
+      <c r="F318" s="2" t="n">
+        <v>0.1486</v>
+      </c>
+      <c r="G318" s="3" t="n">
+        <v>0.1486</v>
+      </c>
+      <c r="H318" s="2" t="n">
+        <v>0.9309000000000001</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C319" t="n">
+        <v>2</v>
+      </c>
+      <c r="D319" t="n">
+        <v>2</v>
+      </c>
+      <c r="E319" t="n">
+        <v>2</v>
+      </c>
+      <c r="F319" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G319" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H319" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C320" t="n">
+        <v>0</v>
+      </c>
+      <c r="D320" t="n">
+        <v>0</v>
+      </c>
+      <c r="E320" t="n">
+        <v>0</v>
+      </c>
+      <c r="F320" s="2" t="n"/>
+      <c r="G320" s="3" t="n"/>
+      <c r="H320" s="2" t="n"/>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C321" t="n">
+        <v>1318</v>
+      </c>
+      <c r="D321" t="n">
+        <v>206</v>
+      </c>
+      <c r="E321" t="n">
+        <v>206</v>
+      </c>
+      <c r="F321" s="2" t="n">
+        <v>0.1563</v>
+      </c>
+      <c r="G321" s="3" t="n">
+        <v>0.1563</v>
+      </c>
+      <c r="H321" s="2" t="n">
+        <v>0.8438</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C322" t="n">
+        <v>10041</v>
+      </c>
+      <c r="D322" t="n">
+        <v>1673</v>
+      </c>
+      <c r="E322" t="n">
+        <v>1673</v>
+      </c>
+      <c r="F322" s="2" t="n">
+        <v>0.1666</v>
+      </c>
+      <c r="G322" s="3" t="n">
+        <v>0.1666</v>
+      </c>
+      <c r="H322" s="2" t="n">
+        <v>0.8547</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C323" t="n">
+        <v>0</v>
+      </c>
+      <c r="D323" t="n">
+        <v>0</v>
+      </c>
+      <c r="E323" t="n">
+        <v>0</v>
+      </c>
+      <c r="F323" s="2" t="n"/>
+      <c r="G323" s="3" t="n"/>
+      <c r="H323" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H309"/>
+  <autoFilter ref="A1:H323"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$323</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$337</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,22 +519,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>46683</v>
+        <v>48144</v>
       </c>
       <c r="C3" t="n">
-        <v>41221</v>
+        <v>42340</v>
       </c>
       <c r="D3" t="n">
-        <v>42628</v>
+        <v>43991</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.883</v>
+        <v>0.8794</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.9131</v>
+        <v>0.9137000000000001</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9274</v>
+        <v>0.9255</v>
       </c>
     </row>
     <row r="4">
@@ -544,22 +544,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>399424</v>
+        <v>412452</v>
       </c>
       <c r="C4" t="n">
-        <v>323107</v>
+        <v>333086</v>
       </c>
       <c r="D4" t="n">
-        <v>367127</v>
+        <v>380141</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.8089</v>
+        <v>0.8076000000000001</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.9190999999999999</v>
+        <v>0.9217</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9211</v>
+        <v>0.9187000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>667397</v>
+        <v>700253</v>
       </c>
       <c r="C6" t="n">
-        <v>551094</v>
+        <v>574479</v>
       </c>
       <c r="D6" t="n">
-        <v>629115</v>
+        <v>660170</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.8256999999999999</v>
+        <v>0.8204</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.9426000000000001</v>
+        <v>0.9428</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.977</v>
+        <v>0.9768000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -613,22 +613,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>147070</v>
+        <v>152875</v>
       </c>
       <c r="C7" t="n">
-        <v>105668</v>
+        <v>108804</v>
       </c>
       <c r="D7" t="n">
-        <v>134522</v>
+        <v>140319</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.7184999999999999</v>
+        <v>0.7117</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.9147</v>
+        <v>0.9179</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6479</v>
+        <v>0.6513</v>
       </c>
     </row>
     <row r="8">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>167692</v>
+        <v>173822</v>
       </c>
       <c r="C8" t="n">
-        <v>129487</v>
+        <v>133572</v>
       </c>
       <c r="D8" t="n">
-        <v>152951</v>
+        <v>159058</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.7722</v>
+        <v>0.7684000000000001</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.9120999999999999</v>
+        <v>0.9151</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.848</v>
+        <v>0.8443999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -663,17 +663,23 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="2" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -682,22 +688,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27823</v>
+        <v>28719</v>
       </c>
       <c r="C10" t="n">
-        <v>19157</v>
+        <v>20023</v>
       </c>
       <c r="D10" t="n">
-        <v>22165</v>
+        <v>23031</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.6884999999999999</v>
+        <v>0.6972</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.7966</v>
+        <v>0.8018999999999999</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9556999999999999</v>
+        <v>0.9543</v>
       </c>
     </row>
     <row r="11">
@@ -707,22 +713,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2595</v>
+        <v>2622</v>
       </c>
       <c r="C11" t="n">
-        <v>2329</v>
+        <v>2356</v>
       </c>
       <c r="D11" t="n">
-        <v>2380</v>
+        <v>2407</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.8975</v>
+        <v>0.8986</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.9170999999999999</v>
+        <v>0.9179999999999999</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.996</v>
+        <v>0.9962000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -757,22 +763,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>83403</v>
+        <v>84497</v>
       </c>
       <c r="C13" t="n">
-        <v>77469</v>
+        <v>78446</v>
       </c>
       <c r="D13" t="n">
-        <v>79528</v>
+        <v>80617</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9289000000000001</v>
+        <v>0.9284</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.9534999999999999</v>
+        <v>0.9540999999999999</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.8931</v>
+        <v>0.8911</v>
       </c>
     </row>
     <row r="14">
@@ -782,22 +788,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>48925</v>
+        <v>57117</v>
       </c>
       <c r="C14" t="n">
-        <v>29193</v>
+        <v>34657</v>
       </c>
       <c r="D14" t="n">
-        <v>36461</v>
+        <v>44447</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.5967</v>
+        <v>0.6068</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.7452</v>
+        <v>0.7781999999999999</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.8320000000000001</v>
+        <v>0.8434</v>
       </c>
     </row>
     <row r="15">
@@ -833,7 +839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H323"/>
+  <dimension ref="A1:H337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9816,8 +9822,404 @@
       <c r="G323" s="3" t="n"/>
       <c r="H323" s="2" t="n"/>
     </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C324" t="n">
+        <v>0</v>
+      </c>
+      <c r="D324" t="n">
+        <v>0</v>
+      </c>
+      <c r="E324" t="n">
+        <v>0</v>
+      </c>
+      <c r="F324" s="2" t="n"/>
+      <c r="G324" s="3" t="n"/>
+      <c r="H324" s="2" t="n"/>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C325" t="n">
+        <v>1461</v>
+      </c>
+      <c r="D325" t="n">
+        <v>1119</v>
+      </c>
+      <c r="E325" t="n">
+        <v>1363</v>
+      </c>
+      <c r="F325" s="2" t="n">
+        <v>0.7659</v>
+      </c>
+      <c r="G325" s="3" t="n">
+        <v>0.9329000000000001</v>
+      </c>
+      <c r="H325" s="2" t="n">
+        <v>0.8756999999999999</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C326" t="n">
+        <v>13028</v>
+      </c>
+      <c r="D326" t="n">
+        <v>9979</v>
+      </c>
+      <c r="E326" t="n">
+        <v>13014</v>
+      </c>
+      <c r="F326" s="2" t="n">
+        <v>0.7659999999999999</v>
+      </c>
+      <c r="G326" s="3" t="n">
+        <v>0.9989</v>
+      </c>
+      <c r="H326" s="2" t="n">
+        <v>0.861</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C327" t="n">
+        <v>0</v>
+      </c>
+      <c r="D327" t="n">
+        <v>0</v>
+      </c>
+      <c r="E327" t="n">
+        <v>0</v>
+      </c>
+      <c r="F327" s="2" t="n"/>
+      <c r="G327" s="3" t="n"/>
+      <c r="H327" s="2" t="n"/>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C328" t="n">
+        <v>32856</v>
+      </c>
+      <c r="D328" t="n">
+        <v>23385</v>
+      </c>
+      <c r="E328" t="n">
+        <v>31055</v>
+      </c>
+      <c r="F328" s="2" t="n">
+        <v>0.7117</v>
+      </c>
+      <c r="G328" s="3" t="n">
+        <v>0.9451999999999999</v>
+      </c>
+      <c r="H328" s="2" t="n">
+        <v>0.9721</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C329" t="n">
+        <v>5805</v>
+      </c>
+      <c r="D329" t="n">
+        <v>3136</v>
+      </c>
+      <c r="E329" t="n">
+        <v>5797</v>
+      </c>
+      <c r="F329" s="2" t="n">
+        <v>0.5402</v>
+      </c>
+      <c r="G329" s="3" t="n">
+        <v>0.9986</v>
+      </c>
+      <c r="H329" s="2" t="n">
+        <v>0.7303000000000001</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C330" t="n">
+        <v>6130</v>
+      </c>
+      <c r="D330" t="n">
+        <v>4085</v>
+      </c>
+      <c r="E330" t="n">
+        <v>6107</v>
+      </c>
+      <c r="F330" s="2" t="n">
+        <v>0.6664</v>
+      </c>
+      <c r="G330" s="3" t="n">
+        <v>0.9962000000000001</v>
+      </c>
+      <c r="H330" s="2" t="n">
+        <v>0.7687999999999999</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C331" t="n">
+        <v>8</v>
+      </c>
+      <c r="D331" t="n">
+        <v>8</v>
+      </c>
+      <c r="E331" t="n">
+        <v>8</v>
+      </c>
+      <c r="F331" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G331" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H331" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C332" t="n">
+        <v>896</v>
+      </c>
+      <c r="D332" t="n">
+        <v>866</v>
+      </c>
+      <c r="E332" t="n">
+        <v>866</v>
+      </c>
+      <c r="F332" s="2" t="n">
+        <v>0.9665</v>
+      </c>
+      <c r="G332" s="3" t="n">
+        <v>0.9665</v>
+      </c>
+      <c r="H332" s="2" t="n">
+        <v>0.9289000000000001</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C333" t="n">
+        <v>27</v>
+      </c>
+      <c r="D333" t="n">
+        <v>27</v>
+      </c>
+      <c r="E333" t="n">
+        <v>27</v>
+      </c>
+      <c r="F333" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G333" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H333" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C334" t="n">
+        <v>0</v>
+      </c>
+      <c r="D334" t="n">
+        <v>0</v>
+      </c>
+      <c r="E334" t="n">
+        <v>0</v>
+      </c>
+      <c r="F334" s="2" t="n"/>
+      <c r="G334" s="3" t="n"/>
+      <c r="H334" s="2" t="n"/>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C335" t="n">
+        <v>1094</v>
+      </c>
+      <c r="D335" t="n">
+        <v>977</v>
+      </c>
+      <c r="E335" t="n">
+        <v>1089</v>
+      </c>
+      <c r="F335" s="2" t="n">
+        <v>0.8931</v>
+      </c>
+      <c r="G335" s="3" t="n">
+        <v>0.9954000000000001</v>
+      </c>
+      <c r="H335" s="2" t="n">
+        <v>0.851</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C336" t="n">
+        <v>8192</v>
+      </c>
+      <c r="D336" t="n">
+        <v>5464</v>
+      </c>
+      <c r="E336" t="n">
+        <v>7986</v>
+      </c>
+      <c r="F336" s="2" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="G336" s="3" t="n">
+        <v>0.9749</v>
+      </c>
+      <c r="H336" s="2" t="n">
+        <v>0.8919</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C337" t="n">
+        <v>0</v>
+      </c>
+      <c r="D337" t="n">
+        <v>0</v>
+      </c>
+      <c r="E337" t="n">
+        <v>0</v>
+      </c>
+      <c r="F337" s="2" t="n"/>
+      <c r="G337" s="3" t="n"/>
+      <c r="H337" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H323"/>
+  <autoFilter ref="A1:H337"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$337</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$351</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,22 +519,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>48144</v>
+        <v>51037</v>
       </c>
       <c r="C3" t="n">
-        <v>42340</v>
+        <v>45099</v>
       </c>
       <c r="D3" t="n">
-        <v>43991</v>
+        <v>46814</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.8794</v>
+        <v>0.8837</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.9137000000000001</v>
+        <v>0.9173</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9255</v>
+        <v>0.9259000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -544,22 +544,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>412452</v>
+        <v>437788</v>
       </c>
       <c r="C4" t="n">
-        <v>333086</v>
+        <v>357703</v>
       </c>
       <c r="D4" t="n">
-        <v>380141</v>
+        <v>405467</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.8076000000000001</v>
+        <v>0.8170999999999999</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.9217</v>
+        <v>0.9262</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9187000000000001</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="5">
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>700253</v>
+        <v>731999</v>
       </c>
       <c r="C6" t="n">
-        <v>574479</v>
+        <v>601400</v>
       </c>
       <c r="D6" t="n">
-        <v>660170</v>
+        <v>691847</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.8204</v>
+        <v>0.8216</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.9428</v>
+        <v>0.9451000000000001</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9768000000000001</v>
+        <v>0.9759</v>
       </c>
     </row>
     <row r="7">
@@ -613,22 +613,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>152875</v>
+        <v>160644</v>
       </c>
       <c r="C7" t="n">
-        <v>108804</v>
+        <v>115417</v>
       </c>
       <c r="D7" t="n">
-        <v>140319</v>
+        <v>148067</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.7117</v>
+        <v>0.7184999999999999</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.9179</v>
+        <v>0.9217</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6513</v>
+        <v>0.655</v>
       </c>
     </row>
     <row r="8">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>173822</v>
+        <v>180370</v>
       </c>
       <c r="C8" t="n">
-        <v>133572</v>
+        <v>139199</v>
       </c>
       <c r="D8" t="n">
-        <v>159058</v>
+        <v>165250</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.7684000000000001</v>
+        <v>0.7717000000000001</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.9151</v>
+        <v>0.9162</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8443999999999999</v>
+        <v>0.8399</v>
       </c>
     </row>
     <row r="9">
@@ -663,13 +663,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1</v>
@@ -688,22 +688,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>28719</v>
+        <v>29954</v>
       </c>
       <c r="C10" t="n">
-        <v>20023</v>
+        <v>21143</v>
       </c>
       <c r="D10" t="n">
-        <v>23031</v>
+        <v>24162</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.6972</v>
+        <v>0.7058</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.8018999999999999</v>
+        <v>0.8066</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9543</v>
+        <v>0.9551999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -713,19 +713,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2622</v>
+        <v>2774</v>
       </c>
       <c r="C11" t="n">
-        <v>2356</v>
+        <v>2508</v>
       </c>
       <c r="D11" t="n">
-        <v>2407</v>
+        <v>2559</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.8986</v>
+        <v>0.9041</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.9179999999999999</v>
+        <v>0.9225</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0.9962000000000001</v>
@@ -763,22 +763,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>84497</v>
+        <v>90330</v>
       </c>
       <c r="C13" t="n">
-        <v>78446</v>
+        <v>84197</v>
       </c>
       <c r="D13" t="n">
-        <v>80617</v>
+        <v>86440</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9284</v>
+        <v>0.9320999999999999</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.9540999999999999</v>
+        <v>0.9569</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.8911</v>
+        <v>0.8924</v>
       </c>
     </row>
     <row r="14">
@@ -788,22 +788,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>57117</v>
+        <v>70169</v>
       </c>
       <c r="C14" t="n">
-        <v>34657</v>
+        <v>45716</v>
       </c>
       <c r="D14" t="n">
-        <v>44447</v>
+        <v>57443</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.6068</v>
+        <v>0.6515000000000001</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.7781999999999999</v>
+        <v>0.8186</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.8434</v>
+        <v>0.8538</v>
       </c>
     </row>
     <row r="15">
@@ -839,7 +839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H337"/>
+  <dimension ref="A1:H351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10218,8 +10218,404 @@
       <c r="G337" s="3" t="n"/>
       <c r="H337" s="2" t="n"/>
     </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C338" t="n">
+        <v>0</v>
+      </c>
+      <c r="D338" t="n">
+        <v>0</v>
+      </c>
+      <c r="E338" t="n">
+        <v>0</v>
+      </c>
+      <c r="F338" s="2" t="n"/>
+      <c r="G338" s="3" t="n"/>
+      <c r="H338" s="2" t="n"/>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C339" t="n">
+        <v>2893</v>
+      </c>
+      <c r="D339" t="n">
+        <v>2759</v>
+      </c>
+      <c r="E339" t="n">
+        <v>2823</v>
+      </c>
+      <c r="F339" s="2" t="n">
+        <v>0.9537</v>
+      </c>
+      <c r="G339" s="3" t="n">
+        <v>0.9758</v>
+      </c>
+      <c r="H339" s="2" t="n">
+        <v>0.9355</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C340" t="n">
+        <v>25336</v>
+      </c>
+      <c r="D340" t="n">
+        <v>24617</v>
+      </c>
+      <c r="E340" t="n">
+        <v>25326</v>
+      </c>
+      <c r="F340" s="2" t="n">
+        <v>0.9716</v>
+      </c>
+      <c r="G340" s="3" t="n">
+        <v>0.9995999999999999</v>
+      </c>
+      <c r="H340" s="2" t="n">
+        <v>0.9527</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C341" t="n">
+        <v>0</v>
+      </c>
+      <c r="D341" t="n">
+        <v>0</v>
+      </c>
+      <c r="E341" t="n">
+        <v>0</v>
+      </c>
+      <c r="F341" s="2" t="n"/>
+      <c r="G341" s="3" t="n"/>
+      <c r="H341" s="2" t="n"/>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C342" t="n">
+        <v>31746</v>
+      </c>
+      <c r="D342" t="n">
+        <v>26921</v>
+      </c>
+      <c r="E342" t="n">
+        <v>31677</v>
+      </c>
+      <c r="F342" s="2" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="G342" s="3" t="n">
+        <v>0.9978</v>
+      </c>
+      <c r="H342" s="2" t="n">
+        <v>0.9545</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C343" t="n">
+        <v>7769</v>
+      </c>
+      <c r="D343" t="n">
+        <v>6613</v>
+      </c>
+      <c r="E343" t="n">
+        <v>7748</v>
+      </c>
+      <c r="F343" s="2" t="n">
+        <v>0.8512000000000001</v>
+      </c>
+      <c r="G343" s="3" t="n">
+        <v>0.9973000000000001</v>
+      </c>
+      <c r="H343" s="2" t="n">
+        <v>0.7314000000000001</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C344" t="n">
+        <v>6548</v>
+      </c>
+      <c r="D344" t="n">
+        <v>5627</v>
+      </c>
+      <c r="E344" t="n">
+        <v>6192</v>
+      </c>
+      <c r="F344" s="2" t="n">
+        <v>0.8593000000000001</v>
+      </c>
+      <c r="G344" s="3" t="n">
+        <v>0.9456</v>
+      </c>
+      <c r="H344" s="2" t="n">
+        <v>0.7421</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C345" t="n">
+        <v>5</v>
+      </c>
+      <c r="D345" t="n">
+        <v>5</v>
+      </c>
+      <c r="E345" t="n">
+        <v>5</v>
+      </c>
+      <c r="F345" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G345" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H345" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C346" t="n">
+        <v>1235</v>
+      </c>
+      <c r="D346" t="n">
+        <v>1120</v>
+      </c>
+      <c r="E346" t="n">
+        <v>1131</v>
+      </c>
+      <c r="F346" s="2" t="n">
+        <v>0.9068999999999999</v>
+      </c>
+      <c r="G346" s="3" t="n">
+        <v>0.9157999999999999</v>
+      </c>
+      <c r="H346" s="2" t="n">
+        <v>0.9731000000000001</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C347" t="n">
+        <v>152</v>
+      </c>
+      <c r="D347" t="n">
+        <v>152</v>
+      </c>
+      <c r="E347" t="n">
+        <v>152</v>
+      </c>
+      <c r="F347" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G347" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H347" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C348" t="n">
+        <v>0</v>
+      </c>
+      <c r="D348" t="n">
+        <v>0</v>
+      </c>
+      <c r="E348" t="n">
+        <v>0</v>
+      </c>
+      <c r="F348" s="2" t="n"/>
+      <c r="G348" s="3" t="n"/>
+      <c r="H348" s="2" t="n"/>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C349" t="n">
+        <v>5833</v>
+      </c>
+      <c r="D349" t="n">
+        <v>5751</v>
+      </c>
+      <c r="E349" t="n">
+        <v>5823</v>
+      </c>
+      <c r="F349" s="2" t="n">
+        <v>0.9859</v>
+      </c>
+      <c r="G349" s="3" t="n">
+        <v>0.9983</v>
+      </c>
+      <c r="H349" s="2" t="n">
+        <v>0.9189000000000001</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C350" t="n">
+        <v>13052</v>
+      </c>
+      <c r="D350" t="n">
+        <v>11059</v>
+      </c>
+      <c r="E350" t="n">
+        <v>12996</v>
+      </c>
+      <c r="F350" s="2" t="n">
+        <v>0.8473000000000001</v>
+      </c>
+      <c r="G350" s="3" t="n">
+        <v>0.9956999999999999</v>
+      </c>
+      <c r="H350" s="2" t="n">
+        <v>0.9009999999999999</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C351" t="n">
+        <v>0</v>
+      </c>
+      <c r="D351" t="n">
+        <v>0</v>
+      </c>
+      <c r="E351" t="n">
+        <v>0</v>
+      </c>
+      <c r="F351" s="2" t="n"/>
+      <c r="G351" s="3" t="n"/>
+      <c r="H351" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H337"/>
+  <autoFilter ref="A1:H351"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$351</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$365</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,22 +519,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>51037</v>
+        <v>53440</v>
       </c>
       <c r="C3" t="n">
-        <v>45099</v>
+        <v>47436</v>
       </c>
       <c r="D3" t="n">
-        <v>46814</v>
+        <v>49177</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.8837</v>
+        <v>0.8876000000000001</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.9173</v>
+        <v>0.9201999999999999</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9259000000000001</v>
+        <v>0.9258</v>
       </c>
     </row>
     <row r="4">
@@ -544,22 +544,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>437788</v>
+        <v>455044</v>
       </c>
       <c r="C4" t="n">
-        <v>357703</v>
+        <v>374669</v>
       </c>
       <c r="D4" t="n">
-        <v>405467</v>
+        <v>422692</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.8170999999999999</v>
+        <v>0.8234</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.9262</v>
+        <v>0.9289000000000001</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.92</v>
+        <v>0.9209000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>731999</v>
+        <v>761593</v>
       </c>
       <c r="C6" t="n">
-        <v>601400</v>
+        <v>627142</v>
       </c>
       <c r="D6" t="n">
-        <v>691847</v>
+        <v>721398</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.8216</v>
+        <v>0.8234999999999999</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.9451000000000001</v>
+        <v>0.9472</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9759</v>
+        <v>0.9754999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -613,22 +613,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>160644</v>
+        <v>168250</v>
       </c>
       <c r="C7" t="n">
-        <v>115417</v>
+        <v>122943</v>
       </c>
       <c r="D7" t="n">
-        <v>148067</v>
+        <v>155655</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.7184999999999999</v>
+        <v>0.7306999999999999</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.9217</v>
+        <v>0.9251</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.655</v>
+        <v>0.6591</v>
       </c>
     </row>
     <row r="8">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>180370</v>
+        <v>186843</v>
       </c>
       <c r="C8" t="n">
-        <v>139199</v>
+        <v>144861</v>
       </c>
       <c r="D8" t="n">
-        <v>165250</v>
+        <v>171713</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.7717000000000001</v>
+        <v>0.7753</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.9162</v>
+        <v>0.919</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8399</v>
+        <v>0.8395</v>
       </c>
     </row>
     <row r="9">
@@ -663,13 +663,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1</v>
@@ -688,22 +688,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29954</v>
+        <v>31046</v>
       </c>
       <c r="C10" t="n">
-        <v>21143</v>
+        <v>22179</v>
       </c>
       <c r="D10" t="n">
-        <v>24162</v>
+        <v>25200</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.7058</v>
+        <v>0.7143999999999999</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.8066</v>
+        <v>0.8117</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9551999999999999</v>
+        <v>0.956</v>
       </c>
     </row>
     <row r="11">
@@ -713,22 +713,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2774</v>
+        <v>2834</v>
       </c>
       <c r="C11" t="n">
-        <v>2508</v>
+        <v>2568</v>
       </c>
       <c r="D11" t="n">
-        <v>2559</v>
+        <v>2619</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.9041</v>
+        <v>0.9061</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.9225</v>
+        <v>0.9240999999999999</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.9962000000000001</v>
+        <v>0.9964</v>
       </c>
     </row>
     <row r="12">
@@ -763,22 +763,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>90330</v>
+        <v>96915</v>
       </c>
       <c r="C13" t="n">
-        <v>84197</v>
+        <v>90676</v>
       </c>
       <c r="D13" t="n">
-        <v>86440</v>
+        <v>93024</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9320999999999999</v>
+        <v>0.9356</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.9569</v>
+        <v>0.9599</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.8924</v>
+        <v>0.894</v>
       </c>
     </row>
     <row r="14">
@@ -788,22 +788,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>70169</v>
+        <v>80695</v>
       </c>
       <c r="C14" t="n">
-        <v>45716</v>
+        <v>55318</v>
       </c>
       <c r="D14" t="n">
-        <v>57443</v>
+        <v>67891</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.6515000000000001</v>
+        <v>0.6855</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.8186</v>
+        <v>0.8412999999999999</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.8538</v>
+        <v>0.8626999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -824,7 +824,7 @@
       <c r="E15" s="2" t="n"/>
       <c r="F15" s="3" t="n"/>
       <c r="G15" s="2" t="n">
-        <v>1</v>
+        <v>0.9941</v>
       </c>
     </row>
   </sheetData>
@@ -839,7 +839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H351"/>
+  <dimension ref="A1:H365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10614,8 +10614,406 @@
       <c r="G351" s="3" t="n"/>
       <c r="H351" s="2" t="n"/>
     </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C352" t="n">
+        <v>0</v>
+      </c>
+      <c r="D352" t="n">
+        <v>0</v>
+      </c>
+      <c r="E352" t="n">
+        <v>0</v>
+      </c>
+      <c r="F352" s="2" t="n"/>
+      <c r="G352" s="3" t="n"/>
+      <c r="H352" s="2" t="n"/>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C353" t="n">
+        <v>2403</v>
+      </c>
+      <c r="D353" t="n">
+        <v>2337</v>
+      </c>
+      <c r="E353" t="n">
+        <v>2363</v>
+      </c>
+      <c r="F353" s="2" t="n">
+        <v>0.9725</v>
+      </c>
+      <c r="G353" s="3" t="n">
+        <v>0.9834000000000001</v>
+      </c>
+      <c r="H353" s="2" t="n">
+        <v>0.9234</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C354" t="n">
+        <v>17256</v>
+      </c>
+      <c r="D354" t="n">
+        <v>16966</v>
+      </c>
+      <c r="E354" t="n">
+        <v>17225</v>
+      </c>
+      <c r="F354" s="2" t="n">
+        <v>0.9832</v>
+      </c>
+      <c r="G354" s="3" t="n">
+        <v>0.9982</v>
+      </c>
+      <c r="H354" s="2" t="n">
+        <v>0.9418000000000001</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C355" t="n">
+        <v>0</v>
+      </c>
+      <c r="D355" t="n">
+        <v>0</v>
+      </c>
+      <c r="E355" t="n">
+        <v>0</v>
+      </c>
+      <c r="F355" s="2" t="n"/>
+      <c r="G355" s="3" t="n"/>
+      <c r="H355" s="2" t="n"/>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C356" t="n">
+        <v>29594</v>
+      </c>
+      <c r="D356" t="n">
+        <v>25742</v>
+      </c>
+      <c r="E356" t="n">
+        <v>29551</v>
+      </c>
+      <c r="F356" s="2" t="n">
+        <v>0.8698</v>
+      </c>
+      <c r="G356" s="3" t="n">
+        <v>0.9984999999999999</v>
+      </c>
+      <c r="H356" s="2" t="n">
+        <v>0.9684999999999999</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C357" t="n">
+        <v>7606</v>
+      </c>
+      <c r="D357" t="n">
+        <v>7526</v>
+      </c>
+      <c r="E357" t="n">
+        <v>7588</v>
+      </c>
+      <c r="F357" s="2" t="n">
+        <v>0.9895</v>
+      </c>
+      <c r="G357" s="3" t="n">
+        <v>0.9976</v>
+      </c>
+      <c r="H357" s="2" t="n">
+        <v>0.7486</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C358" t="n">
+        <v>6473</v>
+      </c>
+      <c r="D358" t="n">
+        <v>5662</v>
+      </c>
+      <c r="E358" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F358" s="2" t="n">
+        <v>0.8747</v>
+      </c>
+      <c r="G358" s="3" t="n">
+        <v>0.9984999999999999</v>
+      </c>
+      <c r="H358" s="2" t="n">
+        <v>0.8281999999999999</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C359" t="n">
+        <v>15</v>
+      </c>
+      <c r="D359" t="n">
+        <v>15</v>
+      </c>
+      <c r="E359" t="n">
+        <v>15</v>
+      </c>
+      <c r="F359" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G359" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H359" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C360" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D360" t="n">
+        <v>1036</v>
+      </c>
+      <c r="E360" t="n">
+        <v>1038</v>
+      </c>
+      <c r="F360" s="2" t="n">
+        <v>0.9487000000000001</v>
+      </c>
+      <c r="G360" s="3" t="n">
+        <v>0.9505</v>
+      </c>
+      <c r="H360" s="2" t="n">
+        <v>0.9681000000000001</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C361" t="n">
+        <v>60</v>
+      </c>
+      <c r="D361" t="n">
+        <v>60</v>
+      </c>
+      <c r="E361" t="n">
+        <v>60</v>
+      </c>
+      <c r="F361" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G361" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H361" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C362" t="n">
+        <v>0</v>
+      </c>
+      <c r="D362" t="n">
+        <v>0</v>
+      </c>
+      <c r="E362" t="n">
+        <v>0</v>
+      </c>
+      <c r="F362" s="2" t="n"/>
+      <c r="G362" s="3" t="n"/>
+      <c r="H362" s="2" t="n"/>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C363" t="n">
+        <v>6585</v>
+      </c>
+      <c r="D363" t="n">
+        <v>6479</v>
+      </c>
+      <c r="E363" t="n">
+        <v>6584</v>
+      </c>
+      <c r="F363" s="2" t="n">
+        <v>0.9839</v>
+      </c>
+      <c r="G363" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="H363" s="2" t="n">
+        <v>0.9264</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C364" t="n">
+        <v>10526</v>
+      </c>
+      <c r="D364" t="n">
+        <v>9602</v>
+      </c>
+      <c r="E364" t="n">
+        <v>10448</v>
+      </c>
+      <c r="F364" s="2" t="n">
+        <v>0.9122</v>
+      </c>
+      <c r="G364" s="3" t="n">
+        <v>0.9926</v>
+      </c>
+      <c r="H364" s="2" t="n">
+        <v>0.9115000000000001</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C365" t="n">
+        <v>0</v>
+      </c>
+      <c r="D365" t="n">
+        <v>0</v>
+      </c>
+      <c r="E365" t="n">
+        <v>0</v>
+      </c>
+      <c r="F365" s="2" t="n"/>
+      <c r="G365" s="3" t="n"/>
+      <c r="H365" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H351"/>
+  <autoFilter ref="A1:H365"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$365</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$379</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,22 +519,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>53440</v>
+        <v>55324</v>
       </c>
       <c r="C3" t="n">
-        <v>47436</v>
+        <v>49279</v>
       </c>
       <c r="D3" t="n">
-        <v>49177</v>
+        <v>51048</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.8876000000000001</v>
+        <v>0.8906999999999999</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.9201999999999999</v>
+        <v>0.9227</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9258</v>
+        <v>0.9267</v>
       </c>
     </row>
     <row r="4">
@@ -544,22 +544,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>455044</v>
+        <v>472325</v>
       </c>
       <c r="C4" t="n">
-        <v>374669</v>
+        <v>391551</v>
       </c>
       <c r="D4" t="n">
-        <v>422692</v>
+        <v>439949</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.8234</v>
+        <v>0.8290000000000001</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.9289000000000001</v>
+        <v>0.9315000000000001</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9209000000000001</v>
+        <v>0.9211</v>
       </c>
     </row>
     <row r="5">
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>761593</v>
+        <v>792719</v>
       </c>
       <c r="C6" t="n">
-        <v>627142</v>
+        <v>654902</v>
       </c>
       <c r="D6" t="n">
-        <v>721398</v>
+        <v>752506</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.8234999999999999</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.9472</v>
+        <v>0.9493</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9754999999999999</v>
+        <v>0.9756</v>
       </c>
     </row>
     <row r="7">
@@ -613,22 +613,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>168250</v>
+        <v>175336</v>
       </c>
       <c r="C7" t="n">
-        <v>122943</v>
+        <v>129918</v>
       </c>
       <c r="D7" t="n">
-        <v>155655</v>
+        <v>162688</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.7306999999999999</v>
+        <v>0.741</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.9251</v>
+        <v>0.9279000000000001</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6591</v>
+        <v>0.6639</v>
       </c>
     </row>
     <row r="8">
@@ -638,19 +638,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>186843</v>
+        <v>193660</v>
       </c>
       <c r="C8" t="n">
-        <v>144861</v>
+        <v>151247</v>
       </c>
       <c r="D8" t="n">
-        <v>171713</v>
+        <v>178099</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.7753</v>
+        <v>0.7809999999999999</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.919</v>
+        <v>0.9196</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>0.8395</v>
@@ -663,13 +663,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D9" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1</v>
@@ -688,22 +688,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31046</v>
+        <v>32416</v>
       </c>
       <c r="C10" t="n">
-        <v>22179</v>
+        <v>23492</v>
       </c>
       <c r="D10" t="n">
-        <v>25200</v>
+        <v>26514</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.7143999999999999</v>
+        <v>0.7247</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.8117</v>
+        <v>0.8179000000000001</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.956</v>
+        <v>0.9573999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -713,19 +713,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2834</v>
+        <v>2898</v>
       </c>
       <c r="C11" t="n">
-        <v>2568</v>
+        <v>2632</v>
       </c>
       <c r="D11" t="n">
-        <v>2619</v>
+        <v>2683</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.9061</v>
+        <v>0.9081999999999999</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.9240999999999999</v>
+        <v>0.9258</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0.9964</v>
@@ -763,22 +763,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>96915</v>
+        <v>99309</v>
       </c>
       <c r="C13" t="n">
-        <v>90676</v>
+        <v>92944</v>
       </c>
       <c r="D13" t="n">
-        <v>93024</v>
+        <v>95410</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9356</v>
+        <v>0.9359000000000001</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.9599</v>
+        <v>0.9606999999999999</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.894</v>
+        <v>0.8952</v>
       </c>
     </row>
     <row r="14">
@@ -788,22 +788,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>80695</v>
+        <v>91398</v>
       </c>
       <c r="C14" t="n">
-        <v>55318</v>
+        <v>65342</v>
       </c>
       <c r="D14" t="n">
-        <v>67891</v>
+        <v>78502</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.6855</v>
+        <v>0.7149</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.8412999999999999</v>
+        <v>0.8589</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.8626999999999999</v>
+        <v>0.8719</v>
       </c>
     </row>
     <row r="15">
@@ -824,7 +824,7 @@
       <c r="E15" s="2" t="n"/>
       <c r="F15" s="3" t="n"/>
       <c r="G15" s="2" t="n">
-        <v>0.9941</v>
+        <v>0.9767</v>
       </c>
     </row>
   </sheetData>
@@ -839,7 +839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H365"/>
+  <dimension ref="A1:H379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11012,8 +11012,406 @@
         <v>0</v>
       </c>
     </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C366" t="n">
+        <v>0</v>
+      </c>
+      <c r="D366" t="n">
+        <v>0</v>
+      </c>
+      <c r="E366" t="n">
+        <v>0</v>
+      </c>
+      <c r="F366" s="2" t="n"/>
+      <c r="G366" s="3" t="n"/>
+      <c r="H366" s="2" t="n"/>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C367" t="n">
+        <v>1884</v>
+      </c>
+      <c r="D367" t="n">
+        <v>1843</v>
+      </c>
+      <c r="E367" t="n">
+        <v>1871</v>
+      </c>
+      <c r="F367" s="2" t="n">
+        <v>0.9782</v>
+      </c>
+      <c r="G367" s="3" t="n">
+        <v>0.9931</v>
+      </c>
+      <c r="H367" s="2" t="n">
+        <v>0.9467</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C368" t="n">
+        <v>17281</v>
+      </c>
+      <c r="D368" t="n">
+        <v>16882</v>
+      </c>
+      <c r="E368" t="n">
+        <v>17257</v>
+      </c>
+      <c r="F368" s="2" t="n">
+        <v>0.9769</v>
+      </c>
+      <c r="G368" s="3" t="n">
+        <v>0.9986</v>
+      </c>
+      <c r="H368" s="2" t="n">
+        <v>0.9268999999999999</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C369" t="n">
+        <v>0</v>
+      </c>
+      <c r="D369" t="n">
+        <v>0</v>
+      </c>
+      <c r="E369" t="n">
+        <v>0</v>
+      </c>
+      <c r="F369" s="2" t="n"/>
+      <c r="G369" s="3" t="n"/>
+      <c r="H369" s="2" t="n"/>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C370" t="n">
+        <v>31126</v>
+      </c>
+      <c r="D370" t="n">
+        <v>27760</v>
+      </c>
+      <c r="E370" t="n">
+        <v>31108</v>
+      </c>
+      <c r="F370" s="2" t="n">
+        <v>0.8919</v>
+      </c>
+      <c r="G370" s="3" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="H370" s="2" t="n">
+        <v>0.9773999999999999</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C371" t="n">
+        <v>7086</v>
+      </c>
+      <c r="D371" t="n">
+        <v>6975</v>
+      </c>
+      <c r="E371" t="n">
+        <v>7033</v>
+      </c>
+      <c r="F371" s="2" t="n">
+        <v>0.9843000000000001</v>
+      </c>
+      <c r="G371" s="3" t="n">
+        <v>0.9925</v>
+      </c>
+      <c r="H371" s="2" t="n">
+        <v>0.7617</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C372" t="n">
+        <v>6817</v>
+      </c>
+      <c r="D372" t="n">
+        <v>6386</v>
+      </c>
+      <c r="E372" t="n">
+        <v>6386</v>
+      </c>
+      <c r="F372" s="2" t="n">
+        <v>0.9368000000000001</v>
+      </c>
+      <c r="G372" s="3" t="n">
+        <v>0.9368000000000001</v>
+      </c>
+      <c r="H372" s="2" t="n">
+        <v>0.8395</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C373" t="n">
+        <v>2</v>
+      </c>
+      <c r="D373" t="n">
+        <v>2</v>
+      </c>
+      <c r="E373" t="n">
+        <v>2</v>
+      </c>
+      <c r="F373" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G373" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H373" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C374" t="n">
+        <v>1370</v>
+      </c>
+      <c r="D374" t="n">
+        <v>1313</v>
+      </c>
+      <c r="E374" t="n">
+        <v>1314</v>
+      </c>
+      <c r="F374" s="2" t="n">
+        <v>0.9584</v>
+      </c>
+      <c r="G374" s="3" t="n">
+        <v>0.9591</v>
+      </c>
+      <c r="H374" s="2" t="n">
+        <v>0.9803000000000001</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C375" t="n">
+        <v>64</v>
+      </c>
+      <c r="D375" t="n">
+        <v>64</v>
+      </c>
+      <c r="E375" t="n">
+        <v>64</v>
+      </c>
+      <c r="F375" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G375" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H375" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C376" t="n">
+        <v>0</v>
+      </c>
+      <c r="D376" t="n">
+        <v>0</v>
+      </c>
+      <c r="E376" t="n">
+        <v>0</v>
+      </c>
+      <c r="F376" s="2" t="n"/>
+      <c r="G376" s="3" t="n"/>
+      <c r="H376" s="2" t="n"/>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C377" t="n">
+        <v>2394</v>
+      </c>
+      <c r="D377" t="n">
+        <v>2268</v>
+      </c>
+      <c r="E377" t="n">
+        <v>2386</v>
+      </c>
+      <c r="F377" s="2" t="n">
+        <v>0.9473999999999999</v>
+      </c>
+      <c r="G377" s="3" t="n">
+        <v>0.9967</v>
+      </c>
+      <c r="H377" s="2" t="n">
+        <v>0.9222</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C378" t="n">
+        <v>10703</v>
+      </c>
+      <c r="D378" t="n">
+        <v>10024</v>
+      </c>
+      <c r="E378" t="n">
+        <v>10611</v>
+      </c>
+      <c r="F378" s="2" t="n">
+        <v>0.9366</v>
+      </c>
+      <c r="G378" s="3" t="n">
+        <v>0.9914000000000001</v>
+      </c>
+      <c r="H378" s="2" t="n">
+        <v>0.9304000000000001</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C379" t="n">
+        <v>0</v>
+      </c>
+      <c r="D379" t="n">
+        <v>0</v>
+      </c>
+      <c r="E379" t="n">
+        <v>0</v>
+      </c>
+      <c r="F379" s="2" t="n"/>
+      <c r="G379" s="3" t="n"/>
+      <c r="H379" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H365"/>
+  <autoFilter ref="A1:H379"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -534,7 +534,7 @@
         <v>0.9227</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9267</v>
+        <v>0.9251999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -559,7 +559,7 @@
         <v>0.9315000000000001</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9211</v>
+        <v>0.9218999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -628,7 +628,7 @@
         <v>0.9279000000000001</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6639</v>
+        <v>0.6618000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -653,7 +653,7 @@
         <v>0.9196</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8395</v>
+        <v>0.8408</v>
       </c>
     </row>
     <row r="9">
@@ -703,7 +703,7 @@
         <v>0.8179000000000001</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9573999999999999</v>
+        <v>0.9560999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -778,7 +778,7 @@
         <v>0.9606999999999999</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.8952</v>
+        <v>0.895</v>
       </c>
     </row>
     <row r="14">
@@ -803,7 +803,7 @@
         <v>0.8589</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.8719</v>
+        <v>0.8698999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -824,7 +824,7 @@
       <c r="E15" s="2" t="n"/>
       <c r="F15" s="3" t="n"/>
       <c r="G15" s="2" t="n">
-        <v>0.9767</v>
+        <v>0.9941</v>
       </c>
     </row>
   </sheetData>
@@ -11063,7 +11063,7 @@
         <v>0.9931</v>
       </c>
       <c r="H367" s="2" t="n">
-        <v>0.9467</v>
+        <v>0.9123</v>
       </c>
     </row>
     <row r="368">
@@ -11093,7 +11093,7 @@
         <v>0.9986</v>
       </c>
       <c r="H368" s="2" t="n">
-        <v>0.9268999999999999</v>
+        <v>0.9433</v>
       </c>
     </row>
     <row r="369">
@@ -11147,7 +11147,7 @@
         <v>0.9994</v>
       </c>
       <c r="H370" s="2" t="n">
-        <v>0.9773999999999999</v>
+        <v>0.9775</v>
       </c>
     </row>
     <row r="371">
@@ -11177,7 +11177,7 @@
         <v>0.9925</v>
       </c>
       <c r="H371" s="2" t="n">
-        <v>0.7617</v>
+        <v>0.7181000000000001</v>
       </c>
     </row>
     <row r="372">
@@ -11207,7 +11207,7 @@
         <v>0.9368000000000001</v>
       </c>
       <c r="H372" s="2" t="n">
-        <v>0.8395</v>
+        <v>0.8729</v>
       </c>
     </row>
     <row r="373">
@@ -11236,9 +11236,7 @@
       <c r="G373" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H373" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="H373" s="2" t="n"/>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -11267,7 +11265,7 @@
         <v>0.9591</v>
       </c>
       <c r="H374" s="2" t="n">
-        <v>0.9803000000000001</v>
+        <v>0.9579000000000001</v>
       </c>
     </row>
     <row r="375">
@@ -11351,7 +11349,7 @@
         <v>0.9967</v>
       </c>
       <c r="H377" s="2" t="n">
-        <v>0.9222</v>
+        <v>0.9153</v>
       </c>
     </row>
     <row r="378">
@@ -11381,7 +11379,7 @@
         <v>0.9914000000000001</v>
       </c>
       <c r="H378" s="2" t="n">
-        <v>0.9304000000000001</v>
+        <v>0.9151</v>
       </c>
     </row>
     <row r="379">
@@ -11406,9 +11404,7 @@
       </c>
       <c r="F379" s="2" t="n"/>
       <c r="G379" s="3" t="n"/>
-      <c r="H379" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="H379" s="2" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H379"/>

--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$379</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$393</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,22 +519,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55324</v>
+        <v>56792</v>
       </c>
       <c r="C3" t="n">
-        <v>49279</v>
+        <v>49760</v>
       </c>
       <c r="D3" t="n">
-        <v>51048</v>
+        <v>51529</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.8906999999999999</v>
+        <v>0.8762000000000001</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.9227</v>
+        <v>0.9073</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9251999999999999</v>
+        <v>0.9248000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -544,22 +544,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>472325</v>
+        <v>485720</v>
       </c>
       <c r="C4" t="n">
-        <v>391551</v>
+        <v>393831</v>
       </c>
       <c r="D4" t="n">
-        <v>439949</v>
+        <v>442229</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.8290000000000001</v>
+        <v>0.8108</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.9315000000000001</v>
+        <v>0.9105</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9218999999999999</v>
+        <v>0.919</v>
       </c>
     </row>
     <row r="5">
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>792719</v>
+        <v>813707</v>
       </c>
       <c r="C6" t="n">
-        <v>654902</v>
+        <v>665047</v>
       </c>
       <c r="D6" t="n">
-        <v>752506</v>
+        <v>762651</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.8260999999999999</v>
+        <v>0.8173</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.9493</v>
+        <v>0.9373</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9756</v>
+        <v>0.9748</v>
       </c>
     </row>
     <row r="7">
@@ -613,22 +613,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>175336</v>
+        <v>181238</v>
       </c>
       <c r="C7" t="n">
-        <v>129918</v>
+        <v>130569</v>
       </c>
       <c r="D7" t="n">
-        <v>162688</v>
+        <v>163339</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.741</v>
+        <v>0.7204</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.9279000000000001</v>
+        <v>0.9012</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6618000000000001</v>
+        <v>0.6606000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>193660</v>
+        <v>199812</v>
       </c>
       <c r="C8" t="n">
-        <v>151247</v>
+        <v>152407</v>
       </c>
       <c r="D8" t="n">
-        <v>178099</v>
+        <v>179259</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.7809999999999999</v>
+        <v>0.7628</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.9196</v>
+        <v>0.8970999999999999</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8408</v>
+        <v>0.8358</v>
       </c>
     </row>
     <row r="9">
@@ -688,22 +688,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32416</v>
+        <v>33181</v>
       </c>
       <c r="C10" t="n">
-        <v>23492</v>
+        <v>23922</v>
       </c>
       <c r="D10" t="n">
-        <v>26514</v>
+        <v>26944</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.7247</v>
+        <v>0.721</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.8179000000000001</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9560999999999999</v>
+        <v>0.9520000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -728,7 +728,7 @@
         <v>0.9258</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.9964</v>
+        <v>0.9965000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -763,22 +763,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>99309</v>
+        <v>100803</v>
       </c>
       <c r="C13" t="n">
-        <v>92944</v>
+        <v>93252</v>
       </c>
       <c r="D13" t="n">
-        <v>95410</v>
+        <v>95718</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9359000000000001</v>
+        <v>0.9251</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.9606999999999999</v>
+        <v>0.9495999999999999</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.895</v>
+        <v>0.8924</v>
       </c>
     </row>
     <row r="14">
@@ -788,22 +788,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>91398</v>
+        <v>99438</v>
       </c>
       <c r="C14" t="n">
-        <v>65342</v>
+        <v>66772</v>
       </c>
       <c r="D14" t="n">
-        <v>78502</v>
+        <v>79932</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.7149</v>
+        <v>0.6715000000000001</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.8589</v>
+        <v>0.8038</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.8698999999999999</v>
+        <v>0.8691</v>
       </c>
     </row>
     <row r="15">
@@ -839,7 +839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H379"/>
+  <dimension ref="A1:H393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11406,8 +11406,396 @@
       <c r="G379" s="3" t="n"/>
       <c r="H379" s="2" t="n"/>
     </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C380" t="n">
+        <v>0</v>
+      </c>
+      <c r="D380" t="n">
+        <v>0</v>
+      </c>
+      <c r="E380" t="n">
+        <v>0</v>
+      </c>
+      <c r="F380" s="2" t="n"/>
+      <c r="G380" s="3" t="n"/>
+      <c r="H380" s="2" t="n"/>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C381" t="n">
+        <v>1468</v>
+      </c>
+      <c r="D381" t="n">
+        <v>481</v>
+      </c>
+      <c r="E381" t="n">
+        <v>481</v>
+      </c>
+      <c r="F381" s="2" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="G381" s="3" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="H381" s="2" t="n">
+        <v>0.9135</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C382" t="n">
+        <v>13395</v>
+      </c>
+      <c r="D382" t="n">
+        <v>2280</v>
+      </c>
+      <c r="E382" t="n">
+        <v>2280</v>
+      </c>
+      <c r="F382" s="2" t="n">
+        <v>0.1702</v>
+      </c>
+      <c r="G382" s="3" t="n">
+        <v>0.1702</v>
+      </c>
+      <c r="H382" s="2" t="n">
+        <v>0.8434999999999999</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C383" t="n">
+        <v>0</v>
+      </c>
+      <c r="D383" t="n">
+        <v>0</v>
+      </c>
+      <c r="E383" t="n">
+        <v>0</v>
+      </c>
+      <c r="F383" s="2" t="n"/>
+      <c r="G383" s="3" t="n"/>
+      <c r="H383" s="2" t="n"/>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C384" t="n">
+        <v>20988</v>
+      </c>
+      <c r="D384" t="n">
+        <v>10145</v>
+      </c>
+      <c r="E384" t="n">
+        <v>10145</v>
+      </c>
+      <c r="F384" s="2" t="n">
+        <v>0.4834000000000001</v>
+      </c>
+      <c r="G384" s="3" t="n">
+        <v>0.4834000000000001</v>
+      </c>
+      <c r="H384" s="2" t="n">
+        <v>0.9555</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C385" t="n">
+        <v>5902</v>
+      </c>
+      <c r="D385" t="n">
+        <v>651</v>
+      </c>
+      <c r="E385" t="n">
+        <v>651</v>
+      </c>
+      <c r="F385" s="2" t="n">
+        <v>0.1103</v>
+      </c>
+      <c r="G385" s="3" t="n">
+        <v>0.1103</v>
+      </c>
+      <c r="H385" s="2" t="n">
+        <v>0.6355</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C386" t="n">
+        <v>6152</v>
+      </c>
+      <c r="D386" t="n">
+        <v>1160</v>
+      </c>
+      <c r="E386" t="n">
+        <v>1160</v>
+      </c>
+      <c r="F386" s="2" t="n">
+        <v>0.1886</v>
+      </c>
+      <c r="G386" s="3" t="n">
+        <v>0.1886</v>
+      </c>
+      <c r="H386" s="2" t="n">
+        <v>0.7238</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C387" t="n">
+        <v>0</v>
+      </c>
+      <c r="D387" t="n">
+        <v>0</v>
+      </c>
+      <c r="E387" t="n">
+        <v>0</v>
+      </c>
+      <c r="F387" s="2" t="n"/>
+      <c r="G387" s="3" t="n"/>
+      <c r="H387" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C388" t="n">
+        <v>765</v>
+      </c>
+      <c r="D388" t="n">
+        <v>430</v>
+      </c>
+      <c r="E388" t="n">
+        <v>430</v>
+      </c>
+      <c r="F388" s="2" t="n">
+        <v>0.5621</v>
+      </c>
+      <c r="G388" s="3" t="n">
+        <v>0.5621</v>
+      </c>
+      <c r="H388" s="2" t="n">
+        <v>0.8845999999999999</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C389" t="n">
+        <v>0</v>
+      </c>
+      <c r="D389" t="n">
+        <v>0</v>
+      </c>
+      <c r="E389" t="n">
+        <v>0</v>
+      </c>
+      <c r="F389" s="2" t="n"/>
+      <c r="G389" s="3" t="n"/>
+      <c r="H389" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C390" t="n">
+        <v>0</v>
+      </c>
+      <c r="D390" t="n">
+        <v>0</v>
+      </c>
+      <c r="E390" t="n">
+        <v>0</v>
+      </c>
+      <c r="F390" s="2" t="n"/>
+      <c r="G390" s="3" t="n"/>
+      <c r="H390" s="2" t="n"/>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C391" t="n">
+        <v>1494</v>
+      </c>
+      <c r="D391" t="n">
+        <v>308</v>
+      </c>
+      <c r="E391" t="n">
+        <v>308</v>
+      </c>
+      <c r="F391" s="2" t="n">
+        <v>0.2062</v>
+      </c>
+      <c r="G391" s="3" t="n">
+        <v>0.2062</v>
+      </c>
+      <c r="H391" s="2" t="n">
+        <v>0.8173999999999999</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C392" t="n">
+        <v>8040</v>
+      </c>
+      <c r="D392" t="n">
+        <v>1430</v>
+      </c>
+      <c r="E392" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F392" s="2" t="n">
+        <v>0.1779</v>
+      </c>
+      <c r="G392" s="3" t="n">
+        <v>0.1779</v>
+      </c>
+      <c r="H392" s="2" t="n">
+        <v>0.8628</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C393" t="n">
+        <v>0</v>
+      </c>
+      <c r="D393" t="n">
+        <v>0</v>
+      </c>
+      <c r="E393" t="n">
+        <v>0</v>
+      </c>
+      <c r="F393" s="2" t="n"/>
+      <c r="G393" s="3" t="n"/>
+      <c r="H393" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H379"/>
+  <autoFilter ref="A1:H393"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Consolidado" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Geral Diário" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consolidado" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Geral Diário" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$393</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$421</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,22 +519,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>56792</v>
+        <v>60684</v>
       </c>
       <c r="C3" t="n">
-        <v>49760</v>
+        <v>53511</v>
       </c>
       <c r="D3" t="n">
-        <v>51529</v>
+        <v>55354</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.8762000000000001</v>
+        <v>0.8818</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.9073</v>
+        <v>0.9122</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9248000000000001</v>
+        <v>0.9258</v>
       </c>
     </row>
     <row r="4">
@@ -544,22 +544,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>485720</v>
+        <v>517918</v>
       </c>
       <c r="C4" t="n">
-        <v>393831</v>
+        <v>422784</v>
       </c>
       <c r="D4" t="n">
-        <v>442229</v>
+        <v>473945</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.8108</v>
+        <v>0.8162999999999999</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.9105</v>
+        <v>0.9151</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.919</v>
+        <v>0.9177</v>
       </c>
     </row>
     <row r="5">
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>813707</v>
+        <v>871439</v>
       </c>
       <c r="C6" t="n">
-        <v>665047</v>
+        <v>720585</v>
       </c>
       <c r="D6" t="n">
-        <v>762651</v>
+        <v>820174</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.8173</v>
+        <v>0.8269</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.9373</v>
+        <v>0.9412</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9748</v>
+        <v>0.9743000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -613,22 +613,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>181238</v>
+        <v>195465</v>
       </c>
       <c r="C7" t="n">
-        <v>130569</v>
+        <v>142243</v>
       </c>
       <c r="D7" t="n">
-        <v>163339</v>
+        <v>177225</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.7204</v>
+        <v>0.7277</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.9012</v>
+        <v>0.9067000000000001</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6606000000000001</v>
+        <v>0.659</v>
       </c>
     </row>
     <row r="8">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>199812</v>
+        <v>212736</v>
       </c>
       <c r="C8" t="n">
-        <v>152407</v>
+        <v>163909</v>
       </c>
       <c r="D8" t="n">
-        <v>179259</v>
+        <v>190897</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.7628</v>
+        <v>0.7705</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.8970999999999999</v>
+        <v>0.8973</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8358</v>
+        <v>0.8306999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -663,13 +663,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D9" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1</v>
@@ -688,22 +688,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>33181</v>
+        <v>35739</v>
       </c>
       <c r="C10" t="n">
-        <v>23922</v>
+        <v>26237</v>
       </c>
       <c r="D10" t="n">
-        <v>26944</v>
+        <v>29273</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.721</v>
+        <v>0.7341</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8190999999999999</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9520000000000001</v>
+        <v>0.9492</v>
       </c>
     </row>
     <row r="11">
@@ -713,22 +713,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2898</v>
+        <v>3074</v>
       </c>
       <c r="C11" t="n">
-        <v>2632</v>
+        <v>2808</v>
       </c>
       <c r="D11" t="n">
-        <v>2683</v>
+        <v>2859</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.9081999999999999</v>
+        <v>0.9135</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.9258</v>
+        <v>0.9301</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.9965000000000001</v>
+        <v>0.9967</v>
       </c>
     </row>
     <row r="12">
@@ -763,22 +763,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>100803</v>
+        <v>116079</v>
       </c>
       <c r="C13" t="n">
-        <v>93252</v>
+        <v>108030</v>
       </c>
       <c r="D13" t="n">
-        <v>95718</v>
+        <v>110816</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9251</v>
+        <v>0.9307</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.9495999999999999</v>
+        <v>0.9547</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.8924</v>
+        <v>0.8923000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -788,22 +788,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>99438</v>
+        <v>118628</v>
       </c>
       <c r="C14" t="n">
-        <v>66772</v>
+        <v>84327</v>
       </c>
       <c r="D14" t="n">
-        <v>79932</v>
+        <v>97775</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.6715000000000001</v>
+        <v>0.7109000000000001</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.8038</v>
+        <v>0.8242</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.8691</v>
+        <v>0.8758</v>
       </c>
     </row>
     <row r="15">
@@ -839,7 +839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H393"/>
+  <dimension ref="A1:H421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11409,7 +11409,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -11433,7 +11433,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -11442,28 +11442,28 @@
         </is>
       </c>
       <c r="C381" t="n">
-        <v>1468</v>
+        <v>2059</v>
       </c>
       <c r="D381" t="n">
-        <v>481</v>
+        <v>2054</v>
       </c>
       <c r="E381" t="n">
-        <v>481</v>
+        <v>2057</v>
       </c>
       <c r="F381" s="2" t="n">
-        <v>0.3277</v>
+        <v>0.9976</v>
       </c>
       <c r="G381" s="3" t="n">
-        <v>0.3277</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="H381" s="2" t="n">
-        <v>0.9135</v>
+        <v>0.9434999999999999</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -11472,28 +11472,28 @@
         </is>
       </c>
       <c r="C382" t="n">
-        <v>13395</v>
+        <v>16214</v>
       </c>
       <c r="D382" t="n">
-        <v>2280</v>
+        <v>15921</v>
       </c>
       <c r="E382" t="n">
-        <v>2280</v>
+        <v>16201</v>
       </c>
       <c r="F382" s="2" t="n">
-        <v>0.1702</v>
+        <v>0.9819</v>
       </c>
       <c r="G382" s="3" t="n">
-        <v>0.1702</v>
+        <v>0.9992</v>
       </c>
       <c r="H382" s="2" t="n">
-        <v>0.8434999999999999</v>
+        <v>0.9333</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -11517,7 +11517,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -11526,28 +11526,28 @@
         </is>
       </c>
       <c r="C384" t="n">
-        <v>20988</v>
+        <v>27607</v>
       </c>
       <c r="D384" t="n">
-        <v>10145</v>
+        <v>27149</v>
       </c>
       <c r="E384" t="n">
-        <v>10145</v>
+        <v>27599</v>
       </c>
       <c r="F384" s="2" t="n">
-        <v>0.4834000000000001</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="G384" s="3" t="n">
-        <v>0.4834000000000001</v>
+        <v>0.9997</v>
       </c>
       <c r="H384" s="2" t="n">
-        <v>0.9555</v>
+        <v>0.9745999999999999</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -11556,28 +11556,28 @@
         </is>
       </c>
       <c r="C385" t="n">
-        <v>5902</v>
+        <v>6965</v>
       </c>
       <c r="D385" t="n">
-        <v>651</v>
+        <v>6872</v>
       </c>
       <c r="E385" t="n">
-        <v>651</v>
+        <v>6942</v>
       </c>
       <c r="F385" s="2" t="n">
-        <v>0.1103</v>
+        <v>0.9865999999999999</v>
       </c>
       <c r="G385" s="3" t="n">
-        <v>0.1103</v>
+        <v>0.9967</v>
       </c>
       <c r="H385" s="2" t="n">
-        <v>0.6355</v>
+        <v>0.705</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -11586,28 +11586,28 @@
         </is>
       </c>
       <c r="C386" t="n">
-        <v>6152</v>
+        <v>6545</v>
       </c>
       <c r="D386" t="n">
-        <v>1160</v>
+        <v>6402</v>
       </c>
       <c r="E386" t="n">
-        <v>1160</v>
+        <v>6538</v>
       </c>
       <c r="F386" s="2" t="n">
-        <v>0.1886</v>
+        <v>0.9782</v>
       </c>
       <c r="G386" s="3" t="n">
-        <v>0.1886</v>
+        <v>0.9989</v>
       </c>
       <c r="H386" s="2" t="n">
-        <v>0.7238</v>
+        <v>0.8293</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -11633,7 +11633,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -11642,28 +11642,28 @@
         </is>
       </c>
       <c r="C388" t="n">
-        <v>765</v>
+        <v>1003</v>
       </c>
       <c r="D388" t="n">
-        <v>430</v>
+        <v>968</v>
       </c>
       <c r="E388" t="n">
-        <v>430</v>
+        <v>968</v>
       </c>
       <c r="F388" s="2" t="n">
-        <v>0.5621</v>
+        <v>0.9651000000000001</v>
       </c>
       <c r="G388" s="3" t="n">
-        <v>0.5621</v>
+        <v>0.9651000000000001</v>
       </c>
       <c r="H388" s="2" t="n">
-        <v>0.8845999999999999</v>
+        <v>0.9664</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -11672,16 +11672,20 @@
         </is>
       </c>
       <c r="C389" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="D389" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="E389" t="n">
-        <v>0</v>
-      </c>
-      <c r="F389" s="2" t="n"/>
-      <c r="G389" s="3" t="n"/>
+        <v>99</v>
+      </c>
+      <c r="F389" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G389" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="H389" s="2" t="n">
         <v>1</v>
       </c>
@@ -11689,7 +11693,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -11713,7 +11717,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -11722,28 +11726,28 @@
         </is>
       </c>
       <c r="C391" t="n">
-        <v>1494</v>
+        <v>5996</v>
       </c>
       <c r="D391" t="n">
-        <v>308</v>
+        <v>5932</v>
       </c>
       <c r="E391" t="n">
-        <v>308</v>
+        <v>5991</v>
       </c>
       <c r="F391" s="2" t="n">
-        <v>0.2062</v>
+        <v>0.9893000000000001</v>
       </c>
       <c r="G391" s="3" t="n">
-        <v>0.2062</v>
+        <v>0.9992</v>
       </c>
       <c r="H391" s="2" t="n">
-        <v>0.8173999999999999</v>
+        <v>0.9225</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -11752,28 +11756,28 @@
         </is>
       </c>
       <c r="C392" t="n">
-        <v>8040</v>
+        <v>9763</v>
       </c>
       <c r="D392" t="n">
-        <v>1430</v>
+        <v>9506</v>
       </c>
       <c r="E392" t="n">
-        <v>1430</v>
+        <v>9696</v>
       </c>
       <c r="F392" s="2" t="n">
-        <v>0.1779</v>
+        <v>0.9737</v>
       </c>
       <c r="G392" s="3" t="n">
-        <v>0.1779</v>
+        <v>0.9931</v>
       </c>
       <c r="H392" s="2" t="n">
-        <v>0.8628</v>
+        <v>0.9325</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -11794,8 +11798,792 @@
       <c r="G393" s="3" t="n"/>
       <c r="H393" s="2" t="n"/>
     </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C394" t="n">
+        <v>0</v>
+      </c>
+      <c r="D394" t="n">
+        <v>0</v>
+      </c>
+      <c r="E394" t="n">
+        <v>0</v>
+      </c>
+      <c r="F394" s="2" t="n"/>
+      <c r="G394" s="3" t="n"/>
+      <c r="H394" s="2" t="n"/>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C395" t="n">
+        <v>1833</v>
+      </c>
+      <c r="D395" t="n">
+        <v>1697</v>
+      </c>
+      <c r="E395" t="n">
+        <v>1768</v>
+      </c>
+      <c r="F395" s="2" t="n">
+        <v>0.9258</v>
+      </c>
+      <c r="G395" s="3" t="n">
+        <v>0.9645</v>
+      </c>
+      <c r="H395" s="2" t="n">
+        <v>0.9325</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C396" t="n">
+        <v>15984</v>
+      </c>
+      <c r="D396" t="n">
+        <v>13032</v>
+      </c>
+      <c r="E396" t="n">
+        <v>15515</v>
+      </c>
+      <c r="F396" s="2" t="n">
+        <v>0.8153</v>
+      </c>
+      <c r="G396" s="3" t="n">
+        <v>0.9706999999999999</v>
+      </c>
+      <c r="H396" s="2" t="n">
+        <v>0.8708</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C397" t="n">
+        <v>0</v>
+      </c>
+      <c r="D397" t="n">
+        <v>0</v>
+      </c>
+      <c r="E397" t="n">
+        <v>0</v>
+      </c>
+      <c r="F397" s="2" t="n"/>
+      <c r="G397" s="3" t="n"/>
+      <c r="H397" s="2" t="n"/>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C398" t="n">
+        <v>30125</v>
+      </c>
+      <c r="D398" t="n">
+        <v>28389</v>
+      </c>
+      <c r="E398" t="n">
+        <v>29924</v>
+      </c>
+      <c r="F398" s="2" t="n">
+        <v>0.9423999999999999</v>
+      </c>
+      <c r="G398" s="3" t="n">
+        <v>0.9933</v>
+      </c>
+      <c r="H398" s="2" t="n">
+        <v>0.9611</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C399" t="n">
+        <v>7262</v>
+      </c>
+      <c r="D399" t="n">
+        <v>4802</v>
+      </c>
+      <c r="E399" t="n">
+        <v>6944</v>
+      </c>
+      <c r="F399" s="2" t="n">
+        <v>0.6613</v>
+      </c>
+      <c r="G399" s="3" t="n">
+        <v>0.9562</v>
+      </c>
+      <c r="H399" s="2" t="n">
+        <v>0.5885</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C400" t="n">
+        <v>6379</v>
+      </c>
+      <c r="D400" t="n">
+        <v>5100</v>
+      </c>
+      <c r="E400" t="n">
+        <v>5100</v>
+      </c>
+      <c r="F400" s="2" t="n">
+        <v>0.7995</v>
+      </c>
+      <c r="G400" s="3" t="n">
+        <v>0.7995</v>
+      </c>
+      <c r="H400" s="2" t="n">
+        <v>0.7121999999999999</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C401" t="n">
+        <v>1</v>
+      </c>
+      <c r="D401" t="n">
+        <v>1</v>
+      </c>
+      <c r="E401" t="n">
+        <v>1</v>
+      </c>
+      <c r="F401" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G401" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H401" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C402" t="n">
+        <v>1555</v>
+      </c>
+      <c r="D402" t="n">
+        <v>1347</v>
+      </c>
+      <c r="E402" t="n">
+        <v>1361</v>
+      </c>
+      <c r="F402" s="2" t="n">
+        <v>0.8662000000000001</v>
+      </c>
+      <c r="G402" s="3" t="n">
+        <v>0.8752</v>
+      </c>
+      <c r="H402" s="2" t="n">
+        <v>0.8854000000000001</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C403" t="n">
+        <v>77</v>
+      </c>
+      <c r="D403" t="n">
+        <v>77</v>
+      </c>
+      <c r="E403" t="n">
+        <v>77</v>
+      </c>
+      <c r="F403" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G403" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H403" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C404" t="n">
+        <v>0</v>
+      </c>
+      <c r="D404" t="n">
+        <v>0</v>
+      </c>
+      <c r="E404" t="n">
+        <v>0</v>
+      </c>
+      <c r="F404" s="2" t="n"/>
+      <c r="G404" s="3" t="n"/>
+      <c r="H404" s="2" t="n"/>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C405" t="n">
+        <v>9280</v>
+      </c>
+      <c r="D405" t="n">
+        <v>8846</v>
+      </c>
+      <c r="E405" t="n">
+        <v>9107</v>
+      </c>
+      <c r="F405" s="2" t="n">
+        <v>0.9531999999999999</v>
+      </c>
+      <c r="G405" s="3" t="n">
+        <v>0.9814000000000001</v>
+      </c>
+      <c r="H405" s="2" t="n">
+        <v>0.8597</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C406" t="n">
+        <v>9427</v>
+      </c>
+      <c r="D406" t="n">
+        <v>8049</v>
+      </c>
+      <c r="E406" t="n">
+        <v>8147</v>
+      </c>
+      <c r="F406" s="2" t="n">
+        <v>0.8538</v>
+      </c>
+      <c r="G406" s="3" t="n">
+        <v>0.8642</v>
+      </c>
+      <c r="H406" s="2" t="n">
+        <v>0.8772</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C407" t="n">
+        <v>0</v>
+      </c>
+      <c r="D407" t="n">
+        <v>0</v>
+      </c>
+      <c r="E407" t="n">
+        <v>0</v>
+      </c>
+      <c r="F407" s="2" t="n"/>
+      <c r="G407" s="3" t="n"/>
+      <c r="H407" s="2" t="n"/>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C408" t="n">
+        <v>0</v>
+      </c>
+      <c r="D408" t="n">
+        <v>0</v>
+      </c>
+      <c r="E408" t="n">
+        <v>0</v>
+      </c>
+      <c r="F408" s="2" t="n"/>
+      <c r="G408" s="3" t="n"/>
+      <c r="H408" s="2" t="n"/>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C409" t="n">
+        <v>1468</v>
+      </c>
+      <c r="D409" t="n">
+        <v>481</v>
+      </c>
+      <c r="E409" t="n">
+        <v>481</v>
+      </c>
+      <c r="F409" s="2" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="G409" s="3" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="H409" s="2" t="n">
+        <v>0.9135</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C410" t="n">
+        <v>13395</v>
+      </c>
+      <c r="D410" t="n">
+        <v>2280</v>
+      </c>
+      <c r="E410" t="n">
+        <v>2280</v>
+      </c>
+      <c r="F410" s="2" t="n">
+        <v>0.1702</v>
+      </c>
+      <c r="G410" s="3" t="n">
+        <v>0.1702</v>
+      </c>
+      <c r="H410" s="2" t="n">
+        <v>0.8434999999999999</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C411" t="n">
+        <v>0</v>
+      </c>
+      <c r="D411" t="n">
+        <v>0</v>
+      </c>
+      <c r="E411" t="n">
+        <v>0</v>
+      </c>
+      <c r="F411" s="2" t="n"/>
+      <c r="G411" s="3" t="n"/>
+      <c r="H411" s="2" t="n"/>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C412" t="n">
+        <v>20988</v>
+      </c>
+      <c r="D412" t="n">
+        <v>10145</v>
+      </c>
+      <c r="E412" t="n">
+        <v>10145</v>
+      </c>
+      <c r="F412" s="2" t="n">
+        <v>0.4834000000000001</v>
+      </c>
+      <c r="G412" s="3" t="n">
+        <v>0.4834000000000001</v>
+      </c>
+      <c r="H412" s="2" t="n">
+        <v>0.9555</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>5902</v>
+      </c>
+      <c r="D413" t="n">
+        <v>651</v>
+      </c>
+      <c r="E413" t="n">
+        <v>651</v>
+      </c>
+      <c r="F413" s="2" t="n">
+        <v>0.1103</v>
+      </c>
+      <c r="G413" s="3" t="n">
+        <v>0.1103</v>
+      </c>
+      <c r="H413" s="2" t="n">
+        <v>0.6355</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>6152</v>
+      </c>
+      <c r="D414" t="n">
+        <v>1160</v>
+      </c>
+      <c r="E414" t="n">
+        <v>1160</v>
+      </c>
+      <c r="F414" s="2" t="n">
+        <v>0.1886</v>
+      </c>
+      <c r="G414" s="3" t="n">
+        <v>0.1886</v>
+      </c>
+      <c r="H414" s="2" t="n">
+        <v>0.7238</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>0</v>
+      </c>
+      <c r="D415" t="n">
+        <v>0</v>
+      </c>
+      <c r="E415" t="n">
+        <v>0</v>
+      </c>
+      <c r="F415" s="2" t="n"/>
+      <c r="G415" s="3" t="n"/>
+      <c r="H415" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>765</v>
+      </c>
+      <c r="D416" t="n">
+        <v>430</v>
+      </c>
+      <c r="E416" t="n">
+        <v>430</v>
+      </c>
+      <c r="F416" s="2" t="n">
+        <v>0.5621</v>
+      </c>
+      <c r="G416" s="3" t="n">
+        <v>0.5621</v>
+      </c>
+      <c r="H416" s="2" t="n">
+        <v>0.8845999999999999</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C417" t="n">
+        <v>0</v>
+      </c>
+      <c r="D417" t="n">
+        <v>0</v>
+      </c>
+      <c r="E417" t="n">
+        <v>0</v>
+      </c>
+      <c r="F417" s="2" t="n"/>
+      <c r="G417" s="3" t="n"/>
+      <c r="H417" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C418" t="n">
+        <v>0</v>
+      </c>
+      <c r="D418" t="n">
+        <v>0</v>
+      </c>
+      <c r="E418" t="n">
+        <v>0</v>
+      </c>
+      <c r="F418" s="2" t="n"/>
+      <c r="G418" s="3" t="n"/>
+      <c r="H418" s="2" t="n"/>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C419" t="n">
+        <v>1494</v>
+      </c>
+      <c r="D419" t="n">
+        <v>308</v>
+      </c>
+      <c r="E419" t="n">
+        <v>308</v>
+      </c>
+      <c r="F419" s="2" t="n">
+        <v>0.2062</v>
+      </c>
+      <c r="G419" s="3" t="n">
+        <v>0.2062</v>
+      </c>
+      <c r="H419" s="2" t="n">
+        <v>0.8173999999999999</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C420" t="n">
+        <v>8040</v>
+      </c>
+      <c r="D420" t="n">
+        <v>1430</v>
+      </c>
+      <c r="E420" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F420" s="2" t="n">
+        <v>0.1779</v>
+      </c>
+      <c r="G420" s="3" t="n">
+        <v>0.1779</v>
+      </c>
+      <c r="H420" s="2" t="n">
+        <v>0.8628</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C421" t="n">
+        <v>0</v>
+      </c>
+      <c r="D421" t="n">
+        <v>0</v>
+      </c>
+      <c r="E421" t="n">
+        <v>0</v>
+      </c>
+      <c r="F421" s="2" t="n"/>
+      <c r="G421" s="3" t="n"/>
+      <c r="H421" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H393"/>
+  <autoFilter ref="A1:H421"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -534,7 +534,7 @@
         <v>0.9073</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9248000000000001</v>
+        <v>0.9244</v>
       </c>
     </row>
     <row r="4">
@@ -559,7 +559,7 @@
         <v>0.9105</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.919</v>
+        <v>0.9189000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -603,7 +603,7 @@
         <v>0.9373</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9748</v>
+        <v>0.9745</v>
       </c>
     </row>
     <row r="7">
@@ -628,7 +628,7 @@
         <v>0.9012</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6606000000000001</v>
+        <v>0.6593000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -653,7 +653,7 @@
         <v>0.8970999999999999</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8358</v>
+        <v>0.8336</v>
       </c>
     </row>
     <row r="9">
@@ -703,7 +703,7 @@
         <v>0.8120000000000001</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9520000000000001</v>
+        <v>0.9517</v>
       </c>
     </row>
     <row r="11">
@@ -778,7 +778,7 @@
         <v>0.9495999999999999</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.8924</v>
+        <v>0.8934000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -803,7 +803,7 @@
         <v>0.8038</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.8691</v>
+        <v>0.8703</v>
       </c>
     </row>
     <row r="15">
@@ -11457,7 +11457,7 @@
         <v>0.3277</v>
       </c>
       <c r="H381" s="2" t="n">
-        <v>0.9135</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="382">
@@ -11487,7 +11487,7 @@
         <v>0.1702</v>
       </c>
       <c r="H382" s="2" t="n">
-        <v>0.8434999999999999</v>
+        <v>0.8465</v>
       </c>
     </row>
     <row r="383">
@@ -11541,7 +11541,7 @@
         <v>0.4834000000000001</v>
       </c>
       <c r="H384" s="2" t="n">
-        <v>0.9555</v>
+        <v>0.9466</v>
       </c>
     </row>
     <row r="385">
@@ -11571,7 +11571,7 @@
         <v>0.1103</v>
       </c>
       <c r="H385" s="2" t="n">
-        <v>0.6355</v>
+        <v>0.6061</v>
       </c>
     </row>
     <row r="386">
@@ -11601,7 +11601,7 @@
         <v>0.1886</v>
       </c>
       <c r="H386" s="2" t="n">
-        <v>0.7238</v>
+        <v>0.6441</v>
       </c>
     </row>
     <row r="387">
@@ -11657,7 +11657,7 @@
         <v>0.5621</v>
       </c>
       <c r="H388" s="2" t="n">
-        <v>0.8845999999999999</v>
+        <v>0.8782</v>
       </c>
     </row>
     <row r="389">
@@ -11737,7 +11737,7 @@
         <v>0.2062</v>
       </c>
       <c r="H391" s="2" t="n">
-        <v>0.8173999999999999</v>
+        <v>0.8487</v>
       </c>
     </row>
     <row r="392">
@@ -11767,7 +11767,7 @@
         <v>0.1779</v>
       </c>
       <c r="H392" s="2" t="n">
-        <v>0.8628</v>
+        <v>0.8734000000000001</v>
       </c>
     </row>
     <row r="393">

--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$393</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$407</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,22 +519,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>56792</v>
+        <v>58178</v>
       </c>
       <c r="C3" t="n">
-        <v>49760</v>
+        <v>51071</v>
       </c>
       <c r="D3" t="n">
-        <v>51529</v>
+        <v>52890</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.8762000000000001</v>
+        <v>0.8778</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.9073</v>
+        <v>0.9091</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9244</v>
+        <v>0.9243000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -544,22 +544,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>485720</v>
+        <v>501429</v>
       </c>
       <c r="C4" t="n">
-        <v>393831</v>
+        <v>404884</v>
       </c>
       <c r="D4" t="n">
-        <v>442229</v>
+        <v>457659</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.8108</v>
+        <v>0.8075</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.9105</v>
+        <v>0.9127</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9189000000000001</v>
+        <v>0.9167000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -588,19 +588,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>813707</v>
+        <v>846721</v>
       </c>
       <c r="C6" t="n">
-        <v>665047</v>
+        <v>690275</v>
       </c>
       <c r="D6" t="n">
-        <v>762651</v>
+        <v>794928</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.8173</v>
+        <v>0.8151999999999999</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.9373</v>
+        <v>0.9388</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>0.9745</v>
@@ -613,22 +613,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>181238</v>
+        <v>187173</v>
       </c>
       <c r="C7" t="n">
-        <v>130569</v>
+        <v>133324</v>
       </c>
       <c r="D7" t="n">
-        <v>163339</v>
+        <v>169185</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.7204</v>
+        <v>0.7123</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.9012</v>
+        <v>0.9039</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6593000000000001</v>
+        <v>0.6602</v>
       </c>
     </row>
     <row r="8">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>199812</v>
+        <v>207087</v>
       </c>
       <c r="C8" t="n">
-        <v>152407</v>
+        <v>157764</v>
       </c>
       <c r="D8" t="n">
-        <v>179259</v>
+        <v>186487</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.7628</v>
+        <v>0.7618</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.8970999999999999</v>
+        <v>0.9005</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8336</v>
+        <v>0.8297</v>
       </c>
     </row>
     <row r="9">
@@ -663,13 +663,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C9" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D9" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1</v>
@@ -688,22 +688,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>33181</v>
+        <v>34665</v>
       </c>
       <c r="C10" t="n">
-        <v>23922</v>
+        <v>25028</v>
       </c>
       <c r="D10" t="n">
-        <v>26944</v>
+        <v>28088</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.721</v>
+        <v>0.722</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8103</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9517</v>
+        <v>0.9440000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -713,19 +713,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2898</v>
+        <v>2970</v>
       </c>
       <c r="C11" t="n">
-        <v>2632</v>
+        <v>2704</v>
       </c>
       <c r="D11" t="n">
-        <v>2683</v>
+        <v>2755</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.9081999999999999</v>
+        <v>0.9104000000000001</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.9258</v>
+        <v>0.9276000000000001</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0.9965000000000001</v>
@@ -763,22 +763,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>100803</v>
+        <v>101776</v>
       </c>
       <c r="C13" t="n">
-        <v>93252</v>
+        <v>94052</v>
       </c>
       <c r="D13" t="n">
-        <v>95718</v>
+        <v>96644</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9251</v>
+        <v>0.9240999999999999</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>0.9495999999999999</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.8934000000000001</v>
+        <v>0.8914</v>
       </c>
     </row>
     <row r="14">
@@ -788,22 +788,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>99438</v>
+        <v>107804</v>
       </c>
       <c r="C14" t="n">
-        <v>66772</v>
+        <v>73575</v>
       </c>
       <c r="D14" t="n">
-        <v>79932</v>
+        <v>88071</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.6715000000000001</v>
+        <v>0.6825</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.8038</v>
+        <v>0.8170000000000001</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.8703</v>
+        <v>0.8731</v>
       </c>
     </row>
     <row r="15">
@@ -839,7 +839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H393"/>
+  <dimension ref="A1:H407"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11794,8 +11794,404 @@
       <c r="G393" s="3" t="n"/>
       <c r="H393" s="2" t="n"/>
     </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C394" t="n">
+        <v>0</v>
+      </c>
+      <c r="D394" t="n">
+        <v>0</v>
+      </c>
+      <c r="E394" t="n">
+        <v>0</v>
+      </c>
+      <c r="F394" s="2" t="n"/>
+      <c r="G394" s="3" t="n"/>
+      <c r="H394" s="2" t="n"/>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C395" t="n">
+        <v>1386</v>
+      </c>
+      <c r="D395" t="n">
+        <v>1311</v>
+      </c>
+      <c r="E395" t="n">
+        <v>1361</v>
+      </c>
+      <c r="F395" s="2" t="n">
+        <v>0.9459000000000001</v>
+      </c>
+      <c r="G395" s="3" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="H395" s="2" t="n">
+        <v>0.9223</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C396" t="n">
+        <v>15709</v>
+      </c>
+      <c r="D396" t="n">
+        <v>11053</v>
+      </c>
+      <c r="E396" t="n">
+        <v>15430</v>
+      </c>
+      <c r="F396" s="2" t="n">
+        <v>0.7036</v>
+      </c>
+      <c r="G396" s="3" t="n">
+        <v>0.9822</v>
+      </c>
+      <c r="H396" s="2" t="n">
+        <v>0.8556999999999999</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C397" t="n">
+        <v>0</v>
+      </c>
+      <c r="D397" t="n">
+        <v>0</v>
+      </c>
+      <c r="E397" t="n">
+        <v>0</v>
+      </c>
+      <c r="F397" s="2" t="n"/>
+      <c r="G397" s="3" t="n"/>
+      <c r="H397" s="2" t="n"/>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C398" t="n">
+        <v>33014</v>
+      </c>
+      <c r="D398" t="n">
+        <v>25228</v>
+      </c>
+      <c r="E398" t="n">
+        <v>32277</v>
+      </c>
+      <c r="F398" s="2" t="n">
+        <v>0.7642</v>
+      </c>
+      <c r="G398" s="3" t="n">
+        <v>0.9777</v>
+      </c>
+      <c r="H398" s="2" t="n">
+        <v>0.9767</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C399" t="n">
+        <v>5935</v>
+      </c>
+      <c r="D399" t="n">
+        <v>2755</v>
+      </c>
+      <c r="E399" t="n">
+        <v>5846</v>
+      </c>
+      <c r="F399" s="2" t="n">
+        <v>0.4642</v>
+      </c>
+      <c r="G399" s="3" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="H399" s="2" t="n">
+        <v>0.6848000000000001</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C400" t="n">
+        <v>7275</v>
+      </c>
+      <c r="D400" t="n">
+        <v>5357</v>
+      </c>
+      <c r="E400" t="n">
+        <v>7228</v>
+      </c>
+      <c r="F400" s="2" t="n">
+        <v>0.7364000000000001</v>
+      </c>
+      <c r="G400" s="3" t="n">
+        <v>0.9934999999999999</v>
+      </c>
+      <c r="H400" s="2" t="n">
+        <v>0.7134</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C401" t="n">
+        <v>8</v>
+      </c>
+      <c r="D401" t="n">
+        <v>8</v>
+      </c>
+      <c r="E401" t="n">
+        <v>8</v>
+      </c>
+      <c r="F401" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G401" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H401" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C402" t="n">
+        <v>1484</v>
+      </c>
+      <c r="D402" t="n">
+        <v>1106</v>
+      </c>
+      <c r="E402" t="n">
+        <v>1144</v>
+      </c>
+      <c r="F402" s="2" t="n">
+        <v>0.7453</v>
+      </c>
+      <c r="G402" s="3" t="n">
+        <v>0.7709</v>
+      </c>
+      <c r="H402" s="2" t="n">
+        <v>0.7920999999999999</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C403" t="n">
+        <v>72</v>
+      </c>
+      <c r="D403" t="n">
+        <v>72</v>
+      </c>
+      <c r="E403" t="n">
+        <v>72</v>
+      </c>
+      <c r="F403" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G403" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H403" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C404" t="n">
+        <v>0</v>
+      </c>
+      <c r="D404" t="n">
+        <v>0</v>
+      </c>
+      <c r="E404" t="n">
+        <v>0</v>
+      </c>
+      <c r="F404" s="2" t="n"/>
+      <c r="G404" s="3" t="n"/>
+      <c r="H404" s="2" t="n"/>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C405" t="n">
+        <v>973</v>
+      </c>
+      <c r="D405" t="n">
+        <v>800</v>
+      </c>
+      <c r="E405" t="n">
+        <v>926</v>
+      </c>
+      <c r="F405" s="2" t="n">
+        <v>0.8222</v>
+      </c>
+      <c r="G405" s="3" t="n">
+        <v>0.9517</v>
+      </c>
+      <c r="H405" s="2" t="n">
+        <v>0.8387</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C406" t="n">
+        <v>8366</v>
+      </c>
+      <c r="D406" t="n">
+        <v>6803</v>
+      </c>
+      <c r="E406" t="n">
+        <v>8139</v>
+      </c>
+      <c r="F406" s="2" t="n">
+        <v>0.8131999999999999</v>
+      </c>
+      <c r="G406" s="3" t="n">
+        <v>0.9729000000000001</v>
+      </c>
+      <c r="H406" s="2" t="n">
+        <v>0.9012</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C407" t="n">
+        <v>0</v>
+      </c>
+      <c r="D407" t="n">
+        <v>0</v>
+      </c>
+      <c r="E407" t="n">
+        <v>0</v>
+      </c>
+      <c r="F407" s="2" t="n"/>
+      <c r="G407" s="3" t="n"/>
+      <c r="H407" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H393"/>
+  <autoFilter ref="A1:H407"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -534,7 +534,7 @@
         <v>0.9091</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9243000000000001</v>
+        <v>0.9239000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -559,7 +559,7 @@
         <v>0.9127</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9167000000000001</v>
+        <v>0.9164</v>
       </c>
     </row>
     <row r="5">
@@ -628,7 +628,7 @@
         <v>0.9039</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6602</v>
+        <v>0.6605</v>
       </c>
     </row>
     <row r="8">
@@ -653,7 +653,7 @@
         <v>0.9005</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8297</v>
+        <v>0.8321999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -703,7 +703,7 @@
         <v>0.8103</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9440000000000001</v>
+        <v>0.9447</v>
       </c>
     </row>
     <row r="11">
@@ -778,7 +778,7 @@
         <v>0.9495999999999999</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.8914</v>
+        <v>0.8920999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -803,7 +803,7 @@
         <v>0.8170000000000001</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.8731</v>
+        <v>0.8712000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -11845,7 +11845,7 @@
         <v>0.982</v>
       </c>
       <c r="H395" s="2" t="n">
-        <v>0.9223</v>
+        <v>0.9104000000000001</v>
       </c>
     </row>
     <row r="396">
@@ -11875,7 +11875,7 @@
         <v>0.9822</v>
       </c>
       <c r="H396" s="2" t="n">
-        <v>0.8556999999999999</v>
+        <v>0.847</v>
       </c>
     </row>
     <row r="397">
@@ -11929,7 +11929,7 @@
         <v>0.9777</v>
       </c>
       <c r="H398" s="2" t="n">
-        <v>0.9767</v>
+        <v>0.9754</v>
       </c>
     </row>
     <row r="399">
@@ -11959,7 +11959,7 @@
         <v>0.985</v>
       </c>
       <c r="H399" s="2" t="n">
-        <v>0.6848000000000001</v>
+        <v>0.6909999999999999</v>
       </c>
     </row>
     <row r="400">
@@ -11989,7 +11989,7 @@
         <v>0.9934999999999999</v>
       </c>
       <c r="H400" s="2" t="n">
-        <v>0.7134</v>
+        <v>0.7931</v>
       </c>
     </row>
     <row r="401">
@@ -12049,7 +12049,7 @@
         <v>0.7709</v>
       </c>
       <c r="H402" s="2" t="n">
-        <v>0.7920999999999999</v>
+        <v>0.7977</v>
       </c>
     </row>
     <row r="403">
@@ -12133,7 +12133,7 @@
         <v>0.9517</v>
       </c>
       <c r="H405" s="2" t="n">
-        <v>0.8387</v>
+        <v>0.8583</v>
       </c>
     </row>
     <row r="406">
@@ -12163,7 +12163,7 @@
         <v>0.9729000000000001</v>
       </c>
       <c r="H406" s="2" t="n">
-        <v>0.9012</v>
+        <v>0.8803</v>
       </c>
     </row>
     <row r="407">

--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -528,7 +528,7 @@
         <v>0.9821</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9465</v>
+        <v>0.9712999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -553,7 +553,7 @@
         <v>0.995</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.8826999999999999</v>
+        <v>0.8951</v>
       </c>
     </row>
     <row r="5">
@@ -597,7 +597,7 @@
         <v>0.9806</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9777</v>
+        <v>0.9829000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -622,7 +622,7 @@
         <v>0.9964</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.7584000000000001</v>
+        <v>0.7619</v>
       </c>
     </row>
     <row r="8">
@@ -647,7 +647,7 @@
         <v>0.8532</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.9031999999999999</v>
+        <v>0.8903</v>
       </c>
     </row>
     <row r="9">
@@ -697,7 +697,7 @@
         <v>0.9113</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9505</v>
+        <v>0.9577</v>
       </c>
     </row>
     <row r="11">
@@ -766,7 +766,7 @@
         <v>0.9971</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.9125</v>
+        <v>0.9228000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -791,7 +791,7 @@
         <v>0.9889</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.9579000000000001</v>
+        <v>0.9556</v>
       </c>
     </row>
     <row r="15">
@@ -931,7 +931,7 @@
         <v>0.9821</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.9465</v>
+        <v>0.9712999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -961,7 +961,7 @@
         <v>0.995</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.8826999999999999</v>
+        <v>0.8951</v>
       </c>
     </row>
     <row r="5">
@@ -1015,7 +1015,7 @@
         <v>0.9806</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9777</v>
+        <v>0.9829000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -1045,7 +1045,7 @@
         <v>0.9964</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.7584000000000001</v>
+        <v>0.7619</v>
       </c>
     </row>
     <row r="8">
@@ -1075,7 +1075,7 @@
         <v>0.8532</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.9031999999999999</v>
+        <v>0.8903</v>
       </c>
     </row>
     <row r="9">
@@ -1135,7 +1135,7 @@
         <v>0.9113</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9505</v>
+        <v>0.9577</v>
       </c>
     </row>
     <row r="11">
@@ -1219,7 +1219,7 @@
         <v>0.9971</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.9125</v>
+        <v>0.9228000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1249,7 +1249,7 @@
         <v>0.9889</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.9579000000000001</v>
+        <v>0.9556</v>
       </c>
     </row>
     <row r="15">

--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -513,22 +513,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3188</v>
+        <v>5280</v>
       </c>
       <c r="C3" t="n">
-        <v>2924</v>
+        <v>4951</v>
       </c>
       <c r="D3" t="n">
-        <v>3131</v>
+        <v>5171</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9172</v>
+        <v>0.9377</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.9821</v>
+        <v>0.9793999999999999</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9712999999999999</v>
+        <v>0.9582999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -538,22 +538,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26444</v>
+        <v>52523</v>
       </c>
       <c r="C4" t="n">
-        <v>22976</v>
+        <v>44522</v>
       </c>
       <c r="D4" t="n">
-        <v>26313</v>
+        <v>50148</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.8689</v>
+        <v>0.8477</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.995</v>
+        <v>0.9548000000000001</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.8951</v>
+        <v>0.8828</v>
       </c>
     </row>
     <row r="5">
@@ -582,22 +582,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38906</v>
+        <v>81645</v>
       </c>
       <c r="C6" t="n">
-        <v>34297</v>
+        <v>71375</v>
       </c>
       <c r="D6" t="n">
-        <v>38152</v>
+        <v>76807</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.8815000000000001</v>
+        <v>0.8742</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.9806</v>
+        <v>0.9407</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9829000000000001</v>
+        <v>0.9859</v>
       </c>
     </row>
     <row r="7">
@@ -607,22 +607,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7127</v>
+        <v>14380</v>
       </c>
       <c r="C7" t="n">
-        <v>5236</v>
+        <v>10996</v>
       </c>
       <c r="D7" t="n">
-        <v>7101</v>
+        <v>13708</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.7347</v>
+        <v>0.7646999999999999</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.9964</v>
+        <v>0.9533</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.7619</v>
+        <v>0.7751</v>
       </c>
     </row>
     <row r="8">
@@ -632,22 +632,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7649</v>
+        <v>15838</v>
       </c>
       <c r="C8" t="n">
-        <v>6526</v>
+        <v>13368</v>
       </c>
       <c r="D8" t="n">
-        <v>6526</v>
+        <v>13368</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.8532</v>
+        <v>0.8440000000000001</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.8532</v>
+        <v>0.8440000000000001</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8903</v>
+        <v>0.9087999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1</v>
@@ -682,22 +682,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3980</v>
+        <v>7777</v>
       </c>
       <c r="C10" t="n">
-        <v>3438</v>
+        <v>7122</v>
       </c>
       <c r="D10" t="n">
-        <v>3627</v>
+        <v>7320</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.8637999999999999</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.9113</v>
+        <v>0.9412</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9577</v>
+        <v>0.9612000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -707,13 +707,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>573</v>
+        <v>1218</v>
       </c>
       <c r="C11" t="n">
-        <v>573</v>
+        <v>1218</v>
       </c>
       <c r="D11" t="n">
-        <v>573</v>
+        <v>1218</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1</v>
@@ -751,22 +751,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12174</v>
+        <v>17464</v>
       </c>
       <c r="C13" t="n">
-        <v>11876</v>
+        <v>17054</v>
       </c>
       <c r="D13" t="n">
-        <v>12139</v>
+        <v>17406</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9754999999999999</v>
+        <v>0.9765</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.9971</v>
+        <v>0.9967</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.9228000000000001</v>
+        <v>0.9217</v>
       </c>
     </row>
     <row r="14">
@@ -776,22 +776,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14978</v>
+        <v>27430</v>
       </c>
       <c r="C14" t="n">
-        <v>13504</v>
+        <v>25313</v>
       </c>
       <c r="D14" t="n">
-        <v>14811</v>
+        <v>26680</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9016</v>
+        <v>0.9228000000000001</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.9889</v>
+        <v>0.9727</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.9556</v>
+        <v>0.9581999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -825,7 +825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1276,8 +1276,404 @@
       <c r="G15" s="3" t="n"/>
       <c r="H15" s="2" t="n"/>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2092</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2027</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2040</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>0.9689</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>0.9751000000000001</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>0.9462</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>26079</v>
+      </c>
+      <c r="D18" t="n">
+        <v>21546</v>
+      </c>
+      <c r="E18" t="n">
+        <v>23835</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>0.8262</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>0.914</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>0.8709</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="2" t="n"/>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>42739</v>
+      </c>
+      <c r="D20" t="n">
+        <v>37078</v>
+      </c>
+      <c r="E20" t="n">
+        <v>38655</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>0.8675</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>0.9044</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>0.9887999999999999</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>7253</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5760</v>
+      </c>
+      <c r="E21" t="n">
+        <v>6607</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>0.7942</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>0.9109</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>0.7881999999999999</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>8189</v>
+      </c>
+      <c r="D22" t="n">
+        <v>6842</v>
+      </c>
+      <c r="E22" t="n">
+        <v>6842</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>0.8355</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>0.8355</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>0.9264</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>3797</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3684</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3693</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>0.9702</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>0.9726</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>0.9640000000000001</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>645</v>
+      </c>
+      <c r="D25" t="n">
+        <v>645</v>
+      </c>
+      <c r="E25" t="n">
+        <v>645</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2" t="n"/>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>5290</v>
+      </c>
+      <c r="D27" t="n">
+        <v>5178</v>
+      </c>
+      <c r="E27" t="n">
+        <v>5267</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>0.9788</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>0.9956999999999999</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>0.9207</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>12452</v>
+      </c>
+      <c r="D28" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E28" t="n">
+        <v>11869</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>0.9484</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>0.9531999999999999</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>0.9606</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2" t="n"/>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H15"/>
+  <autoFilter ref="A1:H29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -528,7 +528,7 @@
         <v>0.9793999999999999</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9582999999999999</v>
+        <v>0.9601999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -553,7 +553,7 @@
         <v>0.9548000000000001</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.8828</v>
+        <v>0.8879</v>
       </c>
     </row>
     <row r="5">
@@ -597,7 +597,7 @@
         <v>0.9407</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9859</v>
+        <v>0.9845999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -622,7 +622,7 @@
         <v>0.9533</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.7751</v>
+        <v>0.7635999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -647,7 +647,7 @@
         <v>0.8440000000000001</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.9087999999999999</v>
+        <v>0.8956000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -697,7 +697,7 @@
         <v>0.9412</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9612000000000001</v>
+        <v>0.9608</v>
       </c>
     </row>
     <row r="11">
@@ -766,7 +766,7 @@
         <v>0.9967</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.9217</v>
+        <v>0.9298000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -791,7 +791,7 @@
         <v>0.9727</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.9581999999999999</v>
+        <v>0.9565</v>
       </c>
     </row>
     <row r="15">
@@ -1327,7 +1327,7 @@
         <v>0.9751000000000001</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>0.9462</v>
+        <v>0.9506999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -1357,7 +1357,7 @@
         <v>0.914</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>0.8709</v>
+        <v>0.8811</v>
       </c>
     </row>
     <row r="19">
@@ -1411,7 +1411,7 @@
         <v>0.9044</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>0.9887999999999999</v>
+        <v>0.9863</v>
       </c>
     </row>
     <row r="21">
@@ -1441,7 +1441,7 @@
         <v>0.9109</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>0.7881999999999999</v>
+        <v>0.7655</v>
       </c>
     </row>
     <row r="22">
@@ -1471,7 +1471,7 @@
         <v>0.8355</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>0.9264</v>
+        <v>0.9006000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1531,7 +1531,7 @@
         <v>0.9726</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>0.9640000000000001</v>
+        <v>0.9634999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1615,7 +1615,7 @@
         <v>0.9956999999999999</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>0.9207</v>
+        <v>0.9356</v>
       </c>
     </row>
     <row r="28">
@@ -1645,7 +1645,7 @@
         <v>0.9531999999999999</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>0.9606</v>
+        <v>0.9573</v>
       </c>
     </row>
     <row r="29">

--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -513,22 +513,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5280</v>
+        <v>7437</v>
       </c>
       <c r="C3" t="n">
-        <v>4951</v>
+        <v>7092</v>
       </c>
       <c r="D3" t="n">
-        <v>5171</v>
+        <v>7327</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9377</v>
+        <v>0.9536</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.9793999999999999</v>
+        <v>0.9852</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9601999999999999</v>
+        <v>0.9517</v>
       </c>
     </row>
     <row r="4">
@@ -538,22 +538,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>52523</v>
+        <v>79389</v>
       </c>
       <c r="C4" t="n">
-        <v>44522</v>
+        <v>69867</v>
       </c>
       <c r="D4" t="n">
-        <v>50148</v>
+        <v>76709</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.8477</v>
+        <v>0.8801000000000001</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.9548000000000001</v>
+        <v>0.9662000000000001</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.8879</v>
+        <v>0.8912</v>
       </c>
     </row>
     <row r="5">
@@ -582,22 +582,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>81645</v>
+        <v>120689</v>
       </c>
       <c r="C6" t="n">
-        <v>71375</v>
+        <v>105434</v>
       </c>
       <c r="D6" t="n">
-        <v>76807</v>
+        <v>115732</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.8742</v>
+        <v>0.8736</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.9407</v>
+        <v>0.9589</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9845999999999999</v>
+        <v>0.9837</v>
       </c>
     </row>
     <row r="7">
@@ -607,22 +607,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14380</v>
+        <v>22703</v>
       </c>
       <c r="C7" t="n">
-        <v>10996</v>
+        <v>18081</v>
       </c>
       <c r="D7" t="n">
-        <v>13708</v>
+        <v>22022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.7646999999999999</v>
+        <v>0.7964</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.9533</v>
+        <v>0.97</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.7635999999999999</v>
+        <v>0.7426999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -632,22 +632,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15838</v>
+        <v>24104</v>
       </c>
       <c r="C8" t="n">
-        <v>13368</v>
+        <v>20704</v>
       </c>
       <c r="D8" t="n">
-        <v>13368</v>
+        <v>21598</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.8440000000000001</v>
+        <v>0.8589</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.8440000000000001</v>
+        <v>0.8959999999999999</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8956000000000001</v>
+        <v>0.8854000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -682,22 +682,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7777</v>
+        <v>11401</v>
       </c>
       <c r="C10" t="n">
-        <v>7122</v>
+        <v>10558</v>
       </c>
       <c r="D10" t="n">
-        <v>7320</v>
+        <v>10851</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9157999999999999</v>
+        <v>0.9261</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.9412</v>
+        <v>0.9518000000000001</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9608</v>
+        <v>0.9689</v>
       </c>
     </row>
     <row r="11">
@@ -707,13 +707,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1218</v>
+        <v>1453</v>
       </c>
       <c r="C11" t="n">
-        <v>1218</v>
+        <v>1453</v>
       </c>
       <c r="D11" t="n">
-        <v>1218</v>
+        <v>1453</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1</v>
@@ -751,22 +751,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17464</v>
+        <v>27258</v>
       </c>
       <c r="C13" t="n">
-        <v>17054</v>
+        <v>26668</v>
       </c>
       <c r="D13" t="n">
-        <v>17406</v>
+        <v>27197</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9765</v>
+        <v>0.9784</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.9967</v>
+        <v>0.9978</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.9298000000000001</v>
+        <v>0.9423</v>
       </c>
     </row>
     <row r="14">
@@ -776,22 +776,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>27430</v>
+        <v>37982</v>
       </c>
       <c r="C14" t="n">
-        <v>25313</v>
+        <v>35485</v>
       </c>
       <c r="D14" t="n">
-        <v>26680</v>
+        <v>37135</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9228000000000001</v>
+        <v>0.9343</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.9727</v>
+        <v>0.9777</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.9565</v>
+        <v>0.9588</v>
       </c>
     </row>
     <row r="15">
@@ -825,7 +825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1672,8 +1672,400 @@
       <c r="G29" s="3" t="n"/>
       <c r="H29" s="2" t="n"/>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>2157</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2141</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2156</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>0.9926</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>0.9995000000000001</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>0.9359999999999999</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>26866</v>
+      </c>
+      <c r="D32" t="n">
+        <v>25345</v>
+      </c>
+      <c r="E32" t="n">
+        <v>26561</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>0.9434</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>0.9886</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>0.8974</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="2" t="n"/>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>39044</v>
+      </c>
+      <c r="D34" t="n">
+        <v>34059</v>
+      </c>
+      <c r="E34" t="n">
+        <v>38925</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>0.8723000000000001</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>0.9818000000000001</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>8323</v>
+      </c>
+      <c r="D35" t="n">
+        <v>7085</v>
+      </c>
+      <c r="E35" t="n">
+        <v>8314</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>0.8512999999999999</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>0.9989</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>0.6940000000000001</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>8266</v>
+      </c>
+      <c r="D36" t="n">
+        <v>7336</v>
+      </c>
+      <c r="E36" t="n">
+        <v>8230</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>0.8875</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>0.9956</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>0.8659</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="2" t="n"/>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>3624</v>
+      </c>
+      <c r="D38" t="n">
+        <v>3436</v>
+      </c>
+      <c r="E38" t="n">
+        <v>3531</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>0.9481000000000001</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>0.9743000000000001</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>0.9808</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>235</v>
+      </c>
+      <c r="D39" t="n">
+        <v>235</v>
+      </c>
+      <c r="E39" t="n">
+        <v>235</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="2" t="n"/>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="2" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>9794</v>
+      </c>
+      <c r="D41" t="n">
+        <v>9614</v>
+      </c>
+      <c r="E41" t="n">
+        <v>9791</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>0.9815999999999999</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>0.9670000000000001</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>10552</v>
+      </c>
+      <c r="D42" t="n">
+        <v>10172</v>
+      </c>
+      <c r="E42" t="n">
+        <v>10455</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>0.9640000000000001</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>0.9908</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>0.963</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="2" t="n"/>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H29"/>
+  <autoFilter ref="A1:H43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -528,7 +528,7 @@
         <v>0.9852</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9517</v>
+        <v>0.9523</v>
       </c>
     </row>
     <row r="4">
@@ -553,7 +553,7 @@
         <v>0.9662000000000001</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.8912</v>
+        <v>0.884</v>
       </c>
     </row>
     <row r="5">
@@ -597,7 +597,7 @@
         <v>0.9589</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9837</v>
+        <v>0.982</v>
       </c>
     </row>
     <row r="7">
@@ -622,7 +622,7 @@
         <v>0.97</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.7426999999999999</v>
+        <v>0.7489</v>
       </c>
     </row>
     <row r="8">
@@ -647,7 +647,7 @@
         <v>0.8959999999999999</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8854000000000001</v>
+        <v>0.8975</v>
       </c>
     </row>
     <row r="9">
@@ -697,7 +697,7 @@
         <v>0.9518000000000001</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9689</v>
+        <v>0.9666</v>
       </c>
     </row>
     <row r="11">
@@ -766,7 +766,7 @@
         <v>0.9978</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.9423</v>
+        <v>0.9451999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -791,7 +791,7 @@
         <v>0.9777</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.9588</v>
+        <v>0.9562</v>
       </c>
     </row>
     <row r="15">
@@ -1723,7 +1723,7 @@
         <v>0.9995000000000001</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>0.9359999999999999</v>
+        <v>0.9381</v>
       </c>
     </row>
     <row r="32">
@@ -1753,7 +1753,7 @@
         <v>0.9886</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>0.8974</v>
+        <v>0.8765999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1807,7 +1807,7 @@
         <v>0.997</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>0.9818000000000001</v>
+        <v>0.9771</v>
       </c>
     </row>
     <row r="35">
@@ -1837,7 +1837,7 @@
         <v>0.9989</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>0.6940000000000001</v>
+        <v>0.7153</v>
       </c>
     </row>
     <row r="36">
@@ -1867,7 +1867,7 @@
         <v>0.9956</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>0.8659</v>
+        <v>0.9012</v>
       </c>
     </row>
     <row r="37">
@@ -1923,7 +1923,7 @@
         <v>0.9743000000000001</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>0.9808</v>
+        <v>0.9761</v>
       </c>
     </row>
     <row r="39">
@@ -2007,7 +2007,7 @@
         <v>0.9997</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>0.9670000000000001</v>
+        <v>0.9784</v>
       </c>
     </row>
     <row r="42">
@@ -2037,7 +2037,7 @@
         <v>0.9908</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>0.963</v>
+        <v>0.9556999999999999</v>
       </c>
     </row>
     <row r="43">

--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$57</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -513,22 +513,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7437</v>
+        <v>9225</v>
       </c>
       <c r="C3" t="n">
-        <v>7092</v>
+        <v>8867</v>
       </c>
       <c r="D3" t="n">
-        <v>7327</v>
+        <v>9114</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9536</v>
+        <v>0.9612000000000001</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.9852</v>
+        <v>0.988</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9523</v>
+        <v>0.9420000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -538,22 +538,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>79389</v>
+        <v>104641</v>
       </c>
       <c r="C4" t="n">
-        <v>69867</v>
+        <v>93078</v>
       </c>
       <c r="D4" t="n">
-        <v>76709</v>
+        <v>100220</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.8801000000000001</v>
+        <v>0.8895000000000001</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.9662000000000001</v>
+        <v>0.9578</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.884</v>
+        <v>0.9009</v>
       </c>
     </row>
     <row r="5">
@@ -582,22 +582,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>120689</v>
+        <v>153898</v>
       </c>
       <c r="C6" t="n">
-        <v>105434</v>
+        <v>135634</v>
       </c>
       <c r="D6" t="n">
-        <v>115732</v>
+        <v>148818</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.8736</v>
+        <v>0.8813</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.9589</v>
+        <v>0.9670000000000001</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.982</v>
+        <v>0.9782</v>
       </c>
     </row>
     <row r="7">
@@ -607,22 +607,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22703</v>
+        <v>27755</v>
       </c>
       <c r="C7" t="n">
-        <v>18081</v>
+        <v>21975</v>
       </c>
       <c r="D7" t="n">
-        <v>22022</v>
+        <v>25916</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.7964</v>
+        <v>0.7917000000000001</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.97</v>
+        <v>0.9337000000000001</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.7489</v>
+        <v>0.7062</v>
       </c>
     </row>
     <row r="8">
@@ -632,22 +632,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24104</v>
+        <v>30917</v>
       </c>
       <c r="C8" t="n">
-        <v>20704</v>
+        <v>26856</v>
       </c>
       <c r="D8" t="n">
-        <v>21598</v>
+        <v>27750</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.8589</v>
+        <v>0.8686</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.8959999999999999</v>
+        <v>0.8976000000000001</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8975</v>
+        <v>0.8928</v>
       </c>
     </row>
     <row r="9">
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1</v>
@@ -682,22 +682,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11401</v>
+        <v>15326</v>
       </c>
       <c r="C10" t="n">
-        <v>10558</v>
+        <v>14320</v>
       </c>
       <c r="D10" t="n">
-        <v>10851</v>
+        <v>14617</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9261</v>
+        <v>0.9344</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.9518000000000001</v>
+        <v>0.9537</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9666</v>
+        <v>0.9681999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -707,13 +707,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1453</v>
+        <v>1588</v>
       </c>
       <c r="C11" t="n">
-        <v>1453</v>
+        <v>1588</v>
       </c>
       <c r="D11" t="n">
-        <v>1453</v>
+        <v>1588</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1</v>
@@ -722,7 +722,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>1</v>
+        <v>0.9899</v>
       </c>
     </row>
     <row r="12">
@@ -751,22 +751,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>27258</v>
+        <v>36356</v>
       </c>
       <c r="C13" t="n">
-        <v>26668</v>
+        <v>35456</v>
       </c>
       <c r="D13" t="n">
-        <v>27197</v>
+        <v>36295</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9784</v>
+        <v>0.9752</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.9978</v>
+        <v>0.9983</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.9451999999999999</v>
+        <v>0.9490999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -776,22 +776,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>37982</v>
+        <v>47604</v>
       </c>
       <c r="C14" t="n">
-        <v>35485</v>
+        <v>44643</v>
       </c>
       <c r="D14" t="n">
-        <v>37135</v>
+        <v>46690</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9343</v>
+        <v>0.9378</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.9777</v>
+        <v>0.9808</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.9562</v>
+        <v>0.9634</v>
       </c>
     </row>
     <row r="15">
@@ -825,7 +825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2064,8 +2064,404 @@
       <c r="G43" s="3" t="n"/>
       <c r="H43" s="2" t="n"/>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="2" t="n"/>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="2" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>1788</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1775</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1787</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>0.9926999999999999</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>0.9126000000000001</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>25252</v>
+      </c>
+      <c r="D46" t="n">
+        <v>23211</v>
+      </c>
+      <c r="E46" t="n">
+        <v>23511</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>0.9192</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>0.9311</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>0.9488</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="2" t="n"/>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="2" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>33209</v>
+      </c>
+      <c r="D48" t="n">
+        <v>30200</v>
+      </c>
+      <c r="E48" t="n">
+        <v>33086</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>0.9094</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>0.9963</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>0.9667</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>5052</v>
+      </c>
+      <c r="D49" t="n">
+        <v>3894</v>
+      </c>
+      <c r="E49" t="n">
+        <v>3894</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>0.7707999999999999</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>0.7707999999999999</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>0.4691</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>6813</v>
+      </c>
+      <c r="D50" t="n">
+        <v>6152</v>
+      </c>
+      <c r="E50" t="n">
+        <v>6152</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>8</v>
+      </c>
+      <c r="D51" t="n">
+        <v>8</v>
+      </c>
+      <c r="E51" t="n">
+        <v>8</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>3925</v>
+      </c>
+      <c r="D52" t="n">
+        <v>3762</v>
+      </c>
+      <c r="E52" t="n">
+        <v>3766</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>0.9584999999999999</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>0.9595</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>0.9728</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>135</v>
+      </c>
+      <c r="D53" t="n">
+        <v>135</v>
+      </c>
+      <c r="E53" t="n">
+        <v>135</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>0.9639</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="2" t="n"/>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="2" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>9098</v>
+      </c>
+      <c r="D55" t="n">
+        <v>8788</v>
+      </c>
+      <c r="E55" t="n">
+        <v>9098</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>0.9659</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>0.9612999999999999</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>9622</v>
+      </c>
+      <c r="D56" t="n">
+        <v>9158</v>
+      </c>
+      <c r="E56" t="n">
+        <v>9555</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>0.9518000000000001</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>0.9838</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="2" t="n"/>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H43"/>
+  <autoFilter ref="A1:H57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -528,7 +528,7 @@
         <v>0.988</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9420000000000001</v>
+        <v>0.9571</v>
       </c>
     </row>
     <row r="4">
@@ -553,7 +553,7 @@
         <v>0.9578</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9009</v>
+        <v>0.9009999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -597,7 +597,7 @@
         <v>0.9670000000000001</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9782</v>
+        <v>0.981</v>
       </c>
     </row>
     <row r="7">
@@ -622,7 +622,7 @@
         <v>0.9337000000000001</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.7062</v>
+        <v>0.7251000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -647,7 +647,7 @@
         <v>0.8976000000000001</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8928</v>
+        <v>0.9045000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -697,7 +697,7 @@
         <v>0.9537</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9681999999999999</v>
+        <v>0.9677</v>
       </c>
     </row>
     <row r="11">
@@ -722,7 +722,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.9899</v>
+        <v>0.9931</v>
       </c>
     </row>
     <row r="12">
@@ -766,7 +766,7 @@
         <v>0.9983</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.9490999999999999</v>
+        <v>0.9527</v>
       </c>
     </row>
     <row r="14">
@@ -791,7 +791,7 @@
         <v>0.9808</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.9634</v>
+        <v>0.9609000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -811,7 +811,9 @@
       </c>
       <c r="E15" s="2" t="n"/>
       <c r="F15" s="3" t="n"/>
-      <c r="G15" s="2" t="n"/>
+      <c r="G15" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G15"/>
@@ -2115,7 +2117,7 @@
         <v>0.9994</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>0.9126000000000001</v>
+        <v>0.9706999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -2145,7 +2147,7 @@
         <v>0.9311</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>0.9488</v>
+        <v>0.9501999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -2199,7 +2201,7 @@
         <v>0.9963</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>0.9667</v>
+        <v>0.9781</v>
       </c>
     </row>
     <row r="49">
@@ -2229,7 +2231,7 @@
         <v>0.7707999999999999</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>0.4691</v>
+        <v>0.5556</v>
       </c>
     </row>
     <row r="50">
@@ -2259,7 +2261,7 @@
         <v>0.903</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>0.88</v>
+        <v>0.9255</v>
       </c>
     </row>
     <row r="51">
@@ -2319,7 +2321,7 @@
         <v>0.9595</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>0.9728</v>
+        <v>0.9706999999999999</v>
       </c>
     </row>
     <row r="53">
@@ -2349,7 +2351,7 @@
         <v>1</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>0.9639</v>
+        <v>0.9732999999999999</v>
       </c>
     </row>
     <row r="54">
@@ -2403,7 +2405,7 @@
         <v>1</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>0.9612999999999999</v>
+        <v>0.9773999999999999</v>
       </c>
     </row>
     <row r="56">
@@ -2433,7 +2435,7 @@
         <v>0.993</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>0.9838</v>
+        <v>0.9756</v>
       </c>
     </row>
     <row r="57">
@@ -2458,7 +2460,9 @@
       </c>
       <c r="F57" s="2" t="n"/>
       <c r="G57" s="3" t="n"/>
-      <c r="H57" s="2" t="n"/>
+      <c r="H57" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H57"/>

--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$71</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -513,22 +513,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9225</v>
+        <v>10913</v>
       </c>
       <c r="C3" t="n">
-        <v>8867</v>
+        <v>10346</v>
       </c>
       <c r="D3" t="n">
-        <v>9114</v>
+        <v>10719</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9612000000000001</v>
+        <v>0.948</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.988</v>
+        <v>0.9822</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9571</v>
+        <v>0.9543</v>
       </c>
     </row>
     <row r="4">
@@ -538,22 +538,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>104641</v>
+        <v>124647</v>
       </c>
       <c r="C4" t="n">
-        <v>93078</v>
+        <v>110397</v>
       </c>
       <c r="D4" t="n">
-        <v>100220</v>
+        <v>118347</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.8895000000000001</v>
+        <v>0.8856999999999999</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.9578</v>
+        <v>0.9495</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9009999999999999</v>
+        <v>0.912</v>
       </c>
     </row>
     <row r="5">
@@ -582,22 +582,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>153898</v>
+        <v>184189</v>
       </c>
       <c r="C6" t="n">
-        <v>135634</v>
+        <v>160722</v>
       </c>
       <c r="D6" t="n">
-        <v>148818</v>
+        <v>174739</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.8813</v>
+        <v>0.8726</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.9670000000000001</v>
+        <v>0.9487000000000001</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.981</v>
+        <v>0.9795999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -607,22 +607,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27755</v>
+        <v>33090</v>
       </c>
       <c r="C7" t="n">
-        <v>21975</v>
+        <v>23577</v>
       </c>
       <c r="D7" t="n">
-        <v>25916</v>
+        <v>31110</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.7917000000000001</v>
+        <v>0.7125</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.9337000000000001</v>
+        <v>0.9401999999999999</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.7251000000000001</v>
+        <v>0.6997</v>
       </c>
     </row>
     <row r="8">
@@ -632,22 +632,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30917</v>
+        <v>38207</v>
       </c>
       <c r="C8" t="n">
-        <v>26856</v>
+        <v>32755</v>
       </c>
       <c r="D8" t="n">
-        <v>27750</v>
+        <v>33649</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.8686</v>
+        <v>0.8573000000000001</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.8976000000000001</v>
+        <v>0.8806999999999999</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.9045000000000001</v>
+        <v>0.9016</v>
       </c>
     </row>
     <row r="9">
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1</v>
@@ -682,22 +682,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15326</v>
+        <v>18795</v>
       </c>
       <c r="C10" t="n">
-        <v>14320</v>
+        <v>17310</v>
       </c>
       <c r="D10" t="n">
-        <v>14617</v>
+        <v>17640</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9344</v>
+        <v>0.9209999999999999</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.9537</v>
+        <v>0.9384999999999999</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9677</v>
+        <v>0.9693000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -707,13 +707,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1588</v>
+        <v>1683</v>
       </c>
       <c r="C11" t="n">
-        <v>1588</v>
+        <v>1683</v>
       </c>
       <c r="D11" t="n">
-        <v>1588</v>
+        <v>1683</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1</v>
@@ -722,7 +722,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.9931</v>
+        <v>0.9947</v>
       </c>
     </row>
     <row r="12">
@@ -751,22 +751,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>36356</v>
+        <v>46073</v>
       </c>
       <c r="C13" t="n">
-        <v>35456</v>
+        <v>44451</v>
       </c>
       <c r="D13" t="n">
-        <v>36295</v>
+        <v>45968</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9752</v>
+        <v>0.9648</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.9983</v>
+        <v>0.9976999999999999</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.9527</v>
+        <v>0.9581999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -776,22 +776,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>47604</v>
+        <v>57295</v>
       </c>
       <c r="C14" t="n">
-        <v>44643</v>
+        <v>52921</v>
       </c>
       <c r="D14" t="n">
-        <v>46690</v>
+        <v>55395</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9378</v>
+        <v>0.9237000000000001</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.9808</v>
+        <v>0.9668000000000001</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.9609000000000001</v>
+        <v>0.9637</v>
       </c>
     </row>
     <row r="15">
@@ -827,7 +827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2464,8 +2464,406 @@
         <v>0</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="2" t="n"/>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="2" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>1688</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1479</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1605</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>0.8762000000000001</v>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>0.9508</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>0.9439</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>20006</v>
+      </c>
+      <c r="D60" t="n">
+        <v>17319</v>
+      </c>
+      <c r="E60" t="n">
+        <v>18127</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>0.8656999999999999</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>0.9061</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>0.9593</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="2" t="n"/>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="2" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>30291</v>
+      </c>
+      <c r="D62" t="n">
+        <v>25088</v>
+      </c>
+      <c r="E62" t="n">
+        <v>25921</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>0.8281999999999999</v>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>0.8556999999999999</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>0.9738</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>5335</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1602</v>
+      </c>
+      <c r="E63" t="n">
+        <v>5194</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>0.3003</v>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>0.9736</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>0.4921</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>7290</v>
+      </c>
+      <c r="D64" t="n">
+        <v>5899</v>
+      </c>
+      <c r="E64" t="n">
+        <v>5899</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>0.8092</v>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>0.8092</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>0.8902</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>6</v>
+      </c>
+      <c r="D65" t="n">
+        <v>6</v>
+      </c>
+      <c r="E65" t="n">
+        <v>6</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>3469</v>
+      </c>
+      <c r="D66" t="n">
+        <v>2990</v>
+      </c>
+      <c r="E66" t="n">
+        <v>3023</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>0.8619</v>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>0.8714</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>0.9753000000000001</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>95</v>
+      </c>
+      <c r="D67" t="n">
+        <v>95</v>
+      </c>
+      <c r="E67" t="n">
+        <v>95</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="2" t="n"/>
+      <c r="G68" s="3" t="n"/>
+      <c r="H68" s="2" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>9717</v>
+      </c>
+      <c r="D69" t="n">
+        <v>8995</v>
+      </c>
+      <c r="E69" t="n">
+        <v>9673</v>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>0.9257</v>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>0.9954999999999999</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>0.9815</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>9691</v>
+      </c>
+      <c r="D70" t="n">
+        <v>8278</v>
+      </c>
+      <c r="E70" t="n">
+        <v>8705</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>0.8542000000000001</v>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>0.8983</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>0.9743000000000001</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="2" t="n"/>
+      <c r="G71" s="3" t="n"/>
+      <c r="H71" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H57"/>
+  <autoFilter ref="A1:H71"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -528,7 +528,7 @@
         <v>0.9822</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9543</v>
+        <v>0.9556999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -553,7 +553,7 @@
         <v>0.9495</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.912</v>
+        <v>0.9097</v>
       </c>
     </row>
     <row r="5">
@@ -597,7 +597,7 @@
         <v>0.9487000000000001</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9795999999999999</v>
+        <v>0.9802</v>
       </c>
     </row>
     <row r="7">
@@ -622,7 +622,7 @@
         <v>0.9401999999999999</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6997</v>
+        <v>0.7039</v>
       </c>
     </row>
     <row r="8">
@@ -647,7 +647,7 @@
         <v>0.8806999999999999</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.9016</v>
+        <v>0.9026000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -697,7 +697,7 @@
         <v>0.9384999999999999</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9693000000000001</v>
+        <v>0.9712999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -722,7 +722,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.9947</v>
+        <v>0.9812000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -766,7 +766,7 @@
         <v>0.9976999999999999</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.9581999999999999</v>
+        <v>0.9570000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -791,7 +791,7 @@
         <v>0.9668000000000001</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.9637</v>
+        <v>0.9643999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -2515,7 +2515,7 @@
         <v>0.9508</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>0.9439</v>
+        <v>0.9505</v>
       </c>
     </row>
     <row r="60">
@@ -2545,7 +2545,7 @@
         <v>0.9061</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>0.9593</v>
+        <v>0.9440999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -2599,7 +2599,7 @@
         <v>0.8556999999999999</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>0.9738</v>
+        <v>0.9771</v>
       </c>
     </row>
     <row r="63">
@@ -2629,7 +2629,7 @@
         <v>0.9736</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>0.4921</v>
+        <v>0.4902</v>
       </c>
     </row>
     <row r="64">
@@ -2659,7 +2659,7 @@
         <v>0.8092</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>0.8902</v>
+        <v>0.8951</v>
       </c>
     </row>
     <row r="65">
@@ -2719,7 +2719,7 @@
         <v>0.8714</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>0.9753000000000001</v>
+        <v>0.9845</v>
       </c>
     </row>
     <row r="67">
@@ -2749,7 +2749,7 @@
         <v>1</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>1</v>
+        <v>0.9412</v>
       </c>
     </row>
     <row r="68">
@@ -2803,7 +2803,7 @@
         <v>0.9954999999999999</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>0.9815</v>
+        <v>0.9745</v>
       </c>
     </row>
     <row r="70">
@@ -2833,7 +2833,7 @@
         <v>0.8983</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>0.9743000000000001</v>
+        <v>0.9773000000000001</v>
       </c>
     </row>
     <row r="71">

--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -513,22 +513,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10913</v>
+        <v>12809</v>
       </c>
       <c r="C3" t="n">
-        <v>10346</v>
+        <v>10684</v>
       </c>
       <c r="D3" t="n">
-        <v>10719</v>
+        <v>11057</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.948</v>
+        <v>0.8341</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.9822</v>
+        <v>0.8632</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9556999999999999</v>
+        <v>0.9564</v>
       </c>
     </row>
     <row r="4">
@@ -538,22 +538,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>124647</v>
+        <v>141321</v>
       </c>
       <c r="C4" t="n">
-        <v>110397</v>
+        <v>114834</v>
       </c>
       <c r="D4" t="n">
-        <v>118347</v>
+        <v>122784</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.8856999999999999</v>
+        <v>0.8126000000000001</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.9495</v>
+        <v>0.8687999999999999</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9097</v>
+        <v>0.9148999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -582,22 +582,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>184189</v>
+        <v>216182</v>
       </c>
       <c r="C6" t="n">
-        <v>160722</v>
+        <v>176481</v>
       </c>
       <c r="D6" t="n">
-        <v>174739</v>
+        <v>190498</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.8726</v>
+        <v>0.8164</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.9487000000000001</v>
+        <v>0.8812000000000001</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9802</v>
+        <v>0.9784999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -607,22 +607,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33090</v>
+        <v>38032</v>
       </c>
       <c r="C7" t="n">
-        <v>23577</v>
+        <v>23981</v>
       </c>
       <c r="D7" t="n">
-        <v>31110</v>
+        <v>31514</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.7125</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.9401999999999999</v>
+        <v>0.8286</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.7039</v>
+        <v>0.6995</v>
       </c>
     </row>
     <row r="8">
@@ -632,22 +632,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>38207</v>
+        <v>45623</v>
       </c>
       <c r="C8" t="n">
-        <v>32755</v>
+        <v>34752</v>
       </c>
       <c r="D8" t="n">
-        <v>33649</v>
+        <v>35646</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.8573000000000001</v>
+        <v>0.7617</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.8806999999999999</v>
+        <v>0.7813</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.9026000000000001</v>
+        <v>0.9037999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -682,22 +682,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18795</v>
+        <v>21674</v>
       </c>
       <c r="C10" t="n">
-        <v>17310</v>
+        <v>18020</v>
       </c>
       <c r="D10" t="n">
-        <v>17640</v>
+        <v>18350</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9209999999999999</v>
+        <v>0.8314</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.9384999999999999</v>
+        <v>0.8466</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9712999999999999</v>
+        <v>0.9723999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -707,13 +707,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="C11" t="n">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="D11" t="n">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1</v>
@@ -722,7 +722,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.9812000000000001</v>
+        <v>0.9792000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -751,22 +751,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>46073</v>
+        <v>51435</v>
       </c>
       <c r="C13" t="n">
-        <v>44451</v>
+        <v>44941</v>
       </c>
       <c r="D13" t="n">
-        <v>45968</v>
+        <v>46458</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9648</v>
+        <v>0.8737</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.9976999999999999</v>
+        <v>0.9031999999999999</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.9570000000000001</v>
+        <v>0.9579000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -776,22 +776,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>57295</v>
+        <v>66868</v>
       </c>
       <c r="C14" t="n">
-        <v>52921</v>
+        <v>54927</v>
       </c>
       <c r="D14" t="n">
-        <v>55395</v>
+        <v>57401</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9237000000000001</v>
+        <v>0.8214</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.9668000000000001</v>
+        <v>0.8584000000000001</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.9643999999999999</v>
+        <v>0.9645</v>
       </c>
     </row>
     <row r="15">
@@ -827,7 +827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2862,8 +2862,402 @@
         <v>0</v>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="2" t="n"/>
+      <c r="G72" s="3" t="n"/>
+      <c r="H72" s="2" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>1896</v>
+      </c>
+      <c r="D73" t="n">
+        <v>338</v>
+      </c>
+      <c r="E73" t="n">
+        <v>338</v>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>0.1783</v>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>0.1783</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>16674</v>
+      </c>
+      <c r="D74" t="n">
+        <v>4437</v>
+      </c>
+      <c r="E74" t="n">
+        <v>4437</v>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>0.2661</v>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>0.2661</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>0.9447</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="2" t="n"/>
+      <c r="G75" s="3" t="n"/>
+      <c r="H75" s="2" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>31993</v>
+      </c>
+      <c r="D76" t="n">
+        <v>15759</v>
+      </c>
+      <c r="E76" t="n">
+        <v>15759</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>0.4926</v>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v>0.4926</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>0.9692000000000001</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>4942</v>
+      </c>
+      <c r="D77" t="n">
+        <v>404</v>
+      </c>
+      <c r="E77" t="n">
+        <v>404</v>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>0.08169999999999999</v>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>0.08169999999999999</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>0.6545000000000001</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>7416</v>
+      </c>
+      <c r="D78" t="n">
+        <v>1997</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1997</v>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>0.2693</v>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>0.2693</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>0.9103</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="2" t="n"/>
+      <c r="G79" s="3" t="n"/>
+      <c r="H79" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>2879</v>
+      </c>
+      <c r="D80" t="n">
+        <v>710</v>
+      </c>
+      <c r="E80" t="n">
+        <v>710</v>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>0.2466</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>0.2466</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>0.9795</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>0.9667</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="2" t="n"/>
+      <c r="G82" s="3" t="n"/>
+      <c r="H82" s="2" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>5362</v>
+      </c>
+      <c r="D83" t="n">
+        <v>490</v>
+      </c>
+      <c r="E83" t="n">
+        <v>490</v>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>0.963</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>9573</v>
+      </c>
+      <c r="D84" t="n">
+        <v>2006</v>
+      </c>
+      <c r="E84" t="n">
+        <v>2006</v>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>0.2095</v>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>0.2095</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>0.9651999999999999</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="2" t="n"/>
+      <c r="G85" s="3" t="n"/>
+      <c r="H85" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H71"/>
+  <autoFilter ref="A1:H85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -528,7 +528,7 @@
         <v>0.8632</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9564</v>
+        <v>0.9543</v>
       </c>
     </row>
     <row r="4">
@@ -553,7 +553,7 @@
         <v>0.8687999999999999</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9148999999999999</v>
+        <v>0.915</v>
       </c>
     </row>
     <row r="5">
@@ -597,7 +597,7 @@
         <v>0.8812000000000001</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9784999999999999</v>
+        <v>0.9804999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -622,7 +622,7 @@
         <v>0.8286</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6995</v>
+        <v>0.6990000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -647,7 +647,7 @@
         <v>0.7813</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.9037999999999999</v>
+        <v>0.9006000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -697,7 +697,7 @@
         <v>0.8466</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9723999999999999</v>
+        <v>0.9739</v>
       </c>
     </row>
     <row r="11">
@@ -722,7 +722,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.9792000000000001</v>
+        <v>0.9741</v>
       </c>
     </row>
     <row r="12">
@@ -766,7 +766,7 @@
         <v>0.9031999999999999</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.9579000000000001</v>
+        <v>0.9543</v>
       </c>
     </row>
     <row r="14">
@@ -791,7 +791,7 @@
         <v>0.8584000000000001</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.9645</v>
+        <v>0.9653</v>
       </c>
     </row>
     <row r="15">
@@ -2913,7 +2913,7 @@
         <v>0.1783</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>0.96</v>
+        <v>0.9465</v>
       </c>
     </row>
     <row r="74">
@@ -2943,7 +2943,7 @@
         <v>0.2661</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>0.9447</v>
+        <v>0.9456</v>
       </c>
     </row>
     <row r="75">
@@ -2997,7 +2997,7 @@
         <v>0.4926</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>0.9692000000000001</v>
+        <v>0.9818000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -3027,7 +3027,7 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>0.6545000000000001</v>
+        <v>0.6175999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -3057,7 +3057,7 @@
         <v>0.2693</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>0.9103</v>
+        <v>0.8909</v>
       </c>
     </row>
     <row r="79">
@@ -3113,7 +3113,7 @@
         <v>0.2466</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>0.9795</v>
+        <v>0.9892</v>
       </c>
     </row>
     <row r="81">
@@ -3143,7 +3143,7 @@
         <v>1</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>0.9667</v>
+        <v>0.9231</v>
       </c>
     </row>
     <row r="82">
@@ -3197,7 +3197,7 @@
         <v>0.09140000000000001</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>0.963</v>
+        <v>0.9390000000000001</v>
       </c>
     </row>
     <row r="84">
@@ -3227,7 +3227,7 @@
         <v>0.2095</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>0.9651999999999999</v>
+        <v>0.9704999999999999</v>
       </c>
     </row>
     <row r="85">
@@ -3252,9 +3252,7 @@
       </c>
       <c r="F85" s="2" t="n"/>
       <c r="G85" s="3" t="n"/>
-      <c r="H85" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="H85" s="2" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H85"/>

--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -513,22 +513,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12809</v>
+        <v>15215</v>
       </c>
       <c r="C3" t="n">
-        <v>10684</v>
+        <v>11258</v>
       </c>
       <c r="D3" t="n">
-        <v>11057</v>
+        <v>11631</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.8341</v>
+        <v>0.7399</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.8632</v>
+        <v>0.7644</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9543</v>
+        <v>0.9516</v>
       </c>
     </row>
     <row r="4">
@@ -538,22 +538,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>141321</v>
+        <v>155530</v>
       </c>
       <c r="C4" t="n">
-        <v>114834</v>
+        <v>116254</v>
       </c>
       <c r="D4" t="n">
-        <v>122784</v>
+        <v>124204</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.8126000000000001</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.8687999999999999</v>
+        <v>0.7986</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.915</v>
+        <v>0.9131</v>
       </c>
     </row>
     <row r="5">
@@ -582,22 +582,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>216182</v>
+        <v>253223</v>
       </c>
       <c r="C6" t="n">
-        <v>176481</v>
+        <v>197287</v>
       </c>
       <c r="D6" t="n">
-        <v>190498</v>
+        <v>211304</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.8164</v>
+        <v>0.7791</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.8812000000000001</v>
+        <v>0.8345</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9804999999999999</v>
+        <v>0.9758</v>
       </c>
     </row>
     <row r="7">
@@ -607,22 +607,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>38032</v>
+        <v>43772</v>
       </c>
       <c r="C7" t="n">
-        <v>23981</v>
+        <v>24695</v>
       </c>
       <c r="D7" t="n">
-        <v>31514</v>
+        <v>32228</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.6304999999999999</v>
+        <v>0.5642</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.8286</v>
+        <v>0.7363</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6990000000000001</v>
+        <v>0.6884999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -632,22 +632,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>45623</v>
+        <v>52217</v>
       </c>
       <c r="C8" t="n">
-        <v>34752</v>
+        <v>35382</v>
       </c>
       <c r="D8" t="n">
-        <v>35646</v>
+        <v>36276</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.7617</v>
+        <v>0.6776000000000001</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.7813</v>
+        <v>0.6947</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.9006000000000001</v>
+        <v>0.8970999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -682,22 +682,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21674</v>
+        <v>26665</v>
       </c>
       <c r="C10" t="n">
-        <v>18020</v>
+        <v>19245</v>
       </c>
       <c r="D10" t="n">
-        <v>18350</v>
+        <v>19575</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.8314</v>
+        <v>0.7217</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.8466</v>
+        <v>0.7341</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9739</v>
+        <v>0.9718000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -722,7 +722,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.9741</v>
+        <v>0.9762000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -751,22 +751,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>51435</v>
+        <v>59137</v>
       </c>
       <c r="C13" t="n">
-        <v>44941</v>
+        <v>48647</v>
       </c>
       <c r="D13" t="n">
-        <v>46458</v>
+        <v>50164</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.8737</v>
+        <v>0.8226</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.9031999999999999</v>
+        <v>0.8482999999999999</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.9543</v>
+        <v>0.9523</v>
       </c>
     </row>
     <row r="14">
@@ -776,22 +776,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>66868</v>
+        <v>76107</v>
       </c>
       <c r="C14" t="n">
-        <v>54927</v>
+        <v>55437</v>
       </c>
       <c r="D14" t="n">
-        <v>57401</v>
+        <v>57911</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.8214</v>
+        <v>0.7284</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.8584000000000001</v>
+        <v>0.7609</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.9653</v>
+        <v>0.9640000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -827,7 +827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H85"/>
+  <dimension ref="A1:H99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3254,8 +3254,396 @@
       <c r="G85" s="3" t="n"/>
       <c r="H85" s="2" t="n"/>
     </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="2" t="n"/>
+      <c r="G86" s="3" t="n"/>
+      <c r="H86" s="2" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>2406</v>
+      </c>
+      <c r="D87" t="n">
+        <v>574</v>
+      </c>
+      <c r="E87" t="n">
+        <v>574</v>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>0.2386</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>0.2386</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>0.9317</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>14209</v>
+      </c>
+      <c r="D88" t="n">
+        <v>1420</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1420</v>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>0.0999</v>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>0.0999</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>0.8976999999999999</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="2" t="n"/>
+      <c r="G89" s="3" t="n"/>
+      <c r="H89" s="2" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>37041</v>
+      </c>
+      <c r="D90" t="n">
+        <v>20806</v>
+      </c>
+      <c r="E90" t="n">
+        <v>20806</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>0.5617</v>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>0.5617</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>0.9409000000000001</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>5740</v>
+      </c>
+      <c r="D91" t="n">
+        <v>714</v>
+      </c>
+      <c r="E91" t="n">
+        <v>714</v>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>0.1244</v>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>0.1244</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>0.5455</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>6594</v>
+      </c>
+      <c r="D92" t="n">
+        <v>630</v>
+      </c>
+      <c r="E92" t="n">
+        <v>630</v>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>0.0955</v>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>0.0955</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="2" t="n"/>
+      <c r="G93" s="3" t="n"/>
+      <c r="H93" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>4991</v>
+      </c>
+      <c r="D94" t="n">
+        <v>1225</v>
+      </c>
+      <c r="E94" t="n">
+        <v>1225</v>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>0.2454</v>
+      </c>
+      <c r="G94" s="3" t="n">
+        <v>0.2454</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>0.9529000000000001</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="2" t="n"/>
+      <c r="G95" s="3" t="n"/>
+      <c r="H95" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="2" t="n"/>
+      <c r="G96" s="3" t="n"/>
+      <c r="H96" s="2" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>7702</v>
+      </c>
+      <c r="D97" t="n">
+        <v>3706</v>
+      </c>
+      <c r="E97" t="n">
+        <v>3706</v>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>0.4812</v>
+      </c>
+      <c r="G97" s="3" t="n">
+        <v>0.4812</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>0.9308</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>9239</v>
+      </c>
+      <c r="D98" t="n">
+        <v>510</v>
+      </c>
+      <c r="E98" t="n">
+        <v>510</v>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>0.0552</v>
+      </c>
+      <c r="G98" s="3" t="n">
+        <v>0.0552</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>0.9521999999999999</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="2" t="n"/>
+      <c r="G99" s="3" t="n"/>
+      <c r="H99" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H85"/>
+  <autoFilter ref="A1:H99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -528,7 +528,7 @@
         <v>0.7644</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9516</v>
+        <v>0.9543</v>
       </c>
     </row>
     <row r="4">
@@ -553,7 +553,7 @@
         <v>0.7986</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9131</v>
+        <v>0.9125</v>
       </c>
     </row>
     <row r="5">
@@ -597,7 +597,7 @@
         <v>0.8345</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9758</v>
+        <v>0.9743000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -622,7 +622,7 @@
         <v>0.7363</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6884999999999999</v>
+        <v>0.6949</v>
       </c>
     </row>
     <row r="8">
@@ -647,7 +647,7 @@
         <v>0.6947</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8970999999999999</v>
+        <v>0.9009</v>
       </c>
     </row>
     <row r="9">
@@ -697,7 +697,7 @@
         <v>0.7341</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9718000000000001</v>
+        <v>0.973</v>
       </c>
     </row>
     <row r="11">
@@ -722,7 +722,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.9762000000000001</v>
+        <v>0.9765999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -766,7 +766,7 @@
         <v>0.8482999999999999</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.9523</v>
+        <v>0.9525</v>
       </c>
     </row>
     <row r="14">
@@ -791,7 +791,7 @@
         <v>0.7609</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.9640000000000001</v>
+        <v>0.9651000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -3305,7 +3305,7 @@
         <v>0.2386</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>0.9317</v>
+        <v>0.9548000000000001</v>
       </c>
     </row>
     <row r="88">
@@ -3335,7 +3335,7 @@
         <v>0.0999</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>0.8976999999999999</v>
+        <v>0.8944</v>
       </c>
     </row>
     <row r="89">
@@ -3389,7 +3389,7 @@
         <v>0.5617</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>0.9409000000000001</v>
+        <v>0.9286</v>
       </c>
     </row>
     <row r="91">
@@ -3419,7 +3419,7 @@
         <v>0.1244</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>0.5455</v>
+        <v>0.6071</v>
       </c>
     </row>
     <row r="92">
@@ -3449,7 +3449,7 @@
         <v>0.0955</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>0.875</v>
+        <v>0.903</v>
       </c>
     </row>
     <row r="93">
@@ -3505,7 +3505,7 @@
         <v>0.2454</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>0.9529000000000001</v>
+        <v>0.9648</v>
       </c>
     </row>
     <row r="95">
@@ -3585,7 +3585,7 @@
         <v>0.4812</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>0.9308</v>
+        <v>0.9349</v>
       </c>
     </row>
     <row r="98">
@@ -3615,7 +3615,7 @@
         <v>0.0552</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>0.9521999999999999</v>
+        <v>0.9631000000000001</v>
       </c>
     </row>
     <row r="99">

--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$113</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -513,22 +513,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15215</v>
+        <v>18571</v>
       </c>
       <c r="C3" t="n">
-        <v>11258</v>
+        <v>13580</v>
       </c>
       <c r="D3" t="n">
-        <v>11631</v>
+        <v>14490</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.7399</v>
+        <v>0.7312000000000001</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.7644</v>
+        <v>0.7802</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9543</v>
+        <v>0.9415</v>
       </c>
     </row>
     <row r="4">
@@ -538,22 +538,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>155530</v>
+        <v>181120</v>
       </c>
       <c r="C4" t="n">
-        <v>116254</v>
+        <v>133121</v>
       </c>
       <c r="D4" t="n">
-        <v>124204</v>
+        <v>148407</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.735</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.7986</v>
+        <v>0.8194</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9125</v>
+        <v>0.9117000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -582,22 +582,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>253223</v>
+        <v>294885</v>
       </c>
       <c r="C6" t="n">
-        <v>197287</v>
+        <v>224107</v>
       </c>
       <c r="D6" t="n">
-        <v>211304</v>
+        <v>243757</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.7791</v>
+        <v>0.76</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.8345</v>
+        <v>0.8266</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9743000000000001</v>
+        <v>0.9745</v>
       </c>
     </row>
     <row r="7">
@@ -607,22 +607,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>43772</v>
+        <v>50634</v>
       </c>
       <c r="C7" t="n">
-        <v>24695</v>
+        <v>26003</v>
       </c>
       <c r="D7" t="n">
-        <v>32228</v>
+        <v>39071</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.5642</v>
+        <v>0.5135000000000001</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7363</v>
+        <v>0.7716</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6949</v>
+        <v>0.6923</v>
       </c>
     </row>
     <row r="8">
@@ -632,22 +632,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>52217</v>
+        <v>60654</v>
       </c>
       <c r="C8" t="n">
-        <v>35382</v>
+        <v>39117</v>
       </c>
       <c r="D8" t="n">
-        <v>36276</v>
+        <v>40011</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.6776000000000001</v>
+        <v>0.6448999999999999</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.6947</v>
+        <v>0.6597</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.9009</v>
+        <v>0.8981</v>
       </c>
     </row>
     <row r="9">
@@ -682,22 +682,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>26665</v>
+        <v>31704</v>
       </c>
       <c r="C10" t="n">
-        <v>19245</v>
+        <v>23288</v>
       </c>
       <c r="D10" t="n">
-        <v>19575</v>
+        <v>23792</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.7217</v>
+        <v>0.7345</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.7341</v>
+        <v>0.7504000000000001</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.973</v>
+        <v>0.9721</v>
       </c>
     </row>
     <row r="11">
@@ -707,13 +707,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1684</v>
+        <v>1852</v>
       </c>
       <c r="C11" t="n">
-        <v>1684</v>
+        <v>1852</v>
       </c>
       <c r="D11" t="n">
-        <v>1684</v>
+        <v>1852</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1</v>
@@ -722,7 +722,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.9765999999999999</v>
+        <v>0.9777</v>
       </c>
     </row>
     <row r="12">
@@ -751,22 +751,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>59137</v>
+        <v>68843</v>
       </c>
       <c r="C13" t="n">
-        <v>48647</v>
+        <v>50653</v>
       </c>
       <c r="D13" t="n">
-        <v>50164</v>
+        <v>59548</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.8226</v>
+        <v>0.7358</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.8482999999999999</v>
+        <v>0.865</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.9525</v>
+        <v>0.9473</v>
       </c>
     </row>
     <row r="14">
@@ -776,22 +776,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>76107</v>
+        <v>91102</v>
       </c>
       <c r="C14" t="n">
-        <v>55437</v>
+        <v>66607</v>
       </c>
       <c r="D14" t="n">
-        <v>57911</v>
+        <v>72620</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.7284</v>
+        <v>0.7311</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.7609</v>
+        <v>0.7970999999999999</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.9651000000000001</v>
+        <v>0.9617</v>
       </c>
     </row>
     <row r="15">
@@ -827,7 +827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H99"/>
+  <dimension ref="A1:H113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3642,8 +3642,400 @@
       <c r="G99" s="3" t="n"/>
       <c r="H99" s="2" t="n"/>
     </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="2" t="n"/>
+      <c r="G100" s="3" t="n"/>
+      <c r="H100" s="2" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>3356</v>
+      </c>
+      <c r="D101" t="n">
+        <v>2322</v>
+      </c>
+      <c r="E101" t="n">
+        <v>2859</v>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>0.6919</v>
+      </c>
+      <c r="G101" s="3" t="n">
+        <v>0.8519</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>0.8401999999999999</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>25590</v>
+      </c>
+      <c r="D102" t="n">
+        <v>16867</v>
+      </c>
+      <c r="E102" t="n">
+        <v>24203</v>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>0.6591</v>
+      </c>
+      <c r="G102" s="3" t="n">
+        <v>0.9458</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>0.904</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="2" t="n"/>
+      <c r="G103" s="3" t="n"/>
+      <c r="H103" s="2" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>41662</v>
+      </c>
+      <c r="D104" t="n">
+        <v>26820</v>
+      </c>
+      <c r="E104" t="n">
+        <v>32453</v>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>0.6437999999999999</v>
+      </c>
+      <c r="G104" s="3" t="n">
+        <v>0.779</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>0.9759</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>6862</v>
+      </c>
+      <c r="D105" t="n">
+        <v>1308</v>
+      </c>
+      <c r="E105" t="n">
+        <v>6843</v>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>0.1906</v>
+      </c>
+      <c r="G105" s="3" t="n">
+        <v>0.9972</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>8437</v>
+      </c>
+      <c r="D106" t="n">
+        <v>3735</v>
+      </c>
+      <c r="E106" t="n">
+        <v>3735</v>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>0.4427</v>
+      </c>
+      <c r="G106" s="3" t="n">
+        <v>0.4427</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="2" t="n"/>
+      <c r="G107" s="3" t="n"/>
+      <c r="H107" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>5039</v>
+      </c>
+      <c r="D108" t="n">
+        <v>4043</v>
+      </c>
+      <c r="E108" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>0.8023</v>
+      </c>
+      <c r="G108" s="3" t="n">
+        <v>0.8369</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>0.9634</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>168</v>
+      </c>
+      <c r="D109" t="n">
+        <v>168</v>
+      </c>
+      <c r="E109" t="n">
+        <v>168</v>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="2" t="n"/>
+      <c r="G110" s="3" t="n"/>
+      <c r="H110" s="2" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>9706</v>
+      </c>
+      <c r="D111" t="n">
+        <v>2006</v>
+      </c>
+      <c r="E111" t="n">
+        <v>9384</v>
+      </c>
+      <c r="F111" s="2" t="n">
+        <v>0.2067</v>
+      </c>
+      <c r="G111" s="3" t="n">
+        <v>0.9668000000000001</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>0.8889</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>14995</v>
+      </c>
+      <c r="D112" t="n">
+        <v>11170</v>
+      </c>
+      <c r="E112" t="n">
+        <v>14709</v>
+      </c>
+      <c r="F112" s="2" t="n">
+        <v>0.7448999999999999</v>
+      </c>
+      <c r="G112" s="3" t="n">
+        <v>0.9809</v>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>0.9276000000000001</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="2" t="n"/>
+      <c r="G113" s="3" t="n"/>
+      <c r="H113" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H99"/>
+  <autoFilter ref="A1:H113"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -528,7 +528,7 @@
         <v>0.7802</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9415</v>
+        <v>0.9429000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -553,7 +553,7 @@
         <v>0.8194</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9117000000000001</v>
+        <v>0.9124</v>
       </c>
     </row>
     <row r="5">
@@ -597,7 +597,7 @@
         <v>0.8266</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9745</v>
+        <v>0.9749</v>
       </c>
     </row>
     <row r="7">
@@ -622,7 +622,7 @@
         <v>0.7716</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6923</v>
+        <v>0.698</v>
       </c>
     </row>
     <row r="8">
@@ -647,7 +647,7 @@
         <v>0.6597</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8981</v>
+        <v>0.8959999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -697,7 +697,7 @@
         <v>0.7504000000000001</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9721</v>
+        <v>0.9709</v>
       </c>
     </row>
     <row r="11">
@@ -722,7 +722,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.9777</v>
+        <v>0.9779000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -766,7 +766,7 @@
         <v>0.865</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.9473</v>
+        <v>0.9439</v>
       </c>
     </row>
     <row r="14">
@@ -791,7 +791,7 @@
         <v>0.7970999999999999</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.9617</v>
+        <v>0.9620000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -3693,7 +3693,7 @@
         <v>0.8519</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>0.8401999999999999</v>
+        <v>0.8431000000000001</v>
       </c>
     </row>
     <row r="102">
@@ -3723,7 +3723,7 @@
         <v>0.9458</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>0.904</v>
+        <v>0.9109999999999999</v>
       </c>
     </row>
     <row r="103">
@@ -3777,7 +3777,7 @@
         <v>0.779</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>0.9759</v>
+        <v>0.9793999999999999</v>
       </c>
     </row>
     <row r="105">
@@ -3807,7 +3807,7 @@
         <v>0.9972</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>0.625</v>
+        <v>0.7826000000000001</v>
       </c>
     </row>
     <row r="106">
@@ -3837,7 +3837,7 @@
         <v>0.4427</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>0.875</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="107">
@@ -3893,7 +3893,7 @@
         <v>0.8369</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>0.9634</v>
+        <v>0.9509000000000001</v>
       </c>
     </row>
     <row r="109">
@@ -3977,7 +3977,7 @@
         <v>0.9668000000000001</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>0.8889</v>
+        <v>0.8484999999999999</v>
       </c>
     </row>
     <row r="112">
@@ -4007,7 +4007,7 @@
         <v>0.9809</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>0.9276000000000001</v>
+        <v>0.9316</v>
       </c>
     </row>
     <row r="113">

--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$127</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -513,22 +513,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18571</v>
+        <v>21780</v>
       </c>
       <c r="C3" t="n">
-        <v>13580</v>
+        <v>16032</v>
       </c>
       <c r="D3" t="n">
-        <v>14490</v>
+        <v>17464</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.7312000000000001</v>
+        <v>0.7361</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.7802</v>
+        <v>0.8018000000000001</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9429000000000001</v>
+        <v>0.9399</v>
       </c>
     </row>
     <row r="4">
@@ -538,22 +538,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>181120</v>
+        <v>209428</v>
       </c>
       <c r="C4" t="n">
-        <v>133121</v>
+        <v>157339</v>
       </c>
       <c r="D4" t="n">
-        <v>148407</v>
+        <v>176481</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.735</v>
+        <v>0.7513</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.8194</v>
+        <v>0.8427</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9124</v>
+        <v>0.9154000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -582,22 +582,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>294885</v>
+        <v>333983</v>
       </c>
       <c r="C6" t="n">
-        <v>224107</v>
+        <v>254954</v>
       </c>
       <c r="D6" t="n">
-        <v>243757</v>
+        <v>278257</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.76</v>
+        <v>0.7634000000000001</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.8266</v>
+        <v>0.8331000000000001</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9749</v>
+        <v>0.9756</v>
       </c>
     </row>
     <row r="7">
@@ -607,22 +607,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>50634</v>
+        <v>57383</v>
       </c>
       <c r="C7" t="n">
-        <v>26003</v>
+        <v>28283</v>
       </c>
       <c r="D7" t="n">
-        <v>39071</v>
+        <v>45799</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.5135000000000001</v>
+        <v>0.4929</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7716</v>
+        <v>0.7981</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.698</v>
+        <v>0.7023999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -632,22 +632,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>60654</v>
+        <v>67437</v>
       </c>
       <c r="C8" t="n">
-        <v>39117</v>
+        <v>44073</v>
       </c>
       <c r="D8" t="n">
-        <v>40011</v>
+        <v>44967</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.6448999999999999</v>
+        <v>0.6535</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.6597</v>
+        <v>0.6668000000000001</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8959999999999999</v>
+        <v>0.8926000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -682,22 +682,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31704</v>
+        <v>37091</v>
       </c>
       <c r="C10" t="n">
-        <v>23288</v>
+        <v>28580</v>
       </c>
       <c r="D10" t="n">
-        <v>23792</v>
+        <v>29149</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.7345</v>
+        <v>0.7705</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.7504000000000001</v>
+        <v>0.7859</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9709</v>
+        <v>0.9684999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -707,13 +707,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1852</v>
+        <v>2095</v>
       </c>
       <c r="C11" t="n">
-        <v>1852</v>
+        <v>2095</v>
       </c>
       <c r="D11" t="n">
-        <v>1852</v>
+        <v>2095</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1</v>
@@ -722,7 +722,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.9779000000000001</v>
+        <v>0.9803000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -751,22 +751,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>68843</v>
+        <v>79970</v>
       </c>
       <c r="C13" t="n">
-        <v>50653</v>
+        <v>60226</v>
       </c>
       <c r="D13" t="n">
-        <v>59548</v>
+        <v>70648</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.7358</v>
+        <v>0.7531</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.865</v>
+        <v>0.8834000000000001</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.9439</v>
+        <v>0.9445999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -776,22 +776,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>91102</v>
+        <v>103373</v>
       </c>
       <c r="C14" t="n">
-        <v>66607</v>
+        <v>77407</v>
       </c>
       <c r="D14" t="n">
-        <v>72620</v>
+        <v>84654</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.7311</v>
+        <v>0.7487999999999999</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.7970999999999999</v>
+        <v>0.8189</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.9620000000000001</v>
+        <v>0.9628</v>
       </c>
     </row>
     <row r="15">
@@ -827,7 +827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H113"/>
+  <dimension ref="A1:H127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4034,8 +4034,400 @@
       <c r="G113" s="3" t="n"/>
       <c r="H113" s="2" t="n"/>
     </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="2" t="n"/>
+      <c r="G114" s="3" t="n"/>
+      <c r="H114" s="2" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>3209</v>
+      </c>
+      <c r="D115" t="n">
+        <v>2452</v>
+      </c>
+      <c r="E115" t="n">
+        <v>2974</v>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>0.7641</v>
+      </c>
+      <c r="G115" s="3" t="n">
+        <v>0.9268000000000001</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>28308</v>
+      </c>
+      <c r="D116" t="n">
+        <v>24218</v>
+      </c>
+      <c r="E116" t="n">
+        <v>28074</v>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>0.8554999999999999</v>
+      </c>
+      <c r="G116" s="3" t="n">
+        <v>0.9917</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>0.9392</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="2" t="n"/>
+      <c r="G117" s="3" t="n"/>
+      <c r="H117" s="2" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>39098</v>
+      </c>
+      <c r="D118" t="n">
+        <v>30847</v>
+      </c>
+      <c r="E118" t="n">
+        <v>34500</v>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>0.789</v>
+      </c>
+      <c r="G118" s="3" t="n">
+        <v>0.8824</v>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>0.9812000000000001</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>6749</v>
+      </c>
+      <c r="D119" t="n">
+        <v>2280</v>
+      </c>
+      <c r="E119" t="n">
+        <v>6728</v>
+      </c>
+      <c r="F119" s="2" t="n">
+        <v>0.3378</v>
+      </c>
+      <c r="G119" s="3" t="n">
+        <v>0.9969</v>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>6783</v>
+      </c>
+      <c r="D120" t="n">
+        <v>4956</v>
+      </c>
+      <c r="E120" t="n">
+        <v>4956</v>
+      </c>
+      <c r="F120" s="2" t="n">
+        <v>0.7306999999999999</v>
+      </c>
+      <c r="G120" s="3" t="n">
+        <v>0.7306999999999999</v>
+      </c>
+      <c r="H120" s="2" t="n">
+        <v>0.8704999999999999</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="2" t="n"/>
+      <c r="G121" s="3" t="n"/>
+      <c r="H121" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>5387</v>
+      </c>
+      <c r="D122" t="n">
+        <v>5292</v>
+      </c>
+      <c r="E122" t="n">
+        <v>5357</v>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>0.9823999999999999</v>
+      </c>
+      <c r="G122" s="3" t="n">
+        <v>0.9944</v>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>0.9533</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>243</v>
+      </c>
+      <c r="D123" t="n">
+        <v>243</v>
+      </c>
+      <c r="E123" t="n">
+        <v>243</v>
+      </c>
+      <c r="F123" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G123" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" s="2" t="n"/>
+      <c r="G124" s="3" t="n"/>
+      <c r="H124" s="2" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>11127</v>
+      </c>
+      <c r="D125" t="n">
+        <v>9573</v>
+      </c>
+      <c r="E125" t="n">
+        <v>11100</v>
+      </c>
+      <c r="F125" s="2" t="n">
+        <v>0.8603000000000001</v>
+      </c>
+      <c r="G125" s="3" t="n">
+        <v>0.9976</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>0.9487000000000001</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>12271</v>
+      </c>
+      <c r="D126" t="n">
+        <v>10800</v>
+      </c>
+      <c r="E126" t="n">
+        <v>12034</v>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>0.8801000000000001</v>
+      </c>
+      <c r="G126" s="3" t="n">
+        <v>0.9806999999999999</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>0.9681999999999999</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>0</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" s="2" t="n"/>
+      <c r="G127" s="3" t="n"/>
+      <c r="H127" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H113"/>
+  <autoFilter ref="A1:H127"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -528,7 +528,7 @@
         <v>0.8018000000000001</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9399</v>
+        <v>0.9442</v>
       </c>
     </row>
     <row r="4">
@@ -553,7 +553,7 @@
         <v>0.8427</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9154000000000001</v>
+        <v>0.9176000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -597,7 +597,7 @@
         <v>0.8331000000000001</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9756</v>
+        <v>0.9754</v>
       </c>
     </row>
     <row r="7">
@@ -622,7 +622,7 @@
         <v>0.7981</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.7023999999999999</v>
+        <v>0.7036</v>
       </c>
     </row>
     <row r="8">
@@ -647,7 +647,7 @@
         <v>0.6668000000000001</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8926000000000001</v>
+        <v>0.8996</v>
       </c>
     </row>
     <row r="9">
@@ -697,7 +697,7 @@
         <v>0.7859</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9684999999999999</v>
+        <v>0.9687</v>
       </c>
     </row>
     <row r="11">
@@ -722,7 +722,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.9803000000000001</v>
+        <v>0.9801000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -766,7 +766,7 @@
         <v>0.8834000000000001</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.9445999999999999</v>
+        <v>0.9449</v>
       </c>
     </row>
     <row r="14">
@@ -791,7 +791,7 @@
         <v>0.8189</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.9628</v>
+        <v>0.961</v>
       </c>
     </row>
     <row r="15">
@@ -4085,7 +4085,7 @@
         <v>0.9268000000000001</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>0.92</v>
+        <v>0.9526</v>
       </c>
     </row>
     <row r="116">
@@ -4115,7 +4115,7 @@
         <v>0.9917</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>0.9392</v>
+        <v>0.9556</v>
       </c>
     </row>
     <row r="117">
@@ -4169,7 +4169,7 @@
         <v>0.8824</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>0.9812000000000001</v>
+        <v>0.9793999999999999</v>
       </c>
     </row>
     <row r="119">
@@ -4199,7 +4199,7 @@
         <v>0.9969</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>0.76</v>
+        <v>0.8056</v>
       </c>
     </row>
     <row r="120">
@@ -4229,7 +4229,7 @@
         <v>0.7306999999999999</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>0.8704999999999999</v>
+        <v>0.9253</v>
       </c>
     </row>
     <row r="121">
@@ -4285,7 +4285,7 @@
         <v>0.9944</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>0.9533</v>
+        <v>0.9534999999999999</v>
       </c>
     </row>
     <row r="123">
@@ -4369,7 +4369,7 @@
         <v>0.9976</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>0.9487000000000001</v>
+        <v>0.9519</v>
       </c>
     </row>
     <row r="126">
@@ -4399,7 +4399,7 @@
         <v>0.9806999999999999</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>0.9681999999999999</v>
+        <v>0.9539</v>
       </c>
     </row>
     <row r="127">

--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$141</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -513,22 +513,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21780</v>
+        <v>24345</v>
       </c>
       <c r="C3" t="n">
-        <v>16032</v>
+        <v>18508</v>
       </c>
       <c r="D3" t="n">
-        <v>17464</v>
+        <v>20007</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.7361</v>
+        <v>0.7602</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.8018000000000001</v>
+        <v>0.8218000000000001</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9442</v>
+        <v>0.9390999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -538,22 +538,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>209428</v>
+        <v>233151</v>
       </c>
       <c r="C4" t="n">
-        <v>157339</v>
+        <v>180202</v>
       </c>
       <c r="D4" t="n">
-        <v>176481</v>
+        <v>199774</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.7513</v>
+        <v>0.7729</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.8427</v>
+        <v>0.8568000000000001</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9176000000000001</v>
+        <v>0.9209000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -582,22 +582,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>333983</v>
+        <v>367823</v>
       </c>
       <c r="C6" t="n">
-        <v>254954</v>
+        <v>279155</v>
       </c>
       <c r="D6" t="n">
-        <v>278257</v>
+        <v>311905</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.7634000000000001</v>
+        <v>0.7589</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.8331000000000001</v>
+        <v>0.848</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9754</v>
+        <v>0.9756</v>
       </c>
     </row>
     <row r="7">
@@ -607,22 +607,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>57383</v>
+        <v>66428</v>
       </c>
       <c r="C7" t="n">
-        <v>28283</v>
+        <v>30535</v>
       </c>
       <c r="D7" t="n">
-        <v>45799</v>
+        <v>54839</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.4929</v>
+        <v>0.4597</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7981</v>
+        <v>0.8255</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.7036</v>
+        <v>0.7059000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -632,22 +632,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>67437</v>
+        <v>75760</v>
       </c>
       <c r="C8" t="n">
-        <v>44073</v>
+        <v>50977</v>
       </c>
       <c r="D8" t="n">
-        <v>44967</v>
+        <v>53197</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.6535</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.6668000000000001</v>
+        <v>0.7021999999999999</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8996</v>
+        <v>0.8974</v>
       </c>
     </row>
     <row r="9">
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1</v>
@@ -682,22 +682,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>37091</v>
+        <v>43126</v>
       </c>
       <c r="C10" t="n">
-        <v>28580</v>
+        <v>34473</v>
       </c>
       <c r="D10" t="n">
-        <v>29149</v>
+        <v>35118</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.7705</v>
+        <v>0.7994</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.7859</v>
+        <v>0.8143</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9687</v>
+        <v>0.9675</v>
       </c>
     </row>
     <row r="11">
@@ -707,13 +707,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2095</v>
+        <v>2295</v>
       </c>
       <c r="C11" t="n">
-        <v>2095</v>
+        <v>2295</v>
       </c>
       <c r="D11" t="n">
-        <v>2095</v>
+        <v>2295</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1</v>
@@ -722,7 +722,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.9801000000000001</v>
+        <v>0.9823999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -751,22 +751,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>79970</v>
+        <v>83191</v>
       </c>
       <c r="C13" t="n">
-        <v>60226</v>
+        <v>62857</v>
       </c>
       <c r="D13" t="n">
-        <v>70648</v>
+        <v>73838</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.7531</v>
+        <v>0.7556</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.8834000000000001</v>
+        <v>0.8876000000000001</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.9449</v>
+        <v>0.9412999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -776,22 +776,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>103373</v>
+        <v>114563</v>
       </c>
       <c r="C14" t="n">
-        <v>77407</v>
+        <v>87209</v>
       </c>
       <c r="D14" t="n">
-        <v>84654</v>
+        <v>95615</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.7487999999999999</v>
+        <v>0.7612000000000001</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.8189</v>
+        <v>0.8345999999999999</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.961</v>
+        <v>0.9626</v>
       </c>
     </row>
     <row r="15">
@@ -827,7 +827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H127"/>
+  <dimension ref="A1:H141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4426,8 +4426,404 @@
       <c r="G127" s="3" t="n"/>
       <c r="H127" s="2" t="n"/>
     </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="2" t="n"/>
+      <c r="G128" s="3" t="n"/>
+      <c r="H128" s="2" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>2565</v>
+      </c>
+      <c r="D129" t="n">
+        <v>2476</v>
+      </c>
+      <c r="E129" t="n">
+        <v>2543</v>
+      </c>
+      <c r="F129" s="2" t="n">
+        <v>0.9653</v>
+      </c>
+      <c r="G129" s="3" t="n">
+        <v>0.9914000000000001</v>
+      </c>
+      <c r="H129" s="2" t="n">
+        <v>0.904</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>23723</v>
+      </c>
+      <c r="D130" t="n">
+        <v>22863</v>
+      </c>
+      <c r="E130" t="n">
+        <v>23293</v>
+      </c>
+      <c r="F130" s="2" t="n">
+        <v>0.9637</v>
+      </c>
+      <c r="G130" s="3" t="n">
+        <v>0.9819</v>
+      </c>
+      <c r="H130" s="2" t="n">
+        <v>0.9467</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="2" t="n"/>
+      <c r="G131" s="3" t="n"/>
+      <c r="H131" s="2" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>33840</v>
+      </c>
+      <c r="D132" t="n">
+        <v>24201</v>
+      </c>
+      <c r="E132" t="n">
+        <v>33648</v>
+      </c>
+      <c r="F132" s="2" t="n">
+        <v>0.7151999999999999</v>
+      </c>
+      <c r="G132" s="3" t="n">
+        <v>0.9943000000000001</v>
+      </c>
+      <c r="H132" s="2" t="n">
+        <v>0.9767</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>9045</v>
+      </c>
+      <c r="D133" t="n">
+        <v>2252</v>
+      </c>
+      <c r="E133" t="n">
+        <v>9040</v>
+      </c>
+      <c r="F133" s="2" t="n">
+        <v>0.249</v>
+      </c>
+      <c r="G133" s="3" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="H133" s="2" t="n">
+        <v>0.7391</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>8323</v>
+      </c>
+      <c r="D134" t="n">
+        <v>6904</v>
+      </c>
+      <c r="E134" t="n">
+        <v>8230</v>
+      </c>
+      <c r="F134" s="2" t="n">
+        <v>0.8295</v>
+      </c>
+      <c r="G134" s="3" t="n">
+        <v>0.9887999999999999</v>
+      </c>
+      <c r="H134" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>1</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1</v>
+      </c>
+      <c r="E135" t="n">
+        <v>1</v>
+      </c>
+      <c r="F135" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G135" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H135" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>6035</v>
+      </c>
+      <c r="D136" t="n">
+        <v>5893</v>
+      </c>
+      <c r="E136" t="n">
+        <v>5969</v>
+      </c>
+      <c r="F136" s="2" t="n">
+        <v>0.9765</v>
+      </c>
+      <c r="G136" s="3" t="n">
+        <v>0.9891</v>
+      </c>
+      <c r="H136" s="2" t="n">
+        <v>0.9594</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>200</v>
+      </c>
+      <c r="D137" t="n">
+        <v>200</v>
+      </c>
+      <c r="E137" t="n">
+        <v>200</v>
+      </c>
+      <c r="F137" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G137" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H137" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>0</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" s="2" t="n"/>
+      <c r="G138" s="3" t="n"/>
+      <c r="H138" s="2" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>3221</v>
+      </c>
+      <c r="D139" t="n">
+        <v>2631</v>
+      </c>
+      <c r="E139" t="n">
+        <v>3190</v>
+      </c>
+      <c r="F139" s="2" t="n">
+        <v>0.8168000000000001</v>
+      </c>
+      <c r="G139" s="3" t="n">
+        <v>0.9904000000000001</v>
+      </c>
+      <c r="H139" s="2" t="n">
+        <v>0.9183</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>11190</v>
+      </c>
+      <c r="D140" t="n">
+        <v>9802</v>
+      </c>
+      <c r="E140" t="n">
+        <v>10961</v>
+      </c>
+      <c r="F140" s="2" t="n">
+        <v>0.8759999999999999</v>
+      </c>
+      <c r="G140" s="3" t="n">
+        <v>0.9795</v>
+      </c>
+      <c r="H140" s="2" t="n">
+        <v>0.9738</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>0</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" s="2" t="n"/>
+      <c r="G141" s="3" t="n"/>
+      <c r="H141" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H127"/>
+  <autoFilter ref="A1:H141"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -528,7 +528,7 @@
         <v>0.8218000000000001</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9390999999999999</v>
+        <v>0.9384999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -597,7 +597,7 @@
         <v>0.848</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9756</v>
+        <v>0.9754999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -622,7 +622,7 @@
         <v>0.8255</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.7059000000000001</v>
+        <v>0.7092000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -647,7 +647,7 @@
         <v>0.7021999999999999</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8974</v>
+        <v>0.8956999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -722,7 +722,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.9823999999999999</v>
+        <v>0.9825</v>
       </c>
     </row>
     <row r="12">
@@ -766,7 +766,7 @@
         <v>0.8876000000000001</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.9412999999999999</v>
+        <v>0.9417</v>
       </c>
     </row>
     <row r="14">
@@ -791,7 +791,7 @@
         <v>0.8345999999999999</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.9626</v>
+        <v>0.9627</v>
       </c>
     </row>
     <row r="15">
@@ -4477,7 +4477,7 @@
         <v>0.9914000000000001</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>0.904</v>
+        <v>0.8984000000000001</v>
       </c>
     </row>
     <row r="130">
@@ -4507,7 +4507,7 @@
         <v>0.9819</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>0.9467</v>
+        <v>0.9472</v>
       </c>
     </row>
     <row r="131">
@@ -4561,7 +4561,7 @@
         <v>0.9943000000000001</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>0.9767</v>
+        <v>0.9761</v>
       </c>
     </row>
     <row r="133">
@@ -4591,7 +4591,7 @@
         <v>0.9994</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>0.7391</v>
+        <v>0.7955</v>
       </c>
     </row>
     <row r="134">
@@ -4621,7 +4621,7 @@
         <v>0.9887999999999999</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>0.88</v>
+        <v>0.8643999999999999</v>
       </c>
     </row>
     <row r="135">
@@ -4765,7 +4765,7 @@
         <v>0.9904000000000001</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>0.9183</v>
+        <v>0.922</v>
       </c>
     </row>
     <row r="140">
@@ -4795,7 +4795,7 @@
         <v>0.9795</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>0.9738</v>
+        <v>0.9752</v>
       </c>
     </row>
     <row r="141">

--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$155</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -513,22 +513,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24345</v>
+        <v>26682</v>
       </c>
       <c r="C3" t="n">
-        <v>18508</v>
+        <v>20806</v>
       </c>
       <c r="D3" t="n">
-        <v>20007</v>
+        <v>22331</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.7602</v>
+        <v>0.7798</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.8218000000000001</v>
+        <v>0.8369</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9384999999999999</v>
+        <v>0.9322</v>
       </c>
     </row>
     <row r="4">
@@ -538,22 +538,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>233151</v>
+        <v>255463</v>
       </c>
       <c r="C4" t="n">
-        <v>180202</v>
+        <v>200332</v>
       </c>
       <c r="D4" t="n">
-        <v>199774</v>
+        <v>221971</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.7729</v>
+        <v>0.7842</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.8568000000000001</v>
+        <v>0.8689</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9209000000000001</v>
+        <v>0.9236</v>
       </c>
     </row>
     <row r="5">
@@ -582,22 +582,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>367823</v>
+        <v>406772</v>
       </c>
       <c r="C6" t="n">
-        <v>279155</v>
+        <v>308825</v>
       </c>
       <c r="D6" t="n">
-        <v>311905</v>
+        <v>344798</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.7589</v>
+        <v>0.7592</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.848</v>
+        <v>0.8476</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9754999999999999</v>
+        <v>0.9749</v>
       </c>
     </row>
     <row r="7">
@@ -607,22 +607,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>66428</v>
+        <v>73675</v>
       </c>
       <c r="C7" t="n">
-        <v>30535</v>
+        <v>33096</v>
       </c>
       <c r="D7" t="n">
-        <v>54839</v>
+        <v>62085</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.4597</v>
+        <v>0.4492</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.8255</v>
+        <v>0.8427</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.7092000000000001</v>
+        <v>0.7106</v>
       </c>
     </row>
     <row r="8">
@@ -632,22 +632,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>75760</v>
+        <v>83825</v>
       </c>
       <c r="C8" t="n">
-        <v>50977</v>
+        <v>57497</v>
       </c>
       <c r="D8" t="n">
-        <v>53197</v>
+        <v>61206</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.6729000000000001</v>
+        <v>0.6859000000000001</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.7021999999999999</v>
+        <v>0.7302</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8956999999999999</v>
+        <v>0.8945000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -682,19 +682,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>43126</v>
+        <v>48569</v>
       </c>
       <c r="C10" t="n">
-        <v>34473</v>
+        <v>39827</v>
       </c>
       <c r="D10" t="n">
-        <v>35118</v>
+        <v>40502</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.7994</v>
+        <v>0.82</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.8143</v>
+        <v>0.8339</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>0.9675</v>
@@ -707,13 +707,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2295</v>
+        <v>2368</v>
       </c>
       <c r="C11" t="n">
-        <v>2295</v>
+        <v>2368</v>
       </c>
       <c r="D11" t="n">
-        <v>2295</v>
+        <v>2368</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1</v>
@@ -722,7 +722,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.9825</v>
+        <v>0.9842</v>
       </c>
     </row>
     <row r="12">
@@ -751,22 +751,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>83191</v>
+        <v>93412</v>
       </c>
       <c r="C13" t="n">
-        <v>62857</v>
+        <v>72691</v>
       </c>
       <c r="D13" t="n">
-        <v>73838</v>
+        <v>84050</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.7556</v>
+        <v>0.7781999999999999</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.8876000000000001</v>
+        <v>0.8998</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.9417</v>
+        <v>0.9401</v>
       </c>
     </row>
     <row r="14">
@@ -776,22 +776,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>114563</v>
+        <v>126005</v>
       </c>
       <c r="C14" t="n">
-        <v>87209</v>
+        <v>98130</v>
       </c>
       <c r="D14" t="n">
-        <v>95615</v>
+        <v>107010</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.7612000000000001</v>
+        <v>0.7787999999999999</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.8345999999999999</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.9627</v>
+        <v>0.9639</v>
       </c>
     </row>
     <row r="15">
@@ -827,7 +827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H141"/>
+  <dimension ref="A1:H155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4822,8 +4822,400 @@
       <c r="G141" s="3" t="n"/>
       <c r="H141" s="2" t="n"/>
     </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>0</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" s="2" t="n"/>
+      <c r="G142" s="3" t="n"/>
+      <c r="H142" s="2" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>2337</v>
+      </c>
+      <c r="D143" t="n">
+        <v>2298</v>
+      </c>
+      <c r="E143" t="n">
+        <v>2324</v>
+      </c>
+      <c r="F143" s="2" t="n">
+        <v>0.9833</v>
+      </c>
+      <c r="G143" s="3" t="n">
+        <v>0.9944</v>
+      </c>
+      <c r="H143" s="2" t="n">
+        <v>0.8842</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>22312</v>
+      </c>
+      <c r="D144" t="n">
+        <v>20130</v>
+      </c>
+      <c r="E144" t="n">
+        <v>22197</v>
+      </c>
+      <c r="F144" s="2" t="n">
+        <v>0.9022</v>
+      </c>
+      <c r="G144" s="3" t="n">
+        <v>0.9948</v>
+      </c>
+      <c r="H144" s="2" t="n">
+        <v>0.9469</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>0</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" s="2" t="n"/>
+      <c r="G145" s="3" t="n"/>
+      <c r="H145" s="2" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>38949</v>
+      </c>
+      <c r="D146" t="n">
+        <v>29670</v>
+      </c>
+      <c r="E146" t="n">
+        <v>32893</v>
+      </c>
+      <c r="F146" s="2" t="n">
+        <v>0.7618</v>
+      </c>
+      <c r="G146" s="3" t="n">
+        <v>0.8445</v>
+      </c>
+      <c r="H146" s="2" t="n">
+        <v>0.9695</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>7247</v>
+      </c>
+      <c r="D147" t="n">
+        <v>2561</v>
+      </c>
+      <c r="E147" t="n">
+        <v>7246</v>
+      </c>
+      <c r="F147" s="2" t="n">
+        <v>0.3534</v>
+      </c>
+      <c r="G147" s="3" t="n">
+        <v>0.9998999999999999</v>
+      </c>
+      <c r="H147" s="2" t="n">
+        <v>0.7308</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>8065</v>
+      </c>
+      <c r="D148" t="n">
+        <v>6520</v>
+      </c>
+      <c r="E148" t="n">
+        <v>8009</v>
+      </c>
+      <c r="F148" s="2" t="n">
+        <v>0.8084</v>
+      </c>
+      <c r="G148" s="3" t="n">
+        <v>0.9931</v>
+      </c>
+      <c r="H148" s="2" t="n">
+        <v>0.8837</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>0</v>
+      </c>
+      <c r="D149" t="n">
+        <v>0</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0</v>
+      </c>
+      <c r="F149" s="2" t="n"/>
+      <c r="G149" s="3" t="n"/>
+      <c r="H149" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>5443</v>
+      </c>
+      <c r="D150" t="n">
+        <v>5354</v>
+      </c>
+      <c r="E150" t="n">
+        <v>5384</v>
+      </c>
+      <c r="F150" s="2" t="n">
+        <v>0.9836</v>
+      </c>
+      <c r="G150" s="3" t="n">
+        <v>0.9892</v>
+      </c>
+      <c r="H150" s="2" t="n">
+        <v>0.9676</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>73</v>
+      </c>
+      <c r="D151" t="n">
+        <v>73</v>
+      </c>
+      <c r="E151" t="n">
+        <v>73</v>
+      </c>
+      <c r="F151" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G151" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H151" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>0</v>
+      </c>
+      <c r="D152" t="n">
+        <v>0</v>
+      </c>
+      <c r="E152" t="n">
+        <v>0</v>
+      </c>
+      <c r="F152" s="2" t="n"/>
+      <c r="G152" s="3" t="n"/>
+      <c r="H152" s="2" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>10221</v>
+      </c>
+      <c r="D153" t="n">
+        <v>9834</v>
+      </c>
+      <c r="E153" t="n">
+        <v>10212</v>
+      </c>
+      <c r="F153" s="2" t="n">
+        <v>0.9621</v>
+      </c>
+      <c r="G153" s="3" t="n">
+        <v>0.9991</v>
+      </c>
+      <c r="H153" s="2" t="n">
+        <v>0.9278</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>11442</v>
+      </c>
+      <c r="D154" t="n">
+        <v>10921</v>
+      </c>
+      <c r="E154" t="n">
+        <v>11395</v>
+      </c>
+      <c r="F154" s="2" t="n">
+        <v>0.9545</v>
+      </c>
+      <c r="G154" s="3" t="n">
+        <v>0.9959</v>
+      </c>
+      <c r="H154" s="2" t="n">
+        <v>0.9729000000000001</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>0</v>
+      </c>
+      <c r="D155" t="n">
+        <v>0</v>
+      </c>
+      <c r="E155" t="n">
+        <v>0</v>
+      </c>
+      <c r="F155" s="2" t="n"/>
+      <c r="G155" s="3" t="n"/>
+      <c r="H155" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H141"/>
+  <autoFilter ref="A1:H155"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -528,7 +528,7 @@
         <v>0.8369</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9322</v>
+        <v>0.9323999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -553,7 +553,7 @@
         <v>0.8689</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9236</v>
+        <v>0.9238</v>
       </c>
     </row>
     <row r="5">
@@ -597,7 +597,7 @@
         <v>0.8476</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9749</v>
+        <v>0.9753000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -622,7 +622,7 @@
         <v>0.8427</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.7106</v>
+        <v>0.7115</v>
       </c>
     </row>
     <row r="8">
@@ -647,7 +647,7 @@
         <v>0.7302</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8945000000000001</v>
+        <v>0.8955</v>
       </c>
     </row>
     <row r="9">
@@ -697,7 +697,7 @@
         <v>0.8339</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9675</v>
+        <v>0.9673999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -722,7 +722,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.9842</v>
+        <v>0.9841</v>
       </c>
     </row>
     <row r="12">
@@ -766,7 +766,7 @@
         <v>0.8998</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.9401</v>
+        <v>0.9390000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -4873,7 +4873,7 @@
         <v>0.9944</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>0.8842</v>
+        <v>0.8848999999999999</v>
       </c>
     </row>
     <row r="144">
@@ -4903,7 +4903,7 @@
         <v>0.9948</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>0.9469</v>
+        <v>0.9495</v>
       </c>
     </row>
     <row r="145">
@@ -4957,7 +4957,7 @@
         <v>0.8445</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>0.9695</v>
+        <v>0.9731000000000001</v>
       </c>
     </row>
     <row r="147">
@@ -4987,7 +4987,7 @@
         <v>0.9998999999999999</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>0.7308</v>
+        <v>0.7451000000000001</v>
       </c>
     </row>
     <row r="148">
@@ -5017,7 +5017,7 @@
         <v>0.9931</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>0.8837</v>
+        <v>0.8941</v>
       </c>
     </row>
     <row r="149">
@@ -5073,7 +5073,7 @@
         <v>0.9892</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>0.9676</v>
+        <v>0.9671</v>
       </c>
     </row>
     <row r="151">
@@ -5157,7 +5157,7 @@
         <v>0.9991</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>0.9278</v>
+        <v>0.9192</v>
       </c>
     </row>
     <row r="154">
@@ -5187,7 +5187,7 @@
         <v>0.9959</v>
       </c>
       <c r="H154" s="2" t="n">
-        <v>0.9729000000000001</v>
+        <v>0.9732</v>
       </c>
     </row>
     <row r="155">

--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$155</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$169</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -513,22 +513,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26682</v>
+        <v>28549</v>
       </c>
       <c r="C3" t="n">
-        <v>20806</v>
+        <v>22326</v>
       </c>
       <c r="D3" t="n">
-        <v>22331</v>
+        <v>24132</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.7798</v>
+        <v>0.782</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.8369</v>
+        <v>0.8453000000000001</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9323999999999999</v>
+        <v>0.9274</v>
       </c>
     </row>
     <row r="4">
@@ -538,22 +538,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>255463</v>
+        <v>274105</v>
       </c>
       <c r="C4" t="n">
-        <v>200332</v>
+        <v>212405</v>
       </c>
       <c r="D4" t="n">
-        <v>221971</v>
+        <v>239703</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.7842</v>
+        <v>0.7748999999999999</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.8689</v>
+        <v>0.8745000000000001</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9238</v>
+        <v>0.9265000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -582,22 +582,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>406772</v>
+        <v>439945</v>
       </c>
       <c r="C6" t="n">
-        <v>308825</v>
+        <v>330951</v>
       </c>
       <c r="D6" t="n">
-        <v>344798</v>
+        <v>377223</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.7592</v>
+        <v>0.7523000000000001</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.8476</v>
+        <v>0.8573999999999999</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9753000000000001</v>
+        <v>0.9745999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -607,22 +607,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>73675</v>
+        <v>78720</v>
       </c>
       <c r="C7" t="n">
-        <v>33096</v>
+        <v>34795</v>
       </c>
       <c r="D7" t="n">
-        <v>62085</v>
+        <v>63790</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.4492</v>
+        <v>0.442</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.8427</v>
+        <v>0.8103</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.7115</v>
+        <v>0.7127</v>
       </c>
     </row>
     <row r="8">
@@ -632,22 +632,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>83825</v>
+        <v>91542</v>
       </c>
       <c r="C8" t="n">
-        <v>57497</v>
+        <v>62960</v>
       </c>
       <c r="D8" t="n">
-        <v>61206</v>
+        <v>68824</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.6859000000000001</v>
+        <v>0.6878</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.7302</v>
+        <v>0.7518</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8955</v>
+        <v>0.895</v>
       </c>
     </row>
     <row r="9">
@@ -682,22 +682,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>48569</v>
+        <v>52908</v>
       </c>
       <c r="C10" t="n">
-        <v>39827</v>
+        <v>43145</v>
       </c>
       <c r="D10" t="n">
-        <v>40502</v>
+        <v>44611</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.82</v>
+        <v>0.8155</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.8339</v>
+        <v>0.8431999999999999</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9673999999999999</v>
+        <v>0.9673</v>
       </c>
     </row>
     <row r="11">
@@ -707,13 +707,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2368</v>
+        <v>2417</v>
       </c>
       <c r="C11" t="n">
-        <v>2368</v>
+        <v>2417</v>
       </c>
       <c r="D11" t="n">
-        <v>2368</v>
+        <v>2417</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1</v>
@@ -722,7 +722,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.9841</v>
+        <v>0.9852</v>
       </c>
     </row>
     <row r="12">
@@ -751,22 +751,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>93412</v>
+        <v>98877</v>
       </c>
       <c r="C13" t="n">
-        <v>72691</v>
+        <v>77159</v>
       </c>
       <c r="D13" t="n">
-        <v>84050</v>
+        <v>89494</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.7781999999999999</v>
+        <v>0.7804000000000001</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.8998</v>
+        <v>0.9051</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.9390000000000001</v>
+        <v>0.9378</v>
       </c>
     </row>
     <row r="14">
@@ -776,22 +776,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>126005</v>
+        <v>137344</v>
       </c>
       <c r="C14" t="n">
-        <v>98130</v>
+        <v>107716</v>
       </c>
       <c r="D14" t="n">
-        <v>107010</v>
+        <v>116596</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.7787999999999999</v>
+        <v>0.7843000000000001</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.8493000000000001</v>
+        <v>0.8489</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.9639</v>
+        <v>0.9654</v>
       </c>
     </row>
     <row r="15">
@@ -827,7 +827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H155"/>
+  <dimension ref="A1:H169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5214,8 +5214,400 @@
       <c r="G155" s="3" t="n"/>
       <c r="H155" s="2" t="n"/>
     </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>0</v>
+      </c>
+      <c r="D156" t="n">
+        <v>0</v>
+      </c>
+      <c r="E156" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" s="2" t="n"/>
+      <c r="G156" s="3" t="n"/>
+      <c r="H156" s="2" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>1867</v>
+      </c>
+      <c r="D157" t="n">
+        <v>1520</v>
+      </c>
+      <c r="E157" t="n">
+        <v>1801</v>
+      </c>
+      <c r="F157" s="2" t="n">
+        <v>0.8140999999999999</v>
+      </c>
+      <c r="G157" s="3" t="n">
+        <v>0.9645999999999999</v>
+      </c>
+      <c r="H157" s="2" t="n">
+        <v>0.8826000000000001</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>18642</v>
+      </c>
+      <c r="D158" t="n">
+        <v>12073</v>
+      </c>
+      <c r="E158" t="n">
+        <v>17732</v>
+      </c>
+      <c r="F158" s="2" t="n">
+        <v>0.6476000000000001</v>
+      </c>
+      <c r="G158" s="3" t="n">
+        <v>0.9512</v>
+      </c>
+      <c r="H158" s="2" t="n">
+        <v>0.9549</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>0</v>
+      </c>
+      <c r="D159" t="n">
+        <v>0</v>
+      </c>
+      <c r="E159" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" s="2" t="n"/>
+      <c r="G159" s="3" t="n"/>
+      <c r="H159" s="2" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>33173</v>
+      </c>
+      <c r="D160" t="n">
+        <v>22126</v>
+      </c>
+      <c r="E160" t="n">
+        <v>32425</v>
+      </c>
+      <c r="F160" s="2" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="G160" s="3" t="n">
+        <v>0.9775</v>
+      </c>
+      <c r="H160" s="2" t="n">
+        <v>0.9671999999999999</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>5045</v>
+      </c>
+      <c r="D161" t="n">
+        <v>1699</v>
+      </c>
+      <c r="E161" t="n">
+        <v>1705</v>
+      </c>
+      <c r="F161" s="2" t="n">
+        <v>0.3368</v>
+      </c>
+      <c r="G161" s="3" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="H161" s="2" t="n">
+        <v>0.7333</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>7717</v>
+      </c>
+      <c r="D162" t="n">
+        <v>5463</v>
+      </c>
+      <c r="E162" t="n">
+        <v>7618</v>
+      </c>
+      <c r="F162" s="2" t="n">
+        <v>0.7079000000000001</v>
+      </c>
+      <c r="G162" s="3" t="n">
+        <v>0.9872</v>
+      </c>
+      <c r="H162" s="2" t="n">
+        <v>0.8895000000000001</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>0</v>
+      </c>
+      <c r="D163" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" t="n">
+        <v>0</v>
+      </c>
+      <c r="F163" s="2" t="n"/>
+      <c r="G163" s="3" t="n"/>
+      <c r="H163" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>4339</v>
+      </c>
+      <c r="D164" t="n">
+        <v>3318</v>
+      </c>
+      <c r="E164" t="n">
+        <v>4109</v>
+      </c>
+      <c r="F164" s="2" t="n">
+        <v>0.7646999999999999</v>
+      </c>
+      <c r="G164" s="3" t="n">
+        <v>0.9470000000000001</v>
+      </c>
+      <c r="H164" s="2" t="n">
+        <v>0.9661</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>49</v>
+      </c>
+      <c r="D165" t="n">
+        <v>49</v>
+      </c>
+      <c r="E165" t="n">
+        <v>49</v>
+      </c>
+      <c r="F165" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G165" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H165" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>0</v>
+      </c>
+      <c r="D166" t="n">
+        <v>0</v>
+      </c>
+      <c r="E166" t="n">
+        <v>0</v>
+      </c>
+      <c r="F166" s="2" t="n"/>
+      <c r="G166" s="3" t="n"/>
+      <c r="H166" s="2" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>5465</v>
+      </c>
+      <c r="D167" t="n">
+        <v>4468</v>
+      </c>
+      <c r="E167" t="n">
+        <v>5444</v>
+      </c>
+      <c r="F167" s="2" t="n">
+        <v>0.8176000000000001</v>
+      </c>
+      <c r="G167" s="3" t="n">
+        <v>0.9962000000000001</v>
+      </c>
+      <c r="H167" s="2" t="n">
+        <v>0.9262</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>11339</v>
+      </c>
+      <c r="D168" t="n">
+        <v>9586</v>
+      </c>
+      <c r="E168" t="n">
+        <v>9586</v>
+      </c>
+      <c r="F168" s="2" t="n">
+        <v>0.8454</v>
+      </c>
+      <c r="G168" s="3" t="n">
+        <v>0.8454</v>
+      </c>
+      <c r="H168" s="2" t="n">
+        <v>0.9806</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>0</v>
+      </c>
+      <c r="D169" t="n">
+        <v>0</v>
+      </c>
+      <c r="E169" t="n">
+        <v>0</v>
+      </c>
+      <c r="F169" s="2" t="n"/>
+      <c r="G169" s="3" t="n"/>
+      <c r="H169" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H155"/>
+  <autoFilter ref="A1:H169"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -528,7 +528,7 @@
         <v>0.8453000000000001</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9274</v>
+        <v>0.9268000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -597,7 +597,7 @@
         <v>0.8573999999999999</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9745999999999999</v>
+        <v>0.9743000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -622,7 +622,7 @@
         <v>0.8103</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.7127</v>
+        <v>0.7112000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -647,7 +647,7 @@
         <v>0.7518</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.895</v>
+        <v>0.8944</v>
       </c>
     </row>
     <row r="9">
@@ -697,7 +697,7 @@
         <v>0.8431999999999999</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9673</v>
+        <v>0.9671999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -722,7 +722,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.9852</v>
+        <v>0.9853000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -766,7 +766,7 @@
         <v>0.9051</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.9378</v>
+        <v>0.9381</v>
       </c>
     </row>
     <row r="14">
@@ -791,7 +791,7 @@
         <v>0.8489</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.9654</v>
+        <v>0.9651000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -5265,7 +5265,7 @@
         <v>0.9645999999999999</v>
       </c>
       <c r="H157" s="2" t="n">
-        <v>0.8826000000000001</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="158">
@@ -5295,7 +5295,7 @@
         <v>0.9512</v>
       </c>
       <c r="H158" s="2" t="n">
-        <v>0.9549</v>
+        <v>0.9547</v>
       </c>
     </row>
     <row r="159">
@@ -5349,7 +5349,7 @@
         <v>0.9775</v>
       </c>
       <c r="H160" s="2" t="n">
-        <v>0.9671999999999999</v>
+        <v>0.9643999999999999</v>
       </c>
     </row>
     <row r="161">
@@ -5379,7 +5379,7 @@
         <v>0.338</v>
       </c>
       <c r="H161" s="2" t="n">
-        <v>0.7333</v>
+        <v>0.7045</v>
       </c>
     </row>
     <row r="162">
@@ -5409,7 +5409,7 @@
         <v>0.9872</v>
       </c>
       <c r="H162" s="2" t="n">
-        <v>0.8895000000000001</v>
+        <v>0.883</v>
       </c>
     </row>
     <row r="163">
@@ -5465,7 +5465,7 @@
         <v>0.9470000000000001</v>
       </c>
       <c r="H164" s="2" t="n">
-        <v>0.9661</v>
+        <v>0.9656</v>
       </c>
     </row>
     <row r="165">
@@ -5549,7 +5549,7 @@
         <v>0.9962000000000001</v>
       </c>
       <c r="H167" s="2" t="n">
-        <v>0.9262</v>
+        <v>0.9292</v>
       </c>
     </row>
     <row r="168">
@@ -5579,7 +5579,7 @@
         <v>0.8454</v>
       </c>
       <c r="H168" s="2" t="n">
-        <v>0.9806</v>
+        <v>0.9768000000000001</v>
       </c>
     </row>
     <row r="169">

--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -513,22 +513,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28549</v>
+        <v>29754</v>
       </c>
       <c r="C3" t="n">
-        <v>22326</v>
+        <v>22743</v>
       </c>
       <c r="D3" t="n">
-        <v>24132</v>
+        <v>24549</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.782</v>
+        <v>0.7644</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.8453000000000001</v>
+        <v>0.8251000000000001</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9268000000000001</v>
+        <v>0.9234</v>
       </c>
     </row>
     <row r="4">
@@ -538,22 +538,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>274105</v>
+        <v>290003</v>
       </c>
       <c r="C4" t="n">
-        <v>212405</v>
+        <v>215375</v>
       </c>
       <c r="D4" t="n">
-        <v>239703</v>
+        <v>242673</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.7748999999999999</v>
+        <v>0.7426999999999999</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.8745000000000001</v>
+        <v>0.8368000000000001</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9265000000000001</v>
+        <v>0.9272</v>
       </c>
     </row>
     <row r="5">
@@ -582,22 +582,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>439945</v>
+        <v>467855</v>
       </c>
       <c r="C6" t="n">
-        <v>330951</v>
+        <v>341686</v>
       </c>
       <c r="D6" t="n">
-        <v>377223</v>
+        <v>387958</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.7523000000000001</v>
+        <v>0.7303000000000001</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.8573999999999999</v>
+        <v>0.8292</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9743000000000001</v>
+        <v>0.973</v>
       </c>
     </row>
     <row r="7">
@@ -607,22 +607,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>78720</v>
+        <v>82411</v>
       </c>
       <c r="C7" t="n">
-        <v>34795</v>
+        <v>35048</v>
       </c>
       <c r="D7" t="n">
-        <v>63790</v>
+        <v>64043</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.442</v>
+        <v>0.4253</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.8103</v>
+        <v>0.7770999999999999</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.7098</v>
       </c>
     </row>
     <row r="8">
@@ -632,22 +632,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>91542</v>
+        <v>97619</v>
       </c>
       <c r="C8" t="n">
-        <v>62960</v>
+        <v>64018</v>
       </c>
       <c r="D8" t="n">
-        <v>68824</v>
+        <v>69882</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.6878</v>
+        <v>0.6557999999999999</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.7518</v>
+        <v>0.7159</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8944</v>
+        <v>0.8935999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -682,22 +682,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52908</v>
+        <v>56634</v>
       </c>
       <c r="C10" t="n">
-        <v>43145</v>
+        <v>43630</v>
       </c>
       <c r="D10" t="n">
-        <v>44611</v>
+        <v>45096</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.8155</v>
+        <v>0.7704000000000001</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.8431999999999999</v>
+        <v>0.7963</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9671999999999999</v>
+        <v>0.9671</v>
       </c>
     </row>
     <row r="11">
@@ -707,13 +707,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2417</v>
+        <v>2448</v>
       </c>
       <c r="C11" t="n">
-        <v>2417</v>
+        <v>2448</v>
       </c>
       <c r="D11" t="n">
-        <v>2417</v>
+        <v>2448</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1</v>
@@ -722,7 +722,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.9853000000000001</v>
+        <v>0.9861</v>
       </c>
     </row>
     <row r="12">
@@ -751,22 +751,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>98877</v>
+        <v>103826</v>
       </c>
       <c r="C13" t="n">
-        <v>77159</v>
+        <v>77527</v>
       </c>
       <c r="D13" t="n">
-        <v>89494</v>
+        <v>89862</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.7804000000000001</v>
+        <v>0.7467</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.9051</v>
+        <v>0.8654999999999999</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.9381</v>
+        <v>0.9362</v>
       </c>
     </row>
     <row r="14">
@@ -776,22 +776,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>137344</v>
+        <v>145461</v>
       </c>
       <c r="C14" t="n">
-        <v>107716</v>
+        <v>109480</v>
       </c>
       <c r="D14" t="n">
-        <v>116596</v>
+        <v>118360</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.7843000000000001</v>
+        <v>0.7526</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.8489</v>
+        <v>0.8137000000000001</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.9651000000000001</v>
+        <v>0.9664</v>
       </c>
     </row>
     <row r="15">
@@ -827,7 +827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H169"/>
+  <dimension ref="A1:H183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5606,8 +5606,400 @@
       <c r="G169" s="3" t="n"/>
       <c r="H169" s="2" t="n"/>
     </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>0</v>
+      </c>
+      <c r="D170" t="n">
+        <v>0</v>
+      </c>
+      <c r="E170" t="n">
+        <v>0</v>
+      </c>
+      <c r="F170" s="2" t="n"/>
+      <c r="G170" s="3" t="n"/>
+      <c r="H170" s="2" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>1205</v>
+      </c>
+      <c r="D171" t="n">
+        <v>417</v>
+      </c>
+      <c r="E171" t="n">
+        <v>417</v>
+      </c>
+      <c r="F171" s="2" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="G171" s="3" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="H171" s="2" t="n">
+        <v>0.8853</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>15898</v>
+      </c>
+      <c r="D172" t="n">
+        <v>2970</v>
+      </c>
+      <c r="E172" t="n">
+        <v>2970</v>
+      </c>
+      <c r="F172" s="2" t="n">
+        <v>0.1868</v>
+      </c>
+      <c r="G172" s="3" t="n">
+        <v>0.1868</v>
+      </c>
+      <c r="H172" s="2" t="n">
+        <v>0.9359000000000001</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>0</v>
+      </c>
+      <c r="D173" t="n">
+        <v>0</v>
+      </c>
+      <c r="E173" t="n">
+        <v>0</v>
+      </c>
+      <c r="F173" s="2" t="n"/>
+      <c r="G173" s="3" t="n"/>
+      <c r="H173" s="2" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>27910</v>
+      </c>
+      <c r="D174" t="n">
+        <v>10735</v>
+      </c>
+      <c r="E174" t="n">
+        <v>10735</v>
+      </c>
+      <c r="F174" s="2" t="n">
+        <v>0.3846</v>
+      </c>
+      <c r="G174" s="3" t="n">
+        <v>0.3846</v>
+      </c>
+      <c r="H174" s="2" t="n">
+        <v>0.9567</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>3691</v>
+      </c>
+      <c r="D175" t="n">
+        <v>253</v>
+      </c>
+      <c r="E175" t="n">
+        <v>253</v>
+      </c>
+      <c r="F175" s="2" t="n">
+        <v>0.06849999999999999</v>
+      </c>
+      <c r="G175" s="3" t="n">
+        <v>0.06849999999999999</v>
+      </c>
+      <c r="H175" s="2" t="n">
+        <v>0.6829000000000001</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>6077</v>
+      </c>
+      <c r="D176" t="n">
+        <v>1058</v>
+      </c>
+      <c r="E176" t="n">
+        <v>1058</v>
+      </c>
+      <c r="F176" s="2" t="n">
+        <v>0.1741</v>
+      </c>
+      <c r="G176" s="3" t="n">
+        <v>0.1741</v>
+      </c>
+      <c r="H176" s="2" t="n">
+        <v>0.8824</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>0</v>
+      </c>
+      <c r="D177" t="n">
+        <v>0</v>
+      </c>
+      <c r="E177" t="n">
+        <v>0</v>
+      </c>
+      <c r="F177" s="2" t="n"/>
+      <c r="G177" s="3" t="n"/>
+      <c r="H177" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>3726</v>
+      </c>
+      <c r="D178" t="n">
+        <v>485</v>
+      </c>
+      <c r="E178" t="n">
+        <v>485</v>
+      </c>
+      <c r="F178" s="2" t="n">
+        <v>0.1302</v>
+      </c>
+      <c r="G178" s="3" t="n">
+        <v>0.1302</v>
+      </c>
+      <c r="H178" s="2" t="n">
+        <v>0.9656999999999999</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>31</v>
+      </c>
+      <c r="D179" t="n">
+        <v>31</v>
+      </c>
+      <c r="E179" t="n">
+        <v>31</v>
+      </c>
+      <c r="F179" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G179" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H179" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>0</v>
+      </c>
+      <c r="D180" t="n">
+        <v>0</v>
+      </c>
+      <c r="E180" t="n">
+        <v>0</v>
+      </c>
+      <c r="F180" s="2" t="n"/>
+      <c r="G180" s="3" t="n"/>
+      <c r="H180" s="2" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>4949</v>
+      </c>
+      <c r="D181" t="n">
+        <v>368</v>
+      </c>
+      <c r="E181" t="n">
+        <v>368</v>
+      </c>
+      <c r="F181" s="2" t="n">
+        <v>0.07440000000000001</v>
+      </c>
+      <c r="G181" s="3" t="n">
+        <v>0.07440000000000001</v>
+      </c>
+      <c r="H181" s="2" t="n">
+        <v>0.9143000000000001</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>8117</v>
+      </c>
+      <c r="D182" t="n">
+        <v>1764</v>
+      </c>
+      <c r="E182" t="n">
+        <v>1764</v>
+      </c>
+      <c r="F182" s="2" t="n">
+        <v>0.2173</v>
+      </c>
+      <c r="G182" s="3" t="n">
+        <v>0.2173</v>
+      </c>
+      <c r="H182" s="2" t="n">
+        <v>0.9823999999999999</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>0</v>
+      </c>
+      <c r="D183" t="n">
+        <v>0</v>
+      </c>
+      <c r="E183" t="n">
+        <v>0</v>
+      </c>
+      <c r="F183" s="2" t="n"/>
+      <c r="G183" s="3" t="n"/>
+      <c r="H183" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H169"/>
+  <autoFilter ref="A1:H183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -528,7 +528,7 @@
         <v>0.8251000000000001</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9234</v>
+        <v>0.9238</v>
       </c>
     </row>
     <row r="4">
@@ -647,7 +647,7 @@
         <v>0.7159</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8935999999999999</v>
+        <v>0.8941</v>
       </c>
     </row>
     <row r="9">
@@ -697,7 +697,7 @@
         <v>0.7963</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9671</v>
+        <v>0.9673</v>
       </c>
     </row>
     <row r="11">
@@ -766,7 +766,7 @@
         <v>0.8654999999999999</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.9362</v>
+        <v>0.9365000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -5657,7 +5657,7 @@
         <v>0.3461</v>
       </c>
       <c r="H171" s="2" t="n">
-        <v>0.8853</v>
+        <v>0.8904000000000001</v>
       </c>
     </row>
     <row r="172">
@@ -5687,7 +5687,7 @@
         <v>0.1868</v>
       </c>
       <c r="H172" s="2" t="n">
-        <v>0.9359000000000001</v>
+        <v>0.9370999999999999</v>
       </c>
     </row>
     <row r="173">
@@ -5741,7 +5741,7 @@
         <v>0.3846</v>
       </c>
       <c r="H174" s="2" t="n">
-        <v>0.9567</v>
+        <v>0.9568000000000001</v>
       </c>
     </row>
     <row r="175">
@@ -5801,7 +5801,7 @@
         <v>0.1741</v>
       </c>
       <c r="H176" s="2" t="n">
-        <v>0.8824</v>
+        <v>0.8903</v>
       </c>
     </row>
     <row r="177">
@@ -5857,7 +5857,7 @@
         <v>0.1302</v>
       </c>
       <c r="H178" s="2" t="n">
-        <v>0.9656999999999999</v>
+        <v>0.9684</v>
       </c>
     </row>
     <row r="179">
@@ -5941,7 +5941,7 @@
         <v>0.07440000000000001</v>
       </c>
       <c r="H181" s="2" t="n">
-        <v>0.9143000000000001</v>
+        <v>0.9187000000000001</v>
       </c>
     </row>
     <row r="182">
@@ -5971,7 +5971,7 @@
         <v>0.2173</v>
       </c>
       <c r="H182" s="2" t="n">
-        <v>0.9823999999999999</v>
+        <v>0.9826999999999999</v>
       </c>
     </row>
     <row r="183">

--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -528,7 +528,7 @@
         <v>0.8251000000000001</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9238</v>
+        <v>0.9236</v>
       </c>
     </row>
     <row r="4">
@@ -553,7 +553,7 @@
         <v>0.8368000000000001</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9272</v>
+        <v>0.9270999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -597,7 +597,7 @@
         <v>0.8292</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.973</v>
+        <v>0.9729000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -622,7 +622,7 @@
         <v>0.7770999999999999</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.7098</v>
+        <v>0.7103</v>
       </c>
     </row>
     <row r="8">
@@ -647,7 +647,7 @@
         <v>0.7159</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8941</v>
+        <v>0.8944</v>
       </c>
     </row>
     <row r="9">
@@ -697,7 +697,7 @@
         <v>0.7963</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9673</v>
+        <v>0.9681999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -722,7 +722,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.9861</v>
+        <v>0.986</v>
       </c>
     </row>
     <row r="12">
@@ -766,7 +766,7 @@
         <v>0.8654999999999999</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.9365000000000001</v>
+        <v>0.9366</v>
       </c>
     </row>
     <row r="14">
@@ -791,7 +791,7 @@
         <v>0.8137000000000001</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.9664</v>
+        <v>0.9666</v>
       </c>
     </row>
     <row r="15">
@@ -5657,7 +5657,7 @@
         <v>0.3461</v>
       </c>
       <c r="H171" s="2" t="n">
-        <v>0.8904000000000001</v>
+        <v>0.8884000000000001</v>
       </c>
     </row>
     <row r="172">
@@ -5687,7 +5687,7 @@
         <v>0.1868</v>
       </c>
       <c r="H172" s="2" t="n">
-        <v>0.9370999999999999</v>
+        <v>0.9351</v>
       </c>
     </row>
     <row r="173">
@@ -5741,7 +5741,7 @@
         <v>0.3846</v>
       </c>
       <c r="H174" s="2" t="n">
-        <v>0.9568000000000001</v>
+        <v>0.9555</v>
       </c>
     </row>
     <row r="175">
@@ -5771,7 +5771,7 @@
         <v>0.06849999999999999</v>
       </c>
       <c r="H175" s="2" t="n">
-        <v>0.6829000000000001</v>
+        <v>0.6923</v>
       </c>
     </row>
     <row r="176">
@@ -5801,7 +5801,7 @@
         <v>0.1741</v>
       </c>
       <c r="H176" s="2" t="n">
-        <v>0.8903</v>
+        <v>0.8937999999999999</v>
       </c>
     </row>
     <row r="177">
@@ -5857,7 +5857,7 @@
         <v>0.1302</v>
       </c>
       <c r="H178" s="2" t="n">
-        <v>0.9684</v>
+        <v>0.9804999999999999</v>
       </c>
     </row>
     <row r="179">
@@ -5941,7 +5941,7 @@
         <v>0.07440000000000001</v>
       </c>
       <c r="H181" s="2" t="n">
-        <v>0.9187000000000001</v>
+        <v>0.9201</v>
       </c>
     </row>
     <row r="182">
@@ -5971,7 +5971,7 @@
         <v>0.2173</v>
       </c>
       <c r="H182" s="2" t="n">
-        <v>0.9826999999999999</v>
+        <v>0.9843999999999999</v>
       </c>
     </row>
     <row r="183">

--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$183</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$197</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -513,22 +513,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29754</v>
+        <v>30903</v>
       </c>
       <c r="C3" t="n">
-        <v>22743</v>
+        <v>23714</v>
       </c>
       <c r="D3" t="n">
-        <v>24549</v>
+        <v>25523</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.7644</v>
+        <v>0.7674</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.8251000000000001</v>
+        <v>0.8259000000000001</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9236</v>
+        <v>0.9023</v>
       </c>
     </row>
     <row r="4">
@@ -538,22 +538,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>290003</v>
+        <v>307372</v>
       </c>
       <c r="C4" t="n">
-        <v>215375</v>
+        <v>225733</v>
       </c>
       <c r="D4" t="n">
-        <v>242673</v>
+        <v>259794</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.7426999999999999</v>
+        <v>0.7343999999999999</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.8368000000000001</v>
+        <v>0.8452</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9270999999999999</v>
+        <v>0.9120999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -582,22 +582,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>467855</v>
+        <v>500214</v>
       </c>
       <c r="C6" t="n">
-        <v>341686</v>
+        <v>365665</v>
       </c>
       <c r="D6" t="n">
-        <v>387958</v>
+        <v>415040</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.7303000000000001</v>
+        <v>0.731</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.8292</v>
+        <v>0.8297</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9729000000000001</v>
+        <v>0.9620000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -607,22 +607,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>82411</v>
+        <v>84623</v>
       </c>
       <c r="C7" t="n">
-        <v>35048</v>
+        <v>35298</v>
       </c>
       <c r="D7" t="n">
-        <v>64043</v>
+        <v>66249</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.4253</v>
+        <v>0.4171</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7770999999999999</v>
+        <v>0.7829</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.7103</v>
+        <v>0.7009000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -632,22 +632,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>97619</v>
+        <v>104956</v>
       </c>
       <c r="C8" t="n">
-        <v>64018</v>
+        <v>68885</v>
       </c>
       <c r="D8" t="n">
-        <v>69882</v>
+        <v>76917</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.6557999999999999</v>
+        <v>0.6563</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.7159</v>
+        <v>0.7328</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8944</v>
+        <v>0.8856000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="D9" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1</v>
@@ -682,22 +682,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>56634</v>
+        <v>60687</v>
       </c>
       <c r="C10" t="n">
-        <v>43630</v>
+        <v>46642</v>
       </c>
       <c r="D10" t="n">
-        <v>45096</v>
+        <v>49059</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.7704000000000001</v>
+        <v>0.7685999999999999</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.7963</v>
+        <v>0.8084</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9681999999999999</v>
+        <v>0.9429000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -707,13 +707,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2448</v>
+        <v>2486</v>
       </c>
       <c r="C11" t="n">
-        <v>2448</v>
+        <v>2486</v>
       </c>
       <c r="D11" t="n">
-        <v>2448</v>
+        <v>2486</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1</v>
@@ -722,7 +722,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.986</v>
+        <v>0.9612999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -751,22 +751,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>103826</v>
+        <v>110064</v>
       </c>
       <c r="C13" t="n">
-        <v>77527</v>
+        <v>83281</v>
       </c>
       <c r="D13" t="n">
-        <v>89862</v>
+        <v>96100</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.7467</v>
+        <v>0.7567</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.8654999999999999</v>
+        <v>0.8731</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.9366</v>
+        <v>0.9137000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -776,22 +776,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>145461</v>
+        <v>155791</v>
       </c>
       <c r="C14" t="n">
-        <v>109480</v>
+        <v>117999</v>
       </c>
       <c r="D14" t="n">
-        <v>118360</v>
+        <v>128613</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.7526</v>
+        <v>0.7574</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.8137000000000001</v>
+        <v>0.8255</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.9666</v>
+        <v>0.9458</v>
       </c>
     </row>
     <row r="15">
@@ -827,7 +827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H183"/>
+  <dimension ref="A1:H197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5998,8 +5998,404 @@
       <c r="G183" s="3" t="n"/>
       <c r="H183" s="2" t="n"/>
     </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>0</v>
+      </c>
+      <c r="D184" t="n">
+        <v>0</v>
+      </c>
+      <c r="E184" t="n">
+        <v>0</v>
+      </c>
+      <c r="F184" s="2" t="n"/>
+      <c r="G184" s="3" t="n"/>
+      <c r="H184" s="2" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>1149</v>
+      </c>
+      <c r="D185" t="n">
+        <v>971</v>
+      </c>
+      <c r="E185" t="n">
+        <v>974</v>
+      </c>
+      <c r="F185" s="2" t="n">
+        <v>0.8451000000000001</v>
+      </c>
+      <c r="G185" s="3" t="n">
+        <v>0.8477</v>
+      </c>
+      <c r="H185" s="2" t="n">
+        <v>0.6225000000000001</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>17369</v>
+      </c>
+      <c r="D186" t="n">
+        <v>10358</v>
+      </c>
+      <c r="E186" t="n">
+        <v>17121</v>
+      </c>
+      <c r="F186" s="2" t="n">
+        <v>0.5963000000000001</v>
+      </c>
+      <c r="G186" s="3" t="n">
+        <v>0.9856999999999999</v>
+      </c>
+      <c r="H186" s="2" t="n">
+        <v>0.6835</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>0</v>
+      </c>
+      <c r="D187" t="n">
+        <v>0</v>
+      </c>
+      <c r="E187" t="n">
+        <v>0</v>
+      </c>
+      <c r="F187" s="2" t="n"/>
+      <c r="G187" s="3" t="n"/>
+      <c r="H187" s="2" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>32359</v>
+      </c>
+      <c r="D188" t="n">
+        <v>23979</v>
+      </c>
+      <c r="E188" t="n">
+        <v>27082</v>
+      </c>
+      <c r="F188" s="2" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="G188" s="3" t="n">
+        <v>0.8369</v>
+      </c>
+      <c r="H188" s="2" t="n">
+        <v>0.8184</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>2212</v>
+      </c>
+      <c r="D189" t="n">
+        <v>250</v>
+      </c>
+      <c r="E189" t="n">
+        <v>2206</v>
+      </c>
+      <c r="F189" s="2" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="G189" s="3" t="n">
+        <v>0.9973000000000001</v>
+      </c>
+      <c r="H189" s="2" t="n">
+        <v>0.5115999999999999</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>7337</v>
+      </c>
+      <c r="D190" t="n">
+        <v>4867</v>
+      </c>
+      <c r="E190" t="n">
+        <v>7035</v>
+      </c>
+      <c r="F190" s="2" t="n">
+        <v>0.6634</v>
+      </c>
+      <c r="G190" s="3" t="n">
+        <v>0.9588</v>
+      </c>
+      <c r="H190" s="2" t="n">
+        <v>0.7662</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>17</v>
+      </c>
+      <c r="D191" t="n">
+        <v>17</v>
+      </c>
+      <c r="E191" t="n">
+        <v>17</v>
+      </c>
+      <c r="F191" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G191" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H191" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>4053</v>
+      </c>
+      <c r="D192" t="n">
+        <v>3012</v>
+      </c>
+      <c r="E192" t="n">
+        <v>3963</v>
+      </c>
+      <c r="F192" s="2" t="n">
+        <v>0.7432</v>
+      </c>
+      <c r="G192" s="3" t="n">
+        <v>0.9778</v>
+      </c>
+      <c r="H192" s="2" t="n">
+        <v>0.5866</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>38</v>
+      </c>
+      <c r="D193" t="n">
+        <v>38</v>
+      </c>
+      <c r="E193" t="n">
+        <v>38</v>
+      </c>
+      <c r="F193" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G193" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H193" s="2" t="n">
+        <v>0.475</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>0</v>
+      </c>
+      <c r="D194" t="n">
+        <v>0</v>
+      </c>
+      <c r="E194" t="n">
+        <v>0</v>
+      </c>
+      <c r="F194" s="2" t="n"/>
+      <c r="G194" s="3" t="n"/>
+      <c r="H194" s="2" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>6238</v>
+      </c>
+      <c r="D195" t="n">
+        <v>5754</v>
+      </c>
+      <c r="E195" t="n">
+        <v>6238</v>
+      </c>
+      <c r="F195" s="2" t="n">
+        <v>0.9224</v>
+      </c>
+      <c r="G195" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H195" s="2" t="n">
+        <v>0.5992000000000001</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>10330</v>
+      </c>
+      <c r="D196" t="n">
+        <v>8519</v>
+      </c>
+      <c r="E196" t="n">
+        <v>10253</v>
+      </c>
+      <c r="F196" s="2" t="n">
+        <v>0.8247</v>
+      </c>
+      <c r="G196" s="3" t="n">
+        <v>0.9925</v>
+      </c>
+      <c r="H196" s="2" t="n">
+        <v>0.6662</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>0</v>
+      </c>
+      <c r="D197" t="n">
+        <v>0</v>
+      </c>
+      <c r="E197" t="n">
+        <v>0</v>
+      </c>
+      <c r="F197" s="2" t="n"/>
+      <c r="G197" s="3" t="n"/>
+      <c r="H197" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H183"/>
+  <autoFilter ref="A1:H197"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -528,7 +528,7 @@
         <v>0.8259000000000001</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9023</v>
+        <v>0.9013</v>
       </c>
     </row>
     <row r="4">
@@ -553,7 +553,7 @@
         <v>0.8452</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9120999999999999</v>
+        <v>0.9109999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -597,7 +597,7 @@
         <v>0.8297</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9620000000000001</v>
+        <v>0.9615</v>
       </c>
     </row>
     <row r="7">
@@ -622,7 +622,7 @@
         <v>0.7829</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.7009000000000001</v>
+        <v>0.6999</v>
       </c>
     </row>
     <row r="8">
@@ -647,7 +647,7 @@
         <v>0.7328</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8856000000000001</v>
+        <v>0.885</v>
       </c>
     </row>
     <row r="9">
@@ -697,7 +697,7 @@
         <v>0.8084</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9429000000000001</v>
+        <v>0.9445</v>
       </c>
     </row>
     <row r="11">
@@ -722,7 +722,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.9612999999999999</v>
+        <v>0.9577</v>
       </c>
     </row>
     <row r="12">
@@ -766,7 +766,7 @@
         <v>0.8731</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.9137000000000001</v>
+        <v>0.9152</v>
       </c>
     </row>
     <row r="14">
@@ -791,7 +791,7 @@
         <v>0.8255</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.9458</v>
+        <v>0.9466</v>
       </c>
     </row>
     <row r="15">
@@ -6049,7 +6049,7 @@
         <v>0.8477</v>
       </c>
       <c r="H185" s="2" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.6098</v>
       </c>
     </row>
     <row r="186">
@@ -6079,7 +6079,7 @@
         <v>0.9856999999999999</v>
       </c>
       <c r="H186" s="2" t="n">
-        <v>0.6835</v>
+        <v>0.6729000000000001</v>
       </c>
     </row>
     <row r="187">
@@ -6133,7 +6133,7 @@
         <v>0.8369</v>
       </c>
       <c r="H188" s="2" t="n">
-        <v>0.8184</v>
+        <v>0.8118000000000001</v>
       </c>
     </row>
     <row r="189">
@@ -6163,7 +6163,7 @@
         <v>0.9973000000000001</v>
       </c>
       <c r="H189" s="2" t="n">
-        <v>0.5115999999999999</v>
+        <v>0.475</v>
       </c>
     </row>
     <row r="190">
@@ -6193,7 +6193,7 @@
         <v>0.9588</v>
       </c>
       <c r="H190" s="2" t="n">
-        <v>0.7662</v>
+        <v>0.7595000000000001</v>
       </c>
     </row>
     <row r="191">
@@ -6253,7 +6253,7 @@
         <v>0.9778</v>
       </c>
       <c r="H192" s="2" t="n">
-        <v>0.5866</v>
+        <v>0.5946</v>
       </c>
     </row>
     <row r="193">
@@ -6283,7 +6283,7 @@
         <v>1</v>
       </c>
       <c r="H193" s="2" t="n">
-        <v>0.475</v>
+        <v>0.4146</v>
       </c>
     </row>
     <row r="194">
@@ -6337,7 +6337,7 @@
         <v>1</v>
       </c>
       <c r="H195" s="2" t="n">
-        <v>0.5992000000000001</v>
+        <v>0.6163000000000001</v>
       </c>
     </row>
     <row r="196">
@@ -6367,7 +6367,7 @@
         <v>0.9925</v>
       </c>
       <c r="H196" s="2" t="n">
-        <v>0.6662</v>
+        <v>0.6728000000000001</v>
       </c>
     </row>
     <row r="197">

--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$197</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$211</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -513,22 +513,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30903</v>
+        <v>33920</v>
       </c>
       <c r="C3" t="n">
-        <v>23714</v>
+        <v>26700</v>
       </c>
       <c r="D3" t="n">
-        <v>25523</v>
+        <v>28522</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.7674</v>
+        <v>0.7870999999999999</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.8259000000000001</v>
+        <v>0.8409</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9013</v>
+        <v>0.8939</v>
       </c>
     </row>
     <row r="4">
@@ -538,22 +538,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>307372</v>
+        <v>329898</v>
       </c>
       <c r="C4" t="n">
-        <v>225733</v>
+        <v>247234</v>
       </c>
       <c r="D4" t="n">
-        <v>259794</v>
+        <v>281817</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.7343999999999999</v>
+        <v>0.7494</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.8452</v>
+        <v>0.8543000000000001</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9109999999999999</v>
+        <v>0.9061</v>
       </c>
     </row>
     <row r="5">
@@ -582,22 +582,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>500214</v>
+        <v>538884</v>
       </c>
       <c r="C6" t="n">
-        <v>365665</v>
+        <v>396397</v>
       </c>
       <c r="D6" t="n">
-        <v>415040</v>
+        <v>447765</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.731</v>
+        <v>0.7356</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.8297</v>
+        <v>0.8309000000000001</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9615</v>
+        <v>0.9540999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -607,22 +607,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>84623</v>
+        <v>89417</v>
       </c>
       <c r="C7" t="n">
-        <v>35298</v>
+        <v>37836</v>
       </c>
       <c r="D7" t="n">
-        <v>66249</v>
+        <v>71033</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.4171</v>
+        <v>0.4231</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7829</v>
+        <v>0.7944</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6999</v>
+        <v>0.6987000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -632,22 +632,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>104956</v>
+        <v>113411</v>
       </c>
       <c r="C8" t="n">
-        <v>68885</v>
+        <v>75697</v>
       </c>
       <c r="D8" t="n">
-        <v>76917</v>
+        <v>85270</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.6563</v>
+        <v>0.6675</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.7328</v>
+        <v>0.7519</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.885</v>
+        <v>0.8801000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C9" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D9" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1</v>
@@ -682,22 +682,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>60687</v>
+        <v>66885</v>
       </c>
       <c r="C10" t="n">
-        <v>46642</v>
+        <v>52437</v>
       </c>
       <c r="D10" t="n">
-        <v>49059</v>
+        <v>55102</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.7685999999999999</v>
+        <v>0.784</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.8084</v>
+        <v>0.8238</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9445</v>
+        <v>0.9357</v>
       </c>
     </row>
     <row r="11">
@@ -707,13 +707,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2486</v>
+        <v>2650</v>
       </c>
       <c r="C11" t="n">
-        <v>2486</v>
+        <v>2650</v>
       </c>
       <c r="D11" t="n">
-        <v>2486</v>
+        <v>2650</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1</v>
@@ -722,7 +722,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.9577</v>
+        <v>0.9521999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -751,22 +751,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>110064</v>
+        <v>119272</v>
       </c>
       <c r="C13" t="n">
-        <v>83281</v>
+        <v>92359</v>
       </c>
       <c r="D13" t="n">
-        <v>96100</v>
+        <v>105297</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.7567</v>
+        <v>0.7744</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.8731</v>
+        <v>0.8828</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.9152</v>
+        <v>0.9061</v>
       </c>
     </row>
     <row r="14">
@@ -776,22 +776,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>155791</v>
+        <v>170265</v>
       </c>
       <c r="C14" t="n">
-        <v>117999</v>
+        <v>130982</v>
       </c>
       <c r="D14" t="n">
-        <v>128613</v>
+        <v>142931</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.7574</v>
+        <v>0.7693000000000001</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.8255</v>
+        <v>0.8395</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.9466</v>
+        <v>0.9405</v>
       </c>
     </row>
     <row r="15">
@@ -827,7 +827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H197"/>
+  <dimension ref="A1:H211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6394,8 +6394,406 @@
       <c r="G197" s="3" t="n"/>
       <c r="H197" s="2" t="n"/>
     </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>0</v>
+      </c>
+      <c r="D198" t="n">
+        <v>0</v>
+      </c>
+      <c r="E198" t="n">
+        <v>0</v>
+      </c>
+      <c r="F198" s="2" t="n"/>
+      <c r="G198" s="3" t="n"/>
+      <c r="H198" s="2" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>3017</v>
+      </c>
+      <c r="D199" t="n">
+        <v>2986</v>
+      </c>
+      <c r="E199" t="n">
+        <v>2999</v>
+      </c>
+      <c r="F199" s="2" t="n">
+        <v>0.9897</v>
+      </c>
+      <c r="G199" s="3" t="n">
+        <v>0.9940000000000001</v>
+      </c>
+      <c r="H199" s="2" t="n">
+        <v>0.8009000000000001</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>22526</v>
+      </c>
+      <c r="D200" t="n">
+        <v>21501</v>
+      </c>
+      <c r="E200" t="n">
+        <v>22023</v>
+      </c>
+      <c r="F200" s="2" t="n">
+        <v>0.9545</v>
+      </c>
+      <c r="G200" s="3" t="n">
+        <v>0.9777</v>
+      </c>
+      <c r="H200" s="2" t="n">
+        <v>0.8368000000000001</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>0</v>
+      </c>
+      <c r="D201" t="n">
+        <v>0</v>
+      </c>
+      <c r="E201" t="n">
+        <v>0</v>
+      </c>
+      <c r="F201" s="2" t="n"/>
+      <c r="G201" s="3" t="n"/>
+      <c r="H201" s="2" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>38670</v>
+      </c>
+      <c r="D202" t="n">
+        <v>30732</v>
+      </c>
+      <c r="E202" t="n">
+        <v>32725</v>
+      </c>
+      <c r="F202" s="2" t="n">
+        <v>0.7947</v>
+      </c>
+      <c r="G202" s="3" t="n">
+        <v>0.8462999999999999</v>
+      </c>
+      <c r="H202" s="2" t="n">
+        <v>0.8559</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>4794</v>
+      </c>
+      <c r="D203" t="n">
+        <v>2538</v>
+      </c>
+      <c r="E203" t="n">
+        <v>4784</v>
+      </c>
+      <c r="F203" s="2" t="n">
+        <v>0.5294</v>
+      </c>
+      <c r="G203" s="3" t="n">
+        <v>0.9979</v>
+      </c>
+      <c r="H203" s="2" t="n">
+        <v>0.6744</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D204" t="n">
+        <v>6812</v>
+      </c>
+      <c r="E204" t="n">
+        <v>8353</v>
+      </c>
+      <c r="F204" s="2" t="n">
+        <v>0.8057</v>
+      </c>
+      <c r="G204" s="3" t="n">
+        <v>0.9879000000000001</v>
+      </c>
+      <c r="H204" s="2" t="n">
+        <v>0.8112999999999999</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>3</v>
+      </c>
+      <c r="D205" t="n">
+        <v>3</v>
+      </c>
+      <c r="E205" t="n">
+        <v>3</v>
+      </c>
+      <c r="F205" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G205" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H205" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>6198</v>
+      </c>
+      <c r="D206" t="n">
+        <v>5795</v>
+      </c>
+      <c r="E206" t="n">
+        <v>6043</v>
+      </c>
+      <c r="F206" s="2" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="G206" s="3" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="H206" s="2" t="n">
+        <v>0.8222</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>164</v>
+      </c>
+      <c r="D207" t="n">
+        <v>164</v>
+      </c>
+      <c r="E207" t="n">
+        <v>164</v>
+      </c>
+      <c r="F207" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G207" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H207" s="2" t="n">
+        <v>0.8889</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>0</v>
+      </c>
+      <c r="D208" t="n">
+        <v>0</v>
+      </c>
+      <c r="E208" t="n">
+        <v>0</v>
+      </c>
+      <c r="F208" s="2" t="n"/>
+      <c r="G208" s="3" t="n"/>
+      <c r="H208" s="2" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>9208</v>
+      </c>
+      <c r="D209" t="n">
+        <v>9078</v>
+      </c>
+      <c r="E209" t="n">
+        <v>9197</v>
+      </c>
+      <c r="F209" s="2" t="n">
+        <v>0.9859</v>
+      </c>
+      <c r="G209" s="3" t="n">
+        <v>0.9987999999999999</v>
+      </c>
+      <c r="H209" s="2" t="n">
+        <v>0.7935</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>14474</v>
+      </c>
+      <c r="D210" t="n">
+        <v>12983</v>
+      </c>
+      <c r="E210" t="n">
+        <v>14318</v>
+      </c>
+      <c r="F210" s="2" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="G210" s="3" t="n">
+        <v>0.9892</v>
+      </c>
+      <c r="H210" s="2" t="n">
+        <v>0.8641</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>0</v>
+      </c>
+      <c r="D211" t="n">
+        <v>0</v>
+      </c>
+      <c r="E211" t="n">
+        <v>0</v>
+      </c>
+      <c r="F211" s="2" t="n"/>
+      <c r="G211" s="3" t="n"/>
+      <c r="H211" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H197"/>
+  <autoFilter ref="A1:H211"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$211</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$225</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -513,22 +513,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33920</v>
+        <v>36591</v>
       </c>
       <c r="C3" t="n">
-        <v>26700</v>
+        <v>29273</v>
       </c>
       <c r="D3" t="n">
-        <v>28522</v>
+        <v>31095</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.7870999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.8409</v>
+        <v>0.8498</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.8939</v>
+        <v>0.8759</v>
       </c>
     </row>
     <row r="4">
@@ -538,22 +538,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>329898</v>
+        <v>346907</v>
       </c>
       <c r="C4" t="n">
-        <v>247234</v>
+        <v>263637</v>
       </c>
       <c r="D4" t="n">
-        <v>281817</v>
+        <v>298580</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.7494</v>
+        <v>0.76</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.8543000000000001</v>
+        <v>0.8606999999999999</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9061</v>
+        <v>0.8912</v>
       </c>
     </row>
     <row r="5">
@@ -582,22 +582,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>538884</v>
+        <v>575729</v>
       </c>
       <c r="C6" t="n">
-        <v>396397</v>
+        <v>427728</v>
       </c>
       <c r="D6" t="n">
-        <v>447765</v>
+        <v>484169</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.7356</v>
+        <v>0.7429000000000001</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.8309000000000001</v>
+        <v>0.841</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9540999999999999</v>
+        <v>0.9427</v>
       </c>
     </row>
     <row r="7">
@@ -607,22 +607,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>89417</v>
+        <v>92936</v>
       </c>
       <c r="C7" t="n">
-        <v>37836</v>
+        <v>40885</v>
       </c>
       <c r="D7" t="n">
-        <v>71033</v>
+        <v>74511</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.4231</v>
+        <v>0.4399</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7944</v>
+        <v>0.8017</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6987000000000001</v>
+        <v>0.6929000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -632,22 +632,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>113411</v>
+        <v>120529</v>
       </c>
       <c r="C8" t="n">
-        <v>75697</v>
+        <v>81849</v>
       </c>
       <c r="D8" t="n">
-        <v>85270</v>
+        <v>92259</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.6675</v>
+        <v>0.6790999999999999</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.7519</v>
+        <v>0.7655</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8801000000000001</v>
+        <v>0.8692</v>
       </c>
     </row>
     <row r="9">
@@ -682,22 +682,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>66885</v>
+        <v>71836</v>
       </c>
       <c r="C10" t="n">
-        <v>52437</v>
+        <v>57150</v>
       </c>
       <c r="D10" t="n">
-        <v>55102</v>
+        <v>59883</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.784</v>
+        <v>0.7956</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.8238</v>
+        <v>0.8336</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9357</v>
+        <v>0.9179999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -707,13 +707,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2650</v>
+        <v>2833</v>
       </c>
       <c r="C11" t="n">
-        <v>2650</v>
+        <v>2833</v>
       </c>
       <c r="D11" t="n">
-        <v>2650</v>
+        <v>2833</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1</v>
@@ -722,7 +722,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.9521999999999999</v>
+        <v>0.9140999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -751,22 +751,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>119272</v>
+        <v>125043</v>
       </c>
       <c r="C13" t="n">
-        <v>92359</v>
+        <v>98030</v>
       </c>
       <c r="D13" t="n">
-        <v>105297</v>
+        <v>111057</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.7744</v>
+        <v>0.784</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.8828</v>
+        <v>0.8881999999999999</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.9061</v>
+        <v>0.8874</v>
       </c>
     </row>
     <row r="14">
@@ -776,22 +776,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>170265</v>
+        <v>182838</v>
       </c>
       <c r="C14" t="n">
-        <v>130982</v>
+        <v>142177</v>
       </c>
       <c r="D14" t="n">
-        <v>142931</v>
+        <v>155266</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.7693000000000001</v>
+        <v>0.7776000000000001</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.8395</v>
+        <v>0.8492000000000001</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.9405</v>
+        <v>0.9223</v>
       </c>
     </row>
     <row r="15">
@@ -827,7 +827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H211"/>
+  <dimension ref="A1:H225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6792,8 +6792,402 @@
         <v>0</v>
       </c>
     </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>0</v>
+      </c>
+      <c r="D212" t="n">
+        <v>0</v>
+      </c>
+      <c r="E212" t="n">
+        <v>0</v>
+      </c>
+      <c r="F212" s="2" t="n"/>
+      <c r="G212" s="3" t="n"/>
+      <c r="H212" s="2" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>2671</v>
+      </c>
+      <c r="D213" t="n">
+        <v>2573</v>
+      </c>
+      <c r="E213" t="n">
+        <v>2573</v>
+      </c>
+      <c r="F213" s="2" t="n">
+        <v>0.9632999999999999</v>
+      </c>
+      <c r="G213" s="3" t="n">
+        <v>0.9632999999999999</v>
+      </c>
+      <c r="H213" s="2" t="n">
+        <v>0.6715000000000001</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>17009</v>
+      </c>
+      <c r="D214" t="n">
+        <v>16403</v>
+      </c>
+      <c r="E214" t="n">
+        <v>16763</v>
+      </c>
+      <c r="F214" s="2" t="n">
+        <v>0.9643999999999999</v>
+      </c>
+      <c r="G214" s="3" t="n">
+        <v>0.9854999999999999</v>
+      </c>
+      <c r="H214" s="2" t="n">
+        <v>0.6815000000000001</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>0</v>
+      </c>
+      <c r="D215" t="n">
+        <v>0</v>
+      </c>
+      <c r="E215" t="n">
+        <v>0</v>
+      </c>
+      <c r="F215" s="2" t="n"/>
+      <c r="G215" s="3" t="n"/>
+      <c r="H215" s="2" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>36845</v>
+      </c>
+      <c r="D216" t="n">
+        <v>31331</v>
+      </c>
+      <c r="E216" t="n">
+        <v>36404</v>
+      </c>
+      <c r="F216" s="2" t="n">
+        <v>0.8503000000000001</v>
+      </c>
+      <c r="G216" s="3" t="n">
+        <v>0.988</v>
+      </c>
+      <c r="H216" s="2" t="n">
+        <v>0.7863</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>3519</v>
+      </c>
+      <c r="D217" t="n">
+        <v>3049</v>
+      </c>
+      <c r="E217" t="n">
+        <v>3478</v>
+      </c>
+      <c r="F217" s="2" t="n">
+        <v>0.8664000000000001</v>
+      </c>
+      <c r="G217" s="3" t="n">
+        <v>0.9883</v>
+      </c>
+      <c r="H217" s="2" t="n">
+        <v>0.5965</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>7118</v>
+      </c>
+      <c r="D218" t="n">
+        <v>6152</v>
+      </c>
+      <c r="E218" t="n">
+        <v>6989</v>
+      </c>
+      <c r="F218" s="2" t="n">
+        <v>0.8643000000000001</v>
+      </c>
+      <c r="G218" s="3" t="n">
+        <v>0.9819</v>
+      </c>
+      <c r="H218" s="2" t="n">
+        <v>0.7222</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>0</v>
+      </c>
+      <c r="D219" t="n">
+        <v>0</v>
+      </c>
+      <c r="E219" t="n">
+        <v>0</v>
+      </c>
+      <c r="F219" s="2" t="n"/>
+      <c r="G219" s="3" t="n"/>
+      <c r="H219" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>4951</v>
+      </c>
+      <c r="D220" t="n">
+        <v>4713</v>
+      </c>
+      <c r="E220" t="n">
+        <v>4781</v>
+      </c>
+      <c r="F220" s="2" t="n">
+        <v>0.9519</v>
+      </c>
+      <c r="G220" s="3" t="n">
+        <v>0.9656999999999999</v>
+      </c>
+      <c r="H220" s="2" t="n">
+        <v>0.7055</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>183</v>
+      </c>
+      <c r="D221" t="n">
+        <v>183</v>
+      </c>
+      <c r="E221" t="n">
+        <v>183</v>
+      </c>
+      <c r="F221" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G221" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H221" s="2" t="n">
+        <v>0.5333</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>0</v>
+      </c>
+      <c r="D222" t="n">
+        <v>0</v>
+      </c>
+      <c r="E222" t="n">
+        <v>0</v>
+      </c>
+      <c r="F222" s="2" t="n"/>
+      <c r="G222" s="3" t="n"/>
+      <c r="H222" s="2" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>5771</v>
+      </c>
+      <c r="D223" t="n">
+        <v>5671</v>
+      </c>
+      <c r="E223" t="n">
+        <v>5760</v>
+      </c>
+      <c r="F223" s="2" t="n">
+        <v>0.9826999999999999</v>
+      </c>
+      <c r="G223" s="3" t="n">
+        <v>0.9981</v>
+      </c>
+      <c r="H223" s="2" t="n">
+        <v>0.6765000000000001</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>12573</v>
+      </c>
+      <c r="D224" t="n">
+        <v>11195</v>
+      </c>
+      <c r="E224" t="n">
+        <v>12335</v>
+      </c>
+      <c r="F224" s="2" t="n">
+        <v>0.8904000000000001</v>
+      </c>
+      <c r="G224" s="3" t="n">
+        <v>0.9811</v>
+      </c>
+      <c r="H224" s="2" t="n">
+        <v>0.6979000000000001</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>0</v>
+      </c>
+      <c r="D225" t="n">
+        <v>0</v>
+      </c>
+      <c r="E225" t="n">
+        <v>0</v>
+      </c>
+      <c r="F225" s="2" t="n"/>
+      <c r="G225" s="3" t="n"/>
+      <c r="H225" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H211"/>
+  <autoFilter ref="A1:H225"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$225</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$239</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -513,22 +513,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36591</v>
+        <v>38718</v>
       </c>
       <c r="C3" t="n">
-        <v>29273</v>
+        <v>31334</v>
       </c>
       <c r="D3" t="n">
-        <v>31095</v>
+        <v>33156</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.8</v>
+        <v>0.8093</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.8498</v>
+        <v>0.8563</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.8759</v>
+        <v>0.858</v>
       </c>
     </row>
     <row r="4">
@@ -538,22 +538,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>346907</v>
+        <v>365447</v>
       </c>
       <c r="C4" t="n">
-        <v>263637</v>
+        <v>281792</v>
       </c>
       <c r="D4" t="n">
-        <v>298580</v>
+        <v>316987</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.76</v>
+        <v>0.7711</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.8606999999999999</v>
+        <v>0.8673999999999999</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.8912</v>
+        <v>0.8745000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -582,22 +582,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>575729</v>
+        <v>607355</v>
       </c>
       <c r="C6" t="n">
-        <v>427728</v>
+        <v>455010</v>
       </c>
       <c r="D6" t="n">
-        <v>484169</v>
+        <v>515785</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.7429000000000001</v>
+        <v>0.7492</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.841</v>
+        <v>0.8492000000000001</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9427</v>
+        <v>0.9326000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -607,22 +607,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>92936</v>
+        <v>95861</v>
       </c>
       <c r="C7" t="n">
-        <v>40885</v>
+        <v>43714</v>
       </c>
       <c r="D7" t="n">
-        <v>74511</v>
+        <v>77419</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.4399</v>
+        <v>0.456</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.8017</v>
+        <v>0.8076000000000001</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6929000000000001</v>
+        <v>0.6853</v>
       </c>
     </row>
     <row r="8">
@@ -632,22 +632,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>120529</v>
+        <v>127176</v>
       </c>
       <c r="C8" t="n">
-        <v>81849</v>
+        <v>87676</v>
       </c>
       <c r="D8" t="n">
-        <v>92259</v>
+        <v>98802</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.6790999999999999</v>
+        <v>0.6894</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.7655</v>
+        <v>0.7768999999999999</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8692</v>
+        <v>0.8618000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C9" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D9" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1</v>
@@ -682,22 +682,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>71836</v>
+        <v>76426</v>
       </c>
       <c r="C10" t="n">
-        <v>57150</v>
+        <v>61485</v>
       </c>
       <c r="D10" t="n">
-        <v>59883</v>
+        <v>64267</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.7956</v>
+        <v>0.8045</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.8336</v>
+        <v>0.8409</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9179999999999999</v>
+        <v>0.9017000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -707,13 +707,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2833</v>
+        <v>2952</v>
       </c>
       <c r="C11" t="n">
-        <v>2833</v>
+        <v>2952</v>
       </c>
       <c r="D11" t="n">
-        <v>2833</v>
+        <v>2952</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1</v>
@@ -722,7 +722,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.9140999999999999</v>
+        <v>0.8786</v>
       </c>
     </row>
     <row r="12">
@@ -751,22 +751,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>125043</v>
+        <v>130962</v>
       </c>
       <c r="C13" t="n">
-        <v>98030</v>
+        <v>103827</v>
       </c>
       <c r="D13" t="n">
-        <v>111057</v>
+        <v>116972</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.784</v>
+        <v>0.7928000000000001</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.8881999999999999</v>
+        <v>0.8931999999999999</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.8874</v>
+        <v>0.8661</v>
       </c>
     </row>
     <row r="14">
@@ -776,22 +776,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>182838</v>
+        <v>195893</v>
       </c>
       <c r="C14" t="n">
-        <v>142177</v>
+        <v>154260</v>
       </c>
       <c r="D14" t="n">
-        <v>155266</v>
+        <v>167981</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.7776000000000001</v>
+        <v>0.7875</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.8492000000000001</v>
+        <v>0.8575</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.9223</v>
+        <v>0.9044</v>
       </c>
     </row>
     <row r="15">
@@ -827,7 +827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H225"/>
+  <dimension ref="A1:H239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7186,8 +7186,406 @@
         <v>0</v>
       </c>
     </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>0</v>
+      </c>
+      <c r="D226" t="n">
+        <v>0</v>
+      </c>
+      <c r="E226" t="n">
+        <v>0</v>
+      </c>
+      <c r="F226" s="2" t="n"/>
+      <c r="G226" s="3" t="n"/>
+      <c r="H226" s="2" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>2127</v>
+      </c>
+      <c r="D227" t="n">
+        <v>2061</v>
+      </c>
+      <c r="E227" t="n">
+        <v>2061</v>
+      </c>
+      <c r="F227" s="2" t="n">
+        <v>0.9690000000000001</v>
+      </c>
+      <c r="G227" s="3" t="n">
+        <v>0.9690000000000001</v>
+      </c>
+      <c r="H227" s="2" t="n">
+        <v>0.626</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>18540</v>
+      </c>
+      <c r="D228" t="n">
+        <v>18155</v>
+      </c>
+      <c r="E228" t="n">
+        <v>18407</v>
+      </c>
+      <c r="F228" s="2" t="n">
+        <v>0.9792000000000001</v>
+      </c>
+      <c r="G228" s="3" t="n">
+        <v>0.9928</v>
+      </c>
+      <c r="H228" s="2" t="n">
+        <v>0.6302</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>0</v>
+      </c>
+      <c r="D229" t="n">
+        <v>0</v>
+      </c>
+      <c r="E229" t="n">
+        <v>0</v>
+      </c>
+      <c r="F229" s="2" t="n"/>
+      <c r="G229" s="3" t="n"/>
+      <c r="H229" s="2" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>31626</v>
+      </c>
+      <c r="D230" t="n">
+        <v>27282</v>
+      </c>
+      <c r="E230" t="n">
+        <v>31616</v>
+      </c>
+      <c r="F230" s="2" t="n">
+        <v>0.8626</v>
+      </c>
+      <c r="G230" s="3" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="H230" s="2" t="n">
+        <v>0.7861</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>2925</v>
+      </c>
+      <c r="D231" t="n">
+        <v>2829</v>
+      </c>
+      <c r="E231" t="n">
+        <v>2908</v>
+      </c>
+      <c r="F231" s="2" t="n">
+        <v>0.9671999999999999</v>
+      </c>
+      <c r="G231" s="3" t="n">
+        <v>0.9942</v>
+      </c>
+      <c r="H231" s="2" t="n">
+        <v>0.5385</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>6647</v>
+      </c>
+      <c r="D232" t="n">
+        <v>5827</v>
+      </c>
+      <c r="E232" t="n">
+        <v>6543</v>
+      </c>
+      <c r="F232" s="2" t="n">
+        <v>0.8765999999999999</v>
+      </c>
+      <c r="G232" s="3" t="n">
+        <v>0.9843999999999999</v>
+      </c>
+      <c r="H232" s="2" t="n">
+        <v>0.7556</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>6</v>
+      </c>
+      <c r="D233" t="n">
+        <v>6</v>
+      </c>
+      <c r="E233" t="n">
+        <v>6</v>
+      </c>
+      <c r="F233" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G233" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H233" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>4590</v>
+      </c>
+      <c r="D234" t="n">
+        <v>4335</v>
+      </c>
+      <c r="E234" t="n">
+        <v>4384</v>
+      </c>
+      <c r="F234" s="2" t="n">
+        <v>0.9444</v>
+      </c>
+      <c r="G234" s="3" t="n">
+        <v>0.9551000000000001</v>
+      </c>
+      <c r="H234" s="2" t="n">
+        <v>0.7005</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>119</v>
+      </c>
+      <c r="D235" t="n">
+        <v>119</v>
+      </c>
+      <c r="E235" t="n">
+        <v>119</v>
+      </c>
+      <c r="F235" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G235" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H235" s="2" t="n">
+        <v>0.5472</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>0</v>
+      </c>
+      <c r="D236" t="n">
+        <v>0</v>
+      </c>
+      <c r="E236" t="n">
+        <v>0</v>
+      </c>
+      <c r="F236" s="2" t="n"/>
+      <c r="G236" s="3" t="n"/>
+      <c r="H236" s="2" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>5919</v>
+      </c>
+      <c r="D237" t="n">
+        <v>5797</v>
+      </c>
+      <c r="E237" t="n">
+        <v>5915</v>
+      </c>
+      <c r="F237" s="2" t="n">
+        <v>0.9793999999999999</v>
+      </c>
+      <c r="G237" s="3" t="n">
+        <v>0.9993000000000001</v>
+      </c>
+      <c r="H237" s="2" t="n">
+        <v>0.5954999999999999</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>13055</v>
+      </c>
+      <c r="D238" t="n">
+        <v>12083</v>
+      </c>
+      <c r="E238" t="n">
+        <v>12715</v>
+      </c>
+      <c r="F238" s="2" t="n">
+        <v>0.9255</v>
+      </c>
+      <c r="G238" s="3" t="n">
+        <v>0.9740000000000001</v>
+      </c>
+      <c r="H238" s="2" t="n">
+        <v>0.6798000000000001</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>0</v>
+      </c>
+      <c r="D239" t="n">
+        <v>0</v>
+      </c>
+      <c r="E239" t="n">
+        <v>0</v>
+      </c>
+      <c r="F239" s="2" t="n"/>
+      <c r="G239" s="3" t="n"/>
+      <c r="H239" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H225"/>
+  <autoFilter ref="A1:H239"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$239</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$253</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -513,22 +513,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38718</v>
+        <v>41031</v>
       </c>
       <c r="C3" t="n">
-        <v>31334</v>
+        <v>33609</v>
       </c>
       <c r="D3" t="n">
-        <v>33156</v>
+        <v>35456</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.8093</v>
+        <v>0.8190999999999999</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.8563</v>
+        <v>0.8641</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.858</v>
+        <v>0.8473000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -538,22 +538,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>365447</v>
+        <v>382235</v>
       </c>
       <c r="C4" t="n">
-        <v>281792</v>
+        <v>298313</v>
       </c>
       <c r="D4" t="n">
-        <v>316987</v>
+        <v>333761</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.7711</v>
+        <v>0.7804000000000001</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.8673999999999999</v>
+        <v>0.8732</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.8745000000000001</v>
+        <v>0.8631</v>
       </c>
     </row>
     <row r="5">
@@ -582,22 +582,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>607355</v>
+        <v>643587</v>
       </c>
       <c r="C6" t="n">
-        <v>455010</v>
+        <v>486269</v>
       </c>
       <c r="D6" t="n">
-        <v>515785</v>
+        <v>550662</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.7492</v>
+        <v>0.7556</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.8492000000000001</v>
+        <v>0.8556</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9326000000000001</v>
+        <v>0.9251999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -607,22 +607,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>95861</v>
+        <v>98895</v>
       </c>
       <c r="C7" t="n">
-        <v>43714</v>
+        <v>46745</v>
       </c>
       <c r="D7" t="n">
-        <v>77419</v>
+        <v>80451</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.456</v>
+        <v>0.4727</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.8076000000000001</v>
+        <v>0.8134999999999999</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6853</v>
+        <v>0.6858</v>
       </c>
     </row>
     <row r="8">
@@ -632,22 +632,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>127176</v>
+        <v>134133</v>
       </c>
       <c r="C8" t="n">
-        <v>87676</v>
+        <v>93663</v>
       </c>
       <c r="D8" t="n">
-        <v>98802</v>
+        <v>105669</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.6894</v>
+        <v>0.6983</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.7768999999999999</v>
+        <v>0.7878000000000001</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8618000000000001</v>
+        <v>0.8537</v>
       </c>
     </row>
     <row r="9">
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D9" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1</v>
@@ -682,22 +682,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>76426</v>
+        <v>82348</v>
       </c>
       <c r="C10" t="n">
-        <v>61485</v>
+        <v>65862</v>
       </c>
       <c r="D10" t="n">
-        <v>64267</v>
+        <v>69723</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.8045</v>
+        <v>0.7998000000000001</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.8409</v>
+        <v>0.8467</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9017000000000001</v>
+        <v>0.8865999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -707,13 +707,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2952</v>
+        <v>3221</v>
       </c>
       <c r="C11" t="n">
-        <v>2952</v>
+        <v>3221</v>
       </c>
       <c r="D11" t="n">
-        <v>2952</v>
+        <v>3221</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1</v>
@@ -722,7 +722,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.8786</v>
+        <v>0.8495999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -751,22 +751,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>130962</v>
+        <v>138187</v>
       </c>
       <c r="C13" t="n">
-        <v>103827</v>
+        <v>110974</v>
       </c>
       <c r="D13" t="n">
-        <v>116972</v>
+        <v>124195</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.7928000000000001</v>
+        <v>0.8031</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.8931999999999999</v>
+        <v>0.8987000000000001</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.8661</v>
+        <v>0.8486</v>
       </c>
     </row>
     <row r="14">
@@ -776,22 +776,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>195893</v>
+        <v>210192</v>
       </c>
       <c r="C14" t="n">
-        <v>154260</v>
+        <v>167819</v>
       </c>
       <c r="D14" t="n">
-        <v>167981</v>
+        <v>182173</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.7875</v>
+        <v>0.7984</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.8575</v>
+        <v>0.8667</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.9044</v>
+        <v>0.892</v>
       </c>
     </row>
     <row r="15">
@@ -827,7 +827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H239"/>
+  <dimension ref="A1:H253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7584,8 +7584,406 @@
         <v>0</v>
       </c>
     </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>0</v>
+      </c>
+      <c r="D240" t="n">
+        <v>0</v>
+      </c>
+      <c r="E240" t="n">
+        <v>0</v>
+      </c>
+      <c r="F240" s="2" t="n"/>
+      <c r="G240" s="3" t="n"/>
+      <c r="H240" s="2" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>2313</v>
+      </c>
+      <c r="D241" t="n">
+        <v>2275</v>
+      </c>
+      <c r="E241" t="n">
+        <v>2300</v>
+      </c>
+      <c r="F241" s="2" t="n">
+        <v>0.9836</v>
+      </c>
+      <c r="G241" s="3" t="n">
+        <v>0.9944</v>
+      </c>
+      <c r="H241" s="2" t="n">
+        <v>0.6846</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>16788</v>
+      </c>
+      <c r="D242" t="n">
+        <v>16521</v>
+      </c>
+      <c r="E242" t="n">
+        <v>16774</v>
+      </c>
+      <c r="F242" s="2" t="n">
+        <v>0.9841</v>
+      </c>
+      <c r="G242" s="3" t="n">
+        <v>0.9992</v>
+      </c>
+      <c r="H242" s="2" t="n">
+        <v>0.6765000000000001</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>0</v>
+      </c>
+      <c r="D243" t="n">
+        <v>0</v>
+      </c>
+      <c r="E243" t="n">
+        <v>0</v>
+      </c>
+      <c r="F243" s="2" t="n"/>
+      <c r="G243" s="3" t="n"/>
+      <c r="H243" s="2" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>36232</v>
+      </c>
+      <c r="D244" t="n">
+        <v>31259</v>
+      </c>
+      <c r="E244" t="n">
+        <v>34877</v>
+      </c>
+      <c r="F244" s="2" t="n">
+        <v>0.8626999999999999</v>
+      </c>
+      <c r="G244" s="3" t="n">
+        <v>0.9626</v>
+      </c>
+      <c r="H244" s="2" t="n">
+        <v>0.8129000000000001</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>3034</v>
+      </c>
+      <c r="D245" t="n">
+        <v>3031</v>
+      </c>
+      <c r="E245" t="n">
+        <v>3032</v>
+      </c>
+      <c r="F245" s="2" t="n">
+        <v>0.9990000000000001</v>
+      </c>
+      <c r="G245" s="3" t="n">
+        <v>0.9993000000000001</v>
+      </c>
+      <c r="H245" s="2" t="n">
+        <v>0.6977</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>6957</v>
+      </c>
+      <c r="D246" t="n">
+        <v>5987</v>
+      </c>
+      <c r="E246" t="n">
+        <v>6867</v>
+      </c>
+      <c r="F246" s="2" t="n">
+        <v>0.8606</v>
+      </c>
+      <c r="G246" s="3" t="n">
+        <v>0.9871</v>
+      </c>
+      <c r="H246" s="2" t="n">
+        <v>0.7241</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>2</v>
+      </c>
+      <c r="D247" t="n">
+        <v>2</v>
+      </c>
+      <c r="E247" t="n">
+        <v>2</v>
+      </c>
+      <c r="F247" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G247" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H247" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>5922</v>
+      </c>
+      <c r="D248" t="n">
+        <v>4377</v>
+      </c>
+      <c r="E248" t="n">
+        <v>5456</v>
+      </c>
+      <c r="F248" s="2" t="n">
+        <v>0.7391</v>
+      </c>
+      <c r="G248" s="3" t="n">
+        <v>0.9213</v>
+      </c>
+      <c r="H248" s="2" t="n">
+        <v>0.6737000000000001</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>269</v>
+      </c>
+      <c r="D249" t="n">
+        <v>269</v>
+      </c>
+      <c r="E249" t="n">
+        <v>269</v>
+      </c>
+      <c r="F249" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G249" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H249" s="2" t="n">
+        <v>0.5702</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>0</v>
+      </c>
+      <c r="D250" t="n">
+        <v>0</v>
+      </c>
+      <c r="E250" t="n">
+        <v>0</v>
+      </c>
+      <c r="F250" s="2" t="n"/>
+      <c r="G250" s="3" t="n"/>
+      <c r="H250" s="2" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>7225</v>
+      </c>
+      <c r="D251" t="n">
+        <v>7147</v>
+      </c>
+      <c r="E251" t="n">
+        <v>7223</v>
+      </c>
+      <c r="F251" s="2" t="n">
+        <v>0.9892</v>
+      </c>
+      <c r="G251" s="3" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="H251" s="2" t="n">
+        <v>0.6051</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>14299</v>
+      </c>
+      <c r="D252" t="n">
+        <v>13559</v>
+      </c>
+      <c r="E252" t="n">
+        <v>14192</v>
+      </c>
+      <c r="F252" s="2" t="n">
+        <v>0.9481999999999999</v>
+      </c>
+      <c r="G252" s="3" t="n">
+        <v>0.9925</v>
+      </c>
+      <c r="H252" s="2" t="n">
+        <v>0.7087</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>0</v>
+      </c>
+      <c r="D253" t="n">
+        <v>0</v>
+      </c>
+      <c r="E253" t="n">
+        <v>0</v>
+      </c>
+      <c r="F253" s="2" t="n"/>
+      <c r="G253" s="3" t="n"/>
+      <c r="H253" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H239"/>
+  <autoFilter ref="A1:H253"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$253</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$267</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -513,22 +513,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>41031</v>
+        <v>43289</v>
       </c>
       <c r="C3" t="n">
-        <v>33609</v>
+        <v>35498</v>
       </c>
       <c r="D3" t="n">
-        <v>35456</v>
+        <v>37625</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.8190999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.8641</v>
+        <v>0.8692</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.8473000000000001</v>
+        <v>0.8351000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -538,22 +538,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>382235</v>
+        <v>397935</v>
       </c>
       <c r="C4" t="n">
-        <v>298313</v>
+        <v>311000</v>
       </c>
       <c r="D4" t="n">
-        <v>333761</v>
+        <v>348544</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.7804000000000001</v>
+        <v>0.7815000000000001</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.8732</v>
+        <v>0.8759</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.8631</v>
+        <v>0.8504999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -582,22 +582,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>643587</v>
+        <v>673260</v>
       </c>
       <c r="C6" t="n">
-        <v>486269</v>
+        <v>509917</v>
       </c>
       <c r="D6" t="n">
-        <v>550662</v>
+        <v>578357</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.7556</v>
+        <v>0.7574</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.8556</v>
+        <v>0.8590000000000001</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9251999999999999</v>
+        <v>0.9153</v>
       </c>
     </row>
     <row r="7">
@@ -607,22 +607,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>98895</v>
+        <v>102140</v>
       </c>
       <c r="C7" t="n">
-        <v>46745</v>
+        <v>49103</v>
       </c>
       <c r="D7" t="n">
-        <v>80451</v>
+        <v>83696</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.4727</v>
+        <v>0.4807</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.8134999999999999</v>
+        <v>0.8194</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6858</v>
+        <v>0.6820999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -632,22 +632,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>134133</v>
+        <v>139534</v>
       </c>
       <c r="C8" t="n">
-        <v>93663</v>
+        <v>97739</v>
       </c>
       <c r="D8" t="n">
-        <v>105669</v>
+        <v>109745</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.6983</v>
+        <v>0.7005</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.7878000000000001</v>
+        <v>0.7865000000000001</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8537</v>
+        <v>0.8426</v>
       </c>
     </row>
     <row r="9">
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D9" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1</v>
@@ -682,22 +682,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>82348</v>
+        <v>86864</v>
       </c>
       <c r="C10" t="n">
-        <v>65862</v>
+        <v>69225</v>
       </c>
       <c r="D10" t="n">
-        <v>69723</v>
+        <v>73540</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.7998000000000001</v>
+        <v>0.7968999999999999</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.8467</v>
+        <v>0.8466</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.8865999999999999</v>
+        <v>0.8695999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -707,13 +707,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3221</v>
+        <v>3298</v>
       </c>
       <c r="C11" t="n">
-        <v>3221</v>
+        <v>3298</v>
       </c>
       <c r="D11" t="n">
-        <v>3221</v>
+        <v>3298</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1</v>
@@ -722,7 +722,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.8495999999999999</v>
+        <v>0.8112999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -751,22 +751,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>138187</v>
+        <v>143091</v>
       </c>
       <c r="C13" t="n">
-        <v>110974</v>
+        <v>115073</v>
       </c>
       <c r="D13" t="n">
-        <v>124195</v>
+        <v>129003</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.8031</v>
+        <v>0.8042</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.8987000000000001</v>
+        <v>0.9015000000000001</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.8486</v>
+        <v>0.8331999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -776,22 +776,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>210192</v>
+        <v>224135</v>
       </c>
       <c r="C14" t="n">
-        <v>167819</v>
+        <v>179510</v>
       </c>
       <c r="D14" t="n">
-        <v>182173</v>
+        <v>193864</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.7984</v>
+        <v>0.8009000000000001</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.8667</v>
+        <v>0.8649</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.892</v>
+        <v>0.8771</v>
       </c>
     </row>
     <row r="15">
@@ -827,7 +827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H253"/>
+  <dimension ref="A1:H267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7982,8 +7982,404 @@
         <v>0</v>
       </c>
     </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>0</v>
+      </c>
+      <c r="D254" t="n">
+        <v>0</v>
+      </c>
+      <c r="E254" t="n">
+        <v>0</v>
+      </c>
+      <c r="F254" s="2" t="n"/>
+      <c r="G254" s="3" t="n"/>
+      <c r="H254" s="2" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>2258</v>
+      </c>
+      <c r="D255" t="n">
+        <v>1889</v>
+      </c>
+      <c r="E255" t="n">
+        <v>2169</v>
+      </c>
+      <c r="F255" s="2" t="n">
+        <v>0.8366</v>
+      </c>
+      <c r="G255" s="3" t="n">
+        <v>0.9606</v>
+      </c>
+      <c r="H255" s="2" t="n">
+        <v>0.6408</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>15700</v>
+      </c>
+      <c r="D256" t="n">
+        <v>12687</v>
+      </c>
+      <c r="E256" t="n">
+        <v>14783</v>
+      </c>
+      <c r="F256" s="2" t="n">
+        <v>0.8081</v>
+      </c>
+      <c r="G256" s="3" t="n">
+        <v>0.9416</v>
+      </c>
+      <c r="H256" s="2" t="n">
+        <v>0.6195000000000001</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>0</v>
+      </c>
+      <c r="D257" t="n">
+        <v>0</v>
+      </c>
+      <c r="E257" t="n">
+        <v>0</v>
+      </c>
+      <c r="F257" s="2" t="n"/>
+      <c r="G257" s="3" t="n"/>
+      <c r="H257" s="2" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>29673</v>
+      </c>
+      <c r="D258" t="n">
+        <v>23648</v>
+      </c>
+      <c r="E258" t="n">
+        <v>27695</v>
+      </c>
+      <c r="F258" s="2" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="G258" s="3" t="n">
+        <v>0.9333</v>
+      </c>
+      <c r="H258" s="2" t="n">
+        <v>0.7494</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>3245</v>
+      </c>
+      <c r="D259" t="n">
+        <v>2358</v>
+      </c>
+      <c r="E259" t="n">
+        <v>3245</v>
+      </c>
+      <c r="F259" s="2" t="n">
+        <v>0.7267</v>
+      </c>
+      <c r="G259" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H259" s="2" t="n">
+        <v>0.5957</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>5401</v>
+      </c>
+      <c r="D260" t="n">
+        <v>4076</v>
+      </c>
+      <c r="E260" t="n">
+        <v>4076</v>
+      </c>
+      <c r="F260" s="2" t="n">
+        <v>0.7547</v>
+      </c>
+      <c r="G260" s="3" t="n">
+        <v>0.7547</v>
+      </c>
+      <c r="H260" s="2" t="n">
+        <v>0.6531999999999999</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>4</v>
+      </c>
+      <c r="D261" t="n">
+        <v>4</v>
+      </c>
+      <c r="E261" t="n">
+        <v>4</v>
+      </c>
+      <c r="F261" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G261" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H261" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C262" t="n">
+        <v>4516</v>
+      </c>
+      <c r="D262" t="n">
+        <v>3363</v>
+      </c>
+      <c r="E262" t="n">
+        <v>3817</v>
+      </c>
+      <c r="F262" s="2" t="n">
+        <v>0.7447</v>
+      </c>
+      <c r="G262" s="3" t="n">
+        <v>0.8452</v>
+      </c>
+      <c r="H262" s="2" t="n">
+        <v>0.6008</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C263" t="n">
+        <v>77</v>
+      </c>
+      <c r="D263" t="n">
+        <v>77</v>
+      </c>
+      <c r="E263" t="n">
+        <v>77</v>
+      </c>
+      <c r="F263" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G263" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H263" s="2" t="n">
+        <v>0.4087</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
+        <v>0</v>
+      </c>
+      <c r="D264" t="n">
+        <v>0</v>
+      </c>
+      <c r="E264" t="n">
+        <v>0</v>
+      </c>
+      <c r="F264" s="2" t="n"/>
+      <c r="G264" s="3" t="n"/>
+      <c r="H264" s="2" t="n"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C265" t="n">
+        <v>4904</v>
+      </c>
+      <c r="D265" t="n">
+        <v>4099</v>
+      </c>
+      <c r="E265" t="n">
+        <v>4808</v>
+      </c>
+      <c r="F265" s="2" t="n">
+        <v>0.8358</v>
+      </c>
+      <c r="G265" s="3" t="n">
+        <v>0.9804</v>
+      </c>
+      <c r="H265" s="2" t="n">
+        <v>0.5846</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>13943</v>
+      </c>
+      <c r="D266" t="n">
+        <v>11691</v>
+      </c>
+      <c r="E266" t="n">
+        <v>11691</v>
+      </c>
+      <c r="F266" s="2" t="n">
+        <v>0.8384999999999999</v>
+      </c>
+      <c r="G266" s="3" t="n">
+        <v>0.8384999999999999</v>
+      </c>
+      <c r="H266" s="2" t="n">
+        <v>0.6227</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>0</v>
+      </c>
+      <c r="D267" t="n">
+        <v>0</v>
+      </c>
+      <c r="E267" t="n">
+        <v>0</v>
+      </c>
+      <c r="F267" s="2" t="n"/>
+      <c r="G267" s="3" t="n"/>
+      <c r="H267" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H253"/>
+  <autoFilter ref="A1:H267"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$267</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$281</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -513,22 +513,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>43289</v>
+        <v>45043</v>
       </c>
       <c r="C3" t="n">
-        <v>35498</v>
+        <v>35963</v>
       </c>
       <c r="D3" t="n">
-        <v>37625</v>
+        <v>38090</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.82</v>
+        <v>0.7984</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.8692</v>
+        <v>0.8456</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.8351000000000001</v>
+        <v>0.7948999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -538,22 +538,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>397935</v>
+        <v>411583</v>
       </c>
       <c r="C4" t="n">
-        <v>311000</v>
+        <v>313332</v>
       </c>
       <c r="D4" t="n">
-        <v>348544</v>
+        <v>350876</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.7815000000000001</v>
+        <v>0.7613</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.8759</v>
+        <v>0.8525</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.8504999999999999</v>
+        <v>0.8120000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -582,22 +582,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>673260</v>
+        <v>702838</v>
       </c>
       <c r="C6" t="n">
-        <v>509917</v>
+        <v>526037</v>
       </c>
       <c r="D6" t="n">
-        <v>578357</v>
+        <v>594477</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.7574</v>
+        <v>0.7484000000000001</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.8590000000000001</v>
+        <v>0.8458</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9153</v>
+        <v>0.8771</v>
       </c>
     </row>
     <row r="7">
@@ -607,22 +607,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>102140</v>
+        <v>105177</v>
       </c>
       <c r="C7" t="n">
-        <v>49103</v>
+        <v>49636</v>
       </c>
       <c r="D7" t="n">
-        <v>83696</v>
+        <v>84229</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.4807</v>
+        <v>0.4719</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.8194</v>
+        <v>0.8008</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6820999999999999</v>
+        <v>0.6596</v>
       </c>
     </row>
     <row r="8">
@@ -632,22 +632,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>139534</v>
+        <v>144589</v>
       </c>
       <c r="C8" t="n">
-        <v>97739</v>
+        <v>98614</v>
       </c>
       <c r="D8" t="n">
-        <v>109745</v>
+        <v>110620</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.7005</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.7865000000000001</v>
+        <v>0.7651</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8426</v>
+        <v>0.8065000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -682,22 +682,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>86864</v>
+        <v>90477</v>
       </c>
       <c r="C10" t="n">
-        <v>69225</v>
+        <v>69670</v>
       </c>
       <c r="D10" t="n">
-        <v>73540</v>
+        <v>73985</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.7968999999999999</v>
+        <v>0.77</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.8466</v>
+        <v>0.8177</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.8695999999999999</v>
+        <v>0.828</v>
       </c>
     </row>
     <row r="11">
@@ -707,13 +707,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3298</v>
+        <v>3315</v>
       </c>
       <c r="C11" t="n">
-        <v>3298</v>
+        <v>3315</v>
       </c>
       <c r="D11" t="n">
-        <v>3298</v>
+        <v>3315</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1</v>
@@ -722,7 +722,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.8112999999999999</v>
+        <v>0.764</v>
       </c>
     </row>
     <row r="12">
@@ -751,22 +751,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>143091</v>
+        <v>145406</v>
       </c>
       <c r="C13" t="n">
-        <v>115073</v>
+        <v>115578</v>
       </c>
       <c r="D13" t="n">
-        <v>129003</v>
+        <v>129508</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.8042</v>
+        <v>0.7948999999999999</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.9015000000000001</v>
+        <v>0.8906999999999999</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.8331999999999999</v>
+        <v>0.7909999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -776,22 +776,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>224135</v>
+        <v>235802</v>
       </c>
       <c r="C14" t="n">
-        <v>179510</v>
+        <v>182898</v>
       </c>
       <c r="D14" t="n">
-        <v>193864</v>
+        <v>197252</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.8009000000000001</v>
+        <v>0.7756000000000001</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.8649</v>
+        <v>0.8365</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.8771</v>
+        <v>0.8362000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -827,7 +827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H267"/>
+  <dimension ref="A1:H281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8378,8 +8378,400 @@
       <c r="G267" s="3" t="n"/>
       <c r="H267" s="2" t="n"/>
     </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>0</v>
+      </c>
+      <c r="D268" t="n">
+        <v>0</v>
+      </c>
+      <c r="E268" t="n">
+        <v>0</v>
+      </c>
+      <c r="F268" s="2" t="n"/>
+      <c r="G268" s="3" t="n"/>
+      <c r="H268" s="2" t="n"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C269" t="n">
+        <v>1754</v>
+      </c>
+      <c r="D269" t="n">
+        <v>465</v>
+      </c>
+      <c r="E269" t="n">
+        <v>465</v>
+      </c>
+      <c r="F269" s="2" t="n">
+        <v>0.2651</v>
+      </c>
+      <c r="G269" s="3" t="n">
+        <v>0.2651</v>
+      </c>
+      <c r="H269" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>13648</v>
+      </c>
+      <c r="D270" t="n">
+        <v>2332</v>
+      </c>
+      <c r="E270" t="n">
+        <v>2332</v>
+      </c>
+      <c r="F270" s="2" t="n">
+        <v>0.1709</v>
+      </c>
+      <c r="G270" s="3" t="n">
+        <v>0.1709</v>
+      </c>
+      <c r="H270" s="2" t="n">
+        <v>0.0125</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>0</v>
+      </c>
+      <c r="D271" t="n">
+        <v>0</v>
+      </c>
+      <c r="E271" t="n">
+        <v>0</v>
+      </c>
+      <c r="F271" s="2" t="n"/>
+      <c r="G271" s="3" t="n"/>
+      <c r="H271" s="2" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>29578</v>
+      </c>
+      <c r="D272" t="n">
+        <v>16120</v>
+      </c>
+      <c r="E272" t="n">
+        <v>16120</v>
+      </c>
+      <c r="F272" s="2" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="G272" s="3" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="H272" s="2" t="n">
+        <v>0.1491</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>3037</v>
+      </c>
+      <c r="D273" t="n">
+        <v>533</v>
+      </c>
+      <c r="E273" t="n">
+        <v>533</v>
+      </c>
+      <c r="F273" s="2" t="n">
+        <v>0.1755</v>
+      </c>
+      <c r="G273" s="3" t="n">
+        <v>0.1755</v>
+      </c>
+      <c r="H273" s="2" t="n">
+        <v>0.0476</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>5055</v>
+      </c>
+      <c r="D274" t="n">
+        <v>875</v>
+      </c>
+      <c r="E274" t="n">
+        <v>875</v>
+      </c>
+      <c r="F274" s="2" t="n">
+        <v>0.1731</v>
+      </c>
+      <c r="G274" s="3" t="n">
+        <v>0.1731</v>
+      </c>
+      <c r="H274" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>0</v>
+      </c>
+      <c r="D275" t="n">
+        <v>0</v>
+      </c>
+      <c r="E275" t="n">
+        <v>0</v>
+      </c>
+      <c r="F275" s="2" t="n"/>
+      <c r="G275" s="3" t="n"/>
+      <c r="H275" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>3613</v>
+      </c>
+      <c r="D276" t="n">
+        <v>445</v>
+      </c>
+      <c r="E276" t="n">
+        <v>445</v>
+      </c>
+      <c r="F276" s="2" t="n">
+        <v>0.1232</v>
+      </c>
+      <c r="G276" s="3" t="n">
+        <v>0.1232</v>
+      </c>
+      <c r="H276" s="2" t="n">
+        <v>0.0024</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>17</v>
+      </c>
+      <c r="D277" t="n">
+        <v>17</v>
+      </c>
+      <c r="E277" t="n">
+        <v>17</v>
+      </c>
+      <c r="F277" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G277" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H277" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>0</v>
+      </c>
+      <c r="D278" t="n">
+        <v>0</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0</v>
+      </c>
+      <c r="F278" s="2" t="n"/>
+      <c r="G278" s="3" t="n"/>
+      <c r="H278" s="2" t="n"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>2315</v>
+      </c>
+      <c r="D279" t="n">
+        <v>505</v>
+      </c>
+      <c r="E279" t="n">
+        <v>505</v>
+      </c>
+      <c r="F279" s="2" t="n">
+        <v>0.2181</v>
+      </c>
+      <c r="G279" s="3" t="n">
+        <v>0.2181</v>
+      </c>
+      <c r="H279" s="2" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>11667</v>
+      </c>
+      <c r="D280" t="n">
+        <v>3388</v>
+      </c>
+      <c r="E280" t="n">
+        <v>3388</v>
+      </c>
+      <c r="F280" s="2" t="n">
+        <v>0.2904</v>
+      </c>
+      <c r="G280" s="3" t="n">
+        <v>0.2904</v>
+      </c>
+      <c r="H280" s="2" t="n">
+        <v>0.0123</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>0</v>
+      </c>
+      <c r="D281" t="n">
+        <v>0</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0</v>
+      </c>
+      <c r="F281" s="2" t="n"/>
+      <c r="G281" s="3" t="n"/>
+      <c r="H281" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H267"/>
+  <autoFilter ref="A1:H281"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$281</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$295</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -513,22 +513,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45043</v>
+        <v>46882</v>
       </c>
       <c r="C3" t="n">
-        <v>35963</v>
+        <v>37685</v>
       </c>
       <c r="D3" t="n">
-        <v>38090</v>
+        <v>39814</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.7984</v>
+        <v>0.8038</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.8456</v>
+        <v>0.8492000000000001</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.7948999999999999</v>
+        <v>0.7862</v>
       </c>
     </row>
     <row r="4">
@@ -538,22 +538,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>411583</v>
+        <v>429893</v>
       </c>
       <c r="C4" t="n">
-        <v>313332</v>
+        <v>329768</v>
       </c>
       <c r="D4" t="n">
-        <v>350876</v>
+        <v>368403</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.7613</v>
+        <v>0.7670999999999999</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.8525</v>
+        <v>0.857</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8022</v>
       </c>
     </row>
     <row r="5">
@@ -582,22 +582,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>702838</v>
+        <v>739672</v>
       </c>
       <c r="C6" t="n">
-        <v>526037</v>
+        <v>555677</v>
       </c>
       <c r="D6" t="n">
-        <v>594477</v>
+        <v>630669</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.7484000000000001</v>
+        <v>0.7512000000000001</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.8458</v>
+        <v>0.8526</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.8771</v>
+        <v>0.8744</v>
       </c>
     </row>
     <row r="7">
@@ -607,22 +607,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>105177</v>
+        <v>108213</v>
       </c>
       <c r="C7" t="n">
-        <v>49636</v>
+        <v>51081</v>
       </c>
       <c r="D7" t="n">
-        <v>84229</v>
+        <v>87265</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.4719</v>
+        <v>0.472</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.8008</v>
+        <v>0.8064</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6596</v>
+        <v>0.6539</v>
       </c>
     </row>
     <row r="8">
@@ -632,22 +632,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>144589</v>
+        <v>150684</v>
       </c>
       <c r="C8" t="n">
-        <v>98614</v>
+        <v>102673</v>
       </c>
       <c r="D8" t="n">
-        <v>110620</v>
+        <v>116581</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.6814</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.7651</v>
+        <v>0.7737000000000001</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8065000000000001</v>
+        <v>0.8039000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="D9" t="n">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1</v>
@@ -682,22 +682,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>90477</v>
+        <v>93887</v>
       </c>
       <c r="C10" t="n">
-        <v>69670</v>
+        <v>72115</v>
       </c>
       <c r="D10" t="n">
-        <v>73985</v>
+        <v>77157</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.77</v>
+        <v>0.7681</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.8177</v>
+        <v>0.8218000000000001</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.828</v>
+        <v>0.8172</v>
       </c>
     </row>
     <row r="11">
@@ -707,13 +707,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3315</v>
+        <v>3480</v>
       </c>
       <c r="C11" t="n">
-        <v>3315</v>
+        <v>3480</v>
       </c>
       <c r="D11" t="n">
-        <v>3315</v>
+        <v>3480</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1</v>
@@ -722,7 +722,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.764</v>
+        <v>0.7487999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -751,22 +751,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>145406</v>
+        <v>147962</v>
       </c>
       <c r="C13" t="n">
-        <v>115578</v>
+        <v>117651</v>
       </c>
       <c r="D13" t="n">
-        <v>129508</v>
+        <v>131968</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.7948999999999999</v>
+        <v>0.7951</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.8906999999999999</v>
+        <v>0.8919</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.7909999999999999</v>
+        <v>0.7778</v>
       </c>
     </row>
     <row r="14">
@@ -776,22 +776,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>235802</v>
+        <v>249090</v>
       </c>
       <c r="C14" t="n">
-        <v>182898</v>
+        <v>194066</v>
       </c>
       <c r="D14" t="n">
-        <v>197252</v>
+        <v>209914</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.7756000000000001</v>
+        <v>0.7791</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.8365</v>
+        <v>0.8427</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.8362000000000001</v>
+        <v>0.8294</v>
       </c>
     </row>
     <row r="15">
@@ -827,7 +827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H281"/>
+  <dimension ref="A1:H295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8770,8 +8770,404 @@
       <c r="G281" s="3" t="n"/>
       <c r="H281" s="2" t="n"/>
     </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C282" t="n">
+        <v>0</v>
+      </c>
+      <c r="D282" t="n">
+        <v>0</v>
+      </c>
+      <c r="E282" t="n">
+        <v>0</v>
+      </c>
+      <c r="F282" s="2" t="n"/>
+      <c r="G282" s="3" t="n"/>
+      <c r="H282" s="2" t="n"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C283" t="n">
+        <v>1839</v>
+      </c>
+      <c r="D283" t="n">
+        <v>1722</v>
+      </c>
+      <c r="E283" t="n">
+        <v>1724</v>
+      </c>
+      <c r="F283" s="2" t="n">
+        <v>0.9364</v>
+      </c>
+      <c r="G283" s="3" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="H283" s="2" t="n">
+        <v>0.6119</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C284" t="n">
+        <v>18310</v>
+      </c>
+      <c r="D284" t="n">
+        <v>16436</v>
+      </c>
+      <c r="E284" t="n">
+        <v>17527</v>
+      </c>
+      <c r="F284" s="2" t="n">
+        <v>0.8976999999999999</v>
+      </c>
+      <c r="G284" s="3" t="n">
+        <v>0.9571999999999999</v>
+      </c>
+      <c r="H284" s="2" t="n">
+        <v>0.5895</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C285" t="n">
+        <v>0</v>
+      </c>
+      <c r="D285" t="n">
+        <v>0</v>
+      </c>
+      <c r="E285" t="n">
+        <v>0</v>
+      </c>
+      <c r="F285" s="2" t="n"/>
+      <c r="G285" s="3" t="n"/>
+      <c r="H285" s="2" t="n"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C286" t="n">
+        <v>36834</v>
+      </c>
+      <c r="D286" t="n">
+        <v>29640</v>
+      </c>
+      <c r="E286" t="n">
+        <v>36192</v>
+      </c>
+      <c r="F286" s="2" t="n">
+        <v>0.8047</v>
+      </c>
+      <c r="G286" s="3" t="n">
+        <v>0.9826</v>
+      </c>
+      <c r="H286" s="2" t="n">
+        <v>0.8204</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C287" t="n">
+        <v>3036</v>
+      </c>
+      <c r="D287" t="n">
+        <v>1445</v>
+      </c>
+      <c r="E287" t="n">
+        <v>3036</v>
+      </c>
+      <c r="F287" s="2" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="G287" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H287" s="2" t="n">
+        <v>0.4878</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C288" t="n">
+        <v>6095</v>
+      </c>
+      <c r="D288" t="n">
+        <v>4059</v>
+      </c>
+      <c r="E288" t="n">
+        <v>5961</v>
+      </c>
+      <c r="F288" s="2" t="n">
+        <v>0.6659999999999999</v>
+      </c>
+      <c r="G288" s="3" t="n">
+        <v>0.978</v>
+      </c>
+      <c r="H288" s="2" t="n">
+        <v>0.7531</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C289" t="n">
+        <v>21</v>
+      </c>
+      <c r="D289" t="n">
+        <v>21</v>
+      </c>
+      <c r="E289" t="n">
+        <v>21</v>
+      </c>
+      <c r="F289" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G289" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H289" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C290" t="n">
+        <v>3410</v>
+      </c>
+      <c r="D290" t="n">
+        <v>2445</v>
+      </c>
+      <c r="E290" t="n">
+        <v>3172</v>
+      </c>
+      <c r="F290" s="2" t="n">
+        <v>0.7170000000000001</v>
+      </c>
+      <c r="G290" s="3" t="n">
+        <v>0.9301999999999999</v>
+      </c>
+      <c r="H290" s="2" t="n">
+        <v>0.5760999999999999</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C291" t="n">
+        <v>165</v>
+      </c>
+      <c r="D291" t="n">
+        <v>165</v>
+      </c>
+      <c r="E291" t="n">
+        <v>165</v>
+      </c>
+      <c r="F291" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G291" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H291" s="2" t="n">
+        <v>0.4242</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C292" t="n">
+        <v>0</v>
+      </c>
+      <c r="D292" t="n">
+        <v>0</v>
+      </c>
+      <c r="E292" t="n">
+        <v>0</v>
+      </c>
+      <c r="F292" s="2" t="n"/>
+      <c r="G292" s="3" t="n"/>
+      <c r="H292" s="2" t="n"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C293" t="n">
+        <v>2556</v>
+      </c>
+      <c r="D293" t="n">
+        <v>2073</v>
+      </c>
+      <c r="E293" t="n">
+        <v>2460</v>
+      </c>
+      <c r="F293" s="2" t="n">
+        <v>0.8109999999999999</v>
+      </c>
+      <c r="G293" s="3" t="n">
+        <v>0.9623999999999999</v>
+      </c>
+      <c r="H293" s="2" t="n">
+        <v>0.5035000000000001</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>13288</v>
+      </c>
+      <c r="D294" t="n">
+        <v>11168</v>
+      </c>
+      <c r="E294" t="n">
+        <v>12662</v>
+      </c>
+      <c r="F294" s="2" t="n">
+        <v>0.8405</v>
+      </c>
+      <c r="G294" s="3" t="n">
+        <v>0.9529000000000001</v>
+      </c>
+      <c r="H294" s="2" t="n">
+        <v>0.6856</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>0</v>
+      </c>
+      <c r="D295" t="n">
+        <v>0</v>
+      </c>
+      <c r="E295" t="n">
+        <v>0</v>
+      </c>
+      <c r="F295" s="2" t="n"/>
+      <c r="G295" s="3" t="n"/>
+      <c r="H295" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H281"/>
+  <autoFilter ref="A1:H295"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$295</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$309</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -513,22 +513,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>46882</v>
+        <v>49913</v>
       </c>
       <c r="C3" t="n">
-        <v>37685</v>
+        <v>40667</v>
       </c>
       <c r="D3" t="n">
-        <v>39814</v>
+        <v>42796</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.8038</v>
+        <v>0.8148000000000001</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.8492000000000001</v>
+        <v>0.8573999999999999</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.7862</v>
+        <v>0.7887000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -538,19 +538,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>429893</v>
+        <v>451207</v>
       </c>
       <c r="C4" t="n">
-        <v>329768</v>
+        <v>349128</v>
       </c>
       <c r="D4" t="n">
-        <v>368403</v>
+        <v>388346</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.7670999999999999</v>
+        <v>0.7737999999999999</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.857</v>
+        <v>0.8606999999999999</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>0.8022</v>
@@ -582,22 +582,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>739672</v>
+        <v>779412</v>
       </c>
       <c r="C6" t="n">
-        <v>555677</v>
+        <v>590717</v>
       </c>
       <c r="D6" t="n">
-        <v>630669</v>
+        <v>670239</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.7512000000000001</v>
+        <v>0.7579</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.8526</v>
+        <v>0.8599</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.8744</v>
+        <v>0.873</v>
       </c>
     </row>
     <row r="7">
@@ -607,22 +607,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>108213</v>
+        <v>113392</v>
       </c>
       <c r="C7" t="n">
-        <v>51081</v>
+        <v>56160</v>
       </c>
       <c r="D7" t="n">
-        <v>87265</v>
+        <v>92436</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.472</v>
+        <v>0.4953</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.8064</v>
+        <v>0.8151999999999999</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6539</v>
+        <v>0.6593000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -632,22 +632,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>150684</v>
+        <v>156618</v>
       </c>
       <c r="C8" t="n">
-        <v>102673</v>
+        <v>106876</v>
       </c>
       <c r="D8" t="n">
-        <v>116581</v>
+        <v>122499</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.6814</v>
+        <v>0.6823999999999999</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.7737000000000001</v>
+        <v>0.7822</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8039000000000001</v>
+        <v>0.7975</v>
       </c>
     </row>
     <row r="9">
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D9" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1</v>
@@ -682,22 +682,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>93887</v>
+        <v>99384</v>
       </c>
       <c r="C10" t="n">
-        <v>72115</v>
+        <v>77417</v>
       </c>
       <c r="D10" t="n">
-        <v>77157</v>
+        <v>82516</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.7681</v>
+        <v>0.779</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.8218000000000001</v>
+        <v>0.8303</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.8172</v>
+        <v>0.8181999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -707,13 +707,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3480</v>
+        <v>3819</v>
       </c>
       <c r="C11" t="n">
-        <v>3480</v>
+        <v>3819</v>
       </c>
       <c r="D11" t="n">
-        <v>3480</v>
+        <v>3819</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1</v>
@@ -722,7 +722,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.7487999999999999</v>
+        <v>0.7504999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -751,22 +751,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>147962</v>
+        <v>159590</v>
       </c>
       <c r="C13" t="n">
-        <v>117651</v>
+        <v>129114</v>
       </c>
       <c r="D13" t="n">
-        <v>131968</v>
+        <v>143594</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.7951</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.8919</v>
+        <v>0.8998</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.7778</v>
+        <v>0.7798</v>
       </c>
     </row>
     <row r="14">
@@ -776,22 +776,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>249090</v>
+        <v>266855</v>
       </c>
       <c r="C14" t="n">
-        <v>194066</v>
+        <v>210489</v>
       </c>
       <c r="D14" t="n">
-        <v>209914</v>
+        <v>227453</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.7791</v>
+        <v>0.7887999999999999</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.8427</v>
+        <v>0.8523000000000001</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.8294</v>
+        <v>0.8315</v>
       </c>
     </row>
     <row r="15">
@@ -827,7 +827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H295"/>
+  <dimension ref="A1:H309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9166,8 +9166,404 @@
       <c r="G295" s="3" t="n"/>
       <c r="H295" s="2" t="n"/>
     </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C296" t="n">
+        <v>0</v>
+      </c>
+      <c r="D296" t="n">
+        <v>0</v>
+      </c>
+      <c r="E296" t="n">
+        <v>0</v>
+      </c>
+      <c r="F296" s="2" t="n"/>
+      <c r="G296" s="3" t="n"/>
+      <c r="H296" s="2" t="n"/>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C297" t="n">
+        <v>3031</v>
+      </c>
+      <c r="D297" t="n">
+        <v>2982</v>
+      </c>
+      <c r="E297" t="n">
+        <v>2982</v>
+      </c>
+      <c r="F297" s="2" t="n">
+        <v>0.9838</v>
+      </c>
+      <c r="G297" s="3" t="n">
+        <v>0.9838</v>
+      </c>
+      <c r="H297" s="2" t="n">
+        <v>0.8367</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C298" t="n">
+        <v>21314</v>
+      </c>
+      <c r="D298" t="n">
+        <v>19360</v>
+      </c>
+      <c r="E298" t="n">
+        <v>19943</v>
+      </c>
+      <c r="F298" s="2" t="n">
+        <v>0.9083</v>
+      </c>
+      <c r="G298" s="3" t="n">
+        <v>0.9357</v>
+      </c>
+      <c r="H298" s="2" t="n">
+        <v>0.8018000000000001</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C299" t="n">
+        <v>0</v>
+      </c>
+      <c r="D299" t="n">
+        <v>0</v>
+      </c>
+      <c r="E299" t="n">
+        <v>0</v>
+      </c>
+      <c r="F299" s="2" t="n"/>
+      <c r="G299" s="3" t="n"/>
+      <c r="H299" s="2" t="n"/>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C300" t="n">
+        <v>39740</v>
+      </c>
+      <c r="D300" t="n">
+        <v>35040</v>
+      </c>
+      <c r="E300" t="n">
+        <v>39570</v>
+      </c>
+      <c r="F300" s="2" t="n">
+        <v>0.8817</v>
+      </c>
+      <c r="G300" s="3" t="n">
+        <v>0.9956999999999999</v>
+      </c>
+      <c r="H300" s="2" t="n">
+        <v>0.8459</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C301" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D301" t="n">
+        <v>5079</v>
+      </c>
+      <c r="E301" t="n">
+        <v>5171</v>
+      </c>
+      <c r="F301" s="2" t="n">
+        <v>0.9806999999999999</v>
+      </c>
+      <c r="G301" s="3" t="n">
+        <v>0.9984999999999999</v>
+      </c>
+      <c r="H301" s="2" t="n">
+        <v>0.8378</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C302" t="n">
+        <v>5934</v>
+      </c>
+      <c r="D302" t="n">
+        <v>4203</v>
+      </c>
+      <c r="E302" t="n">
+        <v>5918</v>
+      </c>
+      <c r="F302" s="2" t="n">
+        <v>0.7082999999999999</v>
+      </c>
+      <c r="G302" s="3" t="n">
+        <v>0.9973000000000001</v>
+      </c>
+      <c r="H302" s="2" t="n">
+        <v>0.6758</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C303" t="n">
+        <v>4</v>
+      </c>
+      <c r="D303" t="n">
+        <v>4</v>
+      </c>
+      <c r="E303" t="n">
+        <v>4</v>
+      </c>
+      <c r="F303" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G303" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H303" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C304" t="n">
+        <v>5497</v>
+      </c>
+      <c r="D304" t="n">
+        <v>5302</v>
+      </c>
+      <c r="E304" t="n">
+        <v>5359</v>
+      </c>
+      <c r="F304" s="2" t="n">
+        <v>0.9645</v>
+      </c>
+      <c r="G304" s="3" t="n">
+        <v>0.9749</v>
+      </c>
+      <c r="H304" s="2" t="n">
+        <v>0.8384</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C305" t="n">
+        <v>339</v>
+      </c>
+      <c r="D305" t="n">
+        <v>339</v>
+      </c>
+      <c r="E305" t="n">
+        <v>339</v>
+      </c>
+      <c r="F305" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G305" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H305" s="2" t="n">
+        <v>0.7903</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C306" t="n">
+        <v>0</v>
+      </c>
+      <c r="D306" t="n">
+        <v>0</v>
+      </c>
+      <c r="E306" t="n">
+        <v>0</v>
+      </c>
+      <c r="F306" s="2" t="n"/>
+      <c r="G306" s="3" t="n"/>
+      <c r="H306" s="2" t="n"/>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C307" t="n">
+        <v>11628</v>
+      </c>
+      <c r="D307" t="n">
+        <v>11463</v>
+      </c>
+      <c r="E307" t="n">
+        <v>11626</v>
+      </c>
+      <c r="F307" s="2" t="n">
+        <v>0.9858</v>
+      </c>
+      <c r="G307" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="H307" s="2" t="n">
+        <v>0.8190000000000001</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C308" t="n">
+        <v>17765</v>
+      </c>
+      <c r="D308" t="n">
+        <v>16423</v>
+      </c>
+      <c r="E308" t="n">
+        <v>17539</v>
+      </c>
+      <c r="F308" s="2" t="n">
+        <v>0.9245</v>
+      </c>
+      <c r="G308" s="3" t="n">
+        <v>0.9873000000000001</v>
+      </c>
+      <c r="H308" s="2" t="n">
+        <v>0.8741</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C309" t="n">
+        <v>0</v>
+      </c>
+      <c r="D309" t="n">
+        <v>0</v>
+      </c>
+      <c r="E309" t="n">
+        <v>0</v>
+      </c>
+      <c r="F309" s="2" t="n"/>
+      <c r="G309" s="3" t="n"/>
+      <c r="H309" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H295"/>
+  <autoFilter ref="A1:H309"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -553,7 +553,7 @@
         <v>0.8606999999999999</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.8022</v>
+        <v>0.8024</v>
       </c>
     </row>
     <row r="5">
@@ -597,7 +597,7 @@
         <v>0.8599</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.873</v>
+        <v>0.8731</v>
       </c>
     </row>
     <row r="7">
@@ -622,7 +622,7 @@
         <v>0.8151999999999999</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6593000000000001</v>
+        <v>0.6587000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -647,7 +647,7 @@
         <v>0.7822</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.7975</v>
+        <v>0.7977</v>
       </c>
     </row>
     <row r="9">
@@ -697,7 +697,7 @@
         <v>0.8303</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.8181999999999999</v>
+        <v>0.8184</v>
       </c>
     </row>
     <row r="11">
@@ -766,7 +766,7 @@
         <v>0.8998</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.7798</v>
+        <v>0.7795000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -791,7 +791,7 @@
         <v>0.8523000000000001</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.8315</v>
+        <v>0.8312999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -9217,7 +9217,7 @@
         <v>0.9838</v>
       </c>
       <c r="H297" s="2" t="n">
-        <v>0.8367</v>
+        <v>0.8368000000000001</v>
       </c>
     </row>
     <row r="298">
@@ -9247,7 +9247,7 @@
         <v>0.9357</v>
       </c>
       <c r="H298" s="2" t="n">
-        <v>0.8018000000000001</v>
+        <v>0.8072</v>
       </c>
     </row>
     <row r="299">
@@ -9301,7 +9301,7 @@
         <v>0.9956999999999999</v>
       </c>
       <c r="H300" s="2" t="n">
-        <v>0.8459</v>
+        <v>0.8481000000000001</v>
       </c>
     </row>
     <row r="301">
@@ -9331,7 +9331,7 @@
         <v>0.9984999999999999</v>
       </c>
       <c r="H301" s="2" t="n">
-        <v>0.8378</v>
+        <v>0.8286</v>
       </c>
     </row>
     <row r="302">
@@ -9361,7 +9361,7 @@
         <v>0.9973000000000001</v>
       </c>
       <c r="H302" s="2" t="n">
-        <v>0.6758</v>
+        <v>0.6743000000000001</v>
       </c>
     </row>
     <row r="303">
@@ -9421,7 +9421,7 @@
         <v>0.9749</v>
       </c>
       <c r="H304" s="2" t="n">
-        <v>0.8384</v>
+        <v>0.8408</v>
       </c>
     </row>
     <row r="305">
@@ -9505,7 +9505,7 @@
         <v>0.9998</v>
       </c>
       <c r="H307" s="2" t="n">
-        <v>0.8190000000000001</v>
+        <v>0.8112999999999999</v>
       </c>
     </row>
     <row r="308">
@@ -9535,7 +9535,7 @@
         <v>0.9873000000000001</v>
       </c>
       <c r="H308" s="2" t="n">
-        <v>0.8741</v>
+        <v>0.8691</v>
       </c>
     </row>
     <row r="309">

--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$309</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$323</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -513,22 +513,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>49913</v>
+        <v>52860</v>
       </c>
       <c r="C3" t="n">
-        <v>40667</v>
+        <v>43496</v>
       </c>
       <c r="D3" t="n">
-        <v>42796</v>
+        <v>45629</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.8148000000000001</v>
+        <v>0.8229000000000001</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.8573999999999999</v>
+        <v>0.8632</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.7887000000000001</v>
+        <v>0.7816</v>
       </c>
     </row>
     <row r="4">
@@ -538,22 +538,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>451207</v>
+        <v>469203</v>
       </c>
       <c r="C4" t="n">
-        <v>349128</v>
+        <v>366323</v>
       </c>
       <c r="D4" t="n">
-        <v>388346</v>
+        <v>405710</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.7737999999999999</v>
+        <v>0.7806999999999999</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.8606999999999999</v>
+        <v>0.8647</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.8024</v>
+        <v>0.797</v>
       </c>
     </row>
     <row r="5">
@@ -573,7 +573,9 @@
       </c>
       <c r="E5" s="2" t="n"/>
       <c r="F5" s="3" t="n"/>
-      <c r="G5" s="2" t="n"/>
+      <c r="G5" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -582,22 +584,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>779412</v>
+        <v>816742</v>
       </c>
       <c r="C6" t="n">
-        <v>590717</v>
+        <v>623483</v>
       </c>
       <c r="D6" t="n">
-        <v>670239</v>
+        <v>707545</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.7579</v>
+        <v>0.7634000000000001</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.8599</v>
+        <v>0.8663</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.8731</v>
+        <v>0.868</v>
       </c>
     </row>
     <row r="7">
@@ -607,22 +609,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>113392</v>
+        <v>118157</v>
       </c>
       <c r="C7" t="n">
-        <v>56160</v>
+        <v>60814</v>
       </c>
       <c r="D7" t="n">
-        <v>92436</v>
+        <v>97201</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.4953</v>
+        <v>0.5146999999999999</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.8151999999999999</v>
+        <v>0.8226</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6587000000000001</v>
+        <v>0.6626000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -632,22 +634,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>156618</v>
+        <v>161812</v>
       </c>
       <c r="C8" t="n">
-        <v>106876</v>
+        <v>110726</v>
       </c>
       <c r="D8" t="n">
-        <v>122499</v>
+        <v>126349</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.6823999999999999</v>
+        <v>0.6843</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.7822</v>
+        <v>0.7807999999999999</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.7977</v>
+        <v>0.7907</v>
       </c>
     </row>
     <row r="9">
@@ -657,13 +659,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C9" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D9" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1</v>
@@ -682,22 +684,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>99384</v>
+        <v>103995</v>
       </c>
       <c r="C10" t="n">
-        <v>77417</v>
+        <v>81465</v>
       </c>
       <c r="D10" t="n">
-        <v>82516</v>
+        <v>86624</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.779</v>
+        <v>0.7834</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.8303</v>
+        <v>0.833</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.8184</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -707,13 +709,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3819</v>
+        <v>4022</v>
       </c>
       <c r="C11" t="n">
-        <v>3819</v>
+        <v>4022</v>
       </c>
       <c r="D11" t="n">
-        <v>3819</v>
+        <v>4022</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1</v>
@@ -722,7 +724,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.7504999999999999</v>
+        <v>0.7382</v>
       </c>
     </row>
     <row r="12">
@@ -751,22 +753,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>159590</v>
+        <v>166703</v>
       </c>
       <c r="C13" t="n">
-        <v>129114</v>
+        <v>136115</v>
       </c>
       <c r="D13" t="n">
-        <v>143594</v>
+        <v>150691</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8165</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.8998</v>
+        <v>0.9039</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.7795000000000001</v>
+        <v>0.7734000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -776,22 +778,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>266855</v>
+        <v>281907</v>
       </c>
       <c r="C14" t="n">
-        <v>210489</v>
+        <v>224330</v>
       </c>
       <c r="D14" t="n">
-        <v>227453</v>
+        <v>242104</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.7887999999999999</v>
+        <v>0.7958</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.8523000000000001</v>
+        <v>0.8588</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.8312999999999999</v>
+        <v>0.8248000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -827,7 +829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H309"/>
+  <dimension ref="A1:H323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9562,8 +9564,408 @@
       <c r="G309" s="3" t="n"/>
       <c r="H309" s="2" t="n"/>
     </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C310" t="n">
+        <v>0</v>
+      </c>
+      <c r="D310" t="n">
+        <v>0</v>
+      </c>
+      <c r="E310" t="n">
+        <v>0</v>
+      </c>
+      <c r="F310" s="2" t="n"/>
+      <c r="G310" s="3" t="n"/>
+      <c r="H310" s="2" t="n"/>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C311" t="n">
+        <v>2947</v>
+      </c>
+      <c r="D311" t="n">
+        <v>2829</v>
+      </c>
+      <c r="E311" t="n">
+        <v>2833</v>
+      </c>
+      <c r="F311" s="2" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G311" s="3" t="n">
+        <v>0.9612999999999999</v>
+      </c>
+      <c r="H311" s="2" t="n">
+        <v>0.6568000000000001</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C312" t="n">
+        <v>17996</v>
+      </c>
+      <c r="D312" t="n">
+        <v>17195</v>
+      </c>
+      <c r="E312" t="n">
+        <v>17364</v>
+      </c>
+      <c r="F312" s="2" t="n">
+        <v>0.9555</v>
+      </c>
+      <c r="G312" s="3" t="n">
+        <v>0.9649</v>
+      </c>
+      <c r="H312" s="2" t="n">
+        <v>0.6884999999999999</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C313" t="n">
+        <v>0</v>
+      </c>
+      <c r="D313" t="n">
+        <v>0</v>
+      </c>
+      <c r="E313" t="n">
+        <v>0</v>
+      </c>
+      <c r="F313" s="2" t="n"/>
+      <c r="G313" s="3" t="n"/>
+      <c r="H313" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C314" t="n">
+        <v>37330</v>
+      </c>
+      <c r="D314" t="n">
+        <v>32766</v>
+      </c>
+      <c r="E314" t="n">
+        <v>37306</v>
+      </c>
+      <c r="F314" s="2" t="n">
+        <v>0.8776999999999999</v>
+      </c>
+      <c r="G314" s="3" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="H314" s="2" t="n">
+        <v>0.7720999999999999</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C315" t="n">
+        <v>4765</v>
+      </c>
+      <c r="D315" t="n">
+        <v>4654</v>
+      </c>
+      <c r="E315" t="n">
+        <v>4765</v>
+      </c>
+      <c r="F315" s="2" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="G315" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H315" s="2" t="n">
+        <v>0.7726999999999999</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C316" t="n">
+        <v>5194</v>
+      </c>
+      <c r="D316" t="n">
+        <v>3850</v>
+      </c>
+      <c r="E316" t="n">
+        <v>3850</v>
+      </c>
+      <c r="F316" s="2" t="n">
+        <v>0.7412000000000001</v>
+      </c>
+      <c r="G316" s="3" t="n">
+        <v>0.7412000000000001</v>
+      </c>
+      <c r="H316" s="2" t="n">
+        <v>0.6456999999999999</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C317" t="n">
+        <v>3</v>
+      </c>
+      <c r="D317" t="n">
+        <v>3</v>
+      </c>
+      <c r="E317" t="n">
+        <v>3</v>
+      </c>
+      <c r="F317" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G317" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H317" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C318" t="n">
+        <v>4611</v>
+      </c>
+      <c r="D318" t="n">
+        <v>4048</v>
+      </c>
+      <c r="E318" t="n">
+        <v>4108</v>
+      </c>
+      <c r="F318" s="2" t="n">
+        <v>0.8779</v>
+      </c>
+      <c r="G318" s="3" t="n">
+        <v>0.8909</v>
+      </c>
+      <c r="H318" s="2" t="n">
+        <v>0.6667000000000001</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C319" t="n">
+        <v>203</v>
+      </c>
+      <c r="D319" t="n">
+        <v>203</v>
+      </c>
+      <c r="E319" t="n">
+        <v>203</v>
+      </c>
+      <c r="F319" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G319" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H319" s="2" t="n">
+        <v>0.4638</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C320" t="n">
+        <v>0</v>
+      </c>
+      <c r="D320" t="n">
+        <v>0</v>
+      </c>
+      <c r="E320" t="n">
+        <v>0</v>
+      </c>
+      <c r="F320" s="2" t="n"/>
+      <c r="G320" s="3" t="n"/>
+      <c r="H320" s="2" t="n"/>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C321" t="n">
+        <v>7113</v>
+      </c>
+      <c r="D321" t="n">
+        <v>7001</v>
+      </c>
+      <c r="E321" t="n">
+        <v>7097</v>
+      </c>
+      <c r="F321" s="2" t="n">
+        <v>0.9843000000000001</v>
+      </c>
+      <c r="G321" s="3" t="n">
+        <v>0.9978</v>
+      </c>
+      <c r="H321" s="2" t="n">
+        <v>0.6556999999999999</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C322" t="n">
+        <v>15052</v>
+      </c>
+      <c r="D322" t="n">
+        <v>13841</v>
+      </c>
+      <c r="E322" t="n">
+        <v>14651</v>
+      </c>
+      <c r="F322" s="2" t="n">
+        <v>0.9195</v>
+      </c>
+      <c r="G322" s="3" t="n">
+        <v>0.9734</v>
+      </c>
+      <c r="H322" s="2" t="n">
+        <v>0.7001000000000001</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C323" t="n">
+        <v>0</v>
+      </c>
+      <c r="D323" t="n">
+        <v>0</v>
+      </c>
+      <c r="E323" t="n">
+        <v>0</v>
+      </c>
+      <c r="F323" s="2" t="n"/>
+      <c r="G323" s="3" t="n"/>
+      <c r="H323" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H309"/>
+  <autoFilter ref="A1:H323"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$323</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$337</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -513,22 +513,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>52860</v>
+        <v>54856</v>
       </c>
       <c r="C3" t="n">
-        <v>43496</v>
+        <v>45468</v>
       </c>
       <c r="D3" t="n">
-        <v>45629</v>
+        <v>47602</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.8229000000000001</v>
+        <v>0.8289</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.8632</v>
+        <v>0.8678</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.7816</v>
+        <v>0.7748</v>
       </c>
     </row>
     <row r="4">
@@ -538,22 +538,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>469203</v>
+        <v>490301</v>
       </c>
       <c r="C4" t="n">
-        <v>366323</v>
+        <v>386936</v>
       </c>
       <c r="D4" t="n">
-        <v>405710</v>
+        <v>426423</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.7806999999999999</v>
+        <v>0.7892</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.8647</v>
+        <v>0.8697</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.797</v>
+        <v>0.7965000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -584,22 +584,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>816742</v>
+        <v>848163</v>
       </c>
       <c r="C6" t="n">
-        <v>623483</v>
+        <v>650697</v>
       </c>
       <c r="D6" t="n">
-        <v>707545</v>
+        <v>738883</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.7634000000000001</v>
+        <v>0.7672</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.8663</v>
+        <v>0.8712000000000001</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.868</v>
+        <v>0.8609</v>
       </c>
     </row>
     <row r="7">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>118157</v>
+        <v>122538</v>
       </c>
       <c r="C7" t="n">
-        <v>60814</v>
+        <v>65190</v>
       </c>
       <c r="D7" t="n">
-        <v>97201</v>
+        <v>101580</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.5146999999999999</v>
+        <v>0.532</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.8226</v>
+        <v>0.8290000000000001</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6626000000000001</v>
+        <v>0.6627</v>
       </c>
     </row>
     <row r="8">
@@ -634,22 +634,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>161812</v>
+        <v>167442</v>
       </c>
       <c r="C8" t="n">
-        <v>110726</v>
+        <v>115002</v>
       </c>
       <c r="D8" t="n">
-        <v>126349</v>
+        <v>131968</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.6843</v>
+        <v>0.6868000000000001</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.7807999999999999</v>
+        <v>0.7881</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.7907</v>
+        <v>0.7875</v>
       </c>
     </row>
     <row r="9">
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="C9" t="n">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="D9" t="n">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1</v>
@@ -684,22 +684,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>103995</v>
+        <v>107449</v>
       </c>
       <c r="C10" t="n">
-        <v>81465</v>
+        <v>84850</v>
       </c>
       <c r="D10" t="n">
-        <v>86624</v>
+        <v>90014</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.7834</v>
+        <v>0.7897</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.833</v>
+        <v>0.8377</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.7998999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -709,13 +709,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4022</v>
+        <v>4445</v>
       </c>
       <c r="C11" t="n">
-        <v>4022</v>
+        <v>4445</v>
       </c>
       <c r="D11" t="n">
-        <v>4022</v>
+        <v>4445</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1</v>
@@ -724,7 +724,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.7382</v>
+        <v>0.7265999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -753,22 +753,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>166703</v>
+        <v>172042</v>
       </c>
       <c r="C13" t="n">
-        <v>136115</v>
+        <v>141324</v>
       </c>
       <c r="D13" t="n">
-        <v>150691</v>
+        <v>156017</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.8165</v>
+        <v>0.8215</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.9039</v>
+        <v>0.9068999999999999</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.7734000000000001</v>
+        <v>0.7672</v>
       </c>
     </row>
     <row r="14">
@@ -778,22 +778,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>281907</v>
+        <v>297551</v>
       </c>
       <c r="C14" t="n">
-        <v>224330</v>
+        <v>238464</v>
       </c>
       <c r="D14" t="n">
-        <v>242104</v>
+        <v>256238</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.7958</v>
+        <v>0.8014</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.8588</v>
+        <v>0.8612000000000001</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.8248000000000001</v>
+        <v>0.8197</v>
       </c>
     </row>
     <row r="15">
@@ -829,7 +829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H323"/>
+  <dimension ref="A1:H337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9964,8 +9964,408 @@
         <v>0</v>
       </c>
     </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C324" t="n">
+        <v>0</v>
+      </c>
+      <c r="D324" t="n">
+        <v>0</v>
+      </c>
+      <c r="E324" t="n">
+        <v>0</v>
+      </c>
+      <c r="F324" s="2" t="n"/>
+      <c r="G324" s="3" t="n"/>
+      <c r="H324" s="2" t="n"/>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C325" t="n">
+        <v>1996</v>
+      </c>
+      <c r="D325" t="n">
+        <v>1972</v>
+      </c>
+      <c r="E325" t="n">
+        <v>1973</v>
+      </c>
+      <c r="F325" s="2" t="n">
+        <v>0.988</v>
+      </c>
+      <c r="G325" s="3" t="n">
+        <v>0.9884999999999999</v>
+      </c>
+      <c r="H325" s="2" t="n">
+        <v>0.6486</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C326" t="n">
+        <v>21098</v>
+      </c>
+      <c r="D326" t="n">
+        <v>20613</v>
+      </c>
+      <c r="E326" t="n">
+        <v>20713</v>
+      </c>
+      <c r="F326" s="2" t="n">
+        <v>0.977</v>
+      </c>
+      <c r="G326" s="3" t="n">
+        <v>0.9818000000000001</v>
+      </c>
+      <c r="H326" s="2" t="n">
+        <v>0.7907</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C327" t="n">
+        <v>0</v>
+      </c>
+      <c r="D327" t="n">
+        <v>0</v>
+      </c>
+      <c r="E327" t="n">
+        <v>0</v>
+      </c>
+      <c r="F327" s="2" t="n"/>
+      <c r="G327" s="3" t="n"/>
+      <c r="H327" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C328" t="n">
+        <v>31421</v>
+      </c>
+      <c r="D328" t="n">
+        <v>27214</v>
+      </c>
+      <c r="E328" t="n">
+        <v>31338</v>
+      </c>
+      <c r="F328" s="2" t="n">
+        <v>0.8661</v>
+      </c>
+      <c r="G328" s="3" t="n">
+        <v>0.9974</v>
+      </c>
+      <c r="H328" s="2" t="n">
+        <v>0.7186</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C329" t="n">
+        <v>4381</v>
+      </c>
+      <c r="D329" t="n">
+        <v>4376</v>
+      </c>
+      <c r="E329" t="n">
+        <v>4379</v>
+      </c>
+      <c r="F329" s="2" t="n">
+        <v>0.9989</v>
+      </c>
+      <c r="G329" s="3" t="n">
+        <v>0.9995000000000001</v>
+      </c>
+      <c r="H329" s="2" t="n">
+        <v>0.6667000000000001</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C330" t="n">
+        <v>5630</v>
+      </c>
+      <c r="D330" t="n">
+        <v>4276</v>
+      </c>
+      <c r="E330" t="n">
+        <v>5619</v>
+      </c>
+      <c r="F330" s="2" t="n">
+        <v>0.7595000000000001</v>
+      </c>
+      <c r="G330" s="3" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="H330" s="2" t="n">
+        <v>0.7184</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C331" t="n">
+        <v>29</v>
+      </c>
+      <c r="D331" t="n">
+        <v>29</v>
+      </c>
+      <c r="E331" t="n">
+        <v>29</v>
+      </c>
+      <c r="F331" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G331" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H331" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C332" t="n">
+        <v>3454</v>
+      </c>
+      <c r="D332" t="n">
+        <v>3385</v>
+      </c>
+      <c r="E332" t="n">
+        <v>3390</v>
+      </c>
+      <c r="F332" s="2" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G332" s="3" t="n">
+        <v>0.9815</v>
+      </c>
+      <c r="H332" s="2" t="n">
+        <v>0.6151</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C333" t="n">
+        <v>423</v>
+      </c>
+      <c r="D333" t="n">
+        <v>423</v>
+      </c>
+      <c r="E333" t="n">
+        <v>423</v>
+      </c>
+      <c r="F333" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G333" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H333" s="2" t="n">
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C334" t="n">
+        <v>0</v>
+      </c>
+      <c r="D334" t="n">
+        <v>0</v>
+      </c>
+      <c r="E334" t="n">
+        <v>0</v>
+      </c>
+      <c r="F334" s="2" t="n"/>
+      <c r="G334" s="3" t="n"/>
+      <c r="H334" s="2" t="n"/>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C335" t="n">
+        <v>5339</v>
+      </c>
+      <c r="D335" t="n">
+        <v>5209</v>
+      </c>
+      <c r="E335" t="n">
+        <v>5326</v>
+      </c>
+      <c r="F335" s="2" t="n">
+        <v>0.9756999999999999</v>
+      </c>
+      <c r="G335" s="3" t="n">
+        <v>0.9976</v>
+      </c>
+      <c r="H335" s="2" t="n">
+        <v>0.6509999999999999</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C336" t="n">
+        <v>15644</v>
+      </c>
+      <c r="D336" t="n">
+        <v>14134</v>
+      </c>
+      <c r="E336" t="n">
+        <v>14134</v>
+      </c>
+      <c r="F336" s="2" t="n">
+        <v>0.9035</v>
+      </c>
+      <c r="G336" s="3" t="n">
+        <v>0.9035</v>
+      </c>
+      <c r="H336" s="2" t="n">
+        <v>0.7212999999999999</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C337" t="n">
+        <v>0</v>
+      </c>
+      <c r="D337" t="n">
+        <v>0</v>
+      </c>
+      <c r="E337" t="n">
+        <v>0</v>
+      </c>
+      <c r="F337" s="2" t="n"/>
+      <c r="G337" s="3" t="n"/>
+      <c r="H337" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H323"/>
+  <autoFilter ref="A1:H337"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$337</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$351</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -513,22 +513,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>54856</v>
+        <v>56418</v>
       </c>
       <c r="C3" t="n">
-        <v>45468</v>
+        <v>46234</v>
       </c>
       <c r="D3" t="n">
-        <v>47602</v>
+        <v>48368</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.8289</v>
+        <v>0.8195</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.8678</v>
+        <v>0.8573000000000001</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.7748</v>
+        <v>0.7464</v>
       </c>
     </row>
     <row r="4">
@@ -538,22 +538,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>490301</v>
+        <v>503350</v>
       </c>
       <c r="C4" t="n">
-        <v>386936</v>
+        <v>389020</v>
       </c>
       <c r="D4" t="n">
-        <v>426423</v>
+        <v>428507</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.7892</v>
+        <v>0.7729</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.8697</v>
+        <v>0.8512999999999999</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.7965000000000001</v>
+        <v>0.7556999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -584,22 +584,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>848163</v>
+        <v>875513</v>
       </c>
       <c r="C6" t="n">
-        <v>650697</v>
+        <v>665967</v>
       </c>
       <c r="D6" t="n">
-        <v>738883</v>
+        <v>754153</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.7672</v>
+        <v>0.7606999999999999</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.8712000000000001</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.8609</v>
+        <v>0.8297</v>
       </c>
     </row>
     <row r="7">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>122538</v>
+        <v>127494</v>
       </c>
       <c r="C7" t="n">
-        <v>65190</v>
+        <v>65847</v>
       </c>
       <c r="D7" t="n">
-        <v>101580</v>
+        <v>102237</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.532</v>
+        <v>0.5165</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.8290000000000001</v>
+        <v>0.8018999999999999</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6627</v>
+        <v>0.6412</v>
       </c>
     </row>
     <row r="8">
@@ -634,22 +634,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>167442</v>
+        <v>172395</v>
       </c>
       <c r="C8" t="n">
-        <v>115002</v>
+        <v>115649</v>
       </c>
       <c r="D8" t="n">
-        <v>131968</v>
+        <v>132615</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.6868000000000001</v>
+        <v>0.6708</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.7881</v>
+        <v>0.7693000000000001</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.7875</v>
+        <v>0.7623000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -684,22 +684,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>107449</v>
+        <v>109876</v>
       </c>
       <c r="C10" t="n">
-        <v>84850</v>
+        <v>85242</v>
       </c>
       <c r="D10" t="n">
-        <v>90014</v>
+        <v>90406</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.7897</v>
+        <v>0.7757999999999999</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.8377</v>
+        <v>0.8228</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.7998999999999999</v>
+        <v>0.769</v>
       </c>
     </row>
     <row r="11">
@@ -709,13 +709,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4445</v>
+        <v>4466</v>
       </c>
       <c r="C11" t="n">
-        <v>4445</v>
+        <v>4466</v>
       </c>
       <c r="D11" t="n">
-        <v>4445</v>
+        <v>4466</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1</v>
@@ -724,7 +724,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.7265999999999999</v>
+        <v>0.7051000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -753,22 +753,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>172042</v>
+        <v>174457</v>
       </c>
       <c r="C13" t="n">
-        <v>141324</v>
+        <v>141678</v>
       </c>
       <c r="D13" t="n">
-        <v>156017</v>
+        <v>156371</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.8215</v>
+        <v>0.8120999999999999</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.9068999999999999</v>
+        <v>0.8963</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.7672</v>
+        <v>0.7393999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -778,22 +778,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>297551</v>
+        <v>307345</v>
       </c>
       <c r="C14" t="n">
-        <v>238464</v>
+        <v>239973</v>
       </c>
       <c r="D14" t="n">
-        <v>256238</v>
+        <v>257747</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.8014</v>
+        <v>0.7807999999999999</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.8612000000000001</v>
+        <v>0.8386</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.8197</v>
+        <v>0.7907</v>
       </c>
     </row>
     <row r="15">
@@ -829,7 +829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H337"/>
+  <dimension ref="A1:H351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10364,8 +10364,404 @@
         <v>0</v>
       </c>
     </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C338" t="n">
+        <v>0</v>
+      </c>
+      <c r="D338" t="n">
+        <v>0</v>
+      </c>
+      <c r="E338" t="n">
+        <v>0</v>
+      </c>
+      <c r="F338" s="2" t="n"/>
+      <c r="G338" s="3" t="n"/>
+      <c r="H338" s="2" t="n"/>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C339" t="n">
+        <v>1562</v>
+      </c>
+      <c r="D339" t="n">
+        <v>766</v>
+      </c>
+      <c r="E339" t="n">
+        <v>766</v>
+      </c>
+      <c r="F339" s="2" t="n">
+        <v>0.4904</v>
+      </c>
+      <c r="G339" s="3" t="n">
+        <v>0.4904</v>
+      </c>
+      <c r="H339" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C340" t="n">
+        <v>13049</v>
+      </c>
+      <c r="D340" t="n">
+        <v>2084</v>
+      </c>
+      <c r="E340" t="n">
+        <v>2084</v>
+      </c>
+      <c r="F340" s="2" t="n">
+        <v>0.1597</v>
+      </c>
+      <c r="G340" s="3" t="n">
+        <v>0.1597</v>
+      </c>
+      <c r="H340" s="2" t="n">
+        <v>0.0131</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C341" t="n">
+        <v>0</v>
+      </c>
+      <c r="D341" t="n">
+        <v>0</v>
+      </c>
+      <c r="E341" t="n">
+        <v>0</v>
+      </c>
+      <c r="F341" s="2" t="n"/>
+      <c r="G341" s="3" t="n"/>
+      <c r="H341" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C342" t="n">
+        <v>27350</v>
+      </c>
+      <c r="D342" t="n">
+        <v>15270</v>
+      </c>
+      <c r="E342" t="n">
+        <v>15270</v>
+      </c>
+      <c r="F342" s="2" t="n">
+        <v>0.5583</v>
+      </c>
+      <c r="G342" s="3" t="n">
+        <v>0.5583</v>
+      </c>
+      <c r="H342" s="2" t="n">
+        <v>0.0895</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C343" t="n">
+        <v>4956</v>
+      </c>
+      <c r="D343" t="n">
+        <v>657</v>
+      </c>
+      <c r="E343" t="n">
+        <v>657</v>
+      </c>
+      <c r="F343" s="2" t="n">
+        <v>0.1326</v>
+      </c>
+      <c r="G343" s="3" t="n">
+        <v>0.1326</v>
+      </c>
+      <c r="H343" s="2" t="n">
+        <v>0.0213</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C344" t="n">
+        <v>4953</v>
+      </c>
+      <c r="D344" t="n">
+        <v>647</v>
+      </c>
+      <c r="E344" t="n">
+        <v>647</v>
+      </c>
+      <c r="F344" s="2" t="n">
+        <v>0.1306</v>
+      </c>
+      <c r="G344" s="3" t="n">
+        <v>0.1306</v>
+      </c>
+      <c r="H344" s="2" t="n">
+        <v>0.0629</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C345" t="n">
+        <v>0</v>
+      </c>
+      <c r="D345" t="n">
+        <v>0</v>
+      </c>
+      <c r="E345" t="n">
+        <v>0</v>
+      </c>
+      <c r="F345" s="2" t="n"/>
+      <c r="G345" s="3" t="n"/>
+      <c r="H345" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C346" t="n">
+        <v>2427</v>
+      </c>
+      <c r="D346" t="n">
+        <v>392</v>
+      </c>
+      <c r="E346" t="n">
+        <v>392</v>
+      </c>
+      <c r="F346" s="2" t="n">
+        <v>0.1615</v>
+      </c>
+      <c r="G346" s="3" t="n">
+        <v>0.1615</v>
+      </c>
+      <c r="H346" s="2" t="n">
+        <v>0.0246</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C347" t="n">
+        <v>21</v>
+      </c>
+      <c r="D347" t="n">
+        <v>21</v>
+      </c>
+      <c r="E347" t="n">
+        <v>21</v>
+      </c>
+      <c r="F347" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G347" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H347" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C348" t="n">
+        <v>0</v>
+      </c>
+      <c r="D348" t="n">
+        <v>0</v>
+      </c>
+      <c r="E348" t="n">
+        <v>0</v>
+      </c>
+      <c r="F348" s="2" t="n"/>
+      <c r="G348" s="3" t="n"/>
+      <c r="H348" s="2" t="n"/>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C349" t="n">
+        <v>2415</v>
+      </c>
+      <c r="D349" t="n">
+        <v>354</v>
+      </c>
+      <c r="E349" t="n">
+        <v>354</v>
+      </c>
+      <c r="F349" s="2" t="n">
+        <v>0.1466</v>
+      </c>
+      <c r="G349" s="3" t="n">
+        <v>0.1466</v>
+      </c>
+      <c r="H349" s="2" t="n">
+        <v>0.0109</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C350" t="n">
+        <v>9794</v>
+      </c>
+      <c r="D350" t="n">
+        <v>1509</v>
+      </c>
+      <c r="E350" t="n">
+        <v>1509</v>
+      </c>
+      <c r="F350" s="2" t="n">
+        <v>0.1541</v>
+      </c>
+      <c r="G350" s="3" t="n">
+        <v>0.1541</v>
+      </c>
+      <c r="H350" s="2" t="n">
+        <v>0.0183</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C351" t="n">
+        <v>0</v>
+      </c>
+      <c r="D351" t="n">
+        <v>0</v>
+      </c>
+      <c r="E351" t="n">
+        <v>0</v>
+      </c>
+      <c r="F351" s="2" t="n"/>
+      <c r="G351" s="3" t="n"/>
+      <c r="H351" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H337"/>
+  <autoFilter ref="A1:H351"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$351</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$365</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -513,22 +513,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>56418</v>
+        <v>58459</v>
       </c>
       <c r="C3" t="n">
-        <v>46234</v>
+        <v>48095</v>
       </c>
       <c r="D3" t="n">
-        <v>48368</v>
+        <v>50408</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.8195</v>
+        <v>0.8227</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.8573000000000001</v>
+        <v>0.8623000000000001</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.7464</v>
+        <v>0.7419</v>
       </c>
     </row>
     <row r="4">
@@ -538,22 +538,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>503350</v>
+        <v>521287</v>
       </c>
       <c r="C4" t="n">
-        <v>389020</v>
+        <v>403958</v>
       </c>
       <c r="D4" t="n">
-        <v>428507</v>
+        <v>445920</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.7729</v>
+        <v>0.7748999999999999</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.8512999999999999</v>
+        <v>0.8554</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.7556999999999999</v>
+        <v>0.7532</v>
       </c>
     </row>
     <row r="5">
@@ -584,22 +584,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>875513</v>
+        <v>908742</v>
       </c>
       <c r="C6" t="n">
-        <v>665967</v>
+        <v>693375</v>
       </c>
       <c r="D6" t="n">
-        <v>754153</v>
+        <v>787277</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.7606999999999999</v>
+        <v>0.763</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.8614000000000001</v>
+        <v>0.8663</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.8297</v>
+        <v>0.8276</v>
       </c>
     </row>
     <row r="7">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>127494</v>
+        <v>131835</v>
       </c>
       <c r="C7" t="n">
-        <v>65847</v>
+        <v>66427</v>
       </c>
       <c r="D7" t="n">
-        <v>102237</v>
+        <v>106187</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.5165</v>
+        <v>0.5039</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.8018999999999999</v>
+        <v>0.8055</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6412</v>
+        <v>0.6322</v>
       </c>
     </row>
     <row r="8">
@@ -634,22 +634,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>172395</v>
+        <v>177368</v>
       </c>
       <c r="C8" t="n">
-        <v>115649</v>
+        <v>119423</v>
       </c>
       <c r="D8" t="n">
-        <v>132615</v>
+        <v>136389</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.6708</v>
+        <v>0.6733</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.7693000000000001</v>
+        <v>0.769</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.7623000000000001</v>
+        <v>0.7656999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -684,22 +684,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>109876</v>
+        <v>112735</v>
       </c>
       <c r="C10" t="n">
-        <v>85242</v>
+        <v>87885</v>
       </c>
       <c r="D10" t="n">
-        <v>90406</v>
+        <v>93121</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.7757999999999999</v>
+        <v>0.7796</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.8228</v>
+        <v>0.826</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.769</v>
+        <v>0.762</v>
       </c>
     </row>
     <row r="11">
@@ -709,13 +709,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4466</v>
+        <v>4499</v>
       </c>
       <c r="C11" t="n">
-        <v>4466</v>
+        <v>4499</v>
       </c>
       <c r="D11" t="n">
-        <v>4466</v>
+        <v>4499</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1</v>
@@ -724,7 +724,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.7051000000000001</v>
+        <v>0.6984999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -753,22 +753,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>174457</v>
+        <v>176218</v>
       </c>
       <c r="C13" t="n">
-        <v>141678</v>
+        <v>143196</v>
       </c>
       <c r="D13" t="n">
-        <v>156371</v>
+        <v>158121</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.8120999999999999</v>
+        <v>0.8126000000000001</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.8963</v>
+        <v>0.8973</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.7393999999999999</v>
+        <v>0.7314000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -778,22 +778,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>307345</v>
+        <v>319671</v>
       </c>
       <c r="C14" t="n">
-        <v>239973</v>
+        <v>250188</v>
       </c>
       <c r="D14" t="n">
-        <v>257747</v>
+        <v>269783</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.7807999999999999</v>
+        <v>0.7826000000000001</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.8386</v>
+        <v>0.8439</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.7907</v>
+        <v>0.7863</v>
       </c>
     </row>
     <row r="15">
@@ -829,7 +829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H351"/>
+  <dimension ref="A1:H365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10760,8 +10760,402 @@
         <v>0</v>
       </c>
     </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C352" t="n">
+        <v>0</v>
+      </c>
+      <c r="D352" t="n">
+        <v>0</v>
+      </c>
+      <c r="E352" t="n">
+        <v>0</v>
+      </c>
+      <c r="F352" s="2" t="n"/>
+      <c r="G352" s="3" t="n"/>
+      <c r="H352" s="2" t="n"/>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C353" t="n">
+        <v>2041</v>
+      </c>
+      <c r="D353" t="n">
+        <v>1861</v>
+      </c>
+      <c r="E353" t="n">
+        <v>2040</v>
+      </c>
+      <c r="F353" s="2" t="n">
+        <v>0.9118000000000001</v>
+      </c>
+      <c r="G353" s="3" t="n">
+        <v>0.9995000000000001</v>
+      </c>
+      <c r="H353" s="2" t="n">
+        <v>0.6256</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C354" t="n">
+        <v>17937</v>
+      </c>
+      <c r="D354" t="n">
+        <v>14938</v>
+      </c>
+      <c r="E354" t="n">
+        <v>17413</v>
+      </c>
+      <c r="F354" s="2" t="n">
+        <v>0.8328</v>
+      </c>
+      <c r="G354" s="3" t="n">
+        <v>0.9708</v>
+      </c>
+      <c r="H354" s="2" t="n">
+        <v>0.6814</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C355" t="n">
+        <v>0</v>
+      </c>
+      <c r="D355" t="n">
+        <v>0</v>
+      </c>
+      <c r="E355" t="n">
+        <v>0</v>
+      </c>
+      <c r="F355" s="2" t="n"/>
+      <c r="G355" s="3" t="n"/>
+      <c r="H355" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C356" t="n">
+        <v>33229</v>
+      </c>
+      <c r="D356" t="n">
+        <v>27408</v>
+      </c>
+      <c r="E356" t="n">
+        <v>33124</v>
+      </c>
+      <c r="F356" s="2" t="n">
+        <v>0.8248000000000001</v>
+      </c>
+      <c r="G356" s="3" t="n">
+        <v>0.9968</v>
+      </c>
+      <c r="H356" s="2" t="n">
+        <v>0.778</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C357" t="n">
+        <v>4341</v>
+      </c>
+      <c r="D357" t="n">
+        <v>580</v>
+      </c>
+      <c r="E357" t="n">
+        <v>3950</v>
+      </c>
+      <c r="F357" s="2" t="n">
+        <v>0.1336</v>
+      </c>
+      <c r="G357" s="3" t="n">
+        <v>0.9098999999999999</v>
+      </c>
+      <c r="H357" s="2" t="n">
+        <v>0.3617</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C358" t="n">
+        <v>4973</v>
+      </c>
+      <c r="D358" t="n">
+        <v>3774</v>
+      </c>
+      <c r="E358" t="n">
+        <v>3774</v>
+      </c>
+      <c r="F358" s="2" t="n">
+        <v>0.7589</v>
+      </c>
+      <c r="G358" s="3" t="n">
+        <v>0.7589</v>
+      </c>
+      <c r="H358" s="2" t="n">
+        <v>0.8534999999999999</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C359" t="n">
+        <v>0</v>
+      </c>
+      <c r="D359" t="n">
+        <v>0</v>
+      </c>
+      <c r="E359" t="n">
+        <v>0</v>
+      </c>
+      <c r="F359" s="2" t="n"/>
+      <c r="G359" s="3" t="n"/>
+      <c r="H359" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C360" t="n">
+        <v>2859</v>
+      </c>
+      <c r="D360" t="n">
+        <v>2643</v>
+      </c>
+      <c r="E360" t="n">
+        <v>2715</v>
+      </c>
+      <c r="F360" s="2" t="n">
+        <v>0.9244</v>
+      </c>
+      <c r="G360" s="3" t="n">
+        <v>0.9495999999999999</v>
+      </c>
+      <c r="H360" s="2" t="n">
+        <v>0.5752</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C361" t="n">
+        <v>33</v>
+      </c>
+      <c r="D361" t="n">
+        <v>33</v>
+      </c>
+      <c r="E361" t="n">
+        <v>33</v>
+      </c>
+      <c r="F361" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G361" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H361" s="2" t="n">
+        <v>0.4286</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C362" t="n">
+        <v>0</v>
+      </c>
+      <c r="D362" t="n">
+        <v>0</v>
+      </c>
+      <c r="E362" t="n">
+        <v>0</v>
+      </c>
+      <c r="F362" s="2" t="n"/>
+      <c r="G362" s="3" t="n"/>
+      <c r="H362" s="2" t="n"/>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C363" t="n">
+        <v>1761</v>
+      </c>
+      <c r="D363" t="n">
+        <v>1518</v>
+      </c>
+      <c r="E363" t="n">
+        <v>1750</v>
+      </c>
+      <c r="F363" s="2" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="G363" s="3" t="n">
+        <v>0.9937999999999999</v>
+      </c>
+      <c r="H363" s="2" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C364" t="n">
+        <v>12326</v>
+      </c>
+      <c r="D364" t="n">
+        <v>10215</v>
+      </c>
+      <c r="E364" t="n">
+        <v>12036</v>
+      </c>
+      <c r="F364" s="2" t="n">
+        <v>0.8287</v>
+      </c>
+      <c r="G364" s="3" t="n">
+        <v>0.9765</v>
+      </c>
+      <c r="H364" s="2" t="n">
+        <v>0.6516</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C365" t="n">
+        <v>0</v>
+      </c>
+      <c r="D365" t="n">
+        <v>0</v>
+      </c>
+      <c r="E365" t="n">
+        <v>0</v>
+      </c>
+      <c r="F365" s="2" t="n"/>
+      <c r="G365" s="3" t="n"/>
+      <c r="H365" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H351"/>
+  <autoFilter ref="A1:H365"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$365</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$379</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -513,22 +513,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>58459</v>
+        <v>61474</v>
       </c>
       <c r="C3" t="n">
-        <v>48095</v>
+        <v>50920</v>
       </c>
       <c r="D3" t="n">
-        <v>50408</v>
+        <v>53421</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.8227</v>
+        <v>0.8283</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.8623000000000001</v>
+        <v>0.8690000000000001</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.7419</v>
+        <v>0.7468</v>
       </c>
     </row>
     <row r="4">
@@ -538,22 +538,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>521287</v>
+        <v>545850</v>
       </c>
       <c r="C4" t="n">
-        <v>403958</v>
+        <v>427049</v>
       </c>
       <c r="D4" t="n">
-        <v>445920</v>
+        <v>470199</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.7748999999999999</v>
+        <v>0.7824</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.8554</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.7532</v>
+        <v>0.7574</v>
       </c>
     </row>
     <row r="5">
@@ -584,22 +584,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>908742</v>
+        <v>946708</v>
       </c>
       <c r="C6" t="n">
-        <v>693375</v>
+        <v>726422</v>
       </c>
       <c r="D6" t="n">
-        <v>787277</v>
+        <v>824730</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.763</v>
+        <v>0.7673000000000001</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.8663</v>
+        <v>0.8712000000000001</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.8276</v>
+        <v>0.8271999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>131835</v>
+        <v>138860</v>
       </c>
       <c r="C7" t="n">
-        <v>66427</v>
+        <v>72353</v>
       </c>
       <c r="D7" t="n">
-        <v>106187</v>
+        <v>113196</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.5039</v>
+        <v>0.521</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.8055</v>
+        <v>0.8151999999999999</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6322</v>
+        <v>0.6307</v>
       </c>
     </row>
     <row r="8">
@@ -634,22 +634,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>177368</v>
+        <v>183399</v>
       </c>
       <c r="C8" t="n">
-        <v>119423</v>
+        <v>124086</v>
       </c>
       <c r="D8" t="n">
-        <v>136389</v>
+        <v>142361</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.6733</v>
+        <v>0.6766</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.769</v>
+        <v>0.7762</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.7656999999999999</v>
+        <v>0.7648999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -684,22 +684,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>112735</v>
+        <v>117918</v>
       </c>
       <c r="C10" t="n">
-        <v>87885</v>
+        <v>92862</v>
       </c>
       <c r="D10" t="n">
-        <v>93121</v>
+        <v>98237</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.7796</v>
+        <v>0.7875</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.826</v>
+        <v>0.8331000000000001</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.762</v>
+        <v>0.7668</v>
       </c>
     </row>
     <row r="11">
@@ -709,13 +709,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4499</v>
+        <v>4683</v>
       </c>
       <c r="C11" t="n">
-        <v>4499</v>
+        <v>4683</v>
       </c>
       <c r="D11" t="n">
-        <v>4499</v>
+        <v>4683</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1</v>
@@ -724,7 +724,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.6984999999999999</v>
+        <v>0.7044</v>
       </c>
     </row>
     <row r="12">
@@ -753,22 +753,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>176218</v>
+        <v>185194</v>
       </c>
       <c r="C13" t="n">
-        <v>143196</v>
+        <v>152024</v>
       </c>
       <c r="D13" t="n">
-        <v>158121</v>
+        <v>167091</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.8126000000000001</v>
+        <v>0.8209000000000001</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.8973</v>
+        <v>0.9022</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.7314000000000001</v>
+        <v>0.7339</v>
       </c>
     </row>
     <row r="14">
@@ -778,22 +778,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>319671</v>
+        <v>334492</v>
       </c>
       <c r="C14" t="n">
-        <v>250188</v>
+        <v>264450</v>
       </c>
       <c r="D14" t="n">
-        <v>269783</v>
+        <v>284432</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.7826000000000001</v>
+        <v>0.7906</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.8439</v>
+        <v>0.8503000000000001</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.7863</v>
+        <v>0.7893000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -829,7 +829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H365"/>
+  <dimension ref="A1:H379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11154,8 +11154,402 @@
       <c r="G365" s="3" t="n"/>
       <c r="H365" s="2" t="n"/>
     </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C366" t="n">
+        <v>0</v>
+      </c>
+      <c r="D366" t="n">
+        <v>0</v>
+      </c>
+      <c r="E366" t="n">
+        <v>0</v>
+      </c>
+      <c r="F366" s="2" t="n"/>
+      <c r="G366" s="3" t="n"/>
+      <c r="H366" s="2" t="n"/>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C367" t="n">
+        <v>3015</v>
+      </c>
+      <c r="D367" t="n">
+        <v>2825</v>
+      </c>
+      <c r="E367" t="n">
+        <v>3013</v>
+      </c>
+      <c r="F367" s="2" t="n">
+        <v>0.9370000000000001</v>
+      </c>
+      <c r="G367" s="3" t="n">
+        <v>0.9993000000000001</v>
+      </c>
+      <c r="H367" s="2" t="n">
+        <v>0.8625</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C368" t="n">
+        <v>24563</v>
+      </c>
+      <c r="D368" t="n">
+        <v>23091</v>
+      </c>
+      <c r="E368" t="n">
+        <v>24279</v>
+      </c>
+      <c r="F368" s="2" t="n">
+        <v>0.9401</v>
+      </c>
+      <c r="G368" s="3" t="n">
+        <v>0.9884000000000001</v>
+      </c>
+      <c r="H368" s="2" t="n">
+        <v>0.8713</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C369" t="n">
+        <v>0</v>
+      </c>
+      <c r="D369" t="n">
+        <v>0</v>
+      </c>
+      <c r="E369" t="n">
+        <v>0</v>
+      </c>
+      <c r="F369" s="2" t="n"/>
+      <c r="G369" s="3" t="n"/>
+      <c r="H369" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C370" t="n">
+        <v>37966</v>
+      </c>
+      <c r="D370" t="n">
+        <v>33047</v>
+      </c>
+      <c r="E370" t="n">
+        <v>37453</v>
+      </c>
+      <c r="F370" s="2" t="n">
+        <v>0.8704000000000001</v>
+      </c>
+      <c r="G370" s="3" t="n">
+        <v>0.9865</v>
+      </c>
+      <c r="H370" s="2" t="n">
+        <v>0.8162999999999999</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C371" t="n">
+        <v>7025</v>
+      </c>
+      <c r="D371" t="n">
+        <v>5926</v>
+      </c>
+      <c r="E371" t="n">
+        <v>7009</v>
+      </c>
+      <c r="F371" s="2" t="n">
+        <v>0.8436</v>
+      </c>
+      <c r="G371" s="3" t="n">
+        <v>0.9976999999999999</v>
+      </c>
+      <c r="H371" s="2" t="n">
+        <v>0.5814</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C372" t="n">
+        <v>6031</v>
+      </c>
+      <c r="D372" t="n">
+        <v>4663</v>
+      </c>
+      <c r="E372" t="n">
+        <v>5972</v>
+      </c>
+      <c r="F372" s="2" t="n">
+        <v>0.7731999999999999</v>
+      </c>
+      <c r="G372" s="3" t="n">
+        <v>0.9902</v>
+      </c>
+      <c r="H372" s="2" t="n">
+        <v>0.7440000000000001</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C373" t="n">
+        <v>0</v>
+      </c>
+      <c r="D373" t="n">
+        <v>0</v>
+      </c>
+      <c r="E373" t="n">
+        <v>0</v>
+      </c>
+      <c r="F373" s="2" t="n"/>
+      <c r="G373" s="3" t="n"/>
+      <c r="H373" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C374" t="n">
+        <v>5183</v>
+      </c>
+      <c r="D374" t="n">
+        <v>4977</v>
+      </c>
+      <c r="E374" t="n">
+        <v>5116</v>
+      </c>
+      <c r="F374" s="2" t="n">
+        <v>0.9603</v>
+      </c>
+      <c r="G374" s="3" t="n">
+        <v>0.9871</v>
+      </c>
+      <c r="H374" s="2" t="n">
+        <v>0.8822</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C375" t="n">
+        <v>184</v>
+      </c>
+      <c r="D375" t="n">
+        <v>184</v>
+      </c>
+      <c r="E375" t="n">
+        <v>184</v>
+      </c>
+      <c r="F375" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G375" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H375" s="2" t="n">
+        <v>0.9037999999999999</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C376" t="n">
+        <v>0</v>
+      </c>
+      <c r="D376" t="n">
+        <v>0</v>
+      </c>
+      <c r="E376" t="n">
+        <v>0</v>
+      </c>
+      <c r="F376" s="2" t="n"/>
+      <c r="G376" s="3" t="n"/>
+      <c r="H376" s="2" t="n"/>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C377" t="n">
+        <v>8976</v>
+      </c>
+      <c r="D377" t="n">
+        <v>8828</v>
+      </c>
+      <c r="E377" t="n">
+        <v>8970</v>
+      </c>
+      <c r="F377" s="2" t="n">
+        <v>0.9834999999999999</v>
+      </c>
+      <c r="G377" s="3" t="n">
+        <v>0.9993000000000001</v>
+      </c>
+      <c r="H377" s="2" t="n">
+        <v>0.7944</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C378" t="n">
+        <v>14821</v>
+      </c>
+      <c r="D378" t="n">
+        <v>14262</v>
+      </c>
+      <c r="E378" t="n">
+        <v>14649</v>
+      </c>
+      <c r="F378" s="2" t="n">
+        <v>0.9623</v>
+      </c>
+      <c r="G378" s="3" t="n">
+        <v>0.9884000000000001</v>
+      </c>
+      <c r="H378" s="2" t="n">
+        <v>0.8656999999999999</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C379" t="n">
+        <v>0</v>
+      </c>
+      <c r="D379" t="n">
+        <v>0</v>
+      </c>
+      <c r="E379" t="n">
+        <v>0</v>
+      </c>
+      <c r="F379" s="2" t="n"/>
+      <c r="G379" s="3" t="n"/>
+      <c r="H379" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H365"/>
+  <autoFilter ref="A1:H379"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -513,22 +513,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2797</v>
+        <v>6004</v>
       </c>
       <c r="C3" t="n">
-        <v>2748</v>
+        <v>5914</v>
       </c>
       <c r="D3" t="n">
-        <v>2789</v>
+        <v>5955</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9825</v>
+        <v>0.985</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.9971</v>
+        <v>0.9918</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.6518999999999999</v>
+        <v>0.7025</v>
       </c>
     </row>
     <row r="4">
@@ -538,22 +538,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24066</v>
+        <v>52028</v>
       </c>
       <c r="C4" t="n">
-        <v>23055</v>
+        <v>49828</v>
       </c>
       <c r="D4" t="n">
-        <v>23848</v>
+        <v>51404</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.958</v>
+        <v>0.9577</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.9909</v>
+        <v>0.988</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.7433</v>
+        <v>0.7365999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -584,22 +584,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38604</v>
+        <v>77911</v>
       </c>
       <c r="C6" t="n">
-        <v>34910</v>
+        <v>69937</v>
       </c>
       <c r="D6" t="n">
-        <v>38567</v>
+        <v>76394</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9043000000000001</v>
+        <v>0.8976999999999999</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.9990000000000001</v>
+        <v>0.9804999999999999</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.7748</v>
+        <v>0.7887999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7555</v>
+        <v>16593</v>
       </c>
       <c r="C7" t="n">
-        <v>7062</v>
+        <v>15492</v>
       </c>
       <c r="D7" t="n">
-        <v>7297</v>
+        <v>16085</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.9347</v>
+        <v>0.9336</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.9659</v>
+        <v>0.9693999999999999</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.625</v>
+        <v>0.6543000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -634,22 +634,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6721</v>
+        <v>12982</v>
       </c>
       <c r="C8" t="n">
-        <v>5372</v>
+        <v>10566</v>
       </c>
       <c r="D8" t="n">
-        <v>6685</v>
+        <v>12919</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.7993000000000001</v>
+        <v>0.8139</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.9945999999999999</v>
+        <v>0.9951000000000001</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.6609999999999999</v>
+        <v>0.6531</v>
       </c>
     </row>
     <row r="9">
@@ -680,22 +680,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5779</v>
+        <v>11467</v>
       </c>
       <c r="C10" t="n">
-        <v>5570</v>
+        <v>11074</v>
       </c>
       <c r="D10" t="n">
-        <v>5726</v>
+        <v>11283</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9638</v>
+        <v>0.9656999999999999</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.9908</v>
+        <v>0.9840000000000001</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.6604000000000001</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="11">
@@ -705,13 +705,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>87</v>
+        <v>219</v>
       </c>
       <c r="C11" t="n">
-        <v>87</v>
+        <v>219</v>
       </c>
       <c r="D11" t="n">
-        <v>87</v>
+        <v>219</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1</v>
@@ -720,7 +720,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6139</v>
       </c>
     </row>
     <row r="12">
@@ -749,22 +749,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5999</v>
+        <v>11234</v>
       </c>
       <c r="C13" t="n">
-        <v>5855</v>
+        <v>10921</v>
       </c>
       <c r="D13" t="n">
-        <v>5993</v>
+        <v>11227</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.976</v>
+        <v>0.9721</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.9990000000000001</v>
+        <v>0.9994</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.6022</v>
+        <v>0.618</v>
       </c>
     </row>
     <row r="14">
@@ -774,22 +774,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14860</v>
+        <v>29945</v>
       </c>
       <c r="C14" t="n">
-        <v>14180</v>
+        <v>28200</v>
       </c>
       <c r="D14" t="n">
-        <v>14750</v>
+        <v>29771</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9542</v>
+        <v>0.9417</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.9926</v>
+        <v>0.9942</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.6601</v>
+        <v>0.6870000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -809,7 +809,9 @@
       </c>
       <c r="E15" s="2" t="n"/>
       <c r="F15" s="3" t="n"/>
-      <c r="G15" s="2" t="n"/>
+      <c r="G15" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G15"/>
@@ -823,7 +825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1272,8 +1274,404 @@
       <c r="G15" s="3" t="n"/>
       <c r="H15" s="2" t="n"/>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>3207</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3166</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3166</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>0.9872</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>0.9872</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>0.7593000000000001</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>27962</v>
+      </c>
+      <c r="D18" t="n">
+        <v>26773</v>
+      </c>
+      <c r="E18" t="n">
+        <v>27556</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>0.9575</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>0.9854999999999999</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>0.7299</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="2" t="n"/>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>39307</v>
+      </c>
+      <c r="D20" t="n">
+        <v>35027</v>
+      </c>
+      <c r="E20" t="n">
+        <v>37827</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>0.8911</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>0.9623</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>0.8027</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>9038</v>
+      </c>
+      <c r="D21" t="n">
+        <v>8430</v>
+      </c>
+      <c r="E21" t="n">
+        <v>8788</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>0.9327</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>0.9723000000000001</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>0.6829000000000001</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>6261</v>
+      </c>
+      <c r="D22" t="n">
+        <v>5194</v>
+      </c>
+      <c r="E22" t="n">
+        <v>6234</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>0.8295999999999999</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>0.9956999999999999</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>0.6446</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="2" t="n"/>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>5688</v>
+      </c>
+      <c r="D24" t="n">
+        <v>5504</v>
+      </c>
+      <c r="E24" t="n">
+        <v>5557</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>0.9677</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>0.977</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>0.6881999999999999</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>132</v>
+      </c>
+      <c r="D25" t="n">
+        <v>132</v>
+      </c>
+      <c r="E25" t="n">
+        <v>132</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>0.6627</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2" t="n"/>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>5235</v>
+      </c>
+      <c r="D27" t="n">
+        <v>5066</v>
+      </c>
+      <c r="E27" t="n">
+        <v>5234</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>0.9677</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>0.6353</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>15085</v>
+      </c>
+      <c r="D28" t="n">
+        <v>14020</v>
+      </c>
+      <c r="E28" t="n">
+        <v>15021</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>0.9294</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>0.9958</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>0.7140000000000001</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2" t="n"/>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H15"/>
+  <autoFilter ref="A1:H29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -513,22 +513,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6004</v>
+        <v>9327</v>
       </c>
       <c r="C3" t="n">
-        <v>5914</v>
+        <v>8840</v>
       </c>
       <c r="D3" t="n">
-        <v>5955</v>
+        <v>9219</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.985</v>
+        <v>0.9478</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.9918</v>
+        <v>0.9884000000000001</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.7025</v>
+        <v>0.6823999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -538,22 +538,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>52028</v>
+        <v>74534</v>
       </c>
       <c r="C4" t="n">
-        <v>49828</v>
+        <v>65486</v>
       </c>
       <c r="D4" t="n">
-        <v>51404</v>
+        <v>71615</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9577</v>
+        <v>0.8786</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.988</v>
+        <v>0.9608</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.7365999999999999</v>
+        <v>0.726</v>
       </c>
     </row>
     <row r="5">
@@ -584,22 +584,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>77911</v>
+        <v>114669</v>
       </c>
       <c r="C6" t="n">
-        <v>69937</v>
+        <v>98679</v>
       </c>
       <c r="D6" t="n">
-        <v>76394</v>
+        <v>110123</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.8976999999999999</v>
+        <v>0.8606</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.9804999999999999</v>
+        <v>0.9604</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.7887999999999999</v>
+        <v>0.7956</v>
       </c>
     </row>
     <row r="7">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16593</v>
+        <v>24486</v>
       </c>
       <c r="C7" t="n">
-        <v>15492</v>
+        <v>18066</v>
       </c>
       <c r="D7" t="n">
-        <v>16085</v>
+        <v>23256</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.9336</v>
+        <v>0.7378</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.9693999999999999</v>
+        <v>0.9498000000000001</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6543000000000001</v>
+        <v>0.5984</v>
       </c>
     </row>
     <row r="8">
@@ -634,22 +634,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12982</v>
+        <v>19336</v>
       </c>
       <c r="C8" t="n">
-        <v>10566</v>
+        <v>14895</v>
       </c>
       <c r="D8" t="n">
-        <v>12919</v>
+        <v>17248</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.8139</v>
+        <v>0.7703</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.9951000000000001</v>
+        <v>0.892</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.6531</v>
+        <v>0.6520999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -659,16 +659,20 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="3" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="G9" s="2" t="n">
         <v>0</v>
       </c>
@@ -680,22 +684,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11467</v>
+        <v>16412</v>
       </c>
       <c r="C10" t="n">
-        <v>11074</v>
+        <v>14769</v>
       </c>
       <c r="D10" t="n">
-        <v>11283</v>
+        <v>15875</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9656999999999999</v>
+        <v>0.8998999999999999</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.9840000000000001</v>
+        <v>0.9673</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.674</v>
+        <v>0.6616</v>
       </c>
     </row>
     <row r="11">
@@ -705,13 +709,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>219</v>
+        <v>435</v>
       </c>
       <c r="C11" t="n">
-        <v>219</v>
+        <v>435</v>
       </c>
       <c r="D11" t="n">
-        <v>219</v>
+        <v>435</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1</v>
@@ -720,7 +724,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.6139</v>
+        <v>0.5760000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -749,22 +753,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>11234</v>
+        <v>17267</v>
       </c>
       <c r="C13" t="n">
-        <v>10921</v>
+        <v>15296</v>
       </c>
       <c r="D13" t="n">
-        <v>11227</v>
+        <v>17181</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9721</v>
+        <v>0.8859</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.9994</v>
+        <v>0.995</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.618</v>
+        <v>0.6115999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -774,22 +778,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>29945</v>
+        <v>44248</v>
       </c>
       <c r="C14" t="n">
-        <v>28200</v>
+        <v>39775</v>
       </c>
       <c r="D14" t="n">
-        <v>29771</v>
+        <v>41346</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9417</v>
+        <v>0.8989</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.9942</v>
+        <v>0.9344</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6748999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -825,7 +829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1670,8 +1674,408 @@
         <v>0</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>3323</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2926</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3264</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>0.8804999999999999</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>0.9822</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>0.6414</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>22506</v>
+      </c>
+      <c r="D32" t="n">
+        <v>15658</v>
+      </c>
+      <c r="E32" t="n">
+        <v>20211</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>0.6957</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>0.898</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>0.7040000000000001</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="2" t="n"/>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>36758</v>
+      </c>
+      <c r="D34" t="n">
+        <v>28742</v>
+      </c>
+      <c r="E34" t="n">
+        <v>33729</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>0.7818999999999999</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>0.9176000000000001</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>0.8092</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>7893</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2574</v>
+      </c>
+      <c r="E35" t="n">
+        <v>7171</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>0.9085</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>0.4878</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>6354</v>
+      </c>
+      <c r="D36" t="n">
+        <v>4329</v>
+      </c>
+      <c r="E36" t="n">
+        <v>4329</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>0.6812999999999999</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>0.6812999999999999</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>4945</v>
+      </c>
+      <c r="D38" t="n">
+        <v>3695</v>
+      </c>
+      <c r="E38" t="n">
+        <v>4592</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>0.7472</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>0.9286</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>0.636</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>216</v>
+      </c>
+      <c r="D39" t="n">
+        <v>216</v>
+      </c>
+      <c r="E39" t="n">
+        <v>216</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>0.5109</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="2" t="n"/>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="2" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>6033</v>
+      </c>
+      <c r="D41" t="n">
+        <v>4375</v>
+      </c>
+      <c r="E41" t="n">
+        <v>5954</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>0.7252</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>0.9869</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>0.5975</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>14303</v>
+      </c>
+      <c r="D42" t="n">
+        <v>11575</v>
+      </c>
+      <c r="E42" t="n">
+        <v>11575</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>0.8093</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>0.8093</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>0.6493000000000001</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="2" t="n"/>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H29"/>
+  <autoFilter ref="A1:H43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Geral Diário" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$53</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -490,335 +490,241 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CARAP 02-SP</t>
+          <t>CHM-SP</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>93225</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>68625</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="2" t="n"/>
+        <v>74754</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.7361</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>0.8018999999999999</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0.5664</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CARAP-SP</t>
+          <t>CLP-SP</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9327</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>8840</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>9219</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0.9478</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>0.9884000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="3" t="n"/>
       <c r="G3" s="2" t="n">
-        <v>0.6823999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CHM-SP</t>
+          <t>F JND-SP</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>74534</v>
+        <v>33910</v>
       </c>
       <c r="C4" t="n">
-        <v>65486</v>
+        <v>18646</v>
       </c>
       <c r="D4" t="n">
-        <v>71615</v>
+        <v>23836</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.8786</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.9608</v>
+        <v>0.7029000000000001</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.726</v>
+        <v>0.4839</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CLP-SP</t>
+          <t>F S-JRG-SP</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>25780</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>16001</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="3" t="n"/>
+        <v>18354</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0.6207</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0.7119</v>
+      </c>
       <c r="G5" s="2" t="n">
-        <v>0</v>
+        <v>0.5449000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>COT-SP</t>
+          <t>ITUP-SP</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>114669</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>98679</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>110123</v>
+        <v>1</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.8606</v>
+        <v>1</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.9604</v>
+        <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.7956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F JND-SP</t>
+          <t>JND 02-SP</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24486</v>
+        <v>19896</v>
       </c>
       <c r="C7" t="n">
-        <v>18066</v>
+        <v>15381</v>
       </c>
       <c r="D7" t="n">
-        <v>23256</v>
+        <v>16487</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.7378</v>
+        <v>0.7731</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.9498000000000001</v>
+        <v>0.8287</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.5984</v>
+        <v>0.5134000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F S-JRG-SP</t>
+          <t>JND-SP</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19336</v>
+        <v>449</v>
       </c>
       <c r="C8" t="n">
-        <v>14895</v>
+        <v>449</v>
       </c>
       <c r="D8" t="n">
-        <v>17248</v>
+        <v>449</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.7703</v>
+        <v>1</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.892</v>
+        <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.6520999999999999</v>
+        <v>0.4341</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ITUP-SP</t>
+          <t>OSC 02-SP</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JND 02-SP</t>
+          <t>OSC-SP</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16412</v>
+        <v>20610</v>
       </c>
       <c r="C10" t="n">
-        <v>14769</v>
+        <v>15557</v>
       </c>
       <c r="D10" t="n">
-        <v>15875</v>
+        <v>17442</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.8998999999999999</v>
+        <v>0.7548</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.9673</v>
+        <v>0.8462999999999999</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.6616</v>
+        <v>0.4742</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>JND-SP</t>
+          <t>S-FREG-SP</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>435</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>435</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>435</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="3" t="n"/>
       <c r="G11" s="2" t="n">
-        <v>0.5760000000000001</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>OSC 02-SP</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="3" t="n"/>
-      <c r="G12" s="2" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>OSC-SP</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>17267</v>
-      </c>
-      <c r="C13" t="n">
-        <v>15296</v>
-      </c>
-      <c r="D13" t="n">
-        <v>17181</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>0.8859</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>0.995</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>0.6115999999999999</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>S-CSVD-SP</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>44248</v>
-      </c>
-      <c r="C14" t="n">
-        <v>39775</v>
-      </c>
-      <c r="D14" t="n">
-        <v>41346</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>0.8989</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>0.9344</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>0.6748999999999999</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>S-FREG-SP</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="2" t="n"/>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="2" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G15"/>
+  <autoFilter ref="A1:G11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -829,7 +735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2074,8 +1980,288 @@
         <v>0</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>18691</v>
+      </c>
+      <c r="D44" t="n">
+        <v>3139</v>
+      </c>
+      <c r="E44" t="n">
+        <v>3139</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>0.1679</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>0.1679</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>0.0131</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="2" t="n"/>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="2" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>9424</v>
+      </c>
+      <c r="D46" t="n">
+        <v>580</v>
+      </c>
+      <c r="E46" t="n">
+        <v>580</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>0.06150000000000001</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>0.06150000000000001</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>0.06059999999999999</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>6444</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1106</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1106</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>0.1716</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>0.1716</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>0.1364</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="2" t="n"/>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>3484</v>
+      </c>
+      <c r="D49" t="n">
+        <v>612</v>
+      </c>
+      <c r="E49" t="n">
+        <v>612</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>0.1757</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>0.1757</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>0.0158</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>14</v>
+      </c>
+      <c r="D50" t="n">
+        <v>14</v>
+      </c>
+      <c r="E50" t="n">
+        <v>14</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>0.0119</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="2" t="n"/>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="2" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>3343</v>
+      </c>
+      <c r="D52" t="n">
+        <v>261</v>
+      </c>
+      <c r="E52" t="n">
+        <v>261</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>0.0781</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>0.0781</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>0.0033</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="2" t="n"/>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H43"/>
+  <autoFilter ref="A1:H53"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Geral Diário" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$62</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -494,22 +494,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>93225</v>
+        <v>114155</v>
       </c>
       <c r="C2" t="n">
-        <v>68625</v>
+        <v>84067</v>
       </c>
       <c r="D2" t="n">
-        <v>74754</v>
+        <v>94748</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.7361</v>
+        <v>0.7364000000000001</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.8018999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.5664</v>
+        <v>0.5893999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -540,22 +540,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>33910</v>
+        <v>39123</v>
       </c>
       <c r="C4" t="n">
-        <v>18646</v>
+        <v>18659</v>
       </c>
       <c r="D4" t="n">
-        <v>23836</v>
+        <v>23849</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.5499000000000001</v>
+        <v>0.4769</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.7029000000000001</v>
+        <v>0.6096</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.4839</v>
+        <v>0.4396</v>
       </c>
     </row>
     <row r="5">
@@ -565,22 +565,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25780</v>
+        <v>31712</v>
       </c>
       <c r="C5" t="n">
-        <v>16001</v>
+        <v>20328</v>
       </c>
       <c r="D5" t="n">
-        <v>18354</v>
+        <v>24225</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.6207</v>
+        <v>0.6409999999999999</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.7119</v>
+        <v>0.7639</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.5449000000000001</v>
+        <v>0.5847</v>
       </c>
     </row>
     <row r="6">
@@ -590,13 +590,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
@@ -615,22 +615,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19896</v>
+        <v>25532</v>
       </c>
       <c r="C7" t="n">
-        <v>15381</v>
+        <v>20246</v>
       </c>
       <c r="D7" t="n">
-        <v>16487</v>
+        <v>21553</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.7731</v>
+        <v>0.7929999999999999</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.8287</v>
+        <v>0.8442000000000001</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.5134000000000001</v>
+        <v>0.5253</v>
       </c>
     </row>
     <row r="8">
@@ -640,13 +640,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>449</v>
+        <v>697</v>
       </c>
       <c r="C8" t="n">
-        <v>449</v>
+        <v>697</v>
       </c>
       <c r="D8" t="n">
-        <v>449</v>
+        <v>697</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
@@ -655,76 +655,57 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.4341</v>
+        <v>0.4595</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>OSC 02-SP</t>
+          <t>S-CSVD-SP</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>55280</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>48775</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="2" t="n"/>
+        <v>52186</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0.8823000000000001</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0.9440000000000001</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0.6661</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>OSC-SP</t>
+          <t>S-FREG-SP</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20610</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>15557</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>17442</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>0.7548</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>0.8462999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="3" t="n"/>
       <c r="G10" s="2" t="n">
-        <v>0.4742</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>S-FREG-SP</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2" t="n"/>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="2" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G11"/>
+  <autoFilter ref="A1:G10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -735,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2260,8 +2241,268 @@
         <v>0</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>20930</v>
+      </c>
+      <c r="D54" t="n">
+        <v>15442</v>
+      </c>
+      <c r="E54" t="n">
+        <v>19994</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>0.7378</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>0.9553</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>0.6962</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="2" t="n"/>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="2" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>5213</v>
+      </c>
+      <c r="D56" t="n">
+        <v>13</v>
+      </c>
+      <c r="E56" t="n">
+        <v>13</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>0.1852</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>5932</v>
+      </c>
+      <c r="D57" t="n">
+        <v>4327</v>
+      </c>
+      <c r="E57" t="n">
+        <v>5871</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>0.7293999999999999</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>0.9897</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>0.7681</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>5636</v>
+      </c>
+      <c r="D59" t="n">
+        <v>4865</v>
+      </c>
+      <c r="E59" t="n">
+        <v>5066</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>0.8632</v>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>0.8989</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>0.5815</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>248</v>
+      </c>
+      <c r="D60" t="n">
+        <v>248</v>
+      </c>
+      <c r="E60" t="n">
+        <v>248</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>0.5753</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>11032</v>
+      </c>
+      <c r="D61" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E61" t="n">
+        <v>10840</v>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>0.8158</v>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>0.9826</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>0.6352</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="2" t="n"/>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H53"/>
+  <autoFilter ref="A1:H62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$71</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -494,22 +494,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>114155</v>
+        <v>147922</v>
       </c>
       <c r="C2" t="n">
-        <v>84067</v>
+        <v>114177</v>
       </c>
       <c r="D2" t="n">
-        <v>94748</v>
+        <v>128314</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.7364000000000001</v>
+        <v>0.7719</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.83</v>
+        <v>0.8673999999999999</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.5893999999999999</v>
+        <v>0.6356000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -540,22 +540,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>39123</v>
+        <v>40710</v>
       </c>
       <c r="C4" t="n">
-        <v>18659</v>
+        <v>18684</v>
       </c>
       <c r="D4" t="n">
-        <v>23849</v>
+        <v>25272</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.4769</v>
+        <v>0.459</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.6096</v>
+        <v>0.6208</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.4396</v>
+        <v>0.396</v>
       </c>
     </row>
     <row r="5">
@@ -565,22 +565,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31712</v>
+        <v>39070</v>
       </c>
       <c r="C5" t="n">
-        <v>20328</v>
+        <v>25092</v>
       </c>
       <c r="D5" t="n">
-        <v>24225</v>
+        <v>31534</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.6409999999999999</v>
+        <v>0.6422</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.7639</v>
+        <v>0.8070999999999999</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.5847</v>
+        <v>0.6013000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -590,13 +590,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
@@ -615,22 +615,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25532</v>
+        <v>38968</v>
       </c>
       <c r="C7" t="n">
-        <v>20246</v>
+        <v>29601</v>
       </c>
       <c r="D7" t="n">
-        <v>21553</v>
+        <v>31005</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.7929999999999999</v>
+        <v>0.7595999999999999</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.8442000000000001</v>
+        <v>0.7957</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.5253</v>
+        <v>0.5842000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -640,13 +640,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>697</v>
+        <v>978</v>
       </c>
       <c r="C8" t="n">
-        <v>697</v>
+        <v>978</v>
       </c>
       <c r="D8" t="n">
-        <v>697</v>
+        <v>978</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
@@ -655,7 +655,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.4595</v>
+        <v>0.501</v>
       </c>
     </row>
     <row r="9">
@@ -665,22 +665,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>55280</v>
+        <v>72278</v>
       </c>
       <c r="C9" t="n">
-        <v>48775</v>
+        <v>63933</v>
       </c>
       <c r="D9" t="n">
-        <v>52186</v>
+        <v>69067</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.8823000000000001</v>
+        <v>0.8845000000000001</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.9440000000000001</v>
+        <v>0.9556</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.6661</v>
+        <v>0.7068000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -716,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2501,8 +2501,268 @@
         <v>0</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>33767</v>
+      </c>
+      <c r="D63" t="n">
+        <v>30110</v>
+      </c>
+      <c r="E63" t="n">
+        <v>33566</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>0.8917</v>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>0.9940000000000001</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>0.8623999999999999</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="2" t="n"/>
+      <c r="G64" s="3" t="n"/>
+      <c r="H64" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>1587</v>
+      </c>
+      <c r="D65" t="n">
+        <v>25</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1423</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>0.0158</v>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>0.8967000000000001</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>7358</v>
+      </c>
+      <c r="D66" t="n">
+        <v>4764</v>
+      </c>
+      <c r="E66" t="n">
+        <v>7309</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>0.6475</v>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>0.9933</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>0.6867</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>13436</v>
+      </c>
+      <c r="D68" t="n">
+        <v>9355</v>
+      </c>
+      <c r="E68" t="n">
+        <v>9452</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>0.6962999999999999</v>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>0.7034999999999999</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>0.8706999999999999</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>281</v>
+      </c>
+      <c r="D69" t="n">
+        <v>281</v>
+      </c>
+      <c r="E69" t="n">
+        <v>281</v>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>0.7237</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>16998</v>
+      </c>
+      <c r="D70" t="n">
+        <v>15158</v>
+      </c>
+      <c r="E70" t="n">
+        <v>16881</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>0.8918</v>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>0.9931</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>0.8637</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="2" t="n"/>
+      <c r="G71" s="3" t="n"/>
+      <c r="H71" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H62"/>
+  <autoFilter ref="A1:H71"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$80</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -494,22 +494,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>147922</v>
+        <v>175356</v>
       </c>
       <c r="C2" t="n">
-        <v>114177</v>
+        <v>139004</v>
       </c>
       <c r="D2" t="n">
-        <v>128314</v>
+        <v>155544</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.7719</v>
+        <v>0.7927</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.8673999999999999</v>
+        <v>0.887</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.6356000000000001</v>
+        <v>0.6452</v>
       </c>
     </row>
     <row r="3">
@@ -555,7 +555,7 @@
         <v>0.6208</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.396</v>
+        <v>0.3652</v>
       </c>
     </row>
     <row r="5">
@@ -565,22 +565,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>39070</v>
+        <v>48406</v>
       </c>
       <c r="C5" t="n">
-        <v>25092</v>
+        <v>31001</v>
       </c>
       <c r="D5" t="n">
-        <v>31534</v>
+        <v>40833</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.6422</v>
+        <v>0.6404000000000001</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.8070999999999999</v>
+        <v>0.8436</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.6013000000000001</v>
+        <v>0.6157</v>
       </c>
     </row>
     <row r="6">
@@ -590,13 +590,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
@@ -615,22 +615,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>38968</v>
+        <v>55889</v>
       </c>
       <c r="C7" t="n">
-        <v>29601</v>
+        <v>39264</v>
       </c>
       <c r="D7" t="n">
-        <v>31005</v>
+        <v>40967</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.7595999999999999</v>
+        <v>0.7025</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7957</v>
+        <v>0.733</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.5842000000000001</v>
+        <v>0.5996</v>
       </c>
     </row>
     <row r="8">
@@ -640,13 +640,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>978</v>
+        <v>1430</v>
       </c>
       <c r="C8" t="n">
-        <v>978</v>
+        <v>1430</v>
       </c>
       <c r="D8" t="n">
-        <v>978</v>
+        <v>1430</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
@@ -655,7 +655,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.501</v>
+        <v>0.5114</v>
       </c>
     </row>
     <row r="9">
@@ -665,22 +665,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>72278</v>
+        <v>92705</v>
       </c>
       <c r="C9" t="n">
-        <v>63933</v>
+        <v>82400</v>
       </c>
       <c r="D9" t="n">
-        <v>69067</v>
+        <v>89331</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.8845000000000001</v>
+        <v>0.8887999999999999</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.9556</v>
+        <v>0.9636</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.7068000000000001</v>
+        <v>0.7125</v>
       </c>
     </row>
     <row r="10">
@@ -716,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2761,8 +2761,266 @@
       <c r="G71" s="3" t="n"/>
       <c r="H71" s="2" t="n"/>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>27434</v>
+      </c>
+      <c r="D72" t="n">
+        <v>24827</v>
+      </c>
+      <c r="E72" t="n">
+        <v>27230</v>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>0.9926</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>0.6983</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="2" t="n"/>
+      <c r="G73" s="3" t="n"/>
+      <c r="H73" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="2" t="n"/>
+      <c r="G74" s="3" t="n"/>
+      <c r="H74" s="2" t="n">
+        <v>0.1429</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>9336</v>
+      </c>
+      <c r="D75" t="n">
+        <v>5909</v>
+      </c>
+      <c r="E75" t="n">
+        <v>9299</v>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>0.6329</v>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>0.7006</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>2</v>
+      </c>
+      <c r="D76" t="n">
+        <v>2</v>
+      </c>
+      <c r="E76" t="n">
+        <v>2</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>16921</v>
+      </c>
+      <c r="D77" t="n">
+        <v>9663</v>
+      </c>
+      <c r="E77" t="n">
+        <v>9962</v>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>0.5710999999999999</v>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>0.5887</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>0.6783</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>452</v>
+      </c>
+      <c r="D78" t="n">
+        <v>452</v>
+      </c>
+      <c r="E78" t="n">
+        <v>452</v>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>0.5698</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>20427</v>
+      </c>
+      <c r="D79" t="n">
+        <v>18467</v>
+      </c>
+      <c r="E79" t="n">
+        <v>20264</v>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>0.904</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>0.992</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>0.7376</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="2" t="n"/>
+      <c r="G80" s="3" t="n"/>
+      <c r="H80" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H71"/>
+  <autoFilter ref="A1:H80"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$89</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -494,22 +494,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>175356</v>
+        <v>203886</v>
       </c>
       <c r="C2" t="n">
-        <v>139004</v>
+        <v>165545</v>
       </c>
       <c r="D2" t="n">
-        <v>155544</v>
+        <v>184067</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.7927</v>
+        <v>0.8119</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.887</v>
+        <v>0.9028</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.6452</v>
+        <v>0.6611</v>
       </c>
     </row>
     <row r="3">
@@ -555,7 +555,7 @@
         <v>0.6208</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.3652</v>
+        <v>0.3387</v>
       </c>
     </row>
     <row r="5">
@@ -565,22 +565,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>48406</v>
+        <v>58803</v>
       </c>
       <c r="C5" t="n">
-        <v>31001</v>
+        <v>37464</v>
       </c>
       <c r="D5" t="n">
-        <v>40833</v>
+        <v>51195</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.6404000000000001</v>
+        <v>0.6371</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.8436</v>
+        <v>0.8706</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.6157</v>
+        <v>0.6259</v>
       </c>
     </row>
     <row r="6">
@@ -590,13 +590,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
@@ -615,22 +615,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>55889</v>
+        <v>71965</v>
       </c>
       <c r="C7" t="n">
-        <v>39264</v>
+        <v>49423</v>
       </c>
       <c r="D7" t="n">
-        <v>40967</v>
+        <v>52213</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.7025</v>
+        <v>0.6868000000000001</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.733</v>
+        <v>0.7254999999999999</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.5996</v>
+        <v>0.6177</v>
       </c>
     </row>
     <row r="8">
@@ -640,13 +640,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1430</v>
+        <v>2328</v>
       </c>
       <c r="C8" t="n">
-        <v>1430</v>
+        <v>2328</v>
       </c>
       <c r="D8" t="n">
-        <v>1430</v>
+        <v>2328</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
@@ -655,7 +655,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.5114</v>
+        <v>0.5125</v>
       </c>
     </row>
     <row r="9">
@@ -665,22 +665,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>92705</v>
+        <v>110245</v>
       </c>
       <c r="C9" t="n">
-        <v>82400</v>
+        <v>98150</v>
       </c>
       <c r="D9" t="n">
-        <v>89331</v>
+        <v>106761</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.8887999999999999</v>
+        <v>0.8903</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.9636</v>
+        <v>0.9684</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.7125</v>
+        <v>0.7208</v>
       </c>
     </row>
     <row r="10">
@@ -716,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H80"/>
+  <dimension ref="A1:H89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3019,8 +3019,266 @@
         <v>0</v>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>28530</v>
+      </c>
+      <c r="D81" t="n">
+        <v>26541</v>
+      </c>
+      <c r="E81" t="n">
+        <v>28523</v>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>0.9303</v>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>0.7595000000000001</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="2" t="n"/>
+      <c r="G82" s="3" t="n"/>
+      <c r="H82" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="2" t="n"/>
+      <c r="G83" s="3" t="n"/>
+      <c r="H83" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>10397</v>
+      </c>
+      <c r="D84" t="n">
+        <v>6463</v>
+      </c>
+      <c r="E84" t="n">
+        <v>10362</v>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>0.6215999999999999</v>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>0.9965999999999999</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>0.6968000000000001</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>2</v>
+      </c>
+      <c r="D85" t="n">
+        <v>2</v>
+      </c>
+      <c r="E85" t="n">
+        <v>2</v>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>16076</v>
+      </c>
+      <c r="D86" t="n">
+        <v>10159</v>
+      </c>
+      <c r="E86" t="n">
+        <v>11246</v>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>0.6319</v>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>0.6995999999999999</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>0.7262999999999999</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>898</v>
+      </c>
+      <c r="D87" t="n">
+        <v>898</v>
+      </c>
+      <c r="E87" t="n">
+        <v>898</v>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>0.5205</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>17540</v>
+      </c>
+      <c r="D88" t="n">
+        <v>15750</v>
+      </c>
+      <c r="E88" t="n">
+        <v>17430</v>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>0.8979</v>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>0.9937</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>0.7623000000000001</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="2" t="n"/>
+      <c r="G89" s="3" t="n"/>
+      <c r="H89" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H80"/>
+  <autoFilter ref="A1:H89"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$98</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -494,22 +494,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>203886</v>
+        <v>232178</v>
       </c>
       <c r="C2" t="n">
-        <v>165545</v>
+        <v>192125</v>
       </c>
       <c r="D2" t="n">
-        <v>184067</v>
+        <v>212322</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.8119</v>
+        <v>0.8275</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.9028</v>
+        <v>0.9145</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.6611</v>
+        <v>0.6705</v>
       </c>
     </row>
     <row r="3">
@@ -555,7 +555,7 @@
         <v>0.6208</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.3387</v>
+        <v>0.3134</v>
       </c>
     </row>
     <row r="5">
@@ -565,22 +565,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58803</v>
+        <v>67272</v>
       </c>
       <c r="C5" t="n">
-        <v>37464</v>
+        <v>43415</v>
       </c>
       <c r="D5" t="n">
-        <v>51195</v>
+        <v>59518</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.6371</v>
+        <v>0.6454000000000001</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.8706</v>
+        <v>0.8847</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.6259</v>
+        <v>0.6297</v>
       </c>
     </row>
     <row r="6">
@@ -615,22 +615,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>71965</v>
+        <v>86319</v>
       </c>
       <c r="C7" t="n">
-        <v>49423</v>
+        <v>61765</v>
       </c>
       <c r="D7" t="n">
-        <v>52213</v>
+        <v>65125</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.6868000000000001</v>
+        <v>0.7155</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7254999999999999</v>
+        <v>0.7545000000000001</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6177</v>
+        <v>0.6253</v>
       </c>
     </row>
     <row r="8">
@@ -640,13 +640,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2328</v>
+        <v>2868</v>
       </c>
       <c r="C8" t="n">
-        <v>2328</v>
+        <v>2868</v>
       </c>
       <c r="D8" t="n">
-        <v>2328</v>
+        <v>2868</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
@@ -655,7 +655,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.5125</v>
+        <v>0.5219</v>
       </c>
     </row>
     <row r="9">
@@ -665,22 +665,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>110245</v>
+        <v>124928</v>
       </c>
       <c r="C9" t="n">
-        <v>98150</v>
+        <v>111136</v>
       </c>
       <c r="D9" t="n">
-        <v>106761</v>
+        <v>121393</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.8903</v>
+        <v>0.8895999999999999</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.9684</v>
+        <v>0.9717</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.7208</v>
+        <v>0.7242000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -716,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H89"/>
+  <dimension ref="A1:H98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3277,8 +3277,262 @@
         <v>0</v>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>28292</v>
+      </c>
+      <c r="D90" t="n">
+        <v>26580</v>
+      </c>
+      <c r="E90" t="n">
+        <v>28255</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>0.9395</v>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>0.9987</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>0.7386</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="2" t="n"/>
+      <c r="G91" s="3" t="n"/>
+      <c r="H91" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="2" t="n"/>
+      <c r="G92" s="3" t="n"/>
+      <c r="H92" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>8469</v>
+      </c>
+      <c r="D93" t="n">
+        <v>5951</v>
+      </c>
+      <c r="E93" t="n">
+        <v>8323</v>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>0.7027</v>
+      </c>
+      <c r="G93" s="3" t="n">
+        <v>0.9828</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>0.657</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="2" t="n"/>
+      <c r="G94" s="3" t="n"/>
+      <c r="H94" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>14354</v>
+      </c>
+      <c r="D95" t="n">
+        <v>12342</v>
+      </c>
+      <c r="E95" t="n">
+        <v>12912</v>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>0.8598</v>
+      </c>
+      <c r="G95" s="3" t="n">
+        <v>0.8995000000000001</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>0.6774</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>540</v>
+      </c>
+      <c r="D96" t="n">
+        <v>540</v>
+      </c>
+      <c r="E96" t="n">
+        <v>540</v>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>0.6119</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>14683</v>
+      </c>
+      <c r="D97" t="n">
+        <v>12986</v>
+      </c>
+      <c r="E97" t="n">
+        <v>14632</v>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>0.8844</v>
+      </c>
+      <c r="G97" s="3" t="n">
+        <v>0.9965000000000001</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>0.7462000000000001</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="2" t="n"/>
+      <c r="G98" s="3" t="n"/>
+      <c r="H98" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H89"/>
+  <autoFilter ref="A1:H98"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$107</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -494,22 +494,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>232178</v>
+        <v>257859</v>
       </c>
       <c r="C2" t="n">
-        <v>192125</v>
+        <v>208339</v>
       </c>
       <c r="D2" t="n">
-        <v>212322</v>
+        <v>229846</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.8275</v>
+        <v>0.8079999999999999</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.9145</v>
+        <v>0.8914</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.6705</v>
+        <v>0.6701999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -555,7 +555,7 @@
         <v>0.6208</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.3134</v>
+        <v>0.2968</v>
       </c>
     </row>
     <row r="5">
@@ -565,22 +565,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>67272</v>
+        <v>76551</v>
       </c>
       <c r="C5" t="n">
-        <v>43415</v>
+        <v>50341</v>
       </c>
       <c r="D5" t="n">
-        <v>59518</v>
+        <v>68586</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.6454000000000001</v>
+        <v>0.6576000000000001</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.8847</v>
+        <v>0.8959999999999999</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.6297</v>
+        <v>0.6254</v>
       </c>
     </row>
     <row r="6">
@@ -615,22 +615,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>86319</v>
+        <v>98503</v>
       </c>
       <c r="C7" t="n">
-        <v>61765</v>
+        <v>70611</v>
       </c>
       <c r="D7" t="n">
-        <v>65125</v>
+        <v>74085</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.7155</v>
+        <v>0.7168000000000001</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7545000000000001</v>
+        <v>0.7521</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6253</v>
+        <v>0.6263000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -640,13 +640,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2868</v>
+        <v>3033</v>
       </c>
       <c r="C8" t="n">
-        <v>2868</v>
+        <v>3033</v>
       </c>
       <c r="D8" t="n">
-        <v>2868</v>
+        <v>3033</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
@@ -655,7 +655,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.5219</v>
+        <v>0.5265</v>
       </c>
     </row>
     <row r="9">
@@ -665,22 +665,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>124928</v>
+        <v>137990</v>
       </c>
       <c r="C9" t="n">
-        <v>111136</v>
+        <v>121124</v>
       </c>
       <c r="D9" t="n">
-        <v>121393</v>
+        <v>134336</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.8895999999999999</v>
+        <v>0.8778</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.9717</v>
+        <v>0.9734999999999999</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.7242000000000001</v>
+        <v>0.7199</v>
       </c>
     </row>
     <row r="10">
@@ -716,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H98"/>
+  <dimension ref="A1:H107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3531,8 +3531,260 @@
         <v>0</v>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>25681</v>
+      </c>
+      <c r="D99" t="n">
+        <v>16214</v>
+      </c>
+      <c r="E99" t="n">
+        <v>17524</v>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>0.6314</v>
+      </c>
+      <c r="G99" s="3" t="n">
+        <v>0.6823999999999999</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>0.6674</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="2" t="n"/>
+      <c r="G100" s="3" t="n"/>
+      <c r="H100" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="2" t="n"/>
+      <c r="G101" s="3" t="n"/>
+      <c r="H101" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>9279</v>
+      </c>
+      <c r="D102" t="n">
+        <v>6926</v>
+      </c>
+      <c r="E102" t="n">
+        <v>9068</v>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>0.7464</v>
+      </c>
+      <c r="G102" s="3" t="n">
+        <v>0.9773000000000001</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>0.5909</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="2" t="n"/>
+      <c r="G103" s="3" t="n"/>
+      <c r="H103" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>12184</v>
+      </c>
+      <c r="D104" t="n">
+        <v>8846</v>
+      </c>
+      <c r="E104" t="n">
+        <v>8960</v>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="G104" s="3" t="n">
+        <v>0.7354000000000001</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>0.6353</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>165</v>
+      </c>
+      <c r="D105" t="n">
+        <v>165</v>
+      </c>
+      <c r="E105" t="n">
+        <v>165</v>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>0.5781000000000001</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>13062</v>
+      </c>
+      <c r="D106" t="n">
+        <v>9988</v>
+      </c>
+      <c r="E106" t="n">
+        <v>12943</v>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>0.7646999999999999</v>
+      </c>
+      <c r="G106" s="3" t="n">
+        <v>0.9909</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>0.6866</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="2" t="n"/>
+      <c r="G107" s="3" t="n"/>
+      <c r="H107" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H98"/>
+  <autoFilter ref="A1:H107"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$116</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -494,22 +494,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>257859</v>
+        <v>280291</v>
       </c>
       <c r="C2" t="n">
-        <v>208339</v>
+        <v>211404</v>
       </c>
       <c r="D2" t="n">
-        <v>229846</v>
+        <v>232911</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.8079999999999999</v>
+        <v>0.7542</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.8914</v>
+        <v>0.831</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.6701999999999999</v>
+        <v>0.6167</v>
       </c>
     </row>
     <row r="3">
@@ -555,7 +555,7 @@
         <v>0.6208</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.2968</v>
+        <v>0.2867</v>
       </c>
     </row>
     <row r="5">
@@ -565,22 +565,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>76551</v>
+        <v>82903</v>
       </c>
       <c r="C5" t="n">
-        <v>50341</v>
+        <v>51590</v>
       </c>
       <c r="D5" t="n">
-        <v>68586</v>
+        <v>69835</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.6576000000000001</v>
+        <v>0.6223</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.8959999999999999</v>
+        <v>0.8423999999999999</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.6254</v>
+        <v>0.5851</v>
       </c>
     </row>
     <row r="6">
@@ -615,22 +615,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>98503</v>
+        <v>110649</v>
       </c>
       <c r="C7" t="n">
-        <v>70611</v>
+        <v>72458</v>
       </c>
       <c r="D7" t="n">
-        <v>74085</v>
+        <v>75932</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.7168000000000001</v>
+        <v>0.6548</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7521</v>
+        <v>0.6862</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6263000000000001</v>
+        <v>0.5752</v>
       </c>
     </row>
     <row r="8">
@@ -640,13 +640,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3033</v>
+        <v>3051</v>
       </c>
       <c r="C8" t="n">
-        <v>3033</v>
+        <v>3051</v>
       </c>
       <c r="D8" t="n">
-        <v>3033</v>
+        <v>3051</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
@@ -655,7 +655,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.5265</v>
+        <v>0.4964</v>
       </c>
     </row>
     <row r="9">
@@ -665,22 +665,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>137990</v>
+        <v>150307</v>
       </c>
       <c r="C9" t="n">
-        <v>121124</v>
+        <v>123675</v>
       </c>
       <c r="D9" t="n">
-        <v>134336</v>
+        <v>136887</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.8778</v>
+        <v>0.8228</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.9734999999999999</v>
+        <v>0.9107</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.7199</v>
+        <v>0.6593000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -716,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H107"/>
+  <dimension ref="A1:H116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3783,8 +3783,260 @@
       <c r="G107" s="3" t="n"/>
       <c r="H107" s="2" t="n"/>
     </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>22432</v>
+      </c>
+      <c r="D108" t="n">
+        <v>3065</v>
+      </c>
+      <c r="E108" t="n">
+        <v>3065</v>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>0.1366</v>
+      </c>
+      <c r="G108" s="3" t="n">
+        <v>0.1366</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>0.0443</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="2" t="n"/>
+      <c r="G109" s="3" t="n"/>
+      <c r="H109" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="2" t="n"/>
+      <c r="G110" s="3" t="n"/>
+      <c r="H110" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>6352</v>
+      </c>
+      <c r="D111" t="n">
+        <v>1249</v>
+      </c>
+      <c r="E111" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F111" s="2" t="n">
+        <v>0.1966</v>
+      </c>
+      <c r="G111" s="3" t="n">
+        <v>0.1966</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="2" t="n"/>
+      <c r="G112" s="3" t="n"/>
+      <c r="H112" s="2" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>12146</v>
+      </c>
+      <c r="D113" t="n">
+        <v>1847</v>
+      </c>
+      <c r="E113" t="n">
+        <v>1847</v>
+      </c>
+      <c r="F113" s="2" t="n">
+        <v>0.1521</v>
+      </c>
+      <c r="G113" s="3" t="n">
+        <v>0.1521</v>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>0.0367</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>18</v>
+      </c>
+      <c r="D114" t="n">
+        <v>18</v>
+      </c>
+      <c r="E114" t="n">
+        <v>18</v>
+      </c>
+      <c r="F114" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>0.0392</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>12317</v>
+      </c>
+      <c r="D115" t="n">
+        <v>2551</v>
+      </c>
+      <c r="E115" t="n">
+        <v>2551</v>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>0.2071</v>
+      </c>
+      <c r="G115" s="3" t="n">
+        <v>0.2071</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>0.07820000000000001</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="2" t="n"/>
+      <c r="G116" s="3" t="n"/>
+      <c r="H116" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H107"/>
+  <autoFilter ref="A1:H116"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$125</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -494,22 +494,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>280291</v>
+        <v>307120</v>
       </c>
       <c r="C2" t="n">
-        <v>211404</v>
+        <v>215303</v>
       </c>
       <c r="D2" t="n">
-        <v>232911</v>
+        <v>236810</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.7542</v>
+        <v>0.701</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.831</v>
+        <v>0.7711</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.6167</v>
+        <v>0.5799</v>
       </c>
     </row>
     <row r="3">
@@ -555,7 +555,7 @@
         <v>0.6208</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.2867</v>
+        <v>0.2781</v>
       </c>
     </row>
     <row r="5">
@@ -565,22 +565,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>82903</v>
+        <v>89034</v>
       </c>
       <c r="C5" t="n">
-        <v>51590</v>
+        <v>51700</v>
       </c>
       <c r="D5" t="n">
-        <v>69835</v>
+        <v>69945</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.6223</v>
+        <v>0.5807</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.8423999999999999</v>
+        <v>0.7856000000000001</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.5851</v>
+        <v>0.5461</v>
       </c>
     </row>
     <row r="6">
@@ -615,22 +615,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>110649</v>
+        <v>120014</v>
       </c>
       <c r="C7" t="n">
-        <v>72458</v>
+        <v>74771</v>
       </c>
       <c r="D7" t="n">
-        <v>75932</v>
+        <v>78245</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.6548</v>
+        <v>0.623</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.6862</v>
+        <v>0.652</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.5752</v>
+        <v>0.5374</v>
       </c>
     </row>
     <row r="8">
@@ -655,7 +655,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.4964</v>
+        <v>0.4772</v>
       </c>
     </row>
     <row r="9">
@@ -665,22 +665,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>150307</v>
+        <v>161812</v>
       </c>
       <c r="C9" t="n">
-        <v>123675</v>
+        <v>125165</v>
       </c>
       <c r="D9" t="n">
-        <v>136887</v>
+        <v>138377</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.8228</v>
+        <v>0.7735</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.9107</v>
+        <v>0.8552</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.6593000000000001</v>
+        <v>0.613</v>
       </c>
     </row>
     <row r="10">
@@ -716,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H116"/>
+  <dimension ref="A1:H125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4035,8 +4035,254 @@
         <v>0</v>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>26829</v>
+      </c>
+      <c r="D117" t="n">
+        <v>3899</v>
+      </c>
+      <c r="E117" t="n">
+        <v>3899</v>
+      </c>
+      <c r="F117" s="2" t="n">
+        <v>0.1453</v>
+      </c>
+      <c r="G117" s="3" t="n">
+        <v>0.1453</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>0.0596</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="2" t="n"/>
+      <c r="G118" s="3" t="n"/>
+      <c r="H118" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>0</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" s="2" t="n"/>
+      <c r="G119" s="3" t="n"/>
+      <c r="H119" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>6131</v>
+      </c>
+      <c r="D120" t="n">
+        <v>110</v>
+      </c>
+      <c r="E120" t="n">
+        <v>110</v>
+      </c>
+      <c r="F120" s="2" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="G120" s="3" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="H120" s="2" t="n">
+        <v>0.0305</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="2" t="n"/>
+      <c r="G121" s="3" t="n"/>
+      <c r="H121" s="2" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>9365</v>
+      </c>
+      <c r="D122" t="n">
+        <v>2313</v>
+      </c>
+      <c r="E122" t="n">
+        <v>2313</v>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>0.247</v>
+      </c>
+      <c r="G122" s="3" t="n">
+        <v>0.247</v>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>0.0089</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="2" t="n"/>
+      <c r="G123" s="3" t="n"/>
+      <c r="H123" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>11505</v>
+      </c>
+      <c r="D124" t="n">
+        <v>1490</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1490</v>
+      </c>
+      <c r="F124" s="2" t="n">
+        <v>0.1295</v>
+      </c>
+      <c r="G124" s="3" t="n">
+        <v>0.1295</v>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>0.0168</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="2" t="n"/>
+      <c r="G125" s="3" t="n"/>
+      <c r="H125" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H116"/>
+  <autoFilter ref="A1:H125"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$134</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -494,22 +494,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>307120</v>
+        <v>337512</v>
       </c>
       <c r="C2" t="n">
-        <v>215303</v>
+        <v>235374</v>
       </c>
       <c r="D2" t="n">
-        <v>236810</v>
+        <v>267155</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.701</v>
+        <v>0.6973999999999999</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.7711</v>
+        <v>0.7915000000000001</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.5799</v>
+        <v>0.6001</v>
       </c>
     </row>
     <row r="3">
@@ -555,7 +555,7 @@
         <v>0.6208</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.2781</v>
+        <v>0.271</v>
       </c>
     </row>
     <row r="5">
@@ -565,22 +565,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>89034</v>
+        <v>96597</v>
       </c>
       <c r="C5" t="n">
-        <v>51700</v>
+        <v>57019</v>
       </c>
       <c r="D5" t="n">
-        <v>69945</v>
+        <v>77485</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.5807</v>
+        <v>0.5903</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.7856000000000001</v>
+        <v>0.8020999999999999</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.5461</v>
+        <v>0.5661</v>
       </c>
     </row>
     <row r="6">
@@ -615,22 +615,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>120014</v>
+        <v>132470</v>
       </c>
       <c r="C7" t="n">
-        <v>74771</v>
+        <v>83174</v>
       </c>
       <c r="D7" t="n">
-        <v>78245</v>
+        <v>86802</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.623</v>
+        <v>0.6279</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.652</v>
+        <v>0.6553</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.5374</v>
+        <v>0.5577000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -655,7 +655,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.4772</v>
+        <v>0.4886</v>
       </c>
     </row>
     <row r="9">
@@ -665,22 +665,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>161812</v>
+        <v>177134</v>
       </c>
       <c r="C9" t="n">
-        <v>125165</v>
+        <v>134535</v>
       </c>
       <c r="D9" t="n">
-        <v>138377</v>
+        <v>153383</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.7735</v>
+        <v>0.7595000000000001</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.8552</v>
+        <v>0.8659</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.613</v>
+        <v>0.632</v>
       </c>
     </row>
     <row r="10">
@@ -716,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H125"/>
+  <dimension ref="A1:H134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4281,8 +4281,256 @@
       <c r="G125" s="3" t="n"/>
       <c r="H125" s="2" t="n"/>
     </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>30392</v>
+      </c>
+      <c r="D126" t="n">
+        <v>20071</v>
+      </c>
+      <c r="E126" t="n">
+        <v>30345</v>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>0.6604000000000001</v>
+      </c>
+      <c r="G126" s="3" t="n">
+        <v>0.9984999999999999</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>0</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" s="2" t="n"/>
+      <c r="G127" s="3" t="n"/>
+      <c r="H127" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="2" t="n"/>
+      <c r="G128" s="3" t="n"/>
+      <c r="H128" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>7563</v>
+      </c>
+      <c r="D129" t="n">
+        <v>5319</v>
+      </c>
+      <c r="E129" t="n">
+        <v>7540</v>
+      </c>
+      <c r="F129" s="2" t="n">
+        <v>0.7033</v>
+      </c>
+      <c r="G129" s="3" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="H129" s="2" t="n">
+        <v>0.7963</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>0</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" s="2" t="n"/>
+      <c r="G130" s="3" t="n"/>
+      <c r="H130" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>12456</v>
+      </c>
+      <c r="D131" t="n">
+        <v>8403</v>
+      </c>
+      <c r="E131" t="n">
+        <v>8557</v>
+      </c>
+      <c r="F131" s="2" t="n">
+        <v>0.6746</v>
+      </c>
+      <c r="G131" s="3" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="H131" s="2" t="n">
+        <v>0.8797</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>0</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" s="2" t="n"/>
+      <c r="G132" s="3" t="n"/>
+      <c r="H132" s="2" t="n">
+        <v>0.9129999999999999</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>15322</v>
+      </c>
+      <c r="D133" t="n">
+        <v>9370</v>
+      </c>
+      <c r="E133" t="n">
+        <v>15006</v>
+      </c>
+      <c r="F133" s="2" t="n">
+        <v>0.6114999999999999</v>
+      </c>
+      <c r="G133" s="3" t="n">
+        <v>0.9793999999999999</v>
+      </c>
+      <c r="H133" s="2" t="n">
+        <v>0.9253</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" s="2" t="n"/>
+      <c r="G134" s="3" t="n"/>
+      <c r="H134" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H125"/>
+  <autoFilter ref="A1:H134"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$134</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$143</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -494,22 +494,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>337512</v>
+        <v>369200</v>
       </c>
       <c r="C2" t="n">
-        <v>235374</v>
+        <v>261035</v>
       </c>
       <c r="D2" t="n">
-        <v>267155</v>
+        <v>298835</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.6973999999999999</v>
+        <v>0.7070000000000001</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.7915000000000001</v>
+        <v>0.8094</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.6001</v>
+        <v>0.6093</v>
       </c>
     </row>
     <row r="3">
@@ -555,7 +555,7 @@
         <v>0.6208</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.271</v>
+        <v>0.2692</v>
       </c>
     </row>
     <row r="5">
@@ -565,22 +565,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>96597</v>
+        <v>103126</v>
       </c>
       <c r="C5" t="n">
-        <v>57019</v>
+        <v>61699</v>
       </c>
       <c r="D5" t="n">
-        <v>77485</v>
+        <v>82165</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.5903</v>
+        <v>0.5982999999999999</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.8020999999999999</v>
+        <v>0.7967</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.5661</v>
+        <v>0.5732</v>
       </c>
     </row>
     <row r="6">
@@ -615,22 +615,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>132470</v>
+        <v>144262</v>
       </c>
       <c r="C7" t="n">
-        <v>83174</v>
+        <v>92404</v>
       </c>
       <c r="D7" t="n">
-        <v>86802</v>
+        <v>97090</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.6279</v>
+        <v>0.6405</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.6553</v>
+        <v>0.6729999999999999</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.5577000000000001</v>
+        <v>0.575</v>
       </c>
     </row>
     <row r="8">
@@ -640,13 +640,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3051</v>
+        <v>3077</v>
       </c>
       <c r="C8" t="n">
-        <v>3051</v>
+        <v>3077</v>
       </c>
       <c r="D8" t="n">
-        <v>3051</v>
+        <v>3077</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
@@ -655,7 +655,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.4886</v>
+        <v>0.4945000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -665,22 +665,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>177134</v>
+        <v>197544</v>
       </c>
       <c r="C9" t="n">
-        <v>134535</v>
+        <v>152967</v>
       </c>
       <c r="D9" t="n">
-        <v>153383</v>
+        <v>173669</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.7595000000000001</v>
+        <v>0.7743000000000001</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.8659</v>
+        <v>0.8791</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.632</v>
+        <v>0.6507999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -716,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H134"/>
+  <dimension ref="A1:H143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4529,8 +4529,262 @@
       <c r="G134" s="3" t="n"/>
       <c r="H134" s="2" t="n"/>
     </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>31688</v>
+      </c>
+      <c r="D135" t="n">
+        <v>25661</v>
+      </c>
+      <c r="E135" t="n">
+        <v>31680</v>
+      </c>
+      <c r="F135" s="2" t="n">
+        <v>0.8098000000000001</v>
+      </c>
+      <c r="G135" s="3" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="H135" s="2" t="n">
+        <v>0.7181999999999999</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>0</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" s="2" t="n"/>
+      <c r="G136" s="3" t="n"/>
+      <c r="H136" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>0</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" s="2" t="n"/>
+      <c r="G137" s="3" t="n"/>
+      <c r="H137" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>6529</v>
+      </c>
+      <c r="D138" t="n">
+        <v>4680</v>
+      </c>
+      <c r="E138" t="n">
+        <v>4680</v>
+      </c>
+      <c r="F138" s="2" t="n">
+        <v>0.7168000000000001</v>
+      </c>
+      <c r="G138" s="3" t="n">
+        <v>0.7168000000000001</v>
+      </c>
+      <c r="H138" s="2" t="n">
+        <v>0.6552</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>0</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" s="2" t="n"/>
+      <c r="G139" s="3" t="n"/>
+      <c r="H139" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>11792</v>
+      </c>
+      <c r="D140" t="n">
+        <v>9230</v>
+      </c>
+      <c r="E140" t="n">
+        <v>10288</v>
+      </c>
+      <c r="F140" s="2" t="n">
+        <v>0.7827</v>
+      </c>
+      <c r="G140" s="3" t="n">
+        <v>0.8725000000000001</v>
+      </c>
+      <c r="H140" s="2" t="n">
+        <v>0.7645000000000001</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>26</v>
+      </c>
+      <c r="D141" t="n">
+        <v>26</v>
+      </c>
+      <c r="E141" t="n">
+        <v>26</v>
+      </c>
+      <c r="F141" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G141" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H141" s="2" t="n">
+        <v>0.6786</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>20410</v>
+      </c>
+      <c r="D142" t="n">
+        <v>18432</v>
+      </c>
+      <c r="E142" t="n">
+        <v>20286</v>
+      </c>
+      <c r="F142" s="2" t="n">
+        <v>0.9031</v>
+      </c>
+      <c r="G142" s="3" t="n">
+        <v>0.9939</v>
+      </c>
+      <c r="H142" s="2" t="n">
+        <v>0.8567</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>0</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0</v>
+      </c>
+      <c r="F143" s="2" t="n"/>
+      <c r="G143" s="3" t="n"/>
+      <c r="H143" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H134"/>
+  <autoFilter ref="A1:H143"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$143</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$152</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -494,22 +494,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>369200</v>
+        <v>397169</v>
       </c>
       <c r="C2" t="n">
-        <v>261035</v>
+        <v>287118</v>
       </c>
       <c r="D2" t="n">
-        <v>298835</v>
+        <v>326799</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.7070000000000001</v>
+        <v>0.7229000000000001</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.8094</v>
+        <v>0.8228</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.6093</v>
+        <v>0.6143999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -555,7 +555,7 @@
         <v>0.6208</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.2692</v>
+        <v>0.2667</v>
       </c>
     </row>
     <row r="5">
@@ -565,22 +565,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>103126</v>
+        <v>108994</v>
       </c>
       <c r="C5" t="n">
-        <v>61699</v>
+        <v>66379</v>
       </c>
       <c r="D5" t="n">
-        <v>82165</v>
+        <v>88030</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.5982999999999999</v>
+        <v>0.609</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.7967</v>
+        <v>0.8077</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.5732</v>
+        <v>0.5768</v>
       </c>
     </row>
     <row r="6">
@@ -615,22 +615,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>144262</v>
+        <v>157303</v>
       </c>
       <c r="C7" t="n">
-        <v>92404</v>
+        <v>104716</v>
       </c>
       <c r="D7" t="n">
-        <v>97090</v>
+        <v>109891</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.6405</v>
+        <v>0.6657</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.6729999999999999</v>
+        <v>0.6986</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.575</v>
+        <v>0.5832000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -640,13 +640,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3077</v>
+        <v>3091</v>
       </c>
       <c r="C8" t="n">
-        <v>3077</v>
+        <v>3091</v>
       </c>
       <c r="D8" t="n">
-        <v>3077</v>
+        <v>3091</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
@@ -655,7 +655,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.4945000000000001</v>
+        <v>0.4958</v>
       </c>
     </row>
     <row r="9">
@@ -665,22 +665,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>197544</v>
+        <v>211080</v>
       </c>
       <c r="C9" t="n">
-        <v>152967</v>
+        <v>164752</v>
       </c>
       <c r="D9" t="n">
-        <v>173669</v>
+        <v>187167</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.7743000000000001</v>
+        <v>0.7805</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.8791</v>
+        <v>0.8867</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.6507999999999999</v>
+        <v>0.6570999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -716,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H143"/>
+  <dimension ref="A1:H152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4783,8 +4783,260 @@
         <v>0</v>
       </c>
     </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>27969</v>
+      </c>
+      <c r="D144" t="n">
+        <v>26083</v>
+      </c>
+      <c r="E144" t="n">
+        <v>27964</v>
+      </c>
+      <c r="F144" s="2" t="n">
+        <v>0.9326000000000001</v>
+      </c>
+      <c r="G144" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="H144" s="2" t="n">
+        <v>0.6794</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>0</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" s="2" t="n"/>
+      <c r="G145" s="3" t="n"/>
+      <c r="H145" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>0</v>
+      </c>
+      <c r="D146" t="n">
+        <v>0</v>
+      </c>
+      <c r="E146" t="n">
+        <v>0</v>
+      </c>
+      <c r="F146" s="2" t="n"/>
+      <c r="G146" s="3" t="n"/>
+      <c r="H146" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>5868</v>
+      </c>
+      <c r="D147" t="n">
+        <v>4680</v>
+      </c>
+      <c r="E147" t="n">
+        <v>5865</v>
+      </c>
+      <c r="F147" s="2" t="n">
+        <v>0.7975</v>
+      </c>
+      <c r="G147" s="3" t="n">
+        <v>0.9995000000000001</v>
+      </c>
+      <c r="H147" s="2" t="n">
+        <v>0.6196</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>0</v>
+      </c>
+      <c r="D148" t="n">
+        <v>0</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0</v>
+      </c>
+      <c r="F148" s="2" t="n"/>
+      <c r="G148" s="3" t="n"/>
+      <c r="H148" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>13041</v>
+      </c>
+      <c r="D149" t="n">
+        <v>12312</v>
+      </c>
+      <c r="E149" t="n">
+        <v>12801</v>
+      </c>
+      <c r="F149" s="2" t="n">
+        <v>0.9440999999999999</v>
+      </c>
+      <c r="G149" s="3" t="n">
+        <v>0.9815999999999999</v>
+      </c>
+      <c r="H149" s="2" t="n">
+        <v>0.6758</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>14</v>
+      </c>
+      <c r="D150" t="n">
+        <v>14</v>
+      </c>
+      <c r="E150" t="n">
+        <v>14</v>
+      </c>
+      <c r="F150" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G150" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H150" s="2" t="n">
+        <v>0.5263</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>13536</v>
+      </c>
+      <c r="D151" t="n">
+        <v>11785</v>
+      </c>
+      <c r="E151" t="n">
+        <v>13498</v>
+      </c>
+      <c r="F151" s="2" t="n">
+        <v>0.8706</v>
+      </c>
+      <c r="G151" s="3" t="n">
+        <v>0.9972</v>
+      </c>
+      <c r="H151" s="2" t="n">
+        <v>0.7292000000000001</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>0</v>
+      </c>
+      <c r="D152" t="n">
+        <v>0</v>
+      </c>
+      <c r="E152" t="n">
+        <v>0</v>
+      </c>
+      <c r="F152" s="2" t="n"/>
+      <c r="G152" s="3" t="n"/>
+      <c r="H152" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H143"/>
+  <autoFilter ref="A1:H152"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$152</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$161</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -494,22 +494,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>397169</v>
+        <v>422461</v>
       </c>
       <c r="C2" t="n">
-        <v>287118</v>
+        <v>311477</v>
       </c>
       <c r="D2" t="n">
-        <v>326799</v>
+        <v>352058</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.7229000000000001</v>
+        <v>0.7373000000000001</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.8228</v>
+        <v>0.8334</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.6143999999999999</v>
+        <v>0.6194</v>
       </c>
     </row>
     <row r="3">
@@ -555,7 +555,7 @@
         <v>0.6208</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.2667</v>
+        <v>0.2658</v>
       </c>
     </row>
     <row r="5">
@@ -565,22 +565,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>108994</v>
+        <v>114937</v>
       </c>
       <c r="C5" t="n">
-        <v>66379</v>
+        <v>71338</v>
       </c>
       <c r="D5" t="n">
-        <v>88030</v>
+        <v>93972</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.609</v>
+        <v>0.6207</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.8077</v>
+        <v>0.8176000000000001</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.5768</v>
+        <v>0.5792</v>
       </c>
     </row>
     <row r="6">
@@ -615,22 +615,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>157303</v>
+        <v>171278</v>
       </c>
       <c r="C7" t="n">
-        <v>104716</v>
+        <v>117406</v>
       </c>
       <c r="D7" t="n">
-        <v>109891</v>
+        <v>123327</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.6657</v>
+        <v>0.6855</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.6986</v>
+        <v>0.72</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.5871999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -640,13 +640,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3091</v>
+        <v>3096</v>
       </c>
       <c r="C8" t="n">
-        <v>3091</v>
+        <v>3096</v>
       </c>
       <c r="D8" t="n">
-        <v>3091</v>
+        <v>3096</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
@@ -655,7 +655,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.4958</v>
+        <v>0.4995000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -665,22 +665,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>211080</v>
+        <v>224357</v>
       </c>
       <c r="C9" t="n">
-        <v>164752</v>
+        <v>177370</v>
       </c>
       <c r="D9" t="n">
-        <v>187167</v>
+        <v>200429</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.7805</v>
+        <v>0.7906</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.8867</v>
+        <v>0.8933</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.6570999999999999</v>
+        <v>0.6598999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -716,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H152"/>
+  <dimension ref="A1:H161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5035,8 +5035,260 @@
       <c r="G152" s="3" t="n"/>
       <c r="H152" s="2" t="n"/>
     </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>25292</v>
+      </c>
+      <c r="D153" t="n">
+        <v>24359</v>
+      </c>
+      <c r="E153" t="n">
+        <v>25259</v>
+      </c>
+      <c r="F153" s="2" t="n">
+        <v>0.9631000000000001</v>
+      </c>
+      <c r="G153" s="3" t="n">
+        <v>0.9987</v>
+      </c>
+      <c r="H153" s="2" t="n">
+        <v>0.6829999999999999</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>0</v>
+      </c>
+      <c r="D154" t="n">
+        <v>0</v>
+      </c>
+      <c r="E154" t="n">
+        <v>0</v>
+      </c>
+      <c r="F154" s="2" t="n"/>
+      <c r="G154" s="3" t="n"/>
+      <c r="H154" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>0</v>
+      </c>
+      <c r="D155" t="n">
+        <v>0</v>
+      </c>
+      <c r="E155" t="n">
+        <v>0</v>
+      </c>
+      <c r="F155" s="2" t="n"/>
+      <c r="G155" s="3" t="n"/>
+      <c r="H155" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>5943</v>
+      </c>
+      <c r="D156" t="n">
+        <v>4959</v>
+      </c>
+      <c r="E156" t="n">
+        <v>5942</v>
+      </c>
+      <c r="F156" s="2" t="n">
+        <v>0.8344</v>
+      </c>
+      <c r="G156" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="H156" s="2" t="n">
+        <v>0.6108</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>0</v>
+      </c>
+      <c r="D157" t="n">
+        <v>0</v>
+      </c>
+      <c r="E157" t="n">
+        <v>0</v>
+      </c>
+      <c r="F157" s="2" t="n"/>
+      <c r="G157" s="3" t="n"/>
+      <c r="H157" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>13975</v>
+      </c>
+      <c r="D158" t="n">
+        <v>12690</v>
+      </c>
+      <c r="E158" t="n">
+        <v>13436</v>
+      </c>
+      <c r="F158" s="2" t="n">
+        <v>0.9081</v>
+      </c>
+      <c r="G158" s="3" t="n">
+        <v>0.9614</v>
+      </c>
+      <c r="H158" s="2" t="n">
+        <v>0.6357</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>5</v>
+      </c>
+      <c r="D159" t="n">
+        <v>5</v>
+      </c>
+      <c r="E159" t="n">
+        <v>5</v>
+      </c>
+      <c r="F159" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G159" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H159" s="2" t="n">
+        <v>0.6296</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>13277</v>
+      </c>
+      <c r="D160" t="n">
+        <v>12618</v>
+      </c>
+      <c r="E160" t="n">
+        <v>13262</v>
+      </c>
+      <c r="F160" s="2" t="n">
+        <v>0.9504</v>
+      </c>
+      <c r="G160" s="3" t="n">
+        <v>0.9989</v>
+      </c>
+      <c r="H160" s="2" t="n">
+        <v>0.6943</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>0</v>
+      </c>
+      <c r="D161" t="n">
+        <v>0</v>
+      </c>
+      <c r="E161" t="n">
+        <v>0</v>
+      </c>
+      <c r="F161" s="2" t="n"/>
+      <c r="G161" s="3" t="n"/>
+      <c r="H161" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H152"/>
+  <autoFilter ref="A1:H161"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$161</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$170</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -494,22 +494,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>422461</v>
+        <v>444973</v>
       </c>
       <c r="C2" t="n">
-        <v>311477</v>
+        <v>328080</v>
       </c>
       <c r="D2" t="n">
-        <v>352058</v>
+        <v>373959</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0.7373000000000001</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.8334</v>
+        <v>0.8404</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.6194</v>
+        <v>0.6246</v>
       </c>
     </row>
     <row r="3">
@@ -555,7 +555,7 @@
         <v>0.6208</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.2658</v>
+        <v>0.2642</v>
       </c>
     </row>
     <row r="5">
@@ -565,22 +565,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>114937</v>
+        <v>120398</v>
       </c>
       <c r="C5" t="n">
-        <v>71338</v>
+        <v>75436</v>
       </c>
       <c r="D5" t="n">
-        <v>93972</v>
+        <v>99428</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.6207</v>
+        <v>0.6265999999999999</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.8176000000000001</v>
+        <v>0.8258</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.5792</v>
+        <v>0.5838</v>
       </c>
     </row>
     <row r="6">
@@ -615,22 +615,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>171278</v>
+        <v>184568</v>
       </c>
       <c r="C7" t="n">
-        <v>117406</v>
+        <v>124696</v>
       </c>
       <c r="D7" t="n">
-        <v>123327</v>
+        <v>133439</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.6855</v>
+        <v>0.6756</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.72</v>
+        <v>0.723</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.5871999999999999</v>
+        <v>0.5821999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -640,13 +640,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3096</v>
+        <v>3105</v>
       </c>
       <c r="C8" t="n">
-        <v>3096</v>
+        <v>3105</v>
       </c>
       <c r="D8" t="n">
-        <v>3096</v>
+        <v>3105</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
@@ -655,7 +655,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.4995000000000001</v>
+        <v>0.5069</v>
       </c>
     </row>
     <row r="9">
@@ -665,22 +665,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>224357</v>
+        <v>236327</v>
       </c>
       <c r="C9" t="n">
-        <v>177370</v>
+        <v>186872</v>
       </c>
       <c r="D9" t="n">
-        <v>200429</v>
+        <v>212258</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.7906</v>
+        <v>0.7907</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.8933</v>
+        <v>0.8981999999999999</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.6598999999999999</v>
+        <v>0.6573</v>
       </c>
     </row>
     <row r="10">
@@ -716,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H161"/>
+  <dimension ref="A1:H170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5287,8 +5287,260 @@
       <c r="G161" s="3" t="n"/>
       <c r="H161" s="2" t="n"/>
     </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>22512</v>
+      </c>
+      <c r="D162" t="n">
+        <v>16603</v>
+      </c>
+      <c r="E162" t="n">
+        <v>21901</v>
+      </c>
+      <c r="F162" s="2" t="n">
+        <v>0.7375</v>
+      </c>
+      <c r="G162" s="3" t="n">
+        <v>0.9729000000000001</v>
+      </c>
+      <c r="H162" s="2" t="n">
+        <v>0.6987000000000001</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>0</v>
+      </c>
+      <c r="D163" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" t="n">
+        <v>0</v>
+      </c>
+      <c r="F163" s="2" t="n"/>
+      <c r="G163" s="3" t="n"/>
+      <c r="H163" s="2" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>0</v>
+      </c>
+      <c r="D164" t="n">
+        <v>0</v>
+      </c>
+      <c r="E164" t="n">
+        <v>0</v>
+      </c>
+      <c r="F164" s="2" t="n"/>
+      <c r="G164" s="3" t="n"/>
+      <c r="H164" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>5461</v>
+      </c>
+      <c r="D165" t="n">
+        <v>4098</v>
+      </c>
+      <c r="E165" t="n">
+        <v>5456</v>
+      </c>
+      <c r="F165" s="2" t="n">
+        <v>0.7504000000000001</v>
+      </c>
+      <c r="G165" s="3" t="n">
+        <v>0.9991</v>
+      </c>
+      <c r="H165" s="2" t="n">
+        <v>0.6581999999999999</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>0</v>
+      </c>
+      <c r="D166" t="n">
+        <v>0</v>
+      </c>
+      <c r="E166" t="n">
+        <v>0</v>
+      </c>
+      <c r="F166" s="2" t="n"/>
+      <c r="G166" s="3" t="n"/>
+      <c r="H166" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>13290</v>
+      </c>
+      <c r="D167" t="n">
+        <v>7290</v>
+      </c>
+      <c r="E167" t="n">
+        <v>10112</v>
+      </c>
+      <c r="F167" s="2" t="n">
+        <v>0.5485</v>
+      </c>
+      <c r="G167" s="3" t="n">
+        <v>0.7609</v>
+      </c>
+      <c r="H167" s="2" t="n">
+        <v>0.512</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>9</v>
+      </c>
+      <c r="D168" t="n">
+        <v>9</v>
+      </c>
+      <c r="E168" t="n">
+        <v>9</v>
+      </c>
+      <c r="F168" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G168" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H168" s="2" t="n">
+        <v>0.7143</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>11970</v>
+      </c>
+      <c r="D169" t="n">
+        <v>9502</v>
+      </c>
+      <c r="E169" t="n">
+        <v>11829</v>
+      </c>
+      <c r="F169" s="2" t="n">
+        <v>0.7938</v>
+      </c>
+      <c r="G169" s="3" t="n">
+        <v>0.9882</v>
+      </c>
+      <c r="H169" s="2" t="n">
+        <v>0.6221</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>0</v>
+      </c>
+      <c r="D170" t="n">
+        <v>0</v>
+      </c>
+      <c r="E170" t="n">
+        <v>0</v>
+      </c>
+      <c r="F170" s="2" t="n"/>
+      <c r="G170" s="3" t="n"/>
+      <c r="H170" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H161"/>
+  <autoFilter ref="A1:H170"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$170</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$179</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -494,22 +494,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>444973</v>
+        <v>463453</v>
       </c>
       <c r="C2" t="n">
-        <v>328080</v>
+        <v>331205</v>
       </c>
       <c r="D2" t="n">
-        <v>373959</v>
+        <v>377084</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.7373000000000001</v>
+        <v>0.7145999999999999</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.8404</v>
+        <v>0.8136</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.6246</v>
+        <v>0.5947</v>
       </c>
     </row>
     <row r="3">
@@ -555,7 +555,7 @@
         <v>0.6208</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.2642</v>
+        <v>0.2633</v>
       </c>
     </row>
     <row r="5">
@@ -565,22 +565,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>120398</v>
+        <v>125399</v>
       </c>
       <c r="C5" t="n">
-        <v>75436</v>
+        <v>76152</v>
       </c>
       <c r="D5" t="n">
-        <v>99428</v>
+        <v>100144</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.6265999999999999</v>
+        <v>0.6073</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.8258</v>
+        <v>0.7986</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.5838</v>
+        <v>0.5596</v>
       </c>
     </row>
     <row r="6">
@@ -615,22 +615,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>184568</v>
+        <v>194760</v>
       </c>
       <c r="C7" t="n">
-        <v>124696</v>
+        <v>126168</v>
       </c>
       <c r="D7" t="n">
-        <v>133439</v>
+        <v>134911</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.6756</v>
+        <v>0.6478</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.723</v>
+        <v>0.6927</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.5821999999999999</v>
+        <v>0.5514</v>
       </c>
     </row>
     <row r="8">
@@ -640,13 +640,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3105</v>
+        <v>3107</v>
       </c>
       <c r="C8" t="n">
-        <v>3105</v>
+        <v>3107</v>
       </c>
       <c r="D8" t="n">
-        <v>3105</v>
+        <v>3107</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
@@ -655,7 +655,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.5069</v>
+        <v>0.4928</v>
       </c>
     </row>
     <row r="9">
@@ -665,22 +665,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>236327</v>
+        <v>246775</v>
       </c>
       <c r="C9" t="n">
-        <v>186872</v>
+        <v>189161</v>
       </c>
       <c r="D9" t="n">
-        <v>212258</v>
+        <v>214547</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.7907</v>
+        <v>0.7665000000000001</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.8981999999999999</v>
+        <v>0.8694</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.6573</v>
+        <v>0.6233</v>
       </c>
     </row>
     <row r="10">
@@ -716,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H170"/>
+  <dimension ref="A1:H179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5539,8 +5539,260 @@
         <v>0</v>
       </c>
     </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>18480</v>
+      </c>
+      <c r="D171" t="n">
+        <v>3125</v>
+      </c>
+      <c r="E171" t="n">
+        <v>3125</v>
+      </c>
+      <c r="F171" s="2" t="n">
+        <v>0.1691</v>
+      </c>
+      <c r="G171" s="3" t="n">
+        <v>0.1691</v>
+      </c>
+      <c r="H171" s="2" t="n">
+        <v>0.0692</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>0</v>
+      </c>
+      <c r="D172" t="n">
+        <v>0</v>
+      </c>
+      <c r="E172" t="n">
+        <v>0</v>
+      </c>
+      <c r="F172" s="2" t="n"/>
+      <c r="G172" s="3" t="n"/>
+      <c r="H172" s="2" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>0</v>
+      </c>
+      <c r="D173" t="n">
+        <v>0</v>
+      </c>
+      <c r="E173" t="n">
+        <v>0</v>
+      </c>
+      <c r="F173" s="2" t="n"/>
+      <c r="G173" s="3" t="n"/>
+      <c r="H173" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>5001</v>
+      </c>
+      <c r="D174" t="n">
+        <v>716</v>
+      </c>
+      <c r="E174" t="n">
+        <v>716</v>
+      </c>
+      <c r="F174" s="2" t="n">
+        <v>0.1432</v>
+      </c>
+      <c r="G174" s="3" t="n">
+        <v>0.1432</v>
+      </c>
+      <c r="H174" s="2" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>0</v>
+      </c>
+      <c r="D175" t="n">
+        <v>0</v>
+      </c>
+      <c r="E175" t="n">
+        <v>0</v>
+      </c>
+      <c r="F175" s="2" t="n"/>
+      <c r="G175" s="3" t="n"/>
+      <c r="H175" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>10192</v>
+      </c>
+      <c r="D176" t="n">
+        <v>1472</v>
+      </c>
+      <c r="E176" t="n">
+        <v>1472</v>
+      </c>
+      <c r="F176" s="2" t="n">
+        <v>0.1444</v>
+      </c>
+      <c r="G176" s="3" t="n">
+        <v>0.1444</v>
+      </c>
+      <c r="H176" s="2" t="n">
+        <v>0.0243</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>2</v>
+      </c>
+      <c r="D177" t="n">
+        <v>2</v>
+      </c>
+      <c r="E177" t="n">
+        <v>2</v>
+      </c>
+      <c r="F177" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G177" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H177" s="2" t="n">
+        <v>0.0323</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>10448</v>
+      </c>
+      <c r="D178" t="n">
+        <v>2289</v>
+      </c>
+      <c r="E178" t="n">
+        <v>2289</v>
+      </c>
+      <c r="F178" s="2" t="n">
+        <v>0.2191</v>
+      </c>
+      <c r="G178" s="3" t="n">
+        <v>0.2191</v>
+      </c>
+      <c r="H178" s="2" t="n">
+        <v>0.04559999999999999</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>0</v>
+      </c>
+      <c r="D179" t="n">
+        <v>0</v>
+      </c>
+      <c r="E179" t="n">
+        <v>0</v>
+      </c>
+      <c r="F179" s="2" t="n"/>
+      <c r="G179" s="3" t="n"/>
+      <c r="H179" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H170"/>
+  <autoFilter ref="A1:H179"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$179</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$188</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -494,22 +494,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>463453</v>
+        <v>489900</v>
       </c>
       <c r="C2" t="n">
-        <v>331205</v>
+        <v>351328</v>
       </c>
       <c r="D2" t="n">
-        <v>377084</v>
+        <v>403337</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.7145999999999999</v>
+        <v>0.7171</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.8136</v>
+        <v>0.8233</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.5947</v>
+        <v>0.6008</v>
       </c>
     </row>
     <row r="3">
@@ -555,7 +555,7 @@
         <v>0.6208</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.2633</v>
+        <v>0.2625</v>
       </c>
     </row>
     <row r="5">
@@ -565,22 +565,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>125399</v>
+        <v>131818</v>
       </c>
       <c r="C5" t="n">
-        <v>76152</v>
+        <v>81018</v>
       </c>
       <c r="D5" t="n">
-        <v>100144</v>
+        <v>106559</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.6073</v>
+        <v>0.6146</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.7986</v>
+        <v>0.8084</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.5596</v>
+        <v>0.5655</v>
       </c>
     </row>
     <row r="6">
@@ -590,13 +590,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
@@ -615,22 +615,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>194760</v>
+        <v>204539</v>
       </c>
       <c r="C7" t="n">
-        <v>126168</v>
+        <v>130869</v>
       </c>
       <c r="D7" t="n">
-        <v>134911</v>
+        <v>140584</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.6478</v>
+        <v>0.6397999999999999</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.6927</v>
+        <v>0.6873</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.5514</v>
+        <v>0.5471</v>
       </c>
     </row>
     <row r="8">
@@ -655,7 +655,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.4928</v>
+        <v>0.4925</v>
       </c>
     </row>
     <row r="9">
@@ -665,22 +665,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>246775</v>
+        <v>259391</v>
       </c>
       <c r="C9" t="n">
-        <v>189161</v>
+        <v>198151</v>
       </c>
       <c r="D9" t="n">
-        <v>214547</v>
+        <v>227100</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.7665000000000001</v>
+        <v>0.7639</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.8694</v>
+        <v>0.8754999999999999</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.6233</v>
+        <v>0.6219</v>
       </c>
     </row>
     <row r="10">
@@ -716,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H179"/>
+  <dimension ref="A1:H188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5791,8 +5791,258 @@
         <v>0</v>
       </c>
     </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>26447</v>
+      </c>
+      <c r="D180" t="n">
+        <v>20123</v>
+      </c>
+      <c r="E180" t="n">
+        <v>26253</v>
+      </c>
+      <c r="F180" s="2" t="n">
+        <v>0.7609</v>
+      </c>
+      <c r="G180" s="3" t="n">
+        <v>0.9926999999999999</v>
+      </c>
+      <c r="H180" s="2" t="n">
+        <v>0.7126</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>0</v>
+      </c>
+      <c r="D181" t="n">
+        <v>0</v>
+      </c>
+      <c r="E181" t="n">
+        <v>0</v>
+      </c>
+      <c r="F181" s="2" t="n"/>
+      <c r="G181" s="3" t="n"/>
+      <c r="H181" s="2" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>0</v>
+      </c>
+      <c r="D182" t="n">
+        <v>0</v>
+      </c>
+      <c r="E182" t="n">
+        <v>0</v>
+      </c>
+      <c r="F182" s="2" t="n"/>
+      <c r="G182" s="3" t="n"/>
+      <c r="H182" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>6419</v>
+      </c>
+      <c r="D183" t="n">
+        <v>4866</v>
+      </c>
+      <c r="E183" t="n">
+        <v>6415</v>
+      </c>
+      <c r="F183" s="2" t="n">
+        <v>0.7581</v>
+      </c>
+      <c r="G183" s="3" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="H183" s="2" t="n">
+        <v>0.6857</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>4</v>
+      </c>
+      <c r="D184" t="n">
+        <v>4</v>
+      </c>
+      <c r="E184" t="n">
+        <v>4</v>
+      </c>
+      <c r="F184" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G184" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H184" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>9779</v>
+      </c>
+      <c r="D185" t="n">
+        <v>4701</v>
+      </c>
+      <c r="E185" t="n">
+        <v>5673</v>
+      </c>
+      <c r="F185" s="2" t="n">
+        <v>0.4807</v>
+      </c>
+      <c r="G185" s="3" t="n">
+        <v>0.5800999999999999</v>
+      </c>
+      <c r="H185" s="2" t="n">
+        <v>0.4675</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>0</v>
+      </c>
+      <c r="D186" t="n">
+        <v>0</v>
+      </c>
+      <c r="E186" t="n">
+        <v>0</v>
+      </c>
+      <c r="F186" s="2" t="n"/>
+      <c r="G186" s="3" t="n"/>
+      <c r="H186" s="2" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>12616</v>
+      </c>
+      <c r="D187" t="n">
+        <v>8990</v>
+      </c>
+      <c r="E187" t="n">
+        <v>12553</v>
+      </c>
+      <c r="F187" s="2" t="n">
+        <v>0.7126</v>
+      </c>
+      <c r="G187" s="3" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="H187" s="2" t="n">
+        <v>0.5943999999999999</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>0</v>
+      </c>
+      <c r="D188" t="n">
+        <v>0</v>
+      </c>
+      <c r="E188" t="n">
+        <v>0</v>
+      </c>
+      <c r="F188" s="2" t="n"/>
+      <c r="G188" s="3" t="n"/>
+      <c r="H188" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H179"/>
+  <autoFilter ref="A1:H188"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$188</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$197</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -494,22 +494,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>489900</v>
+        <v>515896</v>
       </c>
       <c r="C2" t="n">
-        <v>351328</v>
+        <v>374700</v>
       </c>
       <c r="D2" t="n">
-        <v>403337</v>
+        <v>429320</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.7171</v>
+        <v>0.7262999999999999</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.8233</v>
+        <v>0.8321999999999999</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.6008</v>
+        <v>0.607</v>
       </c>
     </row>
     <row r="3">
@@ -555,7 +555,7 @@
         <v>0.6208</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.2625</v>
+        <v>0.2617</v>
       </c>
     </row>
     <row r="5">
@@ -565,22 +565,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>131818</v>
+        <v>138123</v>
       </c>
       <c r="C5" t="n">
-        <v>81018</v>
+        <v>86137</v>
       </c>
       <c r="D5" t="n">
-        <v>106559</v>
+        <v>112860</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.6146</v>
+        <v>0.6236</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.8084</v>
+        <v>0.8170999999999999</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.5655</v>
+        <v>0.5761999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -590,13 +590,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
@@ -615,22 +615,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>204539</v>
+        <v>217863</v>
       </c>
       <c r="C7" t="n">
-        <v>130869</v>
+        <v>141235</v>
       </c>
       <c r="D7" t="n">
-        <v>140584</v>
+        <v>151313</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.6397999999999999</v>
+        <v>0.6483</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.6873</v>
+        <v>0.6945</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.5471</v>
+        <v>0.5629</v>
       </c>
     </row>
     <row r="8">
@@ -640,13 +640,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3107</v>
+        <v>3111</v>
       </c>
       <c r="C8" t="n">
-        <v>3107</v>
+        <v>3111</v>
       </c>
       <c r="D8" t="n">
-        <v>3107</v>
+        <v>3111</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
@@ -655,7 +655,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.4925</v>
+        <v>0.5027</v>
       </c>
     </row>
     <row r="9">
@@ -665,22 +665,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>259391</v>
+        <v>276979</v>
       </c>
       <c r="C9" t="n">
-        <v>198151</v>
+        <v>211954</v>
       </c>
       <c r="D9" t="n">
-        <v>227100</v>
+        <v>244600</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.7639</v>
+        <v>0.7652</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.8754999999999999</v>
+        <v>0.8831</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.6219</v>
+        <v>0.6328</v>
       </c>
     </row>
     <row r="10">
@@ -716,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H188"/>
+  <dimension ref="A1:H197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6041,8 +6041,262 @@
       <c r="G188" s="3" t="n"/>
       <c r="H188" s="2" t="n"/>
     </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>25996</v>
+      </c>
+      <c r="D189" t="n">
+        <v>23372</v>
+      </c>
+      <c r="E189" t="n">
+        <v>25983</v>
+      </c>
+      <c r="F189" s="2" t="n">
+        <v>0.8991</v>
+      </c>
+      <c r="G189" s="3" t="n">
+        <v>0.9995000000000001</v>
+      </c>
+      <c r="H189" s="2" t="n">
+        <v>0.7198</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>0</v>
+      </c>
+      <c r="D190" t="n">
+        <v>0</v>
+      </c>
+      <c r="E190" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" s="2" t="n"/>
+      <c r="G190" s="3" t="n"/>
+      <c r="H190" s="2" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>0</v>
+      </c>
+      <c r="D191" t="n">
+        <v>0</v>
+      </c>
+      <c r="E191" t="n">
+        <v>0</v>
+      </c>
+      <c r="F191" s="2" t="n"/>
+      <c r="G191" s="3" t="n"/>
+      <c r="H191" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>6305</v>
+      </c>
+      <c r="D192" t="n">
+        <v>5119</v>
+      </c>
+      <c r="E192" t="n">
+        <v>6301</v>
+      </c>
+      <c r="F192" s="2" t="n">
+        <v>0.8119</v>
+      </c>
+      <c r="G192" s="3" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="H192" s="2" t="n">
+        <v>0.8244</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>9</v>
+      </c>
+      <c r="D193" t="n">
+        <v>9</v>
+      </c>
+      <c r="E193" t="n">
+        <v>9</v>
+      </c>
+      <c r="F193" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G193" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H193" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>13324</v>
+      </c>
+      <c r="D194" t="n">
+        <v>10366</v>
+      </c>
+      <c r="E194" t="n">
+        <v>10729</v>
+      </c>
+      <c r="F194" s="2" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="G194" s="3" t="n">
+        <v>0.8051999999999999</v>
+      </c>
+      <c r="H194" s="2" t="n">
+        <v>0.8370000000000001</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>4</v>
+      </c>
+      <c r="D195" t="n">
+        <v>4</v>
+      </c>
+      <c r="E195" t="n">
+        <v>4</v>
+      </c>
+      <c r="F195" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G195" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H195" s="2" t="n">
+        <v>0.8056</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>17588</v>
+      </c>
+      <c r="D196" t="n">
+        <v>13803</v>
+      </c>
+      <c r="E196" t="n">
+        <v>17500</v>
+      </c>
+      <c r="F196" s="2" t="n">
+        <v>0.7848000000000001</v>
+      </c>
+      <c r="G196" s="3" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="H196" s="2" t="n">
+        <v>0.8276</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>0</v>
+      </c>
+      <c r="D197" t="n">
+        <v>0</v>
+      </c>
+      <c r="E197" t="n">
+        <v>0</v>
+      </c>
+      <c r="F197" s="2" t="n"/>
+      <c r="G197" s="3" t="n"/>
+      <c r="H197" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H188"/>
+  <autoFilter ref="A1:H197"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$197</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$206</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -494,22 +494,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>515896</v>
+        <v>538541</v>
       </c>
       <c r="C2" t="n">
-        <v>374700</v>
+        <v>396586</v>
       </c>
       <c r="D2" t="n">
-        <v>429320</v>
+        <v>451964</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.7262999999999999</v>
+        <v>0.7364000000000001</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.8321999999999999</v>
+        <v>0.8392000000000001</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.607</v>
+        <v>0.6154999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -555,7 +555,7 @@
         <v>0.6208</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.2617</v>
+        <v>0.2609</v>
       </c>
     </row>
     <row r="5">
@@ -565,22 +565,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>138123</v>
+        <v>143837</v>
       </c>
       <c r="C5" t="n">
-        <v>86137</v>
+        <v>90827</v>
       </c>
       <c r="D5" t="n">
-        <v>112860</v>
+        <v>118571</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.6236</v>
+        <v>0.6315</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.8170999999999999</v>
+        <v>0.8243</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.5761999999999999</v>
+        <v>0.5811999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -590,13 +590,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C6" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D6" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
@@ -615,22 +615,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>217863</v>
+        <v>229193</v>
       </c>
       <c r="C7" t="n">
-        <v>141235</v>
+        <v>151279</v>
       </c>
       <c r="D7" t="n">
-        <v>151313</v>
+        <v>161700</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.6483</v>
+        <v>0.6601</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.6945</v>
+        <v>0.7055</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.5629</v>
+        <v>0.5717</v>
       </c>
     </row>
     <row r="8">
@@ -640,13 +640,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3111</v>
+        <v>3112</v>
       </c>
       <c r="C8" t="n">
-        <v>3111</v>
+        <v>3112</v>
       </c>
       <c r="D8" t="n">
-        <v>3111</v>
+        <v>3112</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
@@ -655,7 +655,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.5027</v>
+        <v>0.4996</v>
       </c>
     </row>
     <row r="9">
@@ -665,22 +665,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>276979</v>
+        <v>292960</v>
       </c>
       <c r="C9" t="n">
-        <v>211954</v>
+        <v>225273</v>
       </c>
       <c r="D9" t="n">
-        <v>244600</v>
+        <v>260526</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.7652</v>
+        <v>0.769</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.8831</v>
+        <v>0.8893000000000001</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.6328</v>
+        <v>0.637</v>
       </c>
     </row>
     <row r="10">
@@ -716,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H197"/>
+  <dimension ref="A1:H206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6295,8 +6295,262 @@
       <c r="G197" s="3" t="n"/>
       <c r="H197" s="2" t="n"/>
     </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>22645</v>
+      </c>
+      <c r="D198" t="n">
+        <v>21886</v>
+      </c>
+      <c r="E198" t="n">
+        <v>22644</v>
+      </c>
+      <c r="F198" s="2" t="n">
+        <v>0.9665</v>
+      </c>
+      <c r="G198" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H198" s="2" t="n">
+        <v>0.7287</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>0</v>
+      </c>
+      <c r="D199" t="n">
+        <v>0</v>
+      </c>
+      <c r="E199" t="n">
+        <v>0</v>
+      </c>
+      <c r="F199" s="2" t="n"/>
+      <c r="G199" s="3" t="n"/>
+      <c r="H199" s="2" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>0</v>
+      </c>
+      <c r="D200" t="n">
+        <v>0</v>
+      </c>
+      <c r="E200" t="n">
+        <v>0</v>
+      </c>
+      <c r="F200" s="2" t="n"/>
+      <c r="G200" s="3" t="n"/>
+      <c r="H200" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>5714</v>
+      </c>
+      <c r="D201" t="n">
+        <v>4690</v>
+      </c>
+      <c r="E201" t="n">
+        <v>5711</v>
+      </c>
+      <c r="F201" s="2" t="n">
+        <v>0.8208</v>
+      </c>
+      <c r="G201" s="3" t="n">
+        <v>0.9995000000000001</v>
+      </c>
+      <c r="H201" s="2" t="n">
+        <v>0.6815000000000001</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>11</v>
+      </c>
+      <c r="D202" t="n">
+        <v>11</v>
+      </c>
+      <c r="E202" t="n">
+        <v>11</v>
+      </c>
+      <c r="F202" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G202" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H202" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>11330</v>
+      </c>
+      <c r="D203" t="n">
+        <v>10044</v>
+      </c>
+      <c r="E203" t="n">
+        <v>10387</v>
+      </c>
+      <c r="F203" s="2" t="n">
+        <v>0.8865000000000001</v>
+      </c>
+      <c r="G203" s="3" t="n">
+        <v>0.9168000000000001</v>
+      </c>
+      <c r="H203" s="2" t="n">
+        <v>0.7167</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>1</v>
+      </c>
+      <c r="D204" t="n">
+        <v>1</v>
+      </c>
+      <c r="E204" t="n">
+        <v>1</v>
+      </c>
+      <c r="F204" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G204" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H204" s="2" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>15981</v>
+      </c>
+      <c r="D205" t="n">
+        <v>13319</v>
+      </c>
+      <c r="E205" t="n">
+        <v>15926</v>
+      </c>
+      <c r="F205" s="2" t="n">
+        <v>0.8334</v>
+      </c>
+      <c r="G205" s="3" t="n">
+        <v>0.9965999999999999</v>
+      </c>
+      <c r="H205" s="2" t="n">
+        <v>0.7081000000000001</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>0</v>
+      </c>
+      <c r="D206" t="n">
+        <v>0</v>
+      </c>
+      <c r="E206" t="n">
+        <v>0</v>
+      </c>
+      <c r="F206" s="2" t="n"/>
+      <c r="G206" s="3" t="n"/>
+      <c r="H206" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H197"/>
+  <autoFilter ref="A1:H206"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$206</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$215</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -494,22 +494,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>538541</v>
+        <v>565706</v>
       </c>
       <c r="C2" t="n">
-        <v>396586</v>
+        <v>423560</v>
       </c>
       <c r="D2" t="n">
-        <v>451964</v>
+        <v>479128</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.7364000000000001</v>
+        <v>0.7487</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.8392000000000001</v>
+        <v>0.847</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.6154999999999999</v>
+        <v>0.6318</v>
       </c>
     </row>
     <row r="3">
@@ -555,7 +555,7 @@
         <v>0.6208</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.2609</v>
+        <v>0.2601</v>
       </c>
     </row>
     <row r="5">
@@ -565,22 +565,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>143837</v>
+        <v>149762</v>
       </c>
       <c r="C5" t="n">
-        <v>90827</v>
+        <v>95192</v>
       </c>
       <c r="D5" t="n">
-        <v>118571</v>
+        <v>124473</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.6315</v>
+        <v>0.6356000000000001</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.8243</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.5811999999999999</v>
+        <v>0.585</v>
       </c>
     </row>
     <row r="6">
@@ -590,13 +590,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C6" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D6" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
@@ -615,22 +615,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>229193</v>
+        <v>241453</v>
       </c>
       <c r="C7" t="n">
-        <v>151279</v>
+        <v>163159</v>
       </c>
       <c r="D7" t="n">
-        <v>161700</v>
+        <v>173885</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.6601</v>
+        <v>0.6757</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7055</v>
+        <v>0.7202</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.5717</v>
+        <v>0.5785</v>
       </c>
     </row>
     <row r="8">
@@ -640,13 +640,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3112</v>
+        <v>3122</v>
       </c>
       <c r="C8" t="n">
-        <v>3112</v>
+        <v>3122</v>
       </c>
       <c r="D8" t="n">
-        <v>3112</v>
+        <v>3122</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
@@ -655,7 +655,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.4996</v>
+        <v>0.5042</v>
       </c>
     </row>
     <row r="9">
@@ -665,22 +665,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>292960</v>
+        <v>308557</v>
       </c>
       <c r="C9" t="n">
-        <v>225273</v>
+        <v>239089</v>
       </c>
       <c r="D9" t="n">
-        <v>260526</v>
+        <v>275929</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.769</v>
+        <v>0.7748999999999999</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.8893000000000001</v>
+        <v>0.8943000000000001</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.637</v>
+        <v>0.6402</v>
       </c>
     </row>
     <row r="10">
@@ -716,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H206"/>
+  <dimension ref="A1:H215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6549,8 +6549,262 @@
       <c r="G206" s="3" t="n"/>
       <c r="H206" s="2" t="n"/>
     </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>27165</v>
+      </c>
+      <c r="D207" t="n">
+        <v>26974</v>
+      </c>
+      <c r="E207" t="n">
+        <v>27164</v>
+      </c>
+      <c r="F207" s="2" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="G207" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H207" s="2" t="n">
+        <v>0.8164</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>0</v>
+      </c>
+      <c r="D208" t="n">
+        <v>0</v>
+      </c>
+      <c r="E208" t="n">
+        <v>0</v>
+      </c>
+      <c r="F208" s="2" t="n"/>
+      <c r="G208" s="3" t="n"/>
+      <c r="H208" s="2" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>0</v>
+      </c>
+      <c r="D209" t="n">
+        <v>0</v>
+      </c>
+      <c r="E209" t="n">
+        <v>0</v>
+      </c>
+      <c r="F209" s="2" t="n"/>
+      <c r="G209" s="3" t="n"/>
+      <c r="H209" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>5925</v>
+      </c>
+      <c r="D210" t="n">
+        <v>4365</v>
+      </c>
+      <c r="E210" t="n">
+        <v>5902</v>
+      </c>
+      <c r="F210" s="2" t="n">
+        <v>0.7367</v>
+      </c>
+      <c r="G210" s="3" t="n">
+        <v>0.9961</v>
+      </c>
+      <c r="H210" s="2" t="n">
+        <v>0.657</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>4</v>
+      </c>
+      <c r="D211" t="n">
+        <v>4</v>
+      </c>
+      <c r="E211" t="n">
+        <v>4</v>
+      </c>
+      <c r="F211" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G211" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H211" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>12260</v>
+      </c>
+      <c r="D212" t="n">
+        <v>11880</v>
+      </c>
+      <c r="E212" t="n">
+        <v>12185</v>
+      </c>
+      <c r="F212" s="2" t="n">
+        <v>0.9690000000000001</v>
+      </c>
+      <c r="G212" s="3" t="n">
+        <v>0.9939</v>
+      </c>
+      <c r="H212" s="2" t="n">
+        <v>0.6955</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>10</v>
+      </c>
+      <c r="D213" t="n">
+        <v>10</v>
+      </c>
+      <c r="E213" t="n">
+        <v>10</v>
+      </c>
+      <c r="F213" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G213" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H213" s="2" t="n">
+        <v>0.6222</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>15597</v>
+      </c>
+      <c r="D214" t="n">
+        <v>13816</v>
+      </c>
+      <c r="E214" t="n">
+        <v>15403</v>
+      </c>
+      <c r="F214" s="2" t="n">
+        <v>0.8858</v>
+      </c>
+      <c r="G214" s="3" t="n">
+        <v>0.9876</v>
+      </c>
+      <c r="H214" s="2" t="n">
+        <v>0.6939</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>0</v>
+      </c>
+      <c r="D215" t="n">
+        <v>0</v>
+      </c>
+      <c r="E215" t="n">
+        <v>0</v>
+      </c>
+      <c r="F215" s="2" t="n"/>
+      <c r="G215" s="3" t="n"/>
+      <c r="H215" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H206"/>
+  <autoFilter ref="A1:H215"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$215</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$224</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -494,22 +494,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>565706</v>
+        <v>588768</v>
       </c>
       <c r="C2" t="n">
-        <v>423560</v>
+        <v>445552</v>
       </c>
       <c r="D2" t="n">
-        <v>479128</v>
+        <v>501935</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.7487</v>
+        <v>0.7568</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.847</v>
+        <v>0.8525</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.6318</v>
+        <v>0.6261</v>
       </c>
     </row>
     <row r="3">
@@ -555,7 +555,7 @@
         <v>0.6208</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.2601</v>
+        <v>0.2593</v>
       </c>
     </row>
     <row r="5">
@@ -565,22 +565,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>149762</v>
+        <v>156896</v>
       </c>
       <c r="C5" t="n">
-        <v>95192</v>
+        <v>100603</v>
       </c>
       <c r="D5" t="n">
-        <v>124473</v>
+        <v>131505</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.6356000000000001</v>
+        <v>0.6412</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.8310999999999999</v>
+        <v>0.8381999999999999</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.585</v>
+        <v>0.5870000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -590,13 +590,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="C6" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="D6" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
@@ -615,22 +615,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>241453</v>
+        <v>253688</v>
       </c>
       <c r="C7" t="n">
-        <v>163159</v>
+        <v>174913</v>
       </c>
       <c r="D7" t="n">
-        <v>173885</v>
+        <v>186117</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.6757</v>
+        <v>0.6895</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7202</v>
+        <v>0.7336</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.5785</v>
+        <v>0.584</v>
       </c>
     </row>
     <row r="8">
@@ -640,13 +640,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3122</v>
+        <v>3124</v>
       </c>
       <c r="C8" t="n">
-        <v>3122</v>
+        <v>3124</v>
       </c>
       <c r="D8" t="n">
-        <v>3122</v>
+        <v>3124</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
@@ -655,7 +655,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.5042</v>
+        <v>0.5053</v>
       </c>
     </row>
     <row r="9">
@@ -665,22 +665,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>308557</v>
+        <v>321976</v>
       </c>
       <c r="C9" t="n">
-        <v>239089</v>
+        <v>251463</v>
       </c>
       <c r="D9" t="n">
-        <v>275929</v>
+        <v>289266</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.7748999999999999</v>
+        <v>0.7809999999999999</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.8943000000000001</v>
+        <v>0.8984000000000001</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.6402</v>
+        <v>0.6426999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -716,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H215"/>
+  <dimension ref="A1:H224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6803,8 +6803,262 @@
       <c r="G215" s="3" t="n"/>
       <c r="H215" s="2" t="n"/>
     </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>23062</v>
+      </c>
+      <c r="D216" t="n">
+        <v>21992</v>
+      </c>
+      <c r="E216" t="n">
+        <v>22807</v>
+      </c>
+      <c r="F216" s="2" t="n">
+        <v>0.9536</v>
+      </c>
+      <c r="G216" s="3" t="n">
+        <v>0.9889</v>
+      </c>
+      <c r="H216" s="2" t="n">
+        <v>0.5543</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>0</v>
+      </c>
+      <c r="D217" t="n">
+        <v>0</v>
+      </c>
+      <c r="E217" t="n">
+        <v>0</v>
+      </c>
+      <c r="F217" s="2" t="n"/>
+      <c r="G217" s="3" t="n"/>
+      <c r="H217" s="2" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>0</v>
+      </c>
+      <c r="D218" t="n">
+        <v>0</v>
+      </c>
+      <c r="E218" t="n">
+        <v>0</v>
+      </c>
+      <c r="F218" s="2" t="n"/>
+      <c r="G218" s="3" t="n"/>
+      <c r="H218" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>7134</v>
+      </c>
+      <c r="D219" t="n">
+        <v>5411</v>
+      </c>
+      <c r="E219" t="n">
+        <v>7032</v>
+      </c>
+      <c r="F219" s="2" t="n">
+        <v>0.7585</v>
+      </c>
+      <c r="G219" s="3" t="n">
+        <v>0.9856999999999999</v>
+      </c>
+      <c r="H219" s="2" t="n">
+        <v>0.6312</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>16</v>
+      </c>
+      <c r="D220" t="n">
+        <v>16</v>
+      </c>
+      <c r="E220" t="n">
+        <v>16</v>
+      </c>
+      <c r="F220" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G220" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H220" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>12235</v>
+      </c>
+      <c r="D221" t="n">
+        <v>11754</v>
+      </c>
+      <c r="E221" t="n">
+        <v>12232</v>
+      </c>
+      <c r="F221" s="2" t="n">
+        <v>0.9606999999999999</v>
+      </c>
+      <c r="G221" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="H221" s="2" t="n">
+        <v>0.6888</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>2</v>
+      </c>
+      <c r="D222" t="n">
+        <v>2</v>
+      </c>
+      <c r="E222" t="n">
+        <v>2</v>
+      </c>
+      <c r="F222" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G222" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H222" s="2" t="n">
+        <v>0.5366</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>13419</v>
+      </c>
+      <c r="D223" t="n">
+        <v>12374</v>
+      </c>
+      <c r="E223" t="n">
+        <v>13337</v>
+      </c>
+      <c r="F223" s="2" t="n">
+        <v>0.9220999999999999</v>
+      </c>
+      <c r="G223" s="3" t="n">
+        <v>0.9939</v>
+      </c>
+      <c r="H223" s="2" t="n">
+        <v>0.6881</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>0</v>
+      </c>
+      <c r="D224" t="n">
+        <v>0</v>
+      </c>
+      <c r="E224" t="n">
+        <v>0</v>
+      </c>
+      <c r="F224" s="2" t="n"/>
+      <c r="G224" s="3" t="n"/>
+      <c r="H224" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H215"/>
+  <autoFilter ref="A1:H224"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$224</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$233</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -494,22 +494,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>588768</v>
+        <v>608852</v>
       </c>
       <c r="C2" t="n">
-        <v>445552</v>
+        <v>459873</v>
       </c>
       <c r="D2" t="n">
-        <v>501935</v>
+        <v>521981</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.7568</v>
+        <v>0.7553</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.8525</v>
+        <v>0.8573000000000001</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.6261</v>
+        <v>0.6113000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -555,7 +555,7 @@
         <v>0.6208</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.2593</v>
+        <v>0.2585</v>
       </c>
     </row>
     <row r="5">
@@ -565,22 +565,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>156896</v>
+        <v>163091</v>
       </c>
       <c r="C5" t="n">
-        <v>100603</v>
+        <v>104621</v>
       </c>
       <c r="D5" t="n">
-        <v>131505</v>
+        <v>137648</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.6412</v>
+        <v>0.6415000000000001</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.8381999999999999</v>
+        <v>0.8440000000000001</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.5870000000000001</v>
+        <v>0.5914</v>
       </c>
     </row>
     <row r="6">
@@ -590,13 +590,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C6" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D6" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
@@ -615,22 +615,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>253688</v>
+        <v>263773</v>
       </c>
       <c r="C7" t="n">
-        <v>174913</v>
+        <v>180392</v>
       </c>
       <c r="D7" t="n">
-        <v>186117</v>
+        <v>194214</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.6895</v>
+        <v>0.6839</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7336</v>
+        <v>0.7363</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.584</v>
+        <v>0.588</v>
       </c>
     </row>
     <row r="8">
@@ -640,13 +640,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3124</v>
+        <v>3170</v>
       </c>
       <c r="C8" t="n">
-        <v>3124</v>
+        <v>3170</v>
       </c>
       <c r="D8" t="n">
-        <v>3124</v>
+        <v>3170</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
@@ -655,7 +655,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.5053</v>
+        <v>0.5047</v>
       </c>
     </row>
     <row r="9">
@@ -665,22 +665,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>321976</v>
+        <v>333666</v>
       </c>
       <c r="C9" t="n">
-        <v>251463</v>
+        <v>260780</v>
       </c>
       <c r="D9" t="n">
-        <v>289266</v>
+        <v>300546</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.7809999999999999</v>
+        <v>0.7816</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.8984000000000001</v>
+        <v>0.9006999999999999</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.6426999999999999</v>
+        <v>0.6418</v>
       </c>
     </row>
     <row r="10">
@@ -716,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H224"/>
+  <dimension ref="A1:H233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7057,8 +7057,262 @@
       <c r="G224" s="3" t="n"/>
       <c r="H224" s="2" t="n"/>
     </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>20084</v>
+      </c>
+      <c r="D225" t="n">
+        <v>14321</v>
+      </c>
+      <c r="E225" t="n">
+        <v>20046</v>
+      </c>
+      <c r="F225" s="2" t="n">
+        <v>0.7131000000000001</v>
+      </c>
+      <c r="G225" s="3" t="n">
+        <v>0.9981</v>
+      </c>
+      <c r="H225" s="2" t="n">
+        <v>0.4042</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>0</v>
+      </c>
+      <c r="D226" t="n">
+        <v>0</v>
+      </c>
+      <c r="E226" t="n">
+        <v>0</v>
+      </c>
+      <c r="F226" s="2" t="n"/>
+      <c r="G226" s="3" t="n"/>
+      <c r="H226" s="2" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>0</v>
+      </c>
+      <c r="D227" t="n">
+        <v>0</v>
+      </c>
+      <c r="E227" t="n">
+        <v>0</v>
+      </c>
+      <c r="F227" s="2" t="n"/>
+      <c r="G227" s="3" t="n"/>
+      <c r="H227" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>6195</v>
+      </c>
+      <c r="D228" t="n">
+        <v>4018</v>
+      </c>
+      <c r="E228" t="n">
+        <v>6143</v>
+      </c>
+      <c r="F228" s="2" t="n">
+        <v>0.6486</v>
+      </c>
+      <c r="G228" s="3" t="n">
+        <v>0.9915999999999999</v>
+      </c>
+      <c r="H228" s="2" t="n">
+        <v>0.6867</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>5</v>
+      </c>
+      <c r="D229" t="n">
+        <v>5</v>
+      </c>
+      <c r="E229" t="n">
+        <v>5</v>
+      </c>
+      <c r="F229" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G229" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H229" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>10085</v>
+      </c>
+      <c r="D230" t="n">
+        <v>5479</v>
+      </c>
+      <c r="E230" t="n">
+        <v>8097</v>
+      </c>
+      <c r="F230" s="2" t="n">
+        <v>0.5433</v>
+      </c>
+      <c r="G230" s="3" t="n">
+        <v>0.8029000000000001</v>
+      </c>
+      <c r="H230" s="2" t="n">
+        <v>0.6657</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>46</v>
+      </c>
+      <c r="D231" t="n">
+        <v>46</v>
+      </c>
+      <c r="E231" t="n">
+        <v>46</v>
+      </c>
+      <c r="F231" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G231" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H231" s="2" t="n">
+        <v>0.4884000000000001</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>11690</v>
+      </c>
+      <c r="D232" t="n">
+        <v>9317</v>
+      </c>
+      <c r="E232" t="n">
+        <v>11280</v>
+      </c>
+      <c r="F232" s="2" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="G232" s="3" t="n">
+        <v>0.9649</v>
+      </c>
+      <c r="H232" s="2" t="n">
+        <v>0.6243</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>0</v>
+      </c>
+      <c r="D233" t="n">
+        <v>0</v>
+      </c>
+      <c r="E233" t="n">
+        <v>0</v>
+      </c>
+      <c r="F233" s="2" t="n"/>
+      <c r="G233" s="3" t="n"/>
+      <c r="H233" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H224"/>
+  <autoFilter ref="A1:H233"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$233</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$242</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -494,22 +494,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>608852</v>
+        <v>624220</v>
       </c>
       <c r="C2" t="n">
-        <v>459873</v>
+        <v>462509</v>
       </c>
       <c r="D2" t="n">
-        <v>521981</v>
+        <v>524617</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.7553</v>
+        <v>0.7409</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.8573000000000001</v>
+        <v>0.8404</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.6113000000000001</v>
+        <v>0.5885</v>
       </c>
     </row>
     <row r="3">
@@ -555,7 +555,7 @@
         <v>0.6208</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.2585</v>
+        <v>0.2577</v>
       </c>
     </row>
     <row r="5">
@@ -565,22 +565,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>163091</v>
+        <v>168721</v>
       </c>
       <c r="C5" t="n">
-        <v>104621</v>
+        <v>105572</v>
       </c>
       <c r="D5" t="n">
-        <v>137648</v>
+        <v>138599</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.6415000000000001</v>
+        <v>0.6257</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.8440000000000001</v>
+        <v>0.8215</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.5914</v>
+        <v>0.5725</v>
       </c>
     </row>
     <row r="6">
@@ -615,22 +615,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>263773</v>
+        <v>271995</v>
       </c>
       <c r="C7" t="n">
-        <v>180392</v>
+        <v>181638</v>
       </c>
       <c r="D7" t="n">
-        <v>194214</v>
+        <v>195460</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.6839</v>
+        <v>0.6678000000000001</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7363</v>
+        <v>0.7186</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.588</v>
+        <v>0.5655</v>
       </c>
     </row>
     <row r="8">
@@ -640,13 +640,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3170</v>
+        <v>3174</v>
       </c>
       <c r="C8" t="n">
-        <v>3170</v>
+        <v>3174</v>
       </c>
       <c r="D8" t="n">
-        <v>3170</v>
+        <v>3174</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
@@ -655,7 +655,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.5047</v>
+        <v>0.495</v>
       </c>
     </row>
     <row r="9">
@@ -665,22 +665,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>333666</v>
+        <v>343644</v>
       </c>
       <c r="C9" t="n">
-        <v>260780</v>
+        <v>262858</v>
       </c>
       <c r="D9" t="n">
-        <v>300546</v>
+        <v>302624</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.7816</v>
+        <v>0.7648999999999999</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.9006999999999999</v>
+        <v>0.8806</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.6418</v>
+        <v>0.6159</v>
       </c>
     </row>
     <row r="10">
@@ -716,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H233"/>
+  <dimension ref="A1:H242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7311,8 +7311,258 @@
       <c r="G233" s="3" t="n"/>
       <c r="H233" s="2" t="n"/>
     </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>15368</v>
+      </c>
+      <c r="D234" t="n">
+        <v>2636</v>
+      </c>
+      <c r="E234" t="n">
+        <v>2636</v>
+      </c>
+      <c r="F234" s="2" t="n">
+        <v>0.1715</v>
+      </c>
+      <c r="G234" s="3" t="n">
+        <v>0.1715</v>
+      </c>
+      <c r="H234" s="2" t="n">
+        <v>0.07519999999999999</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>0</v>
+      </c>
+      <c r="D235" t="n">
+        <v>0</v>
+      </c>
+      <c r="E235" t="n">
+        <v>0</v>
+      </c>
+      <c r="F235" s="2" t="n"/>
+      <c r="G235" s="3" t="n"/>
+      <c r="H235" s="2" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>0</v>
+      </c>
+      <c r="D236" t="n">
+        <v>0</v>
+      </c>
+      <c r="E236" t="n">
+        <v>0</v>
+      </c>
+      <c r="F236" s="2" t="n"/>
+      <c r="G236" s="3" t="n"/>
+      <c r="H236" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>5630</v>
+      </c>
+      <c r="D237" t="n">
+        <v>951</v>
+      </c>
+      <c r="E237" t="n">
+        <v>951</v>
+      </c>
+      <c r="F237" s="2" t="n">
+        <v>0.1689</v>
+      </c>
+      <c r="G237" s="3" t="n">
+        <v>0.1689</v>
+      </c>
+      <c r="H237" s="2" t="n">
+        <v>0.0699</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>0</v>
+      </c>
+      <c r="D238" t="n">
+        <v>0</v>
+      </c>
+      <c r="E238" t="n">
+        <v>0</v>
+      </c>
+      <c r="F238" s="2" t="n"/>
+      <c r="G238" s="3" t="n"/>
+      <c r="H238" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>8222</v>
+      </c>
+      <c r="D239" t="n">
+        <v>1246</v>
+      </c>
+      <c r="E239" t="n">
+        <v>1246</v>
+      </c>
+      <c r="F239" s="2" t="n">
+        <v>0.1515</v>
+      </c>
+      <c r="G239" s="3" t="n">
+        <v>0.1515</v>
+      </c>
+      <c r="H239" s="2" t="n">
+        <v>0.0297</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>4</v>
+      </c>
+      <c r="D240" t="n">
+        <v>4</v>
+      </c>
+      <c r="E240" t="n">
+        <v>4</v>
+      </c>
+      <c r="F240" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G240" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H240" s="2" t="n">
+        <v>0.03700000000000001</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>9978</v>
+      </c>
+      <c r="D241" t="n">
+        <v>2078</v>
+      </c>
+      <c r="E241" t="n">
+        <v>2078</v>
+      </c>
+      <c r="F241" s="2" t="n">
+        <v>0.2083</v>
+      </c>
+      <c r="G241" s="3" t="n">
+        <v>0.2083</v>
+      </c>
+      <c r="H241" s="2" t="n">
+        <v>0.0257</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>0</v>
+      </c>
+      <c r="D242" t="n">
+        <v>0</v>
+      </c>
+      <c r="E242" t="n">
+        <v>0</v>
+      </c>
+      <c r="F242" s="2" t="n"/>
+      <c r="G242" s="3" t="n"/>
+      <c r="H242" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H233"/>
+  <autoFilter ref="A1:H242"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$242</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$251</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -494,22 +494,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>624220</v>
+        <v>640408</v>
       </c>
       <c r="C2" t="n">
-        <v>462509</v>
+        <v>476328</v>
       </c>
       <c r="D2" t="n">
-        <v>524617</v>
+        <v>539197</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.7409</v>
+        <v>0.7437999999999999</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.8404</v>
+        <v>0.8420000000000001</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.5885</v>
+        <v>0.5932999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -555,7 +555,7 @@
         <v>0.6208</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.2577</v>
+        <v>0.2553</v>
       </c>
     </row>
     <row r="5">
@@ -565,22 +565,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>168721</v>
+        <v>173259</v>
       </c>
       <c r="C5" t="n">
-        <v>105572</v>
+        <v>108625</v>
       </c>
       <c r="D5" t="n">
-        <v>138599</v>
+        <v>143113</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.6257</v>
+        <v>0.627</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.8215</v>
+        <v>0.826</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.5725</v>
+        <v>0.575</v>
       </c>
     </row>
     <row r="6">
@@ -590,13 +590,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C6" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D6" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
@@ -615,22 +615,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>271995</v>
+        <v>279190</v>
       </c>
       <c r="C7" t="n">
-        <v>181638</v>
+        <v>185858</v>
       </c>
       <c r="D7" t="n">
-        <v>195460</v>
+        <v>200653</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.6678000000000001</v>
+        <v>0.6657</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7186</v>
+        <v>0.7187</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.5655</v>
+        <v>0.5645</v>
       </c>
     </row>
     <row r="8">
@@ -640,13 +640,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3174</v>
+        <v>3176</v>
       </c>
       <c r="C8" t="n">
-        <v>3174</v>
+        <v>3176</v>
       </c>
       <c r="D8" t="n">
-        <v>3174</v>
+        <v>3176</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
@@ -655,7 +655,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.495</v>
+        <v>0.4966</v>
       </c>
     </row>
     <row r="9">
@@ -665,22 +665,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>343644</v>
+        <v>352808</v>
       </c>
       <c r="C9" t="n">
-        <v>262858</v>
+        <v>269764</v>
       </c>
       <c r="D9" t="n">
-        <v>302624</v>
+        <v>310814</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.7648999999999999</v>
+        <v>0.7645999999999999</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.8806</v>
+        <v>0.8809999999999999</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.6159</v>
+        <v>0.6127</v>
       </c>
     </row>
     <row r="10">
@@ -716,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H242"/>
+  <dimension ref="A1:H251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7561,8 +7561,262 @@
       <c r="G242" s="3" t="n"/>
       <c r="H242" s="2" t="n"/>
     </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>16188</v>
+      </c>
+      <c r="D243" t="n">
+        <v>13819</v>
+      </c>
+      <c r="E243" t="n">
+        <v>14580</v>
+      </c>
+      <c r="F243" s="2" t="n">
+        <v>0.8537</v>
+      </c>
+      <c r="G243" s="3" t="n">
+        <v>0.9006999999999999</v>
+      </c>
+      <c r="H243" s="2" t="n">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>0</v>
+      </c>
+      <c r="D244" t="n">
+        <v>0</v>
+      </c>
+      <c r="E244" t="n">
+        <v>0</v>
+      </c>
+      <c r="F244" s="2" t="n"/>
+      <c r="G244" s="3" t="n"/>
+      <c r="H244" s="2" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>0</v>
+      </c>
+      <c r="D245" t="n">
+        <v>0</v>
+      </c>
+      <c r="E245" t="n">
+        <v>0</v>
+      </c>
+      <c r="F245" s="2" t="n"/>
+      <c r="G245" s="3" t="n"/>
+      <c r="H245" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>4538</v>
+      </c>
+      <c r="D246" t="n">
+        <v>3053</v>
+      </c>
+      <c r="E246" t="n">
+        <v>4514</v>
+      </c>
+      <c r="F246" s="2" t="n">
+        <v>0.6728000000000001</v>
+      </c>
+      <c r="G246" s="3" t="n">
+        <v>0.9947</v>
+      </c>
+      <c r="H246" s="2" t="n">
+        <v>0.6405</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>4</v>
+      </c>
+      <c r="D247" t="n">
+        <v>4</v>
+      </c>
+      <c r="E247" t="n">
+        <v>4</v>
+      </c>
+      <c r="F247" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G247" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H247" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>7195</v>
+      </c>
+      <c r="D248" t="n">
+        <v>4220</v>
+      </c>
+      <c r="E248" t="n">
+        <v>5193</v>
+      </c>
+      <c r="F248" s="2" t="n">
+        <v>0.5865</v>
+      </c>
+      <c r="G248" s="3" t="n">
+        <v>0.7218000000000001</v>
+      </c>
+      <c r="H248" s="2" t="n">
+        <v>0.5367000000000001</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>2</v>
+      </c>
+      <c r="D249" t="n">
+        <v>2</v>
+      </c>
+      <c r="E249" t="n">
+        <v>2</v>
+      </c>
+      <c r="F249" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G249" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H249" s="2" t="n">
+        <v>0.5556</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>9164</v>
+      </c>
+      <c r="D250" t="n">
+        <v>6906</v>
+      </c>
+      <c r="E250" t="n">
+        <v>8190</v>
+      </c>
+      <c r="F250" s="2" t="n">
+        <v>0.7536</v>
+      </c>
+      <c r="G250" s="3" t="n">
+        <v>0.8937</v>
+      </c>
+      <c r="H250" s="2" t="n">
+        <v>0.5284</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>0</v>
+      </c>
+      <c r="D251" t="n">
+        <v>0</v>
+      </c>
+      <c r="E251" t="n">
+        <v>0</v>
+      </c>
+      <c r="F251" s="2" t="n"/>
+      <c r="G251" s="3" t="n"/>
+      <c r="H251" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H242"/>
+  <autoFilter ref="A1:H251"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$251</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$260</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -494,22 +494,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>640408</v>
+        <v>663371</v>
       </c>
       <c r="C2" t="n">
-        <v>476328</v>
+        <v>498394</v>
       </c>
       <c r="D2" t="n">
-        <v>539197</v>
+        <v>561282</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.7437999999999999</v>
+        <v>0.7513</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.8420000000000001</v>
+        <v>0.8461</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.5932999999999999</v>
+        <v>0.6027</v>
       </c>
     </row>
     <row r="3">
@@ -555,7 +555,7 @@
         <v>0.6208</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.2553</v>
+        <v>0.2538</v>
       </c>
     </row>
     <row r="5">
@@ -565,22 +565,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>173259</v>
+        <v>178113</v>
       </c>
       <c r="C5" t="n">
-        <v>108625</v>
+        <v>112495</v>
       </c>
       <c r="D5" t="n">
-        <v>143113</v>
+        <v>147964</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.627</v>
+        <v>0.6315999999999999</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.826</v>
+        <v>0.8306999999999999</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.575</v>
+        <v>0.5797</v>
       </c>
     </row>
     <row r="6">
@@ -615,22 +615,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>279190</v>
+        <v>291843</v>
       </c>
       <c r="C7" t="n">
-        <v>185858</v>
+        <v>196837</v>
       </c>
       <c r="D7" t="n">
-        <v>200653</v>
+        <v>213295</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.6657</v>
+        <v>0.6745</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7187</v>
+        <v>0.7309</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.5645</v>
+        <v>0.5769</v>
       </c>
     </row>
     <row r="8">
@@ -640,13 +640,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3176</v>
+        <v>3190</v>
       </c>
       <c r="C8" t="n">
-        <v>3176</v>
+        <v>3190</v>
       </c>
       <c r="D8" t="n">
-        <v>3176</v>
+        <v>3190</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
@@ -655,7 +655,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.4966</v>
+        <v>0.5022</v>
       </c>
     </row>
     <row r="9">
@@ -665,22 +665,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>352808</v>
+        <v>365880</v>
       </c>
       <c r="C9" t="n">
-        <v>269764</v>
+        <v>281652</v>
       </c>
       <c r="D9" t="n">
-        <v>310814</v>
+        <v>323735</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.7645999999999999</v>
+        <v>0.7698</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.8809999999999999</v>
+        <v>0.8848</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.6127</v>
+        <v>0.6215999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -716,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H251"/>
+  <dimension ref="A1:H260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7815,8 +7815,258 @@
       <c r="G251" s="3" t="n"/>
       <c r="H251" s="2" t="n"/>
     </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>22963</v>
+      </c>
+      <c r="D252" t="n">
+        <v>22066</v>
+      </c>
+      <c r="E252" t="n">
+        <v>22085</v>
+      </c>
+      <c r="F252" s="2" t="n">
+        <v>0.9609000000000001</v>
+      </c>
+      <c r="G252" s="3" t="n">
+        <v>0.9618000000000001</v>
+      </c>
+      <c r="H252" s="2" t="n">
+        <v>0.8645999999999999</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>0</v>
+      </c>
+      <c r="D253" t="n">
+        <v>0</v>
+      </c>
+      <c r="E253" t="n">
+        <v>0</v>
+      </c>
+      <c r="F253" s="2" t="n"/>
+      <c r="G253" s="3" t="n"/>
+      <c r="H253" s="2" t="n"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>0</v>
+      </c>
+      <c r="D254" t="n">
+        <v>0</v>
+      </c>
+      <c r="E254" t="n">
+        <v>0</v>
+      </c>
+      <c r="F254" s="2" t="n"/>
+      <c r="G254" s="3" t="n"/>
+      <c r="H254" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>4854</v>
+      </c>
+      <c r="D255" t="n">
+        <v>3870</v>
+      </c>
+      <c r="E255" t="n">
+        <v>4851</v>
+      </c>
+      <c r="F255" s="2" t="n">
+        <v>0.7973</v>
+      </c>
+      <c r="G255" s="3" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="H255" s="2" t="n">
+        <v>0.7006</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>0</v>
+      </c>
+      <c r="D256" t="n">
+        <v>0</v>
+      </c>
+      <c r="E256" t="n">
+        <v>0</v>
+      </c>
+      <c r="F256" s="2" t="n"/>
+      <c r="G256" s="3" t="n"/>
+      <c r="H256" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>12653</v>
+      </c>
+      <c r="D257" t="n">
+        <v>10979</v>
+      </c>
+      <c r="E257" t="n">
+        <v>12642</v>
+      </c>
+      <c r="F257" s="2" t="n">
+        <v>0.8676999999999999</v>
+      </c>
+      <c r="G257" s="3" t="n">
+        <v>0.9991</v>
+      </c>
+      <c r="H257" s="2" t="n">
+        <v>0.8765000000000001</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>14</v>
+      </c>
+      <c r="D258" t="n">
+        <v>14</v>
+      </c>
+      <c r="E258" t="n">
+        <v>14</v>
+      </c>
+      <c r="F258" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G258" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H258" s="2" t="n">
+        <v>0.7273000000000001</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>13072</v>
+      </c>
+      <c r="D259" t="n">
+        <v>11888</v>
+      </c>
+      <c r="E259" t="n">
+        <v>12921</v>
+      </c>
+      <c r="F259" s="2" t="n">
+        <v>0.9094</v>
+      </c>
+      <c r="G259" s="3" t="n">
+        <v>0.9884000000000001</v>
+      </c>
+      <c r="H259" s="2" t="n">
+        <v>0.8358</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>0</v>
+      </c>
+      <c r="D260" t="n">
+        <v>0</v>
+      </c>
+      <c r="E260" t="n">
+        <v>0</v>
+      </c>
+      <c r="F260" s="2" t="n"/>
+      <c r="G260" s="3" t="n"/>
+      <c r="H260" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H251"/>
+  <autoFilter ref="A1:H260"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$260</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$269</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -494,22 +494,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>663371</v>
+        <v>687026</v>
       </c>
       <c r="C2" t="n">
-        <v>498394</v>
+        <v>520951</v>
       </c>
       <c r="D2" t="n">
-        <v>561282</v>
+        <v>584937</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.7513</v>
+        <v>0.7583</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.8461</v>
+        <v>0.8514</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.6027</v>
+        <v>0.6078</v>
       </c>
     </row>
     <row r="3">
@@ -555,7 +555,7 @@
         <v>0.6208</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.2538</v>
+        <v>0.2523</v>
       </c>
     </row>
     <row r="5">
@@ -565,22 +565,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>178113</v>
+        <v>182577</v>
       </c>
       <c r="C5" t="n">
-        <v>112495</v>
+        <v>116645</v>
       </c>
       <c r="D5" t="n">
-        <v>147964</v>
+        <v>152428</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.6315999999999999</v>
+        <v>0.6389</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.8306999999999999</v>
+        <v>0.8349</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.5797</v>
+        <v>0.5835</v>
       </c>
     </row>
     <row r="6">
@@ -590,13 +590,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D6" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
@@ -615,22 +615,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>291843</v>
+        <v>304815</v>
       </c>
       <c r="C7" t="n">
-        <v>196837</v>
+        <v>208906</v>
       </c>
       <c r="D7" t="n">
-        <v>213295</v>
+        <v>226266</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.6745</v>
+        <v>0.6854</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7309</v>
+        <v>0.7423000000000001</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.5769</v>
+        <v>0.5832999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -640,13 +640,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3190</v>
+        <v>3199</v>
       </c>
       <c r="C8" t="n">
-        <v>3190</v>
+        <v>3199</v>
       </c>
       <c r="D8" t="n">
-        <v>3190</v>
+        <v>3199</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
@@ -655,7 +655,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.5022</v>
+        <v>0.5011</v>
       </c>
     </row>
     <row r="9">
@@ -665,22 +665,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>365880</v>
+        <v>376436</v>
       </c>
       <c r="C9" t="n">
-        <v>281652</v>
+        <v>291814</v>
       </c>
       <c r="D9" t="n">
-        <v>323735</v>
+        <v>334209</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.7698</v>
+        <v>0.7752</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.8848</v>
+        <v>0.8878</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.6215999999999999</v>
+        <v>0.6239</v>
       </c>
     </row>
     <row r="10">
@@ -716,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H260"/>
+  <dimension ref="A1:H269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8065,8 +8065,262 @@
       <c r="G260" s="3" t="n"/>
       <c r="H260" s="2" t="n"/>
     </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>23655</v>
+      </c>
+      <c r="D261" t="n">
+        <v>22557</v>
+      </c>
+      <c r="E261" t="n">
+        <v>23655</v>
+      </c>
+      <c r="F261" s="2" t="n">
+        <v>0.9536</v>
+      </c>
+      <c r="G261" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H261" s="2" t="n">
+        <v>0.7454000000000001</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C262" t="n">
+        <v>0</v>
+      </c>
+      <c r="D262" t="n">
+        <v>0</v>
+      </c>
+      <c r="E262" t="n">
+        <v>0</v>
+      </c>
+      <c r="F262" s="2" t="n"/>
+      <c r="G262" s="3" t="n"/>
+      <c r="H262" s="2" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C263" t="n">
+        <v>0</v>
+      </c>
+      <c r="D263" t="n">
+        <v>0</v>
+      </c>
+      <c r="E263" t="n">
+        <v>0</v>
+      </c>
+      <c r="F263" s="2" t="n"/>
+      <c r="G263" s="3" t="n"/>
+      <c r="H263" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
+        <v>4464</v>
+      </c>
+      <c r="D264" t="n">
+        <v>4150</v>
+      </c>
+      <c r="E264" t="n">
+        <v>4464</v>
+      </c>
+      <c r="F264" s="2" t="n">
+        <v>0.9297</v>
+      </c>
+      <c r="G264" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H264" s="2" t="n">
+        <v>0.6851999999999999</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C265" t="n">
+        <v>51</v>
+      </c>
+      <c r="D265" t="n">
+        <v>51</v>
+      </c>
+      <c r="E265" t="n">
+        <v>51</v>
+      </c>
+      <c r="F265" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G265" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H265" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>12972</v>
+      </c>
+      <c r="D266" t="n">
+        <v>12069</v>
+      </c>
+      <c r="E266" t="n">
+        <v>12971</v>
+      </c>
+      <c r="F266" s="2" t="n">
+        <v>0.9304000000000001</v>
+      </c>
+      <c r="G266" s="3" t="n">
+        <v>0.9998999999999999</v>
+      </c>
+      <c r="H266" s="2" t="n">
+        <v>0.7276</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>9</v>
+      </c>
+      <c r="D267" t="n">
+        <v>9</v>
+      </c>
+      <c r="E267" t="n">
+        <v>9</v>
+      </c>
+      <c r="F267" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G267" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H267" s="2" t="n">
+        <v>0.4571</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>10556</v>
+      </c>
+      <c r="D268" t="n">
+        <v>10162</v>
+      </c>
+      <c r="E268" t="n">
+        <v>10474</v>
+      </c>
+      <c r="F268" s="2" t="n">
+        <v>0.9627</v>
+      </c>
+      <c r="G268" s="3" t="n">
+        <v>0.9922</v>
+      </c>
+      <c r="H268" s="2" t="n">
+        <v>0.6755</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C269" t="n">
+        <v>0</v>
+      </c>
+      <c r="D269" t="n">
+        <v>0</v>
+      </c>
+      <c r="E269" t="n">
+        <v>0</v>
+      </c>
+      <c r="F269" s="2" t="n"/>
+      <c r="G269" s="3" t="n"/>
+      <c r="H269" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H260"/>
+  <autoFilter ref="A1:H269"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$269</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$278</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -494,22 +494,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>687026</v>
+        <v>708589</v>
       </c>
       <c r="C2" t="n">
-        <v>520951</v>
+        <v>541314</v>
       </c>
       <c r="D2" t="n">
-        <v>584937</v>
+        <v>606493</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.7583</v>
+        <v>0.7639</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.8514</v>
+        <v>0.8559</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.6078</v>
+        <v>0.6114999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -519,16 +519,20 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="3" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="G3" s="2" t="n">
         <v>0</v>
       </c>
@@ -555,7 +559,7 @@
         <v>0.6208</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.2523</v>
+        <v>0.2515</v>
       </c>
     </row>
     <row r="5">
@@ -565,22 +569,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>182577</v>
+        <v>187489</v>
       </c>
       <c r="C5" t="n">
-        <v>116645</v>
+        <v>120876</v>
       </c>
       <c r="D5" t="n">
-        <v>152428</v>
+        <v>157340</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.6389</v>
+        <v>0.6446999999999999</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.8349</v>
+        <v>0.8392000000000001</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.5835</v>
+        <v>0.5852000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -590,13 +594,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C6" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D6" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
@@ -615,22 +619,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>304815</v>
+        <v>318489</v>
       </c>
       <c r="C7" t="n">
-        <v>208906</v>
+        <v>221908</v>
       </c>
       <c r="D7" t="n">
-        <v>226266</v>
+        <v>239934</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.6854</v>
+        <v>0.6968000000000001</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7423000000000001</v>
+        <v>0.7534000000000001</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.5832999999999999</v>
+        <v>0.5874</v>
       </c>
     </row>
     <row r="8">
@@ -655,7 +659,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.5011</v>
+        <v>0.4996</v>
       </c>
     </row>
     <row r="9">
@@ -665,22 +669,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>376436</v>
+        <v>386217</v>
       </c>
       <c r="C9" t="n">
-        <v>291814</v>
+        <v>301233</v>
       </c>
       <c r="D9" t="n">
-        <v>334209</v>
+        <v>343920</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.7752</v>
+        <v>0.78</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.8878</v>
+        <v>0.8905</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.6239</v>
+        <v>0.6253</v>
       </c>
     </row>
     <row r="10">
@@ -716,7 +720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H269"/>
+  <dimension ref="A1:H278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8319,8 +8323,262 @@
       <c r="G269" s="3" t="n"/>
       <c r="H269" s="2" t="n"/>
     </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>21563</v>
+      </c>
+      <c r="D270" t="n">
+        <v>20363</v>
+      </c>
+      <c r="E270" t="n">
+        <v>21556</v>
+      </c>
+      <c r="F270" s="2" t="n">
+        <v>0.9443</v>
+      </c>
+      <c r="G270" s="3" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="H270" s="2" t="n">
+        <v>0.7169</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>1</v>
+      </c>
+      <c r="D271" t="n">
+        <v>1</v>
+      </c>
+      <c r="E271" t="n">
+        <v>1</v>
+      </c>
+      <c r="F271" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G271" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H271" s="2" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>0</v>
+      </c>
+      <c r="D272" t="n">
+        <v>0</v>
+      </c>
+      <c r="E272" t="n">
+        <v>0</v>
+      </c>
+      <c r="F272" s="2" t="n"/>
+      <c r="G272" s="3" t="n"/>
+      <c r="H272" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>4912</v>
+      </c>
+      <c r="D273" t="n">
+        <v>4231</v>
+      </c>
+      <c r="E273" t="n">
+        <v>4912</v>
+      </c>
+      <c r="F273" s="2" t="n">
+        <v>0.8614000000000001</v>
+      </c>
+      <c r="G273" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H273" s="2" t="n">
+        <v>0.6271</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>4</v>
+      </c>
+      <c r="D274" t="n">
+        <v>4</v>
+      </c>
+      <c r="E274" t="n">
+        <v>4</v>
+      </c>
+      <c r="F274" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G274" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H274" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>13674</v>
+      </c>
+      <c r="D275" t="n">
+        <v>13002</v>
+      </c>
+      <c r="E275" t="n">
+        <v>13668</v>
+      </c>
+      <c r="F275" s="2" t="n">
+        <v>0.9509000000000001</v>
+      </c>
+      <c r="G275" s="3" t="n">
+        <v>0.9995999999999999</v>
+      </c>
+      <c r="H275" s="2" t="n">
+        <v>0.6823</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>0</v>
+      </c>
+      <c r="D276" t="n">
+        <v>0</v>
+      </c>
+      <c r="E276" t="n">
+        <v>0</v>
+      </c>
+      <c r="F276" s="2" t="n"/>
+      <c r="G276" s="3" t="n"/>
+      <c r="H276" s="2" t="n">
+        <v>0.4286</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>9781</v>
+      </c>
+      <c r="D277" t="n">
+        <v>9419</v>
+      </c>
+      <c r="E277" t="n">
+        <v>9711</v>
+      </c>
+      <c r="F277" s="2" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="G277" s="3" t="n">
+        <v>0.9928</v>
+      </c>
+      <c r="H277" s="2" t="n">
+        <v>0.6603</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>0</v>
+      </c>
+      <c r="D278" t="n">
+        <v>0</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0</v>
+      </c>
+      <c r="F278" s="2" t="n"/>
+      <c r="G278" s="3" t="n"/>
+      <c r="H278" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H269"/>
+  <autoFilter ref="A1:H278"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_painel_mensal.xlsx
+++ b/output/PICKUP_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$G$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$278</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$H$287</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -494,22 +494,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>708589</v>
+        <v>729966</v>
       </c>
       <c r="C2" t="n">
-        <v>541314</v>
+        <v>561926</v>
       </c>
       <c r="D2" t="n">
-        <v>606493</v>
+        <v>627845</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.7639</v>
+        <v>0.7698</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.8559</v>
+        <v>0.8601000000000001</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.6114999999999999</v>
+        <v>0.6173</v>
       </c>
     </row>
     <row r="3">
@@ -559,7 +559,7 @@
         <v>0.6208</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.2515</v>
+        <v>0.2507</v>
       </c>
     </row>
     <row r="5">
@@ -569,22 +569,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>187489</v>
+        <v>192601</v>
       </c>
       <c r="C5" t="n">
-        <v>120876</v>
+        <v>125410</v>
       </c>
       <c r="D5" t="n">
-        <v>157340</v>
+        <v>162452</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.6446999999999999</v>
+        <v>0.6511</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.8392000000000001</v>
+        <v>0.8434999999999999</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.5852000000000001</v>
+        <v>0.5876</v>
       </c>
     </row>
     <row r="6">
@@ -594,13 +594,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C6" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D6" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
@@ -619,22 +619,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>318489</v>
+        <v>333122</v>
       </c>
       <c r="C7" t="n">
-        <v>221908</v>
+        <v>236094</v>
       </c>
       <c r="D7" t="n">
-        <v>239934</v>
+        <v>254567</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.6968000000000001</v>
+        <v>0.7087</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7534000000000001</v>
+        <v>0.7642</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.5874</v>
+        <v>0.5926</v>
       </c>
     </row>
     <row r="8">
@@ -644,13 +644,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3199</v>
+        <v>3235</v>
       </c>
       <c r="C8" t="n">
-        <v>3199</v>
+        <v>3235</v>
       </c>
       <c r="D8" t="n">
-        <v>3199</v>
+        <v>3235</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
@@ -659,7 +659,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.4996</v>
+        <v>0.5024000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -669,22 +669,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>386217</v>
+        <v>396563</v>
       </c>
       <c r="C9" t="n">
-        <v>301233</v>
+        <v>311166</v>
       </c>
       <c r="D9" t="n">
-        <v>343920</v>
+        <v>354229</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.78</v>
+        <v>0.7847</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.8905</v>
+        <v>0.8931999999999999</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.6253</v>
+        <v>0.6279</v>
       </c>
     </row>
     <row r="10">
@@ -720,7 +720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H278"/>
+  <dimension ref="A1:H287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8577,8 +8577,262 @@
       <c r="G278" s="3" t="n"/>
       <c r="H278" s="2" t="n"/>
     </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>21377</v>
+      </c>
+      <c r="D279" t="n">
+        <v>20612</v>
+      </c>
+      <c r="E279" t="n">
+        <v>21352</v>
+      </c>
+      <c r="F279" s="2" t="n">
+        <v>0.9642000000000001</v>
+      </c>
+      <c r="G279" s="3" t="n">
+        <v>0.9987999999999999</v>
+      </c>
+      <c r="H279" s="2" t="n">
+        <v>0.7776000000000001</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>0</v>
+      </c>
+      <c r="D280" t="n">
+        <v>0</v>
+      </c>
+      <c r="E280" t="n">
+        <v>0</v>
+      </c>
+      <c r="F280" s="2" t="n"/>
+      <c r="G280" s="3" t="n"/>
+      <c r="H280" s="2" t="n"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>0</v>
+      </c>
+      <c r="D281" t="n">
+        <v>0</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0</v>
+      </c>
+      <c r="F281" s="2" t="n"/>
+      <c r="G281" s="3" t="n"/>
+      <c r="H281" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C282" t="n">
+        <v>5112</v>
+      </c>
+      <c r="D282" t="n">
+        <v>4534</v>
+      </c>
+      <c r="E282" t="n">
+        <v>5112</v>
+      </c>
+      <c r="F282" s="2" t="n">
+        <v>0.8869</v>
+      </c>
+      <c r="G282" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H282" s="2" t="n">
+        <v>0.6529</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C283" t="n">
+        <v>4</v>
+      </c>
+      <c r="D283" t="n">
+        <v>4</v>
+      </c>
+      <c r="E283" t="n">
+        <v>4</v>
+      </c>
+      <c r="F283" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G283" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H283" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C284" t="n">
+        <v>14633</v>
+      </c>
+      <c r="D284" t="n">
+        <v>14186</v>
+      </c>
+      <c r="E284" t="n">
+        <v>14633</v>
+      </c>
+      <c r="F284" s="2" t="n">
+        <v>0.9695</v>
+      </c>
+      <c r="G284" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H284" s="2" t="n">
+        <v>0.7171999999999999</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C285" t="n">
+        <v>36</v>
+      </c>
+      <c r="D285" t="n">
+        <v>36</v>
+      </c>
+      <c r="E285" t="n">
+        <v>36</v>
+      </c>
+      <c r="F285" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G285" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H285" s="2" t="n">
+        <v>0.6429</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C286" t="n">
+        <v>10346</v>
+      </c>
+      <c r="D286" t="n">
+        <v>9933</v>
+      </c>
+      <c r="E286" t="n">
+        <v>10309</v>
+      </c>
+      <c r="F286" s="2" t="n">
+        <v>0.9601000000000001</v>
+      </c>
+      <c r="G286" s="3" t="n">
+        <v>0.9964</v>
+      </c>
+      <c r="H286" s="2" t="n">
+        <v>0.6951999999999999</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C287" t="n">
+        <v>0</v>
+      </c>
+      <c r="D287" t="n">
+        <v>0</v>
+      </c>
+      <c r="E287" t="n">
+        <v>0</v>
+      </c>
+      <c r="F287" s="2" t="n"/>
+      <c r="G287" s="3" t="n"/>
+      <c r="H287" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H278"/>
+  <autoFilter ref="A1:H287"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>